--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -519,7 +519,7 @@
         <v>311</v>
       </c>
       <c r="H2" t="n">
-        <v>4920</v>
+        <v>4921</v>
       </c>
       <c r="I2" t="n">
         <v>124.32</v>
@@ -609,7 +609,7 @@
         <v>357</v>
       </c>
       <c r="H4" t="n">
-        <v>5589</v>
+        <v>5590</v>
       </c>
       <c r="I4" t="n">
         <v>108.74</v>
@@ -699,7 +699,7 @@
         <v>352</v>
       </c>
       <c r="H6" t="n">
-        <v>5490</v>
+        <v>5491</v>
       </c>
       <c r="I6" t="n">
         <v>107.11</v>
@@ -1017,19 +1017,19 @@
         <v>5749</v>
       </c>
       <c r="I13" t="n">
-        <v>98.39</v>
+        <v>98.37</v>
       </c>
       <c r="J13" t="n">
         <v>29.3</v>
       </c>
       <c r="K13" t="n">
-        <v>205.76</v>
+        <v>205.7</v>
       </c>
       <c r="L13" t="n">
         <v>100</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.61</v>
+        <v>-1.63</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1107,7 +1107,7 @@
         <v>5141</v>
       </c>
       <c r="I15" t="n">
-        <v>97.64</v>
+        <v>97.62</v>
       </c>
       <c r="J15" t="n">
         <v>44.99</v>
@@ -1119,7 +1119,7 @@
         <v>96.94</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1377,7 +1377,7 @@
         <v>5862</v>
       </c>
       <c r="I21" t="n">
-        <v>93.05</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="J21" t="n">
         <v>27.8</v>
@@ -1389,7 +1389,7 @@
         <v>93</v>
       </c>
       <c r="M21" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
         <v>403</v>
       </c>
       <c r="H22" t="n">
-        <v>5801</v>
+        <v>5802</v>
       </c>
       <c r="I22" t="n">
         <v>92.06</v>
@@ -1557,7 +1557,7 @@
         <v>5750</v>
       </c>
       <c r="I25" t="n">
-        <v>90.43000000000001</v>
+        <v>90.42</v>
       </c>
       <c r="J25" t="n">
         <v>25.6</v>
@@ -1569,7 +1569,7 @@
         <v>95</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.57</v>
+        <v>-4.58</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -7037,22 +7037,22 @@
         <v>0.642</v>
       </c>
       <c r="H113" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0951</v>
       </c>
       <c r="I113" t="n">
-        <v>24.54</v>
+        <v>24.44</v>
       </c>
       <c r="J113" t="n">
         <v>342</v>
       </c>
       <c r="K113" t="n">
-        <v>6.091</v>
+        <v>6.082</v>
       </c>
       <c r="L113" t="n">
-        <v>-3.776</v>
+        <v>-3.78</v>
       </c>
       <c r="M113" t="n">
-        <v>21.642</v>
+        <v>21.615</v>
       </c>
     </row>
     <row r="114">
@@ -8885,7 +8885,7 @@
         <v>0.1263</v>
       </c>
       <c r="I154" t="n">
-        <v>26.73</v>
+        <v>26.63</v>
       </c>
       <c r="J154" t="n">
         <v>350.3</v>
@@ -11768,7 +11768,7 @@
         <v>22.24</v>
       </c>
       <c r="J218" t="n">
-        <v>314.6</v>
+        <v>315.8</v>
       </c>
       <c r="K218" t="n">
         <v>6.459</v>
@@ -12125,10 +12125,10 @@
         <v>0.1358</v>
       </c>
       <c r="I226" t="n">
-        <v>24.09</v>
+        <v>24</v>
       </c>
       <c r="J226" t="n">
-        <v>334</v>
+        <v>335.2</v>
       </c>
       <c r="K226" t="n">
         <v>5.841</v>
@@ -14597,7 +14597,7 @@
         <v>0.436</v>
       </c>
       <c r="H281" t="n">
-        <v>0.1339</v>
+        <v>0.1318</v>
       </c>
       <c r="I281" t="n">
         <v>20.99</v>
@@ -14606,13 +14606,13 @@
         <v>317.3</v>
       </c>
       <c r="K281" t="n">
-        <v>6.023</v>
+        <v>6.011</v>
       </c>
       <c r="L281" t="n">
-        <v>-2.492</v>
+        <v>-2.496</v>
       </c>
       <c r="M281" t="n">
-        <v>21.307</v>
+        <v>21.275</v>
       </c>
     </row>
     <row r="282">
@@ -19727,7 +19727,7 @@
         <v>0.542</v>
       </c>
       <c r="H395" t="n">
-        <v>0.1254</v>
+        <v>0.1235</v>
       </c>
       <c r="I395" t="n">
         <v>23.29</v>
@@ -19736,13 +19736,13 @@
         <v>339.4</v>
       </c>
       <c r="K395" t="n">
-        <v>6.124</v>
+        <v>6.113</v>
       </c>
       <c r="L395" t="n">
-        <v>-3.765</v>
+        <v>-3.769</v>
       </c>
       <c r="M395" t="n">
-        <v>21.899</v>
+        <v>21.868</v>
       </c>
     </row>
     <row r="396">
@@ -19907,7 +19907,7 @@
         <v>0.542</v>
       </c>
       <c r="H399" t="n">
-        <v>0.1254</v>
+        <v>0.1235</v>
       </c>
       <c r="I399" t="n">
         <v>21.6</v>
@@ -19916,13 +19916,13 @@
         <v>311.3</v>
       </c>
       <c r="K399" t="n">
-        <v>6.25</v>
+        <v>6.239</v>
       </c>
       <c r="L399" t="n">
-        <v>-2.414</v>
+        <v>-2.418</v>
       </c>
       <c r="M399" t="n">
-        <v>22.087</v>
+        <v>22.055</v>
       </c>
     </row>
     <row r="400">
@@ -21080,7 +21080,7 @@
         <v>0.1353</v>
       </c>
       <c r="I425" t="n">
-        <v>18.55</v>
+        <v>18.58</v>
       </c>
       <c r="J425" t="n">
         <v>299</v>
@@ -21398,7 +21398,7 @@
         <v>21.56</v>
       </c>
       <c r="J432" t="n">
-        <v>317.1</v>
+        <v>318.3</v>
       </c>
       <c r="K432" t="n">
         <v>6.233</v>
@@ -22658,7 +22658,7 @@
         <v>21.42</v>
       </c>
       <c r="J460" t="n">
-        <v>299.7</v>
+        <v>300.9</v>
       </c>
       <c r="K460" t="n">
         <v>6.56</v>
@@ -25307,7 +25307,7 @@
         <v>0.603</v>
       </c>
       <c r="H519" t="n">
-        <v>0.0978</v>
+        <v>0.0963</v>
       </c>
       <c r="I519" t="n">
         <v>25.44</v>
@@ -25316,13 +25316,13 @@
         <v>308</v>
       </c>
       <c r="K519" t="n">
-        <v>5.994</v>
+        <v>5.985</v>
       </c>
       <c r="L519" t="n">
-        <v>-2.502</v>
+        <v>-2.505</v>
       </c>
       <c r="M519" t="n">
-        <v>21.464</v>
+        <v>21.438</v>
       </c>
     </row>
     <row r="520">

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -7310,7 +7310,7 @@
         <v>0.1796</v>
       </c>
       <c r="I119" t="n">
-        <v>23.98</v>
+        <v>23.89</v>
       </c>
       <c r="J119" t="n">
         <v>349</v>
@@ -11360,7 +11360,7 @@
         <v>0.201</v>
       </c>
       <c r="I209" t="n">
-        <v>18.97</v>
+        <v>18.91</v>
       </c>
       <c r="J209" t="n">
         <v>294.7</v>
@@ -12530,7 +12530,7 @@
         <v>0.1649</v>
       </c>
       <c r="I235" t="n">
-        <v>19.58</v>
+        <v>19.35</v>
       </c>
       <c r="J235" t="n">
         <v>303.7</v>
@@ -12542,7 +12542,7 @@
         <v>-2.074</v>
       </c>
       <c r="M235" t="n">
-        <v>22.621</v>
+        <v>24.583</v>
       </c>
     </row>
     <row r="236">
@@ -15590,7 +15590,7 @@
         <v>0.1281</v>
       </c>
       <c r="I303" t="n">
-        <v>20.61</v>
+        <v>20.75</v>
       </c>
       <c r="J303" t="n">
         <v>291.1</v>
@@ -18650,7 +18650,7 @@
         <v>0.1288</v>
       </c>
       <c r="I371" t="n">
-        <v>21.64</v>
+        <v>21.81</v>
       </c>
       <c r="J371" t="n">
         <v>309.5</v>

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -504,13 +504,13 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>39.46</v>
+        <v>39.19</v>
       </c>
       <c r="D2" t="n">
-        <v>14.47</v>
+        <v>14.48</v>
       </c>
       <c r="E2" t="n">
-        <v>8.44</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>2.41</v>
@@ -519,22 +519,22 @@
         <v>311</v>
       </c>
       <c r="H2" t="n">
-        <v>4990</v>
+        <v>4991</v>
       </c>
       <c r="I2" t="n">
-        <v>114.77</v>
+        <v>114.32</v>
       </c>
       <c r="J2" t="n">
-        <v>46.49</v>
+        <v>46.31</v>
       </c>
       <c r="K2" t="n">
-        <v>204.99</v>
+        <v>204.4</v>
       </c>
       <c r="L2" t="n">
         <v>108.24</v>
       </c>
       <c r="M2" t="n">
-        <v>6.53</v>
+        <v>6.08</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -594,37 +594,37 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>39.98</v>
+        <v>39.62</v>
       </c>
       <c r="D4" t="n">
-        <v>12.86</v>
+        <v>12.94</v>
       </c>
       <c r="E4" t="n">
-        <v>8.67</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="G4" t="n">
         <v>322</v>
       </c>
       <c r="H4" t="n">
-        <v>5146</v>
+        <v>5144</v>
       </c>
       <c r="I4" t="n">
-        <v>105.86</v>
+        <v>105.97</v>
       </c>
       <c r="J4" t="n">
-        <v>44.52</v>
+        <v>44.24</v>
       </c>
       <c r="K4" t="n">
-        <v>201.39</v>
+        <v>201.64</v>
       </c>
       <c r="L4" t="n">
         <v>109.18</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.32</v>
+        <v>-3.21</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -639,37 +639,37 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>40.72</v>
+        <v>40.51</v>
       </c>
       <c r="D5" t="n">
-        <v>13.31</v>
+        <v>13.37</v>
       </c>
       <c r="E5" t="n">
         <v>8.65</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="G5" t="n">
         <v>325</v>
       </c>
       <c r="H5" t="n">
-        <v>5070</v>
+        <v>5047</v>
       </c>
       <c r="I5" t="n">
-        <v>104.63</v>
+        <v>105.07</v>
       </c>
       <c r="J5" t="n">
-        <v>46.02</v>
+        <v>45.84</v>
       </c>
       <c r="K5" t="n">
-        <v>199.12</v>
+        <v>199.87</v>
       </c>
       <c r="L5" t="n">
         <v>99.76000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>4.87</v>
+        <v>5.31</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -684,37 +684,37 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>39.86</v>
+        <v>39.66</v>
       </c>
       <c r="D6" t="n">
         <v>12.64</v>
       </c>
       <c r="E6" t="n">
-        <v>7.24</v>
+        <v>7.2</v>
       </c>
       <c r="F6" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="G6" t="n">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="H6" t="n">
-        <v>5216</v>
+        <v>5201</v>
       </c>
       <c r="I6" t="n">
-        <v>102.35</v>
+        <v>101.87</v>
       </c>
       <c r="J6" t="n">
-        <v>42.54</v>
+        <v>42.35</v>
       </c>
       <c r="K6" t="n">
-        <v>200.26</v>
+        <v>200.6</v>
       </c>
       <c r="L6" t="n">
         <v>115.76</v>
       </c>
       <c r="M6" t="n">
-        <v>-13.41</v>
+        <v>-13.89</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -774,37 +774,37 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>42.4</v>
+        <v>42.16</v>
       </c>
       <c r="D8" t="n">
-        <v>12.06</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="n">
-        <v>9.07</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="G8" t="n">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="H8" t="n">
-        <v>5241</v>
+        <v>5243</v>
       </c>
       <c r="I8" t="n">
-        <v>98.95999999999999</v>
+        <v>99.33</v>
       </c>
       <c r="J8" t="n">
-        <v>29.74</v>
+        <v>29.93</v>
       </c>
       <c r="K8" t="n">
-        <v>195.37</v>
+        <v>195.73</v>
       </c>
       <c r="L8" t="n">
         <v>85.65000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>13.31</v>
+        <v>13.68</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -812,44 +812,44 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>38.43</v>
+        <v>39.7</v>
       </c>
       <c r="D9" t="n">
-        <v>12.67</v>
+        <v>14.21</v>
       </c>
       <c r="E9" t="n">
-        <v>7.05</v>
+        <v>8.17</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="G9" t="n">
-        <v>324</v>
+        <v>364</v>
       </c>
       <c r="H9" t="n">
-        <v>5123</v>
+        <v>5417</v>
       </c>
       <c r="I9" t="n">
-        <v>97.04000000000001</v>
+        <v>96.42</v>
       </c>
       <c r="J9" t="n">
-        <v>41.04</v>
+        <v>29.46</v>
       </c>
       <c r="K9" t="n">
-        <v>187.86</v>
+        <v>166.64</v>
       </c>
       <c r="L9" t="n">
-        <v>93.18000000000001</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>3.86</v>
+        <v>12.66</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -885,10 +885,10 @@
         <v>96.09999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>27.39</v>
+        <v>27.76</v>
       </c>
       <c r="K10" t="n">
-        <v>197.68</v>
+        <v>199.04</v>
       </c>
       <c r="L10" t="n">
         <v>88.47</v>
@@ -902,44 +902,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>39.66</v>
+        <v>38.27</v>
       </c>
       <c r="D11" t="n">
-        <v>14.13</v>
+        <v>12.76</v>
       </c>
       <c r="E11" t="n">
-        <v>8.109999999999999</v>
+        <v>7.03</v>
       </c>
       <c r="F11" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="G11" t="n">
-        <v>363</v>
+        <v>328</v>
       </c>
       <c r="H11" t="n">
-        <v>5409</v>
+        <v>5125</v>
       </c>
       <c r="I11" t="n">
-        <v>95.66</v>
+        <v>95.95</v>
       </c>
       <c r="J11" t="n">
-        <v>29.46</v>
+        <v>41.13</v>
       </c>
       <c r="K11" t="n">
-        <v>197.59</v>
+        <v>187.88</v>
       </c>
       <c r="L11" t="n">
-        <v>83.76000000000001</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>11.9</v>
+        <v>2.77</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -999,37 +999,37 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>39.27</v>
+        <v>39.08</v>
       </c>
       <c r="D13" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="E13" t="n">
-        <v>7.33</v>
+        <v>7.42</v>
       </c>
       <c r="F13" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G13" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H13" t="n">
-        <v>5225</v>
+        <v>5204</v>
       </c>
       <c r="I13" t="n">
-        <v>91.73</v>
+        <v>92.02</v>
       </c>
       <c r="J13" t="n">
-        <v>41.69</v>
+        <v>41.88</v>
       </c>
       <c r="K13" t="n">
-        <v>189.44</v>
+        <v>189.8</v>
       </c>
       <c r="L13" t="n">
         <v>96.94</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.21</v>
+        <v>-4.92</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1082,44 +1082,44 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>38.1</v>
+        <v>37.94</v>
       </c>
       <c r="D15" t="n">
-        <v>11.68</v>
+        <v>12.07</v>
       </c>
       <c r="E15" t="n">
-        <v>7.42</v>
+        <v>9.48</v>
       </c>
       <c r="F15" t="n">
-        <v>2.34</v>
+        <v>1.73</v>
       </c>
       <c r="G15" t="n">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="H15" t="n">
-        <v>5576</v>
+        <v>5531</v>
       </c>
       <c r="I15" t="n">
-        <v>90.36</v>
+        <v>91.39</v>
       </c>
       <c r="J15" t="n">
-        <v>24</v>
+        <v>26.54</v>
       </c>
       <c r="K15" t="n">
-        <v>160.43</v>
+        <v>159.34</v>
       </c>
       <c r="L15" t="n">
-        <v>95.06</v>
+        <v>101.65</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.7</v>
+        <v>-10.26</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1127,44 +1127,44 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>38.39</v>
+        <v>38.25</v>
       </c>
       <c r="D16" t="n">
-        <v>12.7</v>
+        <v>11.72</v>
       </c>
       <c r="E16" t="n">
-        <v>8.119999999999999</v>
+        <v>7.39</v>
       </c>
       <c r="F16" t="n">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="G16" t="n">
-        <v>328</v>
+        <v>384</v>
       </c>
       <c r="H16" t="n">
-        <v>4953</v>
+        <v>5585</v>
       </c>
       <c r="I16" t="n">
-        <v>89.84999999999999</v>
+        <v>90.58</v>
       </c>
       <c r="J16" t="n">
-        <v>43.76</v>
+        <v>24.19</v>
       </c>
       <c r="K16" t="n">
-        <v>185.77</v>
+        <v>160.68</v>
       </c>
       <c r="L16" t="n">
-        <v>86.47</v>
+        <v>95.06</v>
       </c>
       <c r="M16" t="n">
-        <v>3.38</v>
+        <v>-4.48</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1172,44 +1172,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>37.78</v>
+        <v>37.58</v>
       </c>
       <c r="D17" t="n">
-        <v>11.85</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="G17" t="n">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="H17" t="n">
-        <v>5539</v>
+        <v>5250</v>
       </c>
       <c r="I17" t="n">
-        <v>89.73999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>25.51</v>
+        <v>40.85</v>
       </c>
       <c r="K17" t="n">
-        <v>157.29</v>
+        <v>189.18</v>
       </c>
       <c r="L17" t="n">
         <v>101.65</v>
       </c>
       <c r="M17" t="n">
-        <v>-11.91</v>
+        <v>-12.25</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1224,37 +1224,37 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>37</v>
+        <v>37.07</v>
       </c>
       <c r="D18" t="n">
-        <v>12.97</v>
+        <v>13.06</v>
       </c>
       <c r="E18" t="n">
-        <v>7.52</v>
+        <v>7.61</v>
       </c>
       <c r="F18" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="G18" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H18" t="n">
-        <v>5418</v>
+        <v>5423</v>
       </c>
       <c r="I18" t="n">
-        <v>88.3</v>
+        <v>89.02</v>
       </c>
       <c r="J18" t="n">
-        <v>24.66</v>
+        <v>24.94</v>
       </c>
       <c r="K18" t="n">
-        <v>155.56</v>
+        <v>156.48</v>
       </c>
       <c r="L18" t="n">
         <v>94.12</v>
       </c>
       <c r="M18" t="n">
-        <v>-5.82</v>
+        <v>-5.1</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1262,44 +1262,44 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>37.51</v>
+        <v>36.08</v>
       </c>
       <c r="D19" t="n">
-        <v>11.86</v>
+        <v>12.86</v>
       </c>
       <c r="E19" t="n">
-        <v>7.93</v>
+        <v>7.01</v>
       </c>
       <c r="F19" t="n">
-        <v>1.79</v>
+        <v>2.11</v>
       </c>
       <c r="G19" t="n">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="H19" t="n">
-        <v>5262</v>
+        <v>5638</v>
       </c>
       <c r="I19" t="n">
-        <v>87.84999999999999</v>
+        <v>88.45</v>
       </c>
       <c r="J19" t="n">
-        <v>40</v>
+        <v>23.53</v>
       </c>
       <c r="K19" t="n">
-        <v>187.28</v>
+        <v>157.48</v>
       </c>
       <c r="L19" t="n">
-        <v>101.65</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-13.8</v>
+        <v>-4.73</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         <v>1.76</v>
       </c>
       <c r="G20" t="n">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="H20" t="n">
-        <v>5596</v>
+        <v>5591</v>
       </c>
       <c r="I20" t="n">
         <v>86.34</v>
@@ -1359,37 +1359,37 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>36.75</v>
+        <v>36.92</v>
       </c>
       <c r="D21" t="n">
-        <v>12.17</v>
+        <v>12.3</v>
       </c>
       <c r="E21" t="n">
-        <v>6.24</v>
+        <v>6.22</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G21" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H21" t="n">
-        <v>5316</v>
+        <v>5309</v>
       </c>
       <c r="I21" t="n">
-        <v>85.78</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>37.93</v>
+        <v>38.31</v>
       </c>
       <c r="K21" t="n">
-        <v>182.74</v>
+        <v>183</v>
       </c>
       <c r="L21" t="n">
         <v>93.18000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-7.4</v>
+        <v>-7.11</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1397,44 +1397,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>35.78</v>
+        <v>36.61</v>
       </c>
       <c r="D22" t="n">
-        <v>12.6</v>
+        <v>11.86</v>
       </c>
       <c r="E22" t="n">
-        <v>6.67</v>
+        <v>7.37</v>
       </c>
       <c r="F22" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="G22" t="n">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="H22" t="n">
-        <v>5619</v>
+        <v>5317</v>
       </c>
       <c r="I22" t="n">
-        <v>85.34</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="J22" t="n">
         <v>22.49</v>
       </c>
       <c r="K22" t="n">
-        <v>153.3</v>
+        <v>184.24</v>
       </c>
       <c r="L22" t="n">
         <v>93.18000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-7.84</v>
+        <v>-7.72</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1449,37 +1449,37 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>34.75</v>
+        <v>34.6</v>
       </c>
       <c r="D23" t="n">
-        <v>11.96</v>
+        <v>12.08</v>
       </c>
       <c r="E23" t="n">
-        <v>7.21</v>
+        <v>7.27</v>
       </c>
       <c r="F23" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="G23" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H23" t="n">
         <v>5401</v>
       </c>
       <c r="I23" t="n">
-        <v>84.84999999999999</v>
+        <v>85.45</v>
       </c>
       <c r="J23" t="n">
-        <v>21.27</v>
+        <v>21.08</v>
       </c>
       <c r="K23" t="n">
-        <v>184.45</v>
+        <v>185.45</v>
       </c>
       <c r="L23" t="n">
         <v>89.41</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.56</v>
+        <v>-3.96</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1487,44 +1487,44 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" t="n">
-        <v>37.64</v>
+        <v>37.53</v>
       </c>
       <c r="D24" t="n">
-        <v>12.13</v>
+        <v>12.4</v>
       </c>
       <c r="E24" t="n">
-        <v>7.51</v>
+        <v>6.64</v>
       </c>
       <c r="F24" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="G24" t="n">
-        <v>396</v>
+        <v>345</v>
       </c>
       <c r="H24" t="n">
-        <v>5614</v>
+        <v>4984</v>
       </c>
       <c r="I24" t="n">
-        <v>84.68000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="J24" t="n">
-        <v>23.81</v>
+        <v>25.94</v>
       </c>
       <c r="K24" t="n">
-        <v>133.68</v>
+        <v>180.35</v>
       </c>
       <c r="L24" t="n">
-        <v>83.76000000000001</v>
+        <v>86.47</v>
       </c>
       <c r="M24" t="n">
-        <v>0.92</v>
+        <v>-1.08</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -1532,44 +1532,44 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>16</v>
       </c>
       <c r="C25" t="n">
-        <v>36.36</v>
+        <v>37.64</v>
       </c>
       <c r="D25" t="n">
-        <v>11.62</v>
+        <v>12.13</v>
       </c>
       <c r="E25" t="n">
-        <v>7.18</v>
+        <v>7.51</v>
       </c>
       <c r="F25" t="n">
-        <v>1.74</v>
+        <v>1.29</v>
       </c>
       <c r="G25" t="n">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="H25" t="n">
-        <v>5327</v>
+        <v>5614</v>
       </c>
       <c r="I25" t="n">
-        <v>84.37</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>21.74</v>
+        <v>23.81</v>
       </c>
       <c r="K25" t="n">
-        <v>182.83</v>
+        <v>133.68</v>
       </c>
       <c r="L25" t="n">
-        <v>93.18000000000001</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-8.81</v>
+        <v>0.92</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -1584,37 +1584,37 @@
         <v>16</v>
       </c>
       <c r="C26" t="n">
-        <v>34.37</v>
+        <v>34.56</v>
       </c>
       <c r="D26" t="n">
-        <v>11.71</v>
+        <v>11.84</v>
       </c>
       <c r="E26" t="n">
-        <v>7.58</v>
+        <v>7.59</v>
       </c>
       <c r="F26" t="n">
         <v>1.7</v>
       </c>
       <c r="G26" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H26" t="n">
-        <v>5544</v>
+        <v>5572</v>
       </c>
       <c r="I26" t="n">
-        <v>83.12</v>
+        <v>83.64</v>
       </c>
       <c r="J26" t="n">
-        <v>20.99</v>
+        <v>21.18</v>
       </c>
       <c r="K26" t="n">
-        <v>133.99</v>
+        <v>134.29</v>
       </c>
       <c r="L26" t="n">
         <v>87.53</v>
       </c>
       <c r="M26" t="n">
-        <v>-4.41</v>
+        <v>-3.89</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -1629,37 +1629,37 @@
         <v>16</v>
       </c>
       <c r="C27" t="n">
-        <v>37.77</v>
+        <v>37.85</v>
       </c>
       <c r="D27" t="n">
-        <v>10.99</v>
+        <v>11.09</v>
       </c>
       <c r="E27" t="n">
-        <v>8.130000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="F27" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G27" t="n">
         <v>404</v>
       </c>
       <c r="H27" t="n">
-        <v>5416</v>
+        <v>5417</v>
       </c>
       <c r="I27" t="n">
-        <v>82.95</v>
+        <v>83.56</v>
       </c>
       <c r="J27" t="n">
-        <v>23.34</v>
+        <v>23.62</v>
       </c>
       <c r="K27" t="n">
-        <v>163.12</v>
+        <v>132.16</v>
       </c>
       <c r="L27" t="n">
         <v>89.41</v>
       </c>
       <c r="M27" t="n">
-        <v>-6.46</v>
+        <v>-5.85</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -1674,37 +1674,37 @@
         <v>16</v>
       </c>
       <c r="C28" t="n">
-        <v>33.52</v>
+        <v>33.64</v>
       </c>
       <c r="D28" t="n">
-        <v>13.17</v>
+        <v>13.54</v>
       </c>
       <c r="E28" t="n">
-        <v>6.86</v>
+        <v>6.79</v>
       </c>
       <c r="F28" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="G28" t="n">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H28" t="n">
-        <v>5763</v>
+        <v>5759</v>
       </c>
       <c r="I28" t="n">
-        <v>82.55</v>
+        <v>82.94</v>
       </c>
       <c r="J28" t="n">
-        <v>5.55</v>
+        <v>6.02</v>
       </c>
       <c r="K28" t="n">
-        <v>134.21</v>
+        <v>134.36</v>
       </c>
       <c r="L28" t="n">
         <v>81.88</v>
       </c>
       <c r="M28" t="n">
-        <v>0.67</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -1712,44 +1712,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>34.42</v>
+        <v>32.49</v>
       </c>
       <c r="D29" t="n">
-        <v>11.35</v>
+        <v>11.99</v>
       </c>
       <c r="E29" t="n">
-        <v>6.68</v>
+        <v>7.56</v>
       </c>
       <c r="F29" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="G29" t="n">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="H29" t="n">
-        <v>4926</v>
+        <v>5491</v>
       </c>
       <c r="I29" t="n">
-        <v>81.77</v>
+        <v>81.41</v>
       </c>
       <c r="J29" t="n">
-        <v>36.35</v>
+        <v>35.76</v>
       </c>
       <c r="K29" t="n">
-        <v>174.3</v>
+        <v>147.52</v>
       </c>
       <c r="L29" t="n">
-        <v>86.47</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>-4.7</v>
+        <v>-8.94</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -1757,44 +1757,44 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>16</v>
       </c>
       <c r="C30" t="n">
-        <v>32.68</v>
+        <v>35.16</v>
       </c>
       <c r="D30" t="n">
-        <v>11.95</v>
+        <v>11.97</v>
       </c>
       <c r="E30" t="n">
-        <v>7.64</v>
+        <v>7.08</v>
       </c>
       <c r="F30" t="n">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="G30" t="n">
-        <v>343</v>
+        <v>382</v>
       </c>
       <c r="H30" t="n">
-        <v>5493</v>
+        <v>5227</v>
       </c>
       <c r="I30" t="n">
-        <v>81.66</v>
+        <v>81.36</v>
       </c>
       <c r="J30" t="n">
-        <v>36.14</v>
+        <v>21.27</v>
       </c>
       <c r="K30" t="n">
-        <v>147.65</v>
+        <v>178.71</v>
       </c>
       <c r="L30" t="n">
-        <v>90.34999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="M30" t="n">
-        <v>-8.69</v>
+        <v>-5.23</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -1802,44 +1802,44 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C31" t="n">
-        <v>35.08</v>
+        <v>35.14</v>
       </c>
       <c r="D31" t="n">
-        <v>11.73</v>
+        <v>11.21</v>
       </c>
       <c r="E31" t="n">
-        <v>6.96</v>
+        <v>6.5</v>
       </c>
       <c r="F31" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="G31" t="n">
-        <v>381</v>
+        <v>328</v>
       </c>
       <c r="H31" t="n">
-        <v>5255</v>
+        <v>4955</v>
       </c>
       <c r="I31" t="n">
-        <v>80.56999999999999</v>
+        <v>80.89</v>
       </c>
       <c r="J31" t="n">
-        <v>20.89</v>
+        <v>36.97</v>
       </c>
       <c r="K31" t="n">
-        <v>177.68</v>
+        <v>175.57</v>
       </c>
       <c r="L31" t="n">
-        <v>86.59</v>
+        <v>86.47</v>
       </c>
       <c r="M31" t="n">
-        <v>-6.02</v>
+        <v>-5.58</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -1869,7 +1869,7 @@
         <v>405</v>
       </c>
       <c r="H32" t="n">
-        <v>5584</v>
+        <v>5575</v>
       </c>
       <c r="I32" t="n">
         <v>79.93000000000001</v>
@@ -1899,37 +1899,37 @@
         <v>16</v>
       </c>
       <c r="C33" t="n">
-        <v>32.09</v>
+        <v>32.15</v>
       </c>
       <c r="D33" t="n">
-        <v>10.87</v>
+        <v>10.91</v>
       </c>
       <c r="E33" t="n">
-        <v>6.59</v>
+        <v>6.7</v>
       </c>
       <c r="F33" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="G33" t="n">
         <v>420</v>
       </c>
       <c r="H33" t="n">
-        <v>5817</v>
+        <v>5829</v>
       </c>
       <c r="I33" t="n">
-        <v>75</v>
+        <v>75.75</v>
       </c>
       <c r="J33" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="K33" t="n">
-        <v>126.7</v>
+        <v>127.79</v>
       </c>
       <c r="L33" t="n">
         <v>85.65000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>-10.65</v>
+        <v>-9.9</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2168,31 +2168,31 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>2.251</v>
+        <v>2.295</v>
       </c>
       <c r="F5" t="n">
-        <v>0.763</v>
+        <v>0.836</v>
       </c>
       <c r="G5" t="n">
-        <v>0.451</v>
+        <v>0.537</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1246</v>
+        <v>0.1344</v>
       </c>
       <c r="I5" t="n">
-        <v>24.83</v>
+        <v>24.89</v>
       </c>
       <c r="J5" t="n">
-        <v>323.6</v>
+        <v>332.8</v>
       </c>
       <c r="K5" t="n">
-        <v>5.427</v>
+        <v>5.847</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.699</v>
+        <v>-2.553</v>
       </c>
       <c r="M5" t="n">
-        <v>20.737</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="6">
@@ -2573,31 +2573,31 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.091</v>
+        <v>2.236</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="G14" t="n">
-        <v>0.529</v>
+        <v>0.453</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1069</v>
+        <v>0.1035</v>
       </c>
       <c r="I14" t="n">
-        <v>25.23</v>
+        <v>25.7</v>
       </c>
       <c r="J14" t="n">
-        <v>339.3</v>
+        <v>357.2</v>
       </c>
       <c r="K14" t="n">
-        <v>5.176</v>
+        <v>5.273</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.093</v>
+        <v>-4.06</v>
       </c>
       <c r="M14" t="n">
-        <v>20.244</v>
+        <v>18.376</v>
       </c>
     </row>
     <row r="15">
@@ -3203,31 +3203,31 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>2.515</v>
+        <v>2.552</v>
       </c>
       <c r="F28" t="n">
-        <v>0.88</v>
+        <v>0.958</v>
       </c>
       <c r="G28" t="n">
-        <v>0.472</v>
+        <v>0.536</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1295</v>
+        <v>0.2019</v>
       </c>
       <c r="I28" t="n">
-        <v>20.55</v>
+        <v>21.97</v>
       </c>
       <c r="J28" t="n">
-        <v>318.3</v>
+        <v>326.1</v>
       </c>
       <c r="K28" t="n">
-        <v>5.996</v>
+        <v>6.751</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.502</v>
+        <v>-2.24</v>
       </c>
       <c r="M28" t="n">
-        <v>21.678</v>
+        <v>23.338</v>
       </c>
     </row>
     <row r="29">
@@ -3743,31 +3743,31 @@
         <v>-1</v>
       </c>
       <c r="E40" t="n">
-        <v>2.461</v>
+        <v>2.511</v>
       </c>
       <c r="F40" t="n">
-        <v>0.854</v>
+        <v>0.913</v>
       </c>
       <c r="G40" t="n">
-        <v>0.508</v>
+        <v>0.578</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1251</v>
+        <v>0.2198</v>
       </c>
       <c r="I40" t="n">
-        <v>20.73</v>
+        <v>21.05</v>
       </c>
       <c r="J40" t="n">
-        <v>332.2</v>
+        <v>310.7</v>
       </c>
       <c r="K40" t="n">
-        <v>5.936</v>
+        <v>6.812</v>
       </c>
       <c r="L40" t="n">
-        <v>-3.83</v>
+        <v>-2.219</v>
       </c>
       <c r="M40" t="n">
-        <v>21.175</v>
+        <v>23.089</v>
       </c>
     </row>
     <row r="41">
@@ -3833,31 +3833,31 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>2.753</v>
+        <v>2.498</v>
       </c>
       <c r="F42" t="n">
-        <v>0.792</v>
+        <v>0.796</v>
       </c>
       <c r="G42" t="n">
-        <v>0.592</v>
+        <v>0.523</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1303</v>
+        <v>0.1226</v>
       </c>
       <c r="I42" t="n">
-        <v>20.78</v>
+        <v>20.57</v>
       </c>
       <c r="J42" t="n">
-        <v>302.7</v>
+        <v>301.1</v>
       </c>
       <c r="K42" t="n">
-        <v>6.303</v>
+        <v>5.872</v>
       </c>
       <c r="L42" t="n">
-        <v>-2.395</v>
+        <v>-2.545</v>
       </c>
       <c r="M42" t="n">
-        <v>21.771</v>
+        <v>21.052</v>
       </c>
     </row>
     <row r="43">
@@ -4193,31 +4193,31 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.596</v>
+        <v>2.382</v>
       </c>
       <c r="F50" t="n">
-        <v>0.722</v>
+        <v>0.706</v>
       </c>
       <c r="G50" t="n">
-        <v>0.458</v>
+        <v>0.418</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1235</v>
+        <v>0.1174</v>
       </c>
       <c r="I50" t="n">
-        <v>20.79</v>
+        <v>21.64</v>
       </c>
       <c r="J50" t="n">
-        <v>314.7</v>
+        <v>313.2</v>
       </c>
       <c r="K50" t="n">
-        <v>5.697</v>
+        <v>5.334</v>
       </c>
       <c r="L50" t="n">
-        <v>-2.605</v>
+        <v>-2.731</v>
       </c>
       <c r="M50" t="n">
-        <v>21.109</v>
+        <v>20.468</v>
       </c>
     </row>
     <row r="51">
@@ -4238,31 +4238,31 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>2.594</v>
+        <v>2.603</v>
       </c>
       <c r="F51" t="n">
-        <v>0.828</v>
+        <v>0.831</v>
       </c>
       <c r="G51" t="n">
         <v>0.459</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1044</v>
+        <v>0.1051</v>
       </c>
       <c r="I51" t="n">
-        <v>20.34</v>
+        <v>21.86</v>
       </c>
       <c r="J51" t="n">
-        <v>327.2</v>
+        <v>325.7</v>
       </c>
       <c r="K51" t="n">
-        <v>5.794</v>
+        <v>5.814</v>
       </c>
       <c r="L51" t="n">
-        <v>-2.572</v>
+        <v>-2.565</v>
       </c>
       <c r="M51" t="n">
-        <v>21.138</v>
+        <v>21.182</v>
       </c>
     </row>
     <row r="52">
@@ -4283,31 +4283,31 @@
         <v>-1</v>
       </c>
       <c r="E52" t="n">
-        <v>2.23</v>
+        <v>2.314</v>
       </c>
       <c r="F52" t="n">
-        <v>0.775</v>
+        <v>0.754</v>
       </c>
       <c r="G52" t="n">
         <v>0.525</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1031</v>
+        <v>0.1022</v>
       </c>
       <c r="I52" t="n">
-        <v>21.81</v>
+        <v>22.46</v>
       </c>
       <c r="J52" t="n">
-        <v>332.6</v>
+        <v>332.1</v>
       </c>
       <c r="K52" t="n">
-        <v>5.449</v>
+        <v>5.485</v>
       </c>
       <c r="L52" t="n">
-        <v>-2.691</v>
+        <v>-2.679</v>
       </c>
       <c r="M52" t="n">
-        <v>20.659</v>
+        <v>20.701</v>
       </c>
     </row>
     <row r="53">
@@ -4328,31 +4328,31 @@
         <v>-1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.451</v>
+        <v>2.531</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8</v>
+        <v>0.792</v>
       </c>
       <c r="G53" t="n">
-        <v>0.415</v>
+        <v>0.408</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1256</v>
+        <v>0.1271</v>
       </c>
       <c r="I53" t="n">
-        <v>21.31</v>
+        <v>22.6</v>
       </c>
       <c r="J53" t="n">
-        <v>325.8</v>
+        <v>323.5</v>
       </c>
       <c r="K53" t="n">
-        <v>5.635</v>
+        <v>5.694</v>
       </c>
       <c r="L53" t="n">
-        <v>-2.627</v>
+        <v>-2.606</v>
       </c>
       <c r="M53" t="n">
-        <v>21.021</v>
+        <v>21.113</v>
       </c>
     </row>
     <row r="54">
@@ -4373,31 +4373,31 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>2.488</v>
+        <v>2.476</v>
       </c>
       <c r="F54" t="n">
-        <v>0.758</v>
+        <v>0.732</v>
       </c>
       <c r="G54" t="n">
-        <v>0.426</v>
+        <v>0.418</v>
       </c>
       <c r="H54" t="n">
-        <v>0.134</v>
+        <v>0.1373</v>
       </c>
       <c r="I54" t="n">
-        <v>21.12</v>
+        <v>21.81</v>
       </c>
       <c r="J54" t="n">
-        <v>312.8</v>
+        <v>315.9</v>
       </c>
       <c r="K54" t="n">
-        <v>5.66</v>
+        <v>5.6</v>
       </c>
       <c r="L54" t="n">
-        <v>-2.618</v>
+        <v>-2.639</v>
       </c>
       <c r="M54" t="n">
-        <v>21.121</v>
+        <v>21.03</v>
       </c>
     </row>
     <row r="55">
@@ -4418,31 +4418,31 @@
         <v>-1</v>
       </c>
       <c r="E55" t="n">
-        <v>2.137</v>
+        <v>2.218</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.795</v>
       </c>
       <c r="G55" t="n">
-        <v>0.446</v>
+        <v>0.439</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1054</v>
+        <v>0.1045</v>
       </c>
       <c r="I55" t="n">
-        <v>21.59</v>
+        <v>22.13</v>
       </c>
       <c r="J55" t="n">
-        <v>351.9</v>
+        <v>351.6</v>
       </c>
       <c r="K55" t="n">
-        <v>5.289</v>
+        <v>5.313</v>
       </c>
       <c r="L55" t="n">
-        <v>-4.054</v>
+        <v>-4.046</v>
       </c>
       <c r="M55" t="n">
-        <v>20.39</v>
+        <v>20.396</v>
       </c>
     </row>
     <row r="56">
@@ -4463,31 +4463,31 @@
         <v>-1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.121</v>
+        <v>2.3</v>
       </c>
       <c r="F56" t="n">
-        <v>0.719</v>
+        <v>0.737</v>
       </c>
       <c r="G56" t="n">
-        <v>0.461</v>
+        <v>0.419</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1078</v>
+        <v>0.1118</v>
       </c>
       <c r="I56" t="n">
-        <v>21.04</v>
+        <v>21.88</v>
       </c>
       <c r="J56" t="n">
-        <v>331.9</v>
+        <v>347.5</v>
       </c>
       <c r="K56" t="n">
-        <v>5.128</v>
+        <v>5.283</v>
       </c>
       <c r="L56" t="n">
-        <v>-2.802</v>
+        <v>-4.056</v>
       </c>
       <c r="M56" t="n">
-        <v>20.141</v>
+        <v>20.368</v>
       </c>
     </row>
     <row r="57">
@@ -4508,31 +4508,31 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>2.062</v>
+        <v>2.12</v>
       </c>
       <c r="F57" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.666</v>
       </c>
       <c r="G57" t="n">
-        <v>0.347</v>
+        <v>0.357</v>
       </c>
       <c r="H57" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.099</v>
       </c>
       <c r="I57" t="n">
-        <v>20.38</v>
+        <v>21.49</v>
       </c>
       <c r="J57" t="n">
-        <v>328.2</v>
+        <v>327.4</v>
       </c>
       <c r="K57" t="n">
-        <v>4.71</v>
+        <v>4.76</v>
       </c>
       <c r="L57" t="n">
-        <v>-2.947</v>
+        <v>-2.929</v>
       </c>
       <c r="M57" t="n">
-        <v>19.303</v>
+        <v>19.392</v>
       </c>
     </row>
     <row r="58">
@@ -4553,31 +4553,31 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>2.282</v>
+        <v>2.308</v>
       </c>
       <c r="F58" t="n">
-        <v>0.737</v>
+        <v>0.711</v>
       </c>
       <c r="G58" t="n">
         <v>0.46</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1054</v>
+        <v>0.1045</v>
       </c>
       <c r="I58" t="n">
-        <v>21.33</v>
+        <v>21.58</v>
       </c>
       <c r="J58" t="n">
-        <v>341.2</v>
+        <v>339.7</v>
       </c>
       <c r="K58" t="n">
-        <v>5.308</v>
+        <v>5.277</v>
       </c>
       <c r="L58" t="n">
-        <v>-4.047</v>
+        <v>-4.058</v>
       </c>
       <c r="M58" t="n">
-        <v>20.39</v>
+        <v>20.318</v>
       </c>
     </row>
     <row r="59">
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.47</v>
+        <v>2.544</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G59" t="n">
         <v>0.459</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1044</v>
+        <v>0.1051</v>
       </c>
       <c r="I59" t="n">
-        <v>21.56</v>
+        <v>22.15</v>
       </c>
       <c r="J59" t="n">
-        <v>338.7</v>
+        <v>338.4</v>
       </c>
       <c r="K59" t="n">
-        <v>5.628</v>
+        <v>5.713</v>
       </c>
       <c r="L59" t="n">
-        <v>-3.937</v>
+        <v>-3.907</v>
       </c>
       <c r="M59" t="n">
-        <v>20.891</v>
+        <v>21.017</v>
       </c>
     </row>
     <row r="60">
@@ -4643,31 +4643,31 @@
         <v>-1</v>
       </c>
       <c r="E60" t="n">
-        <v>1.885</v>
+        <v>1.964</v>
       </c>
       <c r="F60" t="n">
-        <v>0.662</v>
+        <v>0.657</v>
       </c>
       <c r="G60" t="n">
-        <v>0.433</v>
+        <v>0.425</v>
       </c>
       <c r="H60" t="n">
-        <v>0.108</v>
+        <v>0.0984</v>
       </c>
       <c r="I60" t="n">
-        <v>20.79</v>
+        <v>21.87</v>
       </c>
       <c r="J60" t="n">
-        <v>346.9</v>
+        <v>345.6</v>
       </c>
       <c r="K60" t="n">
-        <v>4.723</v>
+        <v>4.718</v>
       </c>
       <c r="L60" t="n">
-        <v>-4.25</v>
+        <v>-4.252</v>
       </c>
       <c r="M60" t="n">
-        <v>19.481</v>
+        <v>19.383</v>
       </c>
     </row>
     <row r="61">
@@ -4688,31 +4688,31 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>2.53</v>
+        <v>2.529</v>
       </c>
       <c r="F61" t="n">
-        <v>0.799</v>
+        <v>0.784</v>
       </c>
       <c r="G61" t="n">
-        <v>0.499</v>
+        <v>0.461</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1318</v>
+        <v>0.1322</v>
       </c>
       <c r="I61" t="n">
-        <v>20.62</v>
+        <v>21.73</v>
       </c>
       <c r="J61" t="n">
-        <v>302.6</v>
+        <v>306</v>
       </c>
       <c r="K61" t="n">
-        <v>5.917</v>
+        <v>5.812</v>
       </c>
       <c r="L61" t="n">
-        <v>-2.529</v>
+        <v>-2.565</v>
       </c>
       <c r="M61" t="n">
-        <v>21.571</v>
+        <v>21.379</v>
       </c>
     </row>
     <row r="62">
@@ -4733,31 +4733,31 @@
         <v>-1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.402</v>
+        <v>2.465</v>
       </c>
       <c r="F62" t="n">
-        <v>0.842</v>
+        <v>0.825</v>
       </c>
       <c r="G62" t="n">
         <v>0.481</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1601</v>
+        <v>0.1631</v>
       </c>
       <c r="I62" t="n">
-        <v>19.73</v>
+        <v>20.7</v>
       </c>
       <c r="J62" t="n">
-        <v>313.5</v>
+        <v>311.3</v>
       </c>
       <c r="K62" t="n">
-        <v>7.009</v>
+        <v>6.056</v>
       </c>
       <c r="L62" t="n">
-        <v>-2.151</v>
+        <v>-2.481</v>
       </c>
       <c r="M62" t="n">
-        <v>22.246</v>
+        <v>21.985</v>
       </c>
     </row>
     <row r="63">
@@ -4778,31 +4778,31 @@
         <v>-1</v>
       </c>
       <c r="E63" t="n">
-        <v>1.939</v>
+        <v>2.014</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.668</v>
       </c>
       <c r="G63" t="n">
-        <v>0.347</v>
+        <v>0.357</v>
       </c>
       <c r="H63" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.099</v>
       </c>
       <c r="I63" t="n">
-        <v>20.95</v>
+        <v>22.1</v>
       </c>
       <c r="J63" t="n">
-        <v>337.3</v>
+        <v>337.2</v>
       </c>
       <c r="K63" t="n">
-        <v>4.587</v>
+        <v>4.658</v>
       </c>
       <c r="L63" t="n">
-        <v>-4.297</v>
+        <v>-4.272</v>
       </c>
       <c r="M63" t="n">
-        <v>19.117</v>
+        <v>19.233</v>
       </c>
     </row>
     <row r="64">
@@ -4823,31 +4823,31 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>2.231</v>
+        <v>2.376</v>
       </c>
       <c r="F64" t="n">
-        <v>0.719</v>
+        <v>0.745</v>
       </c>
       <c r="G64" t="n">
-        <v>0.461</v>
+        <v>0.419</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1078</v>
+        <v>0.1118</v>
       </c>
       <c r="I64" t="n">
-        <v>20.49</v>
+        <v>22.29</v>
       </c>
       <c r="J64" t="n">
-        <v>321</v>
+        <v>339.7</v>
       </c>
       <c r="K64" t="n">
-        <v>5.238</v>
+        <v>5.375</v>
       </c>
       <c r="L64" t="n">
-        <v>-2.764</v>
+        <v>-4.024</v>
       </c>
       <c r="M64" t="n">
-        <v>20.303</v>
+        <v>20.511</v>
       </c>
     </row>
     <row r="65">
@@ -4958,31 +4958,31 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>2.116</v>
+        <v>2.175</v>
       </c>
       <c r="F67" t="n">
-        <v>0.728</v>
+        <v>0.767</v>
       </c>
       <c r="G67" t="n">
-        <v>0.4</v>
+        <v>0.504</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1096</v>
+        <v>0.1771</v>
       </c>
       <c r="I67" t="n">
-        <v>26.09</v>
+        <v>25.96</v>
       </c>
       <c r="J67" t="n">
-        <v>338.2</v>
+        <v>351</v>
       </c>
       <c r="K67" t="n">
-        <v>5.03</v>
+        <v>5.78</v>
       </c>
       <c r="L67" t="n">
-        <v>-2.836</v>
+        <v>-2.576</v>
       </c>
       <c r="M67" t="n">
-        <v>20.345</v>
+        <v>22.097</v>
       </c>
     </row>
     <row r="68">
@@ -5600,7 +5600,7 @@
         <v>0.1048</v>
       </c>
       <c r="I81" t="n">
-        <v>23.74</v>
+        <v>23.54</v>
       </c>
       <c r="J81" t="n">
         <v>360.8</v>
@@ -5645,7 +5645,7 @@
         <v>0.1147</v>
       </c>
       <c r="I82" t="n">
-        <v>24.63</v>
+        <v>24.19</v>
       </c>
       <c r="J82" t="n">
         <v>353.8</v>
@@ -5678,31 +5678,31 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.204</v>
+        <v>2.327</v>
       </c>
       <c r="F83" t="n">
-        <v>0.763</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>0.433</v>
+        <v>0.392</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1071</v>
+        <v>0.1125</v>
       </c>
       <c r="I83" t="n">
-        <v>22.86</v>
+        <v>24.24</v>
       </c>
       <c r="J83" t="n">
-        <v>342</v>
+        <v>360.8</v>
       </c>
       <c r="K83" t="n">
-        <v>5.239</v>
+        <v>5.406</v>
       </c>
       <c r="L83" t="n">
-        <v>-4.071</v>
+        <v>-4.014</v>
       </c>
       <c r="M83" t="n">
-        <v>20.302</v>
+        <v>20.586</v>
       </c>
     </row>
     <row r="84">
@@ -5735,7 +5735,7 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>25.05</v>
+        <v>25.08</v>
       </c>
       <c r="J84" t="n">
         <v>359.2</v>
@@ -5780,7 +5780,7 @@
         <v>0.0954</v>
       </c>
       <c r="I85" t="n">
-        <v>24.61</v>
+        <v>24.73</v>
       </c>
       <c r="J85" t="n">
         <v>365.2</v>
@@ -5825,7 +5825,7 @@
         <v>0.1088</v>
       </c>
       <c r="I86" t="n">
-        <v>22.31</v>
+        <v>22.29</v>
       </c>
       <c r="J86" t="n">
         <v>349.7</v>
@@ -5870,7 +5870,7 @@
         <v>0.1153</v>
       </c>
       <c r="I87" t="n">
-        <v>24.43</v>
+        <v>24.76</v>
       </c>
       <c r="J87" t="n">
         <v>364</v>
@@ -5915,7 +5915,7 @@
         <v>0.1162</v>
       </c>
       <c r="I88" t="n">
-        <v>22.51</v>
+        <v>22.56</v>
       </c>
       <c r="J88" t="n">
         <v>333</v>
@@ -5960,7 +5960,7 @@
         <v>0.122</v>
       </c>
       <c r="I89" t="n">
-        <v>22.49</v>
+        <v>22.61</v>
       </c>
       <c r="J89" t="n">
         <v>347.6</v>
@@ -5993,31 +5993,31 @@
         <v>-1</v>
       </c>
       <c r="E90" t="n">
-        <v>2.256</v>
+        <v>2.343</v>
       </c>
       <c r="F90" t="n">
-        <v>0.795</v>
+        <v>0.879</v>
       </c>
       <c r="G90" t="n">
-        <v>0.404</v>
+        <v>0.53</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1389</v>
+        <v>0.2206</v>
       </c>
       <c r="I90" t="n">
-        <v>24.68</v>
+        <v>24.37</v>
       </c>
       <c r="J90" t="n">
-        <v>350.9</v>
+        <v>354.3</v>
       </c>
       <c r="K90" t="n">
-        <v>5.487</v>
+        <v>6.485</v>
       </c>
       <c r="L90" t="n">
-        <v>-3.986</v>
+        <v>-3.64</v>
       </c>
       <c r="M90" t="n">
-        <v>20.903</v>
+        <v>23.018</v>
       </c>
     </row>
     <row r="91">
@@ -6095,7 +6095,7 @@
         <v>0.1024</v>
       </c>
       <c r="I92" t="n">
-        <v>25.25</v>
+        <v>25.37</v>
       </c>
       <c r="J92" t="n">
         <v>354.6</v>
@@ -6128,31 +6128,31 @@
         <v>-1</v>
       </c>
       <c r="E93" t="n">
-        <v>2.289</v>
+        <v>2.343</v>
       </c>
       <c r="F93" t="n">
-        <v>0.82</v>
+        <v>0.879</v>
       </c>
       <c r="G93" t="n">
-        <v>0.404</v>
+        <v>0.53</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1205</v>
+        <v>0.2206</v>
       </c>
       <c r="I93" t="n">
-        <v>25.13</v>
+        <v>24.37</v>
       </c>
       <c r="J93" t="n">
-        <v>367.3</v>
+        <v>354.3</v>
       </c>
       <c r="K93" t="n">
-        <v>5.46</v>
+        <v>6.485</v>
       </c>
       <c r="L93" t="n">
-        <v>-3.995</v>
+        <v>-3.64</v>
       </c>
       <c r="M93" t="n">
-        <v>20.088</v>
+        <v>23.018</v>
       </c>
     </row>
     <row r="94">
@@ -6218,31 +6218,31 @@
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>2.362</v>
+        <v>2.394</v>
       </c>
       <c r="F95" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.885</v>
       </c>
       <c r="G95" t="n">
-        <v>0.404</v>
+        <v>0.53</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1389</v>
+        <v>0.2206</v>
       </c>
       <c r="I95" t="n">
-        <v>21.11</v>
+        <v>22.87</v>
       </c>
       <c r="J95" t="n">
-        <v>328.4</v>
+        <v>337.3</v>
       </c>
       <c r="K95" t="n">
-        <v>5.623</v>
+        <v>6.548</v>
       </c>
       <c r="L95" t="n">
-        <v>-2.631</v>
+        <v>-3.618</v>
       </c>
       <c r="M95" t="n">
-        <v>21.12</v>
+        <v>23.105</v>
       </c>
     </row>
     <row r="96">
@@ -6275,7 +6275,7 @@
         <v>0.1048</v>
       </c>
       <c r="I96" t="n">
-        <v>24.83</v>
+        <v>24.74</v>
       </c>
       <c r="J96" t="n">
         <v>367.2</v>
@@ -6320,7 +6320,7 @@
         <v>0.1195</v>
       </c>
       <c r="I97" t="n">
-        <v>24.53</v>
+        <v>24.57</v>
       </c>
       <c r="J97" t="n">
         <v>355.2</v>
@@ -6365,7 +6365,7 @@
         <v>0.1203</v>
       </c>
       <c r="I98" t="n">
-        <v>24.79</v>
+        <v>24.83</v>
       </c>
       <c r="J98" t="n">
         <v>347.6</v>
@@ -6410,7 +6410,7 @@
         <v>0.1109</v>
       </c>
       <c r="I99" t="n">
-        <v>22.69</v>
+        <v>22.7</v>
       </c>
       <c r="J99" t="n">
         <v>314.1</v>
@@ -6455,7 +6455,7 @@
         <v>0.0975</v>
       </c>
       <c r="I100" t="n">
-        <v>24.92</v>
+        <v>24.96</v>
       </c>
       <c r="J100" t="n">
         <v>350.4</v>
@@ -6500,7 +6500,7 @@
         <v>0.1082</v>
       </c>
       <c r="I101" t="n">
-        <v>24.63</v>
+        <v>24.67</v>
       </c>
       <c r="J101" t="n">
         <v>351.6</v>
@@ -6545,7 +6545,7 @@
         <v>0.124</v>
       </c>
       <c r="I102" t="n">
-        <v>24.22</v>
+        <v>24.15</v>
       </c>
       <c r="J102" t="n">
         <v>319</v>
@@ -6590,7 +6590,7 @@
         <v>0.1083</v>
       </c>
       <c r="I103" t="n">
-        <v>24.6</v>
+        <v>24.64</v>
       </c>
       <c r="J103" t="n">
         <v>359.1</v>
@@ -6635,7 +6635,7 @@
         <v>0.1203</v>
       </c>
       <c r="I104" t="n">
-        <v>25.42</v>
+        <v>25.15</v>
       </c>
       <c r="J104" t="n">
         <v>329</v>
@@ -6680,7 +6680,7 @@
         <v>0.1249</v>
       </c>
       <c r="I105" t="n">
-        <v>24.2</v>
+        <v>24.22</v>
       </c>
       <c r="J105" t="n">
         <v>361.1</v>
@@ -6725,7 +6725,7 @@
         <v>0.0946</v>
       </c>
       <c r="I106" t="n">
-        <v>25.37</v>
+        <v>25.3</v>
       </c>
       <c r="J106" t="n">
         <v>339.9</v>
@@ -6770,7 +6770,7 @@
         <v>0.1242</v>
       </c>
       <c r="I107" t="n">
-        <v>24.78</v>
+        <v>24.8</v>
       </c>
       <c r="J107" t="n">
         <v>353.9</v>
@@ -6815,7 +6815,7 @@
         <v>0.1033</v>
       </c>
       <c r="I108" t="n">
-        <v>24.6</v>
+        <v>24.43</v>
       </c>
       <c r="J108" t="n">
         <v>355.6</v>
@@ -6860,7 +6860,7 @@
         <v>0.0993</v>
       </c>
       <c r="I109" t="n">
-        <v>24.76</v>
+        <v>24.8</v>
       </c>
       <c r="J109" t="n">
         <v>351.2</v>
@@ -6905,7 +6905,7 @@
         <v>0.1039</v>
       </c>
       <c r="I110" t="n">
-        <v>24.59</v>
+        <v>24.63</v>
       </c>
       <c r="J110" t="n">
         <v>343.2</v>
@@ -6950,7 +6950,7 @@
         <v>0.1082</v>
       </c>
       <c r="I111" t="n">
-        <v>24.18</v>
+        <v>24.12</v>
       </c>
       <c r="J111" t="n">
         <v>332.8</v>
@@ -6995,7 +6995,7 @@
         <v>0.1242</v>
       </c>
       <c r="I112" t="n">
-        <v>24.06</v>
+        <v>23.91</v>
       </c>
       <c r="J112" t="n">
         <v>342</v>
@@ -7040,7 +7040,7 @@
         <v>0.1422</v>
       </c>
       <c r="I113" t="n">
-        <v>26.43</v>
+        <v>26.42</v>
       </c>
       <c r="J113" t="n">
         <v>358.8</v>
@@ -7163,31 +7163,31 @@
         <v>-1</v>
       </c>
       <c r="E116" t="n">
-        <v>2.145</v>
+        <v>2.292</v>
       </c>
       <c r="F116" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.727</v>
       </c>
       <c r="G116" t="n">
-        <v>0.472</v>
+        <v>0.437</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1374</v>
+        <v>0.148</v>
       </c>
       <c r="I116" t="n">
-        <v>26.26</v>
+        <v>24.86</v>
       </c>
       <c r="J116" t="n">
-        <v>362.6</v>
+        <v>371.1</v>
       </c>
       <c r="K116" t="n">
-        <v>5.285</v>
+        <v>5.508</v>
       </c>
       <c r="L116" t="n">
-        <v>-4.055</v>
+        <v>-3.978</v>
       </c>
       <c r="M116" t="n">
-        <v>21.003</v>
+        <v>21.41</v>
       </c>
     </row>
     <row r="117">
@@ -7310,7 +7310,7 @@
         <v>0.1591</v>
       </c>
       <c r="I119" t="n">
-        <v>24.62</v>
+        <v>24.61</v>
       </c>
       <c r="J119" t="n">
         <v>355.4</v>
@@ -7580,7 +7580,7 @@
         <v>0.1382</v>
       </c>
       <c r="I125" t="n">
-        <v>25.48</v>
+        <v>25.47</v>
       </c>
       <c r="J125" t="n">
         <v>364.7</v>
@@ -7715,7 +7715,7 @@
         <v>0.1397</v>
       </c>
       <c r="I128" t="n">
-        <v>25.73</v>
+        <v>25.72</v>
       </c>
       <c r="J128" t="n">
         <v>360.4</v>
@@ -7808,7 +7808,7 @@
         <v>26.13</v>
       </c>
       <c r="J130" t="n">
-        <v>343</v>
+        <v>341.2</v>
       </c>
       <c r="K130" t="n">
         <v>5.156</v>
@@ -7898,7 +7898,7 @@
         <v>23.73</v>
       </c>
       <c r="J132" t="n">
-        <v>335.7</v>
+        <v>333.9</v>
       </c>
       <c r="K132" t="n">
         <v>5.166</v>
@@ -8033,7 +8033,7 @@
         <v>24.45</v>
       </c>
       <c r="J135" t="n">
-        <v>328.2</v>
+        <v>326.4</v>
       </c>
       <c r="K135" t="n">
         <v>5.477</v>
@@ -8168,7 +8168,7 @@
         <v>26.07</v>
       </c>
       <c r="J138" t="n">
-        <v>327.1</v>
+        <v>325.3</v>
       </c>
       <c r="K138" t="n">
         <v>5.507</v>
@@ -8348,7 +8348,7 @@
         <v>24.27</v>
       </c>
       <c r="J142" t="n">
-        <v>322</v>
+        <v>320.2</v>
       </c>
       <c r="K142" t="n">
         <v>5.9</v>
@@ -8603,31 +8603,31 @@
         <v>-1</v>
       </c>
       <c r="E148" t="n">
-        <v>2.624</v>
+        <v>2.41</v>
       </c>
       <c r="F148" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="G148" t="n">
-        <v>0.531</v>
+        <v>0.508</v>
       </c>
       <c r="H148" t="n">
-        <v>0.1577</v>
+        <v>0.1407</v>
       </c>
       <c r="I148" t="n">
-        <v>20.21</v>
+        <v>20.55</v>
       </c>
       <c r="J148" t="n">
-        <v>317.1</v>
+        <v>317.4</v>
       </c>
       <c r="K148" t="n">
-        <v>6.156</v>
+        <v>5.796</v>
       </c>
       <c r="L148" t="n">
-        <v>-2.446</v>
+        <v>-2.571</v>
       </c>
       <c r="M148" t="n">
-        <v>22.102</v>
+        <v>21.452</v>
       </c>
     </row>
     <row r="149">
@@ -8963,31 +8963,31 @@
         <v>-1</v>
       </c>
       <c r="E156" t="n">
-        <v>2.275</v>
+        <v>2.397</v>
       </c>
       <c r="F156" t="n">
-        <v>0.768</v>
+        <v>0.798</v>
       </c>
       <c r="G156" t="n">
-        <v>0.551</v>
+        <v>0.523</v>
       </c>
       <c r="H156" t="n">
-        <v>0.1454</v>
+        <v>0.1531</v>
       </c>
       <c r="I156" t="n">
-        <v>19.48</v>
+        <v>20.53</v>
       </c>
       <c r="J156" t="n">
-        <v>322.1</v>
+        <v>337.3</v>
       </c>
       <c r="K156" t="n">
-        <v>6.785</v>
+        <v>5.958</v>
       </c>
       <c r="L156" t="n">
-        <v>-2.229</v>
+        <v>-3.823</v>
       </c>
       <c r="M156" t="n">
-        <v>21.855</v>
+        <v>21.795</v>
       </c>
     </row>
     <row r="157">
@@ -9053,31 +9053,31 @@
         <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>2.579</v>
+        <v>2.589</v>
       </c>
       <c r="F158" t="n">
-        <v>0.831</v>
+        <v>0.887</v>
       </c>
       <c r="G158" t="n">
-        <v>0.536</v>
+        <v>0.55</v>
       </c>
       <c r="H158" t="n">
-        <v>0.1521</v>
+        <v>0.2498</v>
       </c>
       <c r="I158" t="n">
-        <v>20.26</v>
+        <v>19.52</v>
       </c>
       <c r="J158" t="n">
-        <v>329.7</v>
+        <v>312.8</v>
       </c>
       <c r="K158" t="n">
-        <v>6.226</v>
+        <v>7.962</v>
       </c>
       <c r="L158" t="n">
-        <v>-2.422</v>
+        <v>-1.821</v>
       </c>
       <c r="M158" t="n">
-        <v>22.209</v>
+        <v>24.237</v>
       </c>
     </row>
     <row r="159">
@@ -9143,31 +9143,31 @@
         <v>1</v>
       </c>
       <c r="E160" t="n">
-        <v>2.765</v>
+        <v>2.489</v>
       </c>
       <c r="F160" t="n">
-        <v>0.769</v>
+        <v>0.763</v>
       </c>
       <c r="G160" t="n">
-        <v>0.531</v>
+        <v>0.508</v>
       </c>
       <c r="H160" t="n">
-        <v>0.1577</v>
+        <v>0.1407</v>
       </c>
       <c r="I160" t="n">
-        <v>21.09</v>
+        <v>20.39</v>
       </c>
       <c r="J160" t="n">
-        <v>311.1</v>
+        <v>310.9</v>
       </c>
       <c r="K160" t="n">
-        <v>6.311</v>
+        <v>5.875</v>
       </c>
       <c r="L160" t="n">
-        <v>-2.393</v>
+        <v>-2.544</v>
       </c>
       <c r="M160" t="n">
-        <v>22.333</v>
+        <v>21.571</v>
       </c>
     </row>
     <row r="161">
@@ -9188,31 +9188,31 @@
         <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>2.51</v>
+        <v>2.502</v>
       </c>
       <c r="F161" t="n">
-        <v>0.79</v>
+        <v>0.825</v>
       </c>
       <c r="G161" t="n">
-        <v>0.551</v>
+        <v>0.422</v>
       </c>
       <c r="H161" t="n">
-        <v>0.1113</v>
+        <v>0.1068</v>
       </c>
       <c r="I161" t="n">
-        <v>22.17</v>
+        <v>24.02</v>
       </c>
       <c r="J161" t="n">
-        <v>325.2</v>
+        <v>340.2</v>
       </c>
       <c r="K161" t="n">
-        <v>5.86</v>
+        <v>5.637</v>
       </c>
       <c r="L161" t="n">
-        <v>-3.856</v>
+        <v>-3.934</v>
       </c>
       <c r="M161" t="n">
-        <v>20.962</v>
+        <v>20.504</v>
       </c>
     </row>
     <row r="162">
@@ -9233,31 +9233,31 @@
         <v>-1</v>
       </c>
       <c r="E162" t="n">
-        <v>2.72</v>
+        <v>2.683</v>
       </c>
       <c r="F162" t="n">
-        <v>0.913</v>
+        <v>0.888</v>
       </c>
       <c r="G162" t="n">
-        <v>0.579</v>
+        <v>0.498</v>
       </c>
       <c r="H162" t="n">
         <v>0.1163</v>
       </c>
       <c r="I162" t="n">
-        <v>21.77</v>
+        <v>22.98</v>
       </c>
       <c r="J162" t="n">
-        <v>334.8</v>
+        <v>336.7</v>
       </c>
       <c r="K162" t="n">
-        <v>6.402</v>
+        <v>6.153</v>
       </c>
       <c r="L162" t="n">
-        <v>-3.669</v>
+        <v>-3.755</v>
       </c>
       <c r="M162" t="n">
-        <v>21.852</v>
+        <v>21.425</v>
       </c>
     </row>
     <row r="163">
@@ -9278,31 +9278,31 @@
         <v>-1</v>
       </c>
       <c r="E163" t="n">
-        <v>2.692</v>
+        <v>2.634</v>
       </c>
       <c r="F163" t="n">
-        <v>0.887</v>
+        <v>0.882</v>
       </c>
       <c r="G163" t="n">
-        <v>0.581</v>
+        <v>0.459</v>
       </c>
       <c r="H163" t="n">
         <v>0.1154</v>
       </c>
       <c r="I163" t="n">
-        <v>20.84</v>
+        <v>21.87</v>
       </c>
       <c r="J163" t="n">
-        <v>325.8</v>
+        <v>326.5</v>
       </c>
       <c r="K163" t="n">
-        <v>6.32</v>
+        <v>6.008</v>
       </c>
       <c r="L163" t="n">
-        <v>-3.697</v>
+        <v>-3.805</v>
       </c>
       <c r="M163" t="n">
-        <v>21.709</v>
+        <v>21.176</v>
       </c>
     </row>
     <row r="164">
@@ -9323,31 +9323,31 @@
         <v>1</v>
       </c>
       <c r="E164" t="n">
-        <v>2.336</v>
+        <v>2.276</v>
       </c>
       <c r="F164" t="n">
-        <v>0.751</v>
+        <v>0.717</v>
       </c>
       <c r="G164" t="n">
-        <v>0.502</v>
+        <v>0.416</v>
       </c>
       <c r="H164" t="n">
         <v>0.095</v>
       </c>
       <c r="I164" t="n">
-        <v>22.76</v>
+        <v>23.78</v>
       </c>
       <c r="J164" t="n">
-        <v>331.8</v>
+        <v>331.4</v>
       </c>
       <c r="K164" t="n">
-        <v>5.412</v>
+        <v>5.112</v>
       </c>
       <c r="L164" t="n">
-        <v>-4.012</v>
+        <v>-4.115</v>
       </c>
       <c r="M164" t="n">
-        <v>20.121</v>
+        <v>19.599</v>
       </c>
     </row>
     <row r="165">
@@ -9368,31 +9368,31 @@
         <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>2.494</v>
+        <v>2.435</v>
       </c>
       <c r="F165" t="n">
-        <v>0.908</v>
+        <v>0.887</v>
       </c>
       <c r="G165" t="n">
-        <v>0.541</v>
+        <v>0.443</v>
       </c>
       <c r="H165" t="n">
         <v>0.1029</v>
       </c>
       <c r="I165" t="n">
-        <v>22.65</v>
+        <v>24.03</v>
       </c>
       <c r="J165" t="n">
-        <v>338.5</v>
+        <v>341.2</v>
       </c>
       <c r="K165" t="n">
-        <v>6.009</v>
+        <v>5.712</v>
       </c>
       <c r="L165" t="n">
-        <v>-3.805</v>
+        <v>-3.908</v>
       </c>
       <c r="M165" t="n">
-        <v>21.143</v>
+        <v>20.635</v>
       </c>
     </row>
     <row r="166">
@@ -9413,31 +9413,31 @@
         <v>-1</v>
       </c>
       <c r="E166" t="n">
-        <v>2.326</v>
+        <v>2.158</v>
       </c>
       <c r="F166" t="n">
-        <v>0.763</v>
+        <v>0.734</v>
       </c>
       <c r="G166" t="n">
-        <v>0.424</v>
+        <v>0.346</v>
       </c>
       <c r="H166" t="n">
         <v>0.1016</v>
       </c>
       <c r="I166" t="n">
-        <v>21.52</v>
+        <v>22.68</v>
       </c>
       <c r="J166" t="n">
-        <v>335.3</v>
+        <v>334.3</v>
       </c>
       <c r="K166" t="n">
-        <v>5.31</v>
+        <v>4.928</v>
       </c>
       <c r="L166" t="n">
-        <v>-4.047</v>
+        <v>-4.179</v>
       </c>
       <c r="M166" t="n">
-        <v>19.979</v>
+        <v>19.323</v>
       </c>
     </row>
     <row r="167">
@@ -9458,31 +9458,31 @@
         <v>1</v>
       </c>
       <c r="E167" t="n">
-        <v>2.815</v>
+        <v>2.771</v>
       </c>
       <c r="F167" t="n">
-        <v>0.9</v>
+        <v>0.883</v>
       </c>
       <c r="G167" t="n">
-        <v>0.536</v>
+        <v>0.439</v>
       </c>
       <c r="H167" t="n">
         <v>0.1068</v>
       </c>
       <c r="I167" t="n">
-        <v>22.49</v>
+        <v>23.43</v>
       </c>
       <c r="J167" t="n">
-        <v>330.4</v>
+        <v>330.3</v>
       </c>
       <c r="K167" t="n">
-        <v>6.328</v>
+        <v>6.056</v>
       </c>
       <c r="L167" t="n">
-        <v>-3.694</v>
+        <v>-3.789</v>
       </c>
       <c r="M167" t="n">
-        <v>21.613</v>
+        <v>21.146</v>
       </c>
     </row>
     <row r="168">
@@ -9503,31 +9503,31 @@
         <v>1</v>
       </c>
       <c r="E168" t="n">
-        <v>2.784</v>
+        <v>2.737</v>
       </c>
       <c r="F168" t="n">
-        <v>0.805</v>
+        <v>0.766</v>
       </c>
       <c r="G168" t="n">
-        <v>0.541</v>
+        <v>0.446</v>
       </c>
       <c r="H168" t="n">
         <v>0.1088</v>
       </c>
       <c r="I168" t="n">
-        <v>21.72</v>
+        <v>22.18</v>
       </c>
       <c r="J168" t="n">
-        <v>317.2</v>
+        <v>318</v>
       </c>
       <c r="K168" t="n">
-        <v>6.129</v>
+        <v>5.814</v>
       </c>
       <c r="L168" t="n">
-        <v>-2.456</v>
+        <v>-2.565</v>
       </c>
       <c r="M168" t="n">
-        <v>21.307</v>
+        <v>20.773</v>
       </c>
     </row>
     <row r="169">
@@ -9548,31 +9548,31 @@
         <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>2.73</v>
+        <v>2.686</v>
       </c>
       <c r="F169" t="n">
-        <v>0.891</v>
+        <v>0.865</v>
       </c>
       <c r="G169" t="n">
-        <v>0.612</v>
+        <v>0.499</v>
       </c>
       <c r="H169" t="n">
         <v>0.1165</v>
       </c>
       <c r="I169" t="n">
-        <v>21.7</v>
+        <v>22.48</v>
       </c>
       <c r="J169" t="n">
-        <v>315.8</v>
+        <v>316.6</v>
       </c>
       <c r="K169" t="n">
-        <v>6.435</v>
+        <v>6.113</v>
       </c>
       <c r="L169" t="n">
-        <v>-2.35</v>
+        <v>-2.461</v>
       </c>
       <c r="M169" t="n">
-        <v>21.915</v>
+        <v>21.346</v>
       </c>
     </row>
     <row r="170">
@@ -9593,31 +9593,31 @@
         <v>-1</v>
       </c>
       <c r="E170" t="n">
-        <v>2.318</v>
+        <v>2.245</v>
       </c>
       <c r="F170" t="n">
-        <v>0.797</v>
+        <v>0.778</v>
       </c>
       <c r="G170" t="n">
-        <v>0.555</v>
+        <v>0.459</v>
       </c>
       <c r="H170" t="n">
         <v>0.0992</v>
       </c>
       <c r="I170" t="n">
-        <v>21.42</v>
+        <v>22.18</v>
       </c>
       <c r="J170" t="n">
-        <v>343.2</v>
+        <v>345.7</v>
       </c>
       <c r="K170" t="n">
-        <v>5.617</v>
+        <v>5.314</v>
       </c>
       <c r="L170" t="n">
-        <v>-3.941</v>
+        <v>-4.045</v>
       </c>
       <c r="M170" t="n">
-        <v>20.527</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="171">
@@ -9638,31 +9638,31 @@
         <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>2.69</v>
+        <v>2.655</v>
       </c>
       <c r="F171" t="n">
-        <v>0.925</v>
+        <v>0.891</v>
       </c>
       <c r="G171" t="n">
-        <v>0.493</v>
+        <v>0.411</v>
       </c>
       <c r="H171" t="n">
         <v>0.1404</v>
       </c>
       <c r="I171" t="n">
-        <v>21.81</v>
+        <v>23.14</v>
       </c>
       <c r="J171" t="n">
-        <v>307.6</v>
+        <v>311.3</v>
       </c>
       <c r="K171" t="n">
-        <v>6.368</v>
+        <v>6.101</v>
       </c>
       <c r="L171" t="n">
-        <v>-2.373</v>
+        <v>-2.465</v>
       </c>
       <c r="M171" t="n">
-        <v>21.918</v>
+        <v>21.447</v>
       </c>
     </row>
     <row r="172">
@@ -9683,31 +9683,31 @@
         <v>-1</v>
       </c>
       <c r="E172" t="n">
-        <v>2.458</v>
+        <v>2.396</v>
       </c>
       <c r="F172" t="n">
-        <v>0.874</v>
+        <v>0.861</v>
       </c>
       <c r="G172" t="n">
-        <v>0.541</v>
+        <v>0.443</v>
       </c>
       <c r="H172" t="n">
         <v>0.1029</v>
       </c>
       <c r="I172" t="n">
-        <v>21.39</v>
+        <v>22.79</v>
       </c>
       <c r="J172" t="n">
-        <v>343.9</v>
+        <v>346.4</v>
       </c>
       <c r="K172" t="n">
-        <v>5.905</v>
+        <v>5.621</v>
       </c>
       <c r="L172" t="n">
-        <v>-3.841</v>
+        <v>-3.939</v>
       </c>
       <c r="M172" t="n">
-        <v>20.322</v>
+        <v>19.845</v>
       </c>
     </row>
     <row r="173">
@@ -9728,31 +9728,31 @@
         <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>2.583</v>
+        <v>2.532</v>
       </c>
       <c r="F173" t="n">
-        <v>0.863</v>
+        <v>0.836</v>
       </c>
       <c r="G173" t="n">
-        <v>0.545</v>
+        <v>0.442</v>
       </c>
       <c r="H173" t="n">
         <v>0.1082</v>
       </c>
       <c r="I173" t="n">
-        <v>22.59</v>
+        <v>23.73</v>
       </c>
       <c r="J173" t="n">
-        <v>334.2</v>
+        <v>332.9</v>
       </c>
       <c r="K173" t="n">
-        <v>6.048</v>
+        <v>5.737</v>
       </c>
       <c r="L173" t="n">
-        <v>-3.791</v>
+        <v>-3.899</v>
       </c>
       <c r="M173" t="n">
-        <v>21.232</v>
+        <v>20.699</v>
       </c>
     </row>
     <row r="174">
@@ -9773,31 +9773,31 @@
         <v>-1</v>
       </c>
       <c r="E174" t="n">
-        <v>2.695</v>
+        <v>2.647</v>
       </c>
       <c r="F174" t="n">
-        <v>0.883</v>
+        <v>0.865</v>
       </c>
       <c r="G174" t="n">
-        <v>0.612</v>
+        <v>0.499</v>
       </c>
       <c r="H174" t="n">
         <v>0.1165</v>
       </c>
       <c r="I174" t="n">
-        <v>22.28</v>
+        <v>23.13</v>
       </c>
       <c r="J174" t="n">
-        <v>332.2</v>
+        <v>333.9</v>
       </c>
       <c r="K174" t="n">
-        <v>6.384</v>
+        <v>6.074</v>
       </c>
       <c r="L174" t="n">
-        <v>-3.675</v>
+        <v>-3.782</v>
       </c>
       <c r="M174" t="n">
-        <v>21.832</v>
+        <v>21.293</v>
       </c>
     </row>
     <row r="175">
@@ -9818,31 +9818,31 @@
         <v>-1</v>
       </c>
       <c r="E175" t="n">
-        <v>2.243</v>
+        <v>2.169</v>
       </c>
       <c r="F175" t="n">
-        <v>0.754</v>
+        <v>0.719</v>
       </c>
       <c r="G175" t="n">
-        <v>0.502</v>
+        <v>0.416</v>
       </c>
       <c r="H175" t="n">
         <v>0.095</v>
       </c>
       <c r="I175" t="n">
-        <v>20.98</v>
+        <v>22.65</v>
       </c>
       <c r="J175" t="n">
-        <v>337.5</v>
+        <v>338.4</v>
       </c>
       <c r="K175" t="n">
-        <v>5.325</v>
+        <v>5.009</v>
       </c>
       <c r="L175" t="n">
-        <v>-4.042</v>
+        <v>-4.151</v>
       </c>
       <c r="M175" t="n">
-        <v>20.006</v>
+        <v>19.459</v>
       </c>
     </row>
     <row r="176">
@@ -9863,31 +9863,31 @@
         <v>-1</v>
       </c>
       <c r="E176" t="n">
-        <v>2.081</v>
+        <v>2.215</v>
       </c>
       <c r="F176" t="n">
-        <v>0.694</v>
+        <v>0.72</v>
       </c>
       <c r="G176" t="n">
-        <v>0.459</v>
+        <v>0.419</v>
       </c>
       <c r="H176" t="n">
-        <v>0.106</v>
+        <v>0.1017</v>
       </c>
       <c r="I176" t="n">
-        <v>24.32</v>
+        <v>24.14</v>
       </c>
       <c r="J176" t="n">
-        <v>334.4</v>
+        <v>349.6</v>
       </c>
       <c r="K176" t="n">
-        <v>5.023</v>
+        <v>5.103</v>
       </c>
       <c r="L176" t="n">
-        <v>-2.838</v>
+        <v>-4.118</v>
       </c>
       <c r="M176" t="n">
-        <v>19.953</v>
+        <v>19.999</v>
       </c>
     </row>
     <row r="177">
@@ -9920,10 +9920,10 @@
         <v>0.0945</v>
       </c>
       <c r="I177" t="n">
-        <v>21.66</v>
+        <v>21.75</v>
       </c>
       <c r="J177" t="n">
-        <v>339.7</v>
+        <v>338.5</v>
       </c>
       <c r="K177" t="n">
         <v>4.78</v>
@@ -9965,10 +9965,10 @@
         <v>0.1036</v>
       </c>
       <c r="I178" t="n">
-        <v>24.71</v>
+        <v>24.47</v>
       </c>
       <c r="J178" t="n">
-        <v>331.6</v>
+        <v>332.8</v>
       </c>
       <c r="K178" t="n">
         <v>5.251</v>
@@ -10010,10 +10010,10 @@
         <v>0.1109</v>
       </c>
       <c r="I179" t="n">
-        <v>21.73</v>
+        <v>21.7</v>
       </c>
       <c r="J179" t="n">
-        <v>312.7</v>
+        <v>312.1</v>
       </c>
       <c r="K179" t="n">
         <v>5.687</v>
@@ -10055,10 +10055,10 @@
         <v>0.0927</v>
       </c>
       <c r="I180" t="n">
-        <v>22.17</v>
+        <v>22.07</v>
       </c>
       <c r="J180" t="n">
-        <v>339</v>
+        <v>337.4</v>
       </c>
       <c r="K180" t="n">
         <v>4.835</v>
@@ -10088,31 +10088,31 @@
         <v>-1</v>
       </c>
       <c r="E181" t="n">
-        <v>2.193</v>
+        <v>2.268</v>
       </c>
       <c r="F181" t="n">
-        <v>0.718</v>
+        <v>0.801</v>
       </c>
       <c r="G181" t="n">
-        <v>0.414</v>
+        <v>0.498</v>
       </c>
       <c r="H181" t="n">
-        <v>0.1217</v>
+        <v>0.1313</v>
       </c>
       <c r="I181" t="n">
-        <v>23.94</v>
+        <v>23.73</v>
       </c>
       <c r="J181" t="n">
-        <v>323.4</v>
+        <v>325.8</v>
       </c>
       <c r="K181" t="n">
-        <v>5.187</v>
+        <v>5.654</v>
       </c>
       <c r="L181" t="n">
-        <v>-2.782</v>
+        <v>-2.62</v>
       </c>
       <c r="M181" t="n">
-        <v>20.297</v>
+        <v>21.178</v>
       </c>
     </row>
     <row r="182">
@@ -10145,10 +10145,10 @@
         <v>0.1108</v>
       </c>
       <c r="I182" t="n">
-        <v>22.27</v>
+        <v>22.2</v>
       </c>
       <c r="J182" t="n">
-        <v>333.5</v>
+        <v>331.1</v>
       </c>
       <c r="K182" t="n">
         <v>5.808</v>
@@ -10190,10 +10190,10 @@
         <v>0.1017</v>
       </c>
       <c r="I183" t="n">
-        <v>24.48</v>
+        <v>23.89</v>
       </c>
       <c r="J183" t="n">
-        <v>347.4</v>
+        <v>347.2</v>
       </c>
       <c r="K183" t="n">
         <v>5.516</v>
@@ -10235,10 +10235,10 @@
         <v>0.098</v>
       </c>
       <c r="I184" t="n">
-        <v>22.56</v>
+        <v>22.45</v>
       </c>
       <c r="J184" t="n">
-        <v>341.6</v>
+        <v>339.2</v>
       </c>
       <c r="K184" t="n">
         <v>5.234</v>
@@ -10280,10 +10280,10 @@
         <v>0.0975</v>
       </c>
       <c r="I185" t="n">
-        <v>24.5</v>
+        <v>24.25</v>
       </c>
       <c r="J185" t="n">
-        <v>340.1</v>
+        <v>341.3</v>
       </c>
       <c r="K185" t="n">
         <v>5.296</v>
@@ -10325,10 +10325,10 @@
         <v>0.1065</v>
       </c>
       <c r="I186" t="n">
-        <v>22.93</v>
+        <v>22.6</v>
       </c>
       <c r="J186" t="n">
-        <v>339.3</v>
+        <v>340.1</v>
       </c>
       <c r="K186" t="n">
         <v>5.225</v>
@@ -10358,31 +10358,31 @@
         <v>1</v>
       </c>
       <c r="E187" t="n">
-        <v>2.381</v>
+        <v>2.36</v>
       </c>
       <c r="F187" t="n">
-        <v>0.748</v>
+        <v>0.801</v>
       </c>
       <c r="G187" t="n">
-        <v>0.432</v>
+        <v>0.498</v>
       </c>
       <c r="H187" t="n">
-        <v>0.1496</v>
+        <v>0.1313</v>
       </c>
       <c r="I187" t="n">
-        <v>23.46</v>
+        <v>22.4</v>
       </c>
       <c r="J187" t="n">
-        <v>340.3</v>
+        <v>314.7</v>
       </c>
       <c r="K187" t="n">
-        <v>5.639</v>
+        <v>5.746</v>
       </c>
       <c r="L187" t="n">
-        <v>-3.933</v>
+        <v>-2.588</v>
       </c>
       <c r="M187" t="n">
-        <v>21.186</v>
+        <v>21.315</v>
       </c>
     </row>
     <row r="188">
@@ -10415,10 +10415,10 @@
         <v>0.0968</v>
       </c>
       <c r="I188" t="n">
-        <v>21.71</v>
+        <v>21.77</v>
       </c>
       <c r="J188" t="n">
-        <v>330</v>
+        <v>328.9</v>
       </c>
       <c r="K188" t="n">
         <v>4.567</v>
@@ -10460,10 +10460,10 @@
         <v>0.1109</v>
       </c>
       <c r="I189" t="n">
-        <v>24.83</v>
+        <v>24.27</v>
       </c>
       <c r="J189" t="n">
-        <v>326</v>
+        <v>327.3</v>
       </c>
       <c r="K189" t="n">
         <v>5.575</v>
@@ -10505,10 +10505,10 @@
         <v>0.1129</v>
       </c>
       <c r="I190" t="n">
-        <v>22.17</v>
+        <v>21.98</v>
       </c>
       <c r="J190" t="n">
-        <v>337.8</v>
+        <v>336.7</v>
       </c>
       <c r="K190" t="n">
         <v>5.442</v>
@@ -10538,31 +10538,31 @@
         <v>1</v>
       </c>
       <c r="E191" t="n">
-        <v>2.299</v>
+        <v>2.36</v>
       </c>
       <c r="F191" t="n">
-        <v>0.723</v>
+        <v>0.801</v>
       </c>
       <c r="G191" t="n">
-        <v>0.414</v>
+        <v>0.498</v>
       </c>
       <c r="H191" t="n">
-        <v>0.1217</v>
+        <v>0.1313</v>
       </c>
       <c r="I191" t="n">
-        <v>21.31</v>
+        <v>22.4</v>
       </c>
       <c r="J191" t="n">
-        <v>310.6</v>
+        <v>314.7</v>
       </c>
       <c r="K191" t="n">
-        <v>5.303</v>
+        <v>5.746</v>
       </c>
       <c r="L191" t="n">
-        <v>-2.741</v>
+        <v>-2.588</v>
       </c>
       <c r="M191" t="n">
-        <v>20.468</v>
+        <v>21.315</v>
       </c>
     </row>
     <row r="192">
@@ -10595,10 +10595,10 @@
         <v>0.158</v>
       </c>
       <c r="I192" t="n">
-        <v>20.97</v>
+        <v>21.32</v>
       </c>
       <c r="J192" t="n">
-        <v>317.7</v>
+        <v>316.9</v>
       </c>
       <c r="K192" t="n">
         <v>6.109</v>
@@ -10640,10 +10640,10 @@
         <v>0.168</v>
       </c>
       <c r="I193" t="n">
-        <v>22.12</v>
+        <v>21.54</v>
       </c>
       <c r="J193" t="n">
-        <v>325.3</v>
+        <v>322.9</v>
       </c>
       <c r="K193" t="n">
         <v>5.981</v>
@@ -10685,10 +10685,10 @@
         <v>0.1523</v>
       </c>
       <c r="I194" t="n">
-        <v>21.45</v>
+        <v>21.87</v>
       </c>
       <c r="J194" t="n">
-        <v>332.4</v>
+        <v>332.5</v>
       </c>
       <c r="K194" t="n">
         <v>5.608</v>
@@ -10730,10 +10730,10 @@
         <v>0.201</v>
       </c>
       <c r="I195" t="n">
-        <v>22.81</v>
+        <v>22.05</v>
       </c>
       <c r="J195" t="n">
-        <v>320.6</v>
+        <v>318.2</v>
       </c>
       <c r="K195" t="n">
         <v>6.226</v>
@@ -10775,10 +10775,10 @@
         <v>0.1742</v>
       </c>
       <c r="I196" t="n">
-        <v>21.8</v>
+        <v>21.58</v>
       </c>
       <c r="J196" t="n">
-        <v>320.5</v>
+        <v>318.1</v>
       </c>
       <c r="K196" t="n">
         <v>6.476</v>
@@ -10820,7 +10820,7 @@
         <v>0.1686</v>
       </c>
       <c r="I197" t="n">
-        <v>20.32</v>
+        <v>20.68</v>
       </c>
       <c r="J197" t="n">
         <v>332.6</v>
@@ -10853,31 +10853,31 @@
         <v>-1</v>
       </c>
       <c r="E198" t="n">
-        <v>2.616</v>
+        <v>2.414</v>
       </c>
       <c r="F198" t="n">
-        <v>0.754</v>
+        <v>0.75</v>
       </c>
       <c r="G198" t="n">
-        <v>0.465</v>
+        <v>0.425</v>
       </c>
       <c r="H198" t="n">
-        <v>0.1838</v>
+        <v>0.1514</v>
       </c>
       <c r="I198" t="n">
-        <v>23.31</v>
+        <v>21.52</v>
       </c>
       <c r="J198" t="n">
-        <v>331.2</v>
+        <v>329.8</v>
       </c>
       <c r="K198" t="n">
-        <v>6.157</v>
+        <v>5.672</v>
       </c>
       <c r="L198" t="n">
-        <v>-2.446</v>
+        <v>-2.614</v>
       </c>
       <c r="M198" t="n">
-        <v>22.222</v>
+        <v>21.264</v>
       </c>
     </row>
     <row r="199">
@@ -10910,10 +10910,10 @@
         <v>0.1722</v>
       </c>
       <c r="I199" t="n">
-        <v>22.54</v>
+        <v>21.85</v>
       </c>
       <c r="J199" t="n">
-        <v>350.8</v>
+        <v>350.3</v>
       </c>
       <c r="K199" t="n">
         <v>5.857</v>
@@ -10955,7 +10955,7 @@
         <v>0.168</v>
       </c>
       <c r="I200" t="n">
-        <v>20.81</v>
+        <v>21.29</v>
       </c>
       <c r="J200" t="n">
         <v>302.1</v>
@@ -11000,10 +11000,10 @@
         <v>0.1712</v>
       </c>
       <c r="I201" t="n">
-        <v>20.87</v>
+        <v>21.18</v>
       </c>
       <c r="J201" t="n">
-        <v>314.2</v>
+        <v>312.9</v>
       </c>
       <c r="K201" t="n">
         <v>6.035</v>
@@ -11045,10 +11045,10 @@
         <v>0.194</v>
       </c>
       <c r="I202" t="n">
-        <v>22.68</v>
+        <v>21.58</v>
       </c>
       <c r="J202" t="n">
-        <v>330.4</v>
+        <v>328</v>
       </c>
       <c r="K202" t="n">
         <v>6.113</v>
@@ -11090,10 +11090,10 @@
         <v>0.1545</v>
       </c>
       <c r="I203" t="n">
-        <v>22.32</v>
+        <v>21.5</v>
       </c>
       <c r="J203" t="n">
-        <v>353.1</v>
+        <v>352.7</v>
       </c>
       <c r="K203" t="n">
         <v>5.716</v>
@@ -11135,10 +11135,10 @@
         <v>0.1742</v>
       </c>
       <c r="I204" t="n">
-        <v>19.36</v>
+        <v>19.73</v>
       </c>
       <c r="J204" t="n">
-        <v>294.1</v>
+        <v>294</v>
       </c>
       <c r="K204" t="n">
         <v>9.596</v>
@@ -11147,7 +11147,7 @@
         <v>-1.256</v>
       </c>
       <c r="M204" t="n">
-        <v>25.889</v>
+        <v>23.927</v>
       </c>
     </row>
     <row r="205">
@@ -11180,10 +11180,10 @@
         <v>0.182</v>
       </c>
       <c r="I205" t="n">
-        <v>22.88</v>
+        <v>21.64</v>
       </c>
       <c r="J205" t="n">
-        <v>348.6</v>
+        <v>348.1</v>
       </c>
       <c r="K205" t="n">
         <v>5.788</v>
@@ -11225,10 +11225,10 @@
         <v>0.1646</v>
       </c>
       <c r="I206" t="n">
-        <v>22.95</v>
+        <v>21.73</v>
       </c>
       <c r="J206" t="n">
-        <v>347.9</v>
+        <v>347</v>
       </c>
       <c r="K206" t="n">
         <v>5.339</v>
@@ -11270,10 +11270,10 @@
         <v>0.201</v>
       </c>
       <c r="I207" t="n">
-        <v>18.91</v>
+        <v>19.47</v>
       </c>
       <c r="J207" t="n">
-        <v>294.7</v>
+        <v>294.6</v>
       </c>
       <c r="K207" t="n">
         <v>9.324999999999999</v>
@@ -11282,7 +11282,7 @@
         <v>-1.349</v>
       </c>
       <c r="M207" t="n">
-        <v>25.551</v>
+        <v>23.589</v>
       </c>
     </row>
     <row r="208">
@@ -11315,10 +11315,10 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="I208" t="n">
-        <v>24.83</v>
+        <v>24.92</v>
       </c>
       <c r="J208" t="n">
-        <v>368.3</v>
+        <v>367.6</v>
       </c>
       <c r="K208" t="n">
         <v>5.134</v>
@@ -11360,7 +11360,7 @@
         <v>0.1148</v>
       </c>
       <c r="I209" t="n">
-        <v>25.56</v>
+        <v>24.72</v>
       </c>
       <c r="J209" t="n">
         <v>351.6</v>
@@ -11372,7 +11372,7 @@
         <v>-3.962</v>
       </c>
       <c r="M209" t="n">
-        <v>18.949</v>
+        <v>20.911</v>
       </c>
     </row>
     <row r="210">
@@ -11405,10 +11405,10 @@
         <v>0.093</v>
       </c>
       <c r="I210" t="n">
-        <v>25.08</v>
+        <v>25.04</v>
       </c>
       <c r="J210" t="n">
-        <v>365.9</v>
+        <v>365.2</v>
       </c>
       <c r="K210" t="n">
         <v>5.025</v>
@@ -11450,7 +11450,7 @@
         <v>0.1158</v>
       </c>
       <c r="I211" t="n">
-        <v>25.03</v>
+        <v>25.1</v>
       </c>
       <c r="J211" t="n">
         <v>345.7</v>
@@ -11495,7 +11495,7 @@
         <v>0.136</v>
       </c>
       <c r="I212" t="n">
-        <v>25.29</v>
+        <v>25</v>
       </c>
       <c r="J212" t="n">
         <v>320.7</v>
@@ -11540,10 +11540,10 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I213" t="n">
-        <v>25.04</v>
+        <v>25.02</v>
       </c>
       <c r="J213" t="n">
-        <v>367.1</v>
+        <v>366.5</v>
       </c>
       <c r="K213" t="n">
         <v>5.298</v>
@@ -11585,7 +11585,7 @@
         <v>0.1268</v>
       </c>
       <c r="I214" t="n">
-        <v>24.34</v>
+        <v>24.15</v>
       </c>
       <c r="J214" t="n">
         <v>342.7</v>
@@ -11630,10 +11630,10 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>24.65</v>
+        <v>24.5</v>
       </c>
       <c r="J215" t="n">
-        <v>355</v>
+        <v>354.9</v>
       </c>
       <c r="K215" t="n">
         <v>4.884</v>
@@ -11675,10 +11675,10 @@
         <v>0.0978</v>
       </c>
       <c r="I216" t="n">
-        <v>25.28</v>
+        <v>24.77</v>
       </c>
       <c r="J216" t="n">
-        <v>344.8</v>
+        <v>344.7</v>
       </c>
       <c r="K216" t="n">
         <v>4.643</v>
@@ -11720,10 +11720,10 @@
         <v>0.1148</v>
       </c>
       <c r="I217" t="n">
-        <v>24.93</v>
+        <v>24.99</v>
       </c>
       <c r="J217" t="n">
-        <v>360.3</v>
+        <v>359.6</v>
       </c>
       <c r="K217" t="n">
         <v>5.469</v>
@@ -11765,7 +11765,7 @@
         <v>0.1032</v>
       </c>
       <c r="I218" t="n">
-        <v>25.72</v>
+        <v>24.73</v>
       </c>
       <c r="J218" t="n">
         <v>352.5</v>
@@ -11777,7 +11777,7 @@
         <v>-3.988</v>
       </c>
       <c r="M218" t="n">
-        <v>18.747</v>
+        <v>20.709</v>
       </c>
     </row>
     <row r="219">
@@ -11810,10 +11810,10 @@
         <v>0.1064</v>
       </c>
       <c r="I219" t="n">
-        <v>24.79</v>
+        <v>24.87</v>
       </c>
       <c r="J219" t="n">
-        <v>357.6</v>
+        <v>356.9</v>
       </c>
       <c r="K219" t="n">
         <v>5.097</v>
@@ -11855,7 +11855,7 @@
         <v>0.136</v>
       </c>
       <c r="I220" t="n">
-        <v>25.76</v>
+        <v>25.25</v>
       </c>
       <c r="J220" t="n">
         <v>343</v>
@@ -11867,7 +11867,7 @@
         <v>-3.941</v>
       </c>
       <c r="M220" t="n">
-        <v>19.189</v>
+        <v>21.151</v>
       </c>
     </row>
     <row r="221">
@@ -11900,10 +11900,10 @@
         <v>0.0992</v>
       </c>
       <c r="I221" t="n">
-        <v>25.22</v>
+        <v>24.77</v>
       </c>
       <c r="J221" t="n">
-        <v>338.7</v>
+        <v>338.6</v>
       </c>
       <c r="K221" t="n">
         <v>5.622</v>
@@ -11945,10 +11945,10 @@
         <v>0.1048</v>
       </c>
       <c r="I222" t="n">
-        <v>25.17</v>
+        <v>25.38</v>
       </c>
       <c r="J222" t="n">
-        <v>361.5</v>
+        <v>360.8</v>
       </c>
       <c r="K222" t="n">
         <v>5.288</v>
@@ -11957,7 +11957,7 @@
         <v>-4.054</v>
       </c>
       <c r="M222" t="n">
-        <v>19.748</v>
+        <v>20.401</v>
       </c>
     </row>
     <row r="223">
@@ -11990,7 +11990,7 @@
         <v>0.1268</v>
       </c>
       <c r="I223" t="n">
-        <v>23.07</v>
+        <v>23.34</v>
       </c>
       <c r="J223" t="n">
         <v>320.1</v>
@@ -12350,7 +12350,7 @@
         <v>0.1649</v>
       </c>
       <c r="I231" t="n">
-        <v>22.32</v>
+        <v>22.33</v>
       </c>
       <c r="J231" t="n">
         <v>321.4</v>
@@ -12395,7 +12395,7 @@
         <v>0.1151</v>
       </c>
       <c r="I232" t="n">
-        <v>20.23</v>
+        <v>20.24</v>
       </c>
       <c r="J232" t="n">
         <v>339.4</v>
@@ -12485,7 +12485,7 @@
         <v>0.1907</v>
       </c>
       <c r="I234" t="n">
-        <v>22.87</v>
+        <v>22.7</v>
       </c>
       <c r="J234" t="n">
         <v>322.1</v>
@@ -12575,7 +12575,7 @@
         <v>0.1288</v>
       </c>
       <c r="I236" t="n">
-        <v>20.38</v>
+        <v>20.4</v>
       </c>
       <c r="J236" t="n">
         <v>343.2</v>
@@ -12755,19 +12755,19 @@
         <v>0.1173</v>
       </c>
       <c r="I240" t="n">
-        <v>19.91</v>
+        <v>20.02</v>
       </c>
       <c r="J240" t="n">
         <v>296</v>
       </c>
       <c r="K240" t="n">
-        <v>8.679</v>
+        <v>7.679</v>
       </c>
       <c r="L240" t="n">
-        <v>-1.573</v>
+        <v>-1.919</v>
       </c>
       <c r="M240" t="n">
-        <v>22.09</v>
+        <v>21.744</v>
       </c>
     </row>
     <row r="241">
@@ -12800,10 +12800,10 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I241" t="n">
-        <v>20.48</v>
+        <v>20.86</v>
       </c>
       <c r="J241" t="n">
-        <v>334.1</v>
+        <v>335.7</v>
       </c>
       <c r="K241" t="n">
         <v>4.728</v>
@@ -12845,10 +12845,10 @@
         <v>0.1173</v>
       </c>
       <c r="I242" t="n">
-        <v>21.56</v>
+        <v>21.49</v>
       </c>
       <c r="J242" t="n">
-        <v>321.7</v>
+        <v>322.5</v>
       </c>
       <c r="K242" t="n">
         <v>5.81</v>
@@ -12878,31 +12878,31 @@
         <v>1</v>
       </c>
       <c r="E243" t="n">
-        <v>2.598</v>
+        <v>2.395</v>
       </c>
       <c r="F243" t="n">
-        <v>0.754</v>
+        <v>0.757</v>
       </c>
       <c r="G243" t="n">
-        <v>0.458</v>
+        <v>0.417</v>
       </c>
       <c r="H243" t="n">
-        <v>0.1045</v>
+        <v>0.099</v>
       </c>
       <c r="I243" t="n">
-        <v>20.68</v>
+        <v>19.96</v>
       </c>
       <c r="J243" t="n">
-        <v>303.1</v>
+        <v>304.4</v>
       </c>
       <c r="K243" t="n">
-        <v>5.649</v>
+        <v>6.337</v>
       </c>
       <c r="L243" t="n">
-        <v>-2.622</v>
+        <v>-2.384</v>
       </c>
       <c r="M243" t="n">
-        <v>20.898</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="244">
@@ -12935,7 +12935,7 @@
         <v>0.093</v>
       </c>
       <c r="I244" t="n">
-        <v>20.36</v>
+        <v>20.62</v>
       </c>
       <c r="J244" t="n">
         <v>343.3</v>
@@ -12980,10 +12980,10 @@
         <v>0.1292</v>
       </c>
       <c r="I245" t="n">
-        <v>20.35</v>
+        <v>20.44</v>
       </c>
       <c r="J245" t="n">
-        <v>310.1</v>
+        <v>310.9</v>
       </c>
       <c r="K245" t="n">
         <v>5.827</v>
@@ -13013,31 +13013,31 @@
         <v>1</v>
       </c>
       <c r="E246" t="n">
-        <v>2.274</v>
+        <v>2.4</v>
       </c>
       <c r="F246" t="n">
-        <v>0.758</v>
+        <v>0.779</v>
       </c>
       <c r="G246" t="n">
-        <v>0.453</v>
+        <v>0.448</v>
       </c>
       <c r="H246" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.0934</v>
       </c>
       <c r="I246" t="n">
-        <v>20.07</v>
+        <v>19.99</v>
       </c>
       <c r="J246" t="n">
-        <v>309.5</v>
+        <v>328.2</v>
       </c>
       <c r="K246" t="n">
-        <v>5.27</v>
+        <v>6.414</v>
       </c>
       <c r="L246" t="n">
-        <v>-2.753</v>
+        <v>-2.357</v>
       </c>
       <c r="M246" t="n">
-        <v>20.27</v>
+        <v>20.794</v>
       </c>
     </row>
     <row r="247">
@@ -13070,7 +13070,7 @@
         <v>0.0852</v>
       </c>
       <c r="I247" t="n">
-        <v>21.25</v>
+        <v>21.66</v>
       </c>
       <c r="J247" t="n">
         <v>343.5</v>
@@ -13115,7 +13115,7 @@
         <v>0.1404</v>
       </c>
       <c r="I248" t="n">
-        <v>19.92</v>
+        <v>19.84</v>
       </c>
       <c r="J248" t="n">
         <v>300.6</v>
@@ -13148,31 +13148,31 @@
         <v>-1</v>
       </c>
       <c r="E249" t="n">
-        <v>2.35</v>
+        <v>2.421</v>
       </c>
       <c r="F249" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.864</v>
       </c>
       <c r="G249" t="n">
-        <v>0.459</v>
+        <v>0.53</v>
       </c>
       <c r="H249" t="n">
-        <v>0.1373</v>
+        <v>0.1356</v>
       </c>
       <c r="I249" t="n">
-        <v>19.99</v>
+        <v>21.37</v>
       </c>
       <c r="J249" t="n">
-        <v>338.9</v>
+        <v>313.6</v>
       </c>
       <c r="K249" t="n">
-        <v>6.712</v>
+        <v>6.023</v>
       </c>
       <c r="L249" t="n">
-        <v>-3.562</v>
+        <v>-2.492</v>
       </c>
       <c r="M249" t="n">
-        <v>21.631</v>
+        <v>21.813</v>
       </c>
     </row>
     <row r="250">
@@ -13205,19 +13205,19 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>19.82</v>
+        <v>20.14</v>
       </c>
       <c r="J250" t="n">
-        <v>329.6</v>
+        <v>331.2</v>
       </c>
       <c r="K250" t="n">
-        <v>6.527</v>
+        <v>5.527</v>
       </c>
       <c r="L250" t="n">
-        <v>-2.318</v>
+        <v>-2.664</v>
       </c>
       <c r="M250" t="n">
-        <v>20.996</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="251">
@@ -13250,10 +13250,10 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I251" t="n">
-        <v>20.89</v>
+        <v>21.21</v>
       </c>
       <c r="J251" t="n">
-        <v>327.3</v>
+        <v>328.1</v>
       </c>
       <c r="K251" t="n">
         <v>5.551</v>
@@ -13295,7 +13295,7 @@
         <v>0.1001</v>
       </c>
       <c r="I252" t="n">
-        <v>19.93</v>
+        <v>19.96</v>
       </c>
       <c r="J252" t="n">
         <v>323</v>
@@ -13340,7 +13340,7 @@
         <v>0.0878</v>
       </c>
       <c r="I253" t="n">
-        <v>18.75</v>
+        <v>18.85</v>
       </c>
       <c r="J253" t="n">
         <v>320.3</v>
@@ -13373,31 +13373,31 @@
         <v>-1</v>
       </c>
       <c r="E254" t="n">
-        <v>2.497</v>
+        <v>2.342</v>
       </c>
       <c r="F254" t="n">
-        <v>0.733</v>
+        <v>0.751</v>
       </c>
       <c r="G254" t="n">
-        <v>0.458</v>
+        <v>0.417</v>
       </c>
       <c r="H254" t="n">
-        <v>0.1045</v>
+        <v>0.099</v>
       </c>
       <c r="I254" t="n">
-        <v>20.84</v>
+        <v>21.56</v>
       </c>
       <c r="J254" t="n">
-        <v>316.7</v>
+        <v>318.4</v>
       </c>
       <c r="K254" t="n">
-        <v>5.506</v>
+        <v>5.272</v>
       </c>
       <c r="L254" t="n">
-        <v>-2.671</v>
+        <v>-2.752</v>
       </c>
       <c r="M254" t="n">
-        <v>20.672</v>
+        <v>20.253</v>
       </c>
     </row>
     <row r="255">
@@ -13430,7 +13430,7 @@
         <v>0.1173</v>
       </c>
       <c r="I255" t="n">
-        <v>19.5</v>
+        <v>19.76</v>
       </c>
       <c r="J255" t="n">
         <v>305.3</v>
@@ -13520,7 +13520,7 @@
         <v>0.1375</v>
       </c>
       <c r="I257" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="J257" t="n">
         <v>314.9</v>
@@ -13565,7 +13565,7 @@
         <v>0.1109</v>
       </c>
       <c r="I258" t="n">
-        <v>20.89</v>
+        <v>20.9</v>
       </c>
       <c r="J258" t="n">
         <v>330.3</v>
@@ -13598,31 +13598,31 @@
         <v>1</v>
       </c>
       <c r="E259" t="n">
-        <v>2.541</v>
+        <v>2.577</v>
       </c>
       <c r="F259" t="n">
-        <v>0.858</v>
+        <v>0.907</v>
       </c>
       <c r="G259" t="n">
-        <v>0.444</v>
+        <v>0.576</v>
       </c>
       <c r="H259" t="n">
-        <v>0.1168</v>
+        <v>0.1291</v>
       </c>
       <c r="I259" t="n">
-        <v>21.33</v>
+        <v>20.95</v>
       </c>
       <c r="J259" t="n">
-        <v>334.7</v>
+        <v>313.1</v>
       </c>
       <c r="K259" t="n">
-        <v>5.846</v>
+        <v>6.318</v>
       </c>
       <c r="L259" t="n">
-        <v>-3.861</v>
+        <v>-2.39</v>
       </c>
       <c r="M259" t="n">
-        <v>20.928</v>
+        <v>21.826</v>
       </c>
     </row>
     <row r="260">
@@ -13700,7 +13700,7 @@
         <v>0.1177</v>
       </c>
       <c r="I261" t="n">
-        <v>21.33</v>
+        <v>21.34</v>
       </c>
       <c r="J261" t="n">
         <v>326.5</v>
@@ -13733,31 +13733,31 @@
         <v>1</v>
       </c>
       <c r="E262" t="n">
-        <v>2.731</v>
+        <v>2.502</v>
       </c>
       <c r="F262" t="n">
-        <v>0.733</v>
+        <v>0.779</v>
       </c>
       <c r="G262" t="n">
-        <v>0.467</v>
+        <v>0.428</v>
       </c>
       <c r="H262" t="n">
-        <v>0.1099</v>
+        <v>0.1157</v>
       </c>
       <c r="I262" t="n">
-        <v>20.45</v>
+        <v>20.3</v>
       </c>
       <c r="J262" t="n">
-        <v>315.4</v>
+        <v>316</v>
       </c>
       <c r="K262" t="n">
-        <v>5.79</v>
+        <v>5.61</v>
       </c>
       <c r="L262" t="n">
-        <v>-2.573</v>
+        <v>-2.635</v>
       </c>
       <c r="M262" t="n">
-        <v>20.761</v>
+        <v>20.543</v>
       </c>
     </row>
     <row r="263">
@@ -13790,7 +13790,7 @@
         <v>0.1002</v>
       </c>
       <c r="I263" t="n">
-        <v>21.22</v>
+        <v>21.08</v>
       </c>
       <c r="J263" t="n">
         <v>337.6</v>
@@ -13835,7 +13835,7 @@
         <v>0.1152</v>
       </c>
       <c r="I264" t="n">
-        <v>19.97</v>
+        <v>19.83</v>
       </c>
       <c r="J264" t="n">
         <v>320.7</v>
@@ -13970,7 +13970,7 @@
         <v>0.1038</v>
       </c>
       <c r="I267" t="n">
-        <v>21.18</v>
+        <v>21.03</v>
       </c>
       <c r="J267" t="n">
         <v>325.2</v>
@@ -14195,7 +14195,7 @@
         <v>0.1167</v>
       </c>
       <c r="I272" t="n">
-        <v>20.46</v>
+        <v>20.58</v>
       </c>
       <c r="J272" t="n">
         <v>313.8</v>
@@ -14228,31 +14228,31 @@
         <v>-1</v>
       </c>
       <c r="E273" t="n">
-        <v>2.283</v>
+        <v>2.295</v>
       </c>
       <c r="F273" t="n">
-        <v>0.771</v>
+        <v>0.851</v>
       </c>
       <c r="G273" t="n">
-        <v>0.394</v>
+        <v>0.374</v>
       </c>
       <c r="H273" t="n">
-        <v>0.1467</v>
+        <v>0.1321</v>
       </c>
       <c r="I273" t="n">
-        <v>21.9</v>
+        <v>21.98</v>
       </c>
       <c r="J273" t="n">
-        <v>345.1</v>
+        <v>320.7</v>
       </c>
       <c r="K273" t="n">
-        <v>5.493</v>
+        <v>5.538</v>
       </c>
       <c r="L273" t="n">
-        <v>-3.983</v>
+        <v>-2.66</v>
       </c>
       <c r="M273" t="n">
-        <v>20.937</v>
+        <v>20.914</v>
       </c>
     </row>
     <row r="274">
@@ -14285,7 +14285,7 @@
         <v>0.095</v>
       </c>
       <c r="I274" t="n">
-        <v>21.93</v>
+        <v>21.85</v>
       </c>
       <c r="J274" t="n">
         <v>349</v>
@@ -14330,7 +14330,7 @@
         <v>0.1301</v>
       </c>
       <c r="I275" t="n">
-        <v>19.53</v>
+        <v>19.62</v>
       </c>
       <c r="J275" t="n">
         <v>310.5</v>
@@ -14375,7 +14375,7 @@
         <v>0.0882</v>
       </c>
       <c r="I276" t="n">
-        <v>22.47</v>
+        <v>22.54</v>
       </c>
       <c r="J276" t="n">
         <v>349.6</v>
@@ -14420,7 +14420,7 @@
         <v>0.0885</v>
       </c>
       <c r="I277" t="n">
-        <v>21.68</v>
+        <v>21.75</v>
       </c>
       <c r="J277" t="n">
         <v>340.4</v>
@@ -14510,7 +14510,7 @@
         <v>0.116</v>
       </c>
       <c r="I279" t="n">
-        <v>22.53</v>
+        <v>22.54</v>
       </c>
       <c r="J279" t="n">
         <v>328.7</v>
@@ -14543,31 +14543,31 @@
         <v>1</v>
       </c>
       <c r="E280" t="n">
-        <v>2.183</v>
+        <v>2.34</v>
       </c>
       <c r="F280" t="n">
-        <v>0.728</v>
+        <v>0.772</v>
       </c>
       <c r="G280" t="n">
-        <v>0.405</v>
+        <v>0.398</v>
       </c>
       <c r="H280" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0998</v>
       </c>
       <c r="I280" t="n">
-        <v>20.59</v>
+        <v>21.69</v>
       </c>
       <c r="J280" t="n">
-        <v>317.6</v>
+        <v>334.8</v>
       </c>
       <c r="K280" t="n">
-        <v>5.032</v>
+        <v>5.279</v>
       </c>
       <c r="L280" t="n">
-        <v>-2.835</v>
+        <v>-2.75</v>
       </c>
       <c r="M280" t="n">
-        <v>19.858</v>
+        <v>20.268</v>
       </c>
     </row>
     <row r="281">
@@ -14600,7 +14600,7 @@
         <v>0.1</v>
       </c>
       <c r="I281" t="n">
-        <v>20.92</v>
+        <v>21.02</v>
       </c>
       <c r="J281" t="n">
         <v>330.6</v>
@@ -14690,7 +14690,7 @@
         <v>0.1167</v>
       </c>
       <c r="I283" t="n">
-        <v>22.22</v>
+        <v>22.23</v>
       </c>
       <c r="J283" t="n">
         <v>331.2</v>
@@ -14735,7 +14735,7 @@
         <v>0.0897</v>
       </c>
       <c r="I284" t="n">
-        <v>19.7</v>
+        <v>19.67</v>
       </c>
       <c r="J284" t="n">
         <v>326.9</v>
@@ -14780,7 +14780,7 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="I285" t="n">
-        <v>22.08</v>
+        <v>22.13</v>
       </c>
       <c r="J285" t="n">
         <v>342.6</v>
@@ -14825,7 +14825,7 @@
         <v>0.0882</v>
       </c>
       <c r="I286" t="n">
-        <v>21.81</v>
+        <v>21.78</v>
       </c>
       <c r="J286" t="n">
         <v>337.5</v>
@@ -14870,7 +14870,7 @@
         <v>0.1301</v>
       </c>
       <c r="I287" t="n">
-        <v>21.4</v>
+        <v>21.46</v>
       </c>
       <c r="J287" t="n">
         <v>326.7</v>
@@ -14903,31 +14903,31 @@
         <v>-1</v>
       </c>
       <c r="E288" t="n">
-        <v>2.761</v>
+        <v>2.599</v>
       </c>
       <c r="F288" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.706</v>
       </c>
       <c r="G288" t="n">
-        <v>0.505</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H288" t="n">
-        <v>0.0979</v>
+        <v>0.1043</v>
       </c>
       <c r="I288" t="n">
-        <v>25.04</v>
+        <v>23.67</v>
       </c>
       <c r="J288" t="n">
-        <v>325.2</v>
+        <v>327.4</v>
       </c>
       <c r="K288" t="n">
-        <v>5.734</v>
+        <v>5.769</v>
       </c>
       <c r="L288" t="n">
-        <v>-2.592</v>
+        <v>-2.58</v>
       </c>
       <c r="M288" t="n">
-        <v>20.949</v>
+        <v>21.122</v>
       </c>
     </row>
     <row r="289">
@@ -15083,31 +15083,31 @@
         <v>1</v>
       </c>
       <c r="E292" t="n">
-        <v>2.698</v>
+        <v>2.663</v>
       </c>
       <c r="F292" t="n">
-        <v>0.778</v>
+        <v>0.844</v>
       </c>
       <c r="G292" t="n">
-        <v>0.527</v>
+        <v>0.657</v>
       </c>
       <c r="H292" t="n">
-        <v>0.1521</v>
+        <v>0.1259</v>
       </c>
       <c r="I292" t="n">
-        <v>23.94</v>
+        <v>21.5</v>
       </c>
       <c r="J292" t="n">
-        <v>331.1</v>
+        <v>307.4</v>
       </c>
       <c r="K292" t="n">
-        <v>6.221</v>
+        <v>6.42</v>
       </c>
       <c r="L292" t="n">
-        <v>-2.424</v>
+        <v>-2.355</v>
       </c>
       <c r="M292" t="n">
-        <v>22.168</v>
+        <v>22.395</v>
       </c>
     </row>
     <row r="293">
@@ -15173,31 +15173,31 @@
         <v>-1</v>
       </c>
       <c r="E294" t="n">
-        <v>2.427</v>
+        <v>2.567</v>
       </c>
       <c r="F294" t="n">
-        <v>0.699</v>
+        <v>0.745</v>
       </c>
       <c r="G294" t="n">
-        <v>0.545</v>
+        <v>0.501</v>
       </c>
       <c r="H294" t="n">
         <v>0.1034</v>
       </c>
       <c r="I294" t="n">
-        <v>25.51</v>
+        <v>23.72</v>
       </c>
       <c r="J294" t="n">
-        <v>332.1</v>
+        <v>353.9</v>
       </c>
       <c r="K294" t="n">
-        <v>5.535</v>
+        <v>5.679</v>
       </c>
       <c r="L294" t="n">
-        <v>-2.661</v>
+        <v>-3.919</v>
       </c>
       <c r="M294" t="n">
-        <v>18.796</v>
+        <v>20.964</v>
       </c>
     </row>
     <row r="295">
@@ -15398,31 +15398,31 @@
         <v>1</v>
       </c>
       <c r="E299" t="n">
-        <v>2.848</v>
+        <v>2.655</v>
       </c>
       <c r="F299" t="n">
-        <v>0.694</v>
+        <v>0.706</v>
       </c>
       <c r="G299" t="n">
-        <v>0.505</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H299" t="n">
-        <v>0.0979</v>
+        <v>0.1043</v>
       </c>
       <c r="I299" t="n">
-        <v>21.71</v>
+        <v>21.45</v>
       </c>
       <c r="J299" t="n">
-        <v>307.7</v>
+        <v>309</v>
       </c>
       <c r="K299" t="n">
-        <v>5.833</v>
+        <v>5.825</v>
       </c>
       <c r="L299" t="n">
-        <v>-2.558</v>
+        <v>-2.561</v>
       </c>
       <c r="M299" t="n">
-        <v>21.108</v>
+        <v>21.207</v>
       </c>
     </row>
     <row r="300">
@@ -15680,7 +15680,7 @@
         <v>0.0922</v>
       </c>
       <c r="I305" t="n">
-        <v>24.84</v>
+        <v>24.88</v>
       </c>
       <c r="J305" t="n">
         <v>371</v>
@@ -15770,7 +15770,7 @@
         <v>0.0919</v>
       </c>
       <c r="I307" t="n">
-        <v>25.75</v>
+        <v>25.84</v>
       </c>
       <c r="J307" t="n">
         <v>352.6</v>
@@ -15803,31 +15803,31 @@
         <v>-1</v>
       </c>
       <c r="E308" t="n">
-        <v>1.893</v>
+        <v>1.998</v>
       </c>
       <c r="F308" t="n">
-        <v>0.769</v>
+        <v>0.802</v>
       </c>
       <c r="G308" t="n">
-        <v>0.445</v>
+        <v>0.409</v>
       </c>
       <c r="H308" t="n">
-        <v>0.0989</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="I308" t="n">
-        <v>26.57</v>
+        <v>26.44</v>
       </c>
       <c r="J308" t="n">
-        <v>364.8</v>
+        <v>378.4</v>
       </c>
       <c r="K308" t="n">
-        <v>4.914</v>
+        <v>5</v>
       </c>
       <c r="L308" t="n">
-        <v>-4.184</v>
+        <v>-4.154</v>
       </c>
       <c r="M308" t="n">
-        <v>20.123</v>
+        <v>20.231</v>
       </c>
     </row>
     <row r="309">
@@ -15860,7 +15860,7 @@
         <v>0.0953</v>
       </c>
       <c r="I309" t="n">
-        <v>24.41</v>
+        <v>24.36</v>
       </c>
       <c r="J309" t="n">
         <v>357.1</v>
@@ -15893,31 +15893,31 @@
         <v>1</v>
       </c>
       <c r="E310" t="n">
-        <v>2.124</v>
+        <v>2.186</v>
       </c>
       <c r="F310" t="n">
-        <v>0.833</v>
+        <v>0.918</v>
       </c>
       <c r="G310" t="n">
-        <v>0.409</v>
+        <v>0.431</v>
       </c>
       <c r="H310" t="n">
-        <v>0.1097</v>
+        <v>0.1136</v>
       </c>
       <c r="I310" t="n">
-        <v>23.16</v>
+        <v>24.43</v>
       </c>
       <c r="J310" t="n">
-        <v>337.3</v>
+        <v>344.3</v>
       </c>
       <c r="K310" t="n">
-        <v>5.266</v>
+        <v>5.566</v>
       </c>
       <c r="L310" t="n">
-        <v>-2.754</v>
+        <v>-2.65</v>
       </c>
       <c r="M310" t="n">
-        <v>20.764</v>
+        <v>21.325</v>
       </c>
     </row>
     <row r="311">
@@ -15983,31 +15983,31 @@
         <v>-1</v>
       </c>
       <c r="E312" t="n">
-        <v>2.042</v>
+        <v>2.105</v>
       </c>
       <c r="F312" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.905</v>
       </c>
       <c r="G312" t="n">
-        <v>0.423</v>
+        <v>0.431</v>
       </c>
       <c r="H312" t="n">
-        <v>0.142</v>
+        <v>0.1136</v>
       </c>
       <c r="I312" t="n">
-        <v>26.51</v>
+        <v>25.39</v>
       </c>
       <c r="J312" t="n">
-        <v>377.1</v>
+        <v>358.3</v>
       </c>
       <c r="K312" t="n">
-        <v>5.372</v>
+        <v>5.459</v>
       </c>
       <c r="L312" t="n">
-        <v>-4.025</v>
+        <v>-3.995</v>
       </c>
       <c r="M312" t="n">
-        <v>21.198</v>
+        <v>21.158</v>
       </c>
     </row>
     <row r="313">
@@ -16028,31 +16028,31 @@
         <v>1</v>
       </c>
       <c r="E313" t="n">
-        <v>2.003</v>
+        <v>2.113</v>
       </c>
       <c r="F313" t="n">
-        <v>0.794</v>
+        <v>0.829</v>
       </c>
       <c r="G313" t="n">
-        <v>0.445</v>
+        <v>0.409</v>
       </c>
       <c r="H313" t="n">
-        <v>0.0989</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="I313" t="n">
-        <v>24.61</v>
+        <v>25.63</v>
       </c>
       <c r="J313" t="n">
-        <v>350.8</v>
+        <v>368.8</v>
       </c>
       <c r="K313" t="n">
-        <v>5.074</v>
+        <v>5.169</v>
       </c>
       <c r="L313" t="n">
-        <v>-2.821</v>
+        <v>-4.096</v>
       </c>
       <c r="M313" t="n">
-        <v>20.394</v>
+        <v>20.505</v>
       </c>
     </row>
     <row r="314">
@@ -16130,7 +16130,7 @@
         <v>0.1017</v>
       </c>
       <c r="I315" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="J315" t="n">
         <v>339.3</v>
@@ -16208,31 +16208,31 @@
         <v>1</v>
       </c>
       <c r="E317" t="n">
-        <v>2.344</v>
+        <v>2.112</v>
       </c>
       <c r="F317" t="n">
-        <v>0.747</v>
+        <v>0.8</v>
       </c>
       <c r="G317" t="n">
-        <v>0.45</v>
+        <v>0.412</v>
       </c>
       <c r="H317" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.1018</v>
       </c>
       <c r="I317" t="n">
-        <v>24.46</v>
+        <v>23.75</v>
       </c>
       <c r="J317" t="n">
-        <v>345.2</v>
+        <v>343.2</v>
       </c>
       <c r="K317" t="n">
-        <v>5.318</v>
+        <v>5.147</v>
       </c>
       <c r="L317" t="n">
-        <v>-2.736</v>
+        <v>-2.795</v>
       </c>
       <c r="M317" t="n">
-        <v>20.744</v>
+        <v>20.506</v>
       </c>
     </row>
     <row r="318">
@@ -16253,31 +16253,31 @@
         <v>1</v>
       </c>
       <c r="E318" t="n">
-        <v>2.168</v>
+        <v>2.186</v>
       </c>
       <c r="F318" t="n">
-        <v>0.852</v>
+        <v>0.918</v>
       </c>
       <c r="G318" t="n">
-        <v>0.423</v>
+        <v>0.431</v>
       </c>
       <c r="H318" t="n">
-        <v>0.142</v>
+        <v>0.1136</v>
       </c>
       <c r="I318" t="n">
-        <v>25.61</v>
+        <v>24.43</v>
       </c>
       <c r="J318" t="n">
-        <v>366.4</v>
+        <v>344.3</v>
       </c>
       <c r="K318" t="n">
-        <v>5.57</v>
+        <v>5.566</v>
       </c>
       <c r="L318" t="n">
-        <v>-3.957</v>
+        <v>-2.65</v>
       </c>
       <c r="M318" t="n">
-        <v>21.522</v>
+        <v>21.325</v>
       </c>
     </row>
     <row r="319">
@@ -16568,31 +16568,31 @@
         <v>-1</v>
       </c>
       <c r="E325" t="n">
-        <v>2.358</v>
+        <v>2.386</v>
       </c>
       <c r="F325" t="n">
-        <v>0.75</v>
+        <v>0.819</v>
       </c>
       <c r="G325" t="n">
-        <v>0.493</v>
+        <v>0.679</v>
       </c>
       <c r="H325" t="n">
-        <v>0.1133</v>
+        <v>0.1199</v>
       </c>
       <c r="I325" t="n">
-        <v>24.69</v>
+        <v>23.71</v>
       </c>
       <c r="J325" t="n">
-        <v>339.8</v>
+        <v>340.7</v>
       </c>
       <c r="K325" t="n">
-        <v>5.524</v>
+        <v>6.101</v>
       </c>
       <c r="L325" t="n">
-        <v>-2.665</v>
+        <v>-2.465</v>
       </c>
       <c r="M325" t="n">
-        <v>21.229</v>
+        <v>22.335</v>
       </c>
     </row>
     <row r="326">
@@ -16613,31 +16613,31 @@
         <v>1</v>
       </c>
       <c r="E326" t="n">
-        <v>2.455</v>
+        <v>2.437</v>
       </c>
       <c r="F326" t="n">
-        <v>0.776</v>
+        <v>0.819</v>
       </c>
       <c r="G326" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H326" t="n">
-        <v>0.1061</v>
+        <v>0.1199</v>
       </c>
       <c r="I326" t="n">
-        <v>22.62</v>
+        <v>21.68</v>
       </c>
       <c r="J326" t="n">
-        <v>352.9</v>
+        <v>322.5</v>
       </c>
       <c r="K326" t="n">
-        <v>5.758</v>
+        <v>6.152</v>
       </c>
       <c r="L326" t="n">
-        <v>-2.584</v>
+        <v>-2.448</v>
       </c>
       <c r="M326" t="n">
-        <v>21.595</v>
+        <v>22.411</v>
       </c>
     </row>
     <row r="327">
@@ -16883,31 +16883,31 @@
         <v>1</v>
       </c>
       <c r="E332" t="n">
-        <v>2.428</v>
+        <v>2.437</v>
       </c>
       <c r="F332" t="n">
-        <v>0.756</v>
+        <v>0.819</v>
       </c>
       <c r="G332" t="n">
-        <v>0.493</v>
+        <v>0.679</v>
       </c>
       <c r="H332" t="n">
-        <v>0.1133</v>
+        <v>0.1199</v>
       </c>
       <c r="I332" t="n">
-        <v>21.45</v>
+        <v>21.68</v>
       </c>
       <c r="J332" t="n">
-        <v>318.5</v>
+        <v>322.5</v>
       </c>
       <c r="K332" t="n">
-        <v>5.606</v>
+        <v>6.152</v>
       </c>
       <c r="L332" t="n">
-        <v>-2.637</v>
+        <v>-2.448</v>
       </c>
       <c r="M332" t="n">
-        <v>21.362</v>
+        <v>22.411</v>
       </c>
     </row>
     <row r="333">
@@ -16973,31 +16973,31 @@
         <v>-1</v>
       </c>
       <c r="E334" t="n">
-        <v>2.192</v>
+        <v>2.331</v>
       </c>
       <c r="F334" t="n">
-        <v>0.705</v>
+        <v>0.746</v>
       </c>
       <c r="G334" t="n">
-        <v>0.545</v>
+        <v>0.53</v>
       </c>
       <c r="H334" t="n">
-        <v>0.109</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="I334" t="n">
-        <v>24.15</v>
+        <v>22.93</v>
       </c>
       <c r="J334" t="n">
-        <v>349.9</v>
+        <v>366.8</v>
       </c>
       <c r="K334" t="n">
-        <v>5.346</v>
+        <v>5.478</v>
       </c>
       <c r="L334" t="n">
-        <v>-2.727</v>
+        <v>-3.989</v>
       </c>
       <c r="M334" t="n">
-        <v>20.937</v>
+        <v>21.061</v>
       </c>
     </row>
     <row r="335">
@@ -17075,7 +17075,7 @@
         <v>0.1212</v>
       </c>
       <c r="I336" t="n">
-        <v>20.8</v>
+        <v>20.65</v>
       </c>
       <c r="J336" t="n">
         <v>315</v>
@@ -17120,7 +17120,7 @@
         <v>0.1298</v>
       </c>
       <c r="I337" t="n">
-        <v>22.29</v>
+        <v>22.21</v>
       </c>
       <c r="J337" t="n">
         <v>322</v>
@@ -17153,31 +17153,31 @@
         <v>-1</v>
       </c>
       <c r="E338" t="n">
-        <v>2.35</v>
+        <v>2.361</v>
       </c>
       <c r="F338" t="n">
-        <v>0.771</v>
+        <v>0.839</v>
       </c>
       <c r="G338" t="n">
-        <v>0.458</v>
+        <v>0.585</v>
       </c>
       <c r="H338" t="n">
-        <v>0.1167</v>
+        <v>0.143</v>
       </c>
       <c r="I338" t="n">
-        <v>21.36</v>
+        <v>22.61</v>
       </c>
       <c r="J338" t="n">
-        <v>349.1</v>
+        <v>324</v>
       </c>
       <c r="K338" t="n">
-        <v>5.508</v>
+        <v>6.067</v>
       </c>
       <c r="L338" t="n">
-        <v>-3.978</v>
+        <v>-2.477</v>
       </c>
       <c r="M338" t="n">
-        <v>20.798</v>
+        <v>21.957</v>
       </c>
     </row>
     <row r="339">
@@ -17210,7 +17210,7 @@
         <v>0.1144</v>
       </c>
       <c r="I339" t="n">
-        <v>20.62</v>
+        <v>20.55</v>
       </c>
       <c r="J339" t="n">
         <v>311.4</v>
@@ -17243,31 +17243,31 @@
         <v>1</v>
       </c>
       <c r="E340" t="n">
-        <v>2.284</v>
+        <v>2.395</v>
       </c>
       <c r="F340" t="n">
-        <v>0.699</v>
+        <v>0.752</v>
       </c>
       <c r="G340" t="n">
-        <v>0.534</v>
+        <v>0.436</v>
       </c>
       <c r="H340" t="n">
-        <v>0.1075</v>
+        <v>0.1089</v>
       </c>
       <c r="I340" t="n">
-        <v>20.46</v>
+        <v>21.72</v>
       </c>
       <c r="J340" t="n">
-        <v>323.3</v>
+        <v>339.9</v>
       </c>
       <c r="K340" t="n">
-        <v>5.395</v>
+        <v>5.424</v>
       </c>
       <c r="L340" t="n">
-        <v>-2.71</v>
+        <v>-4.007</v>
       </c>
       <c r="M340" t="n">
-        <v>20.582</v>
+        <v>20.577</v>
       </c>
     </row>
     <row r="341">
@@ -17300,7 +17300,7 @@
         <v>0.1205</v>
       </c>
       <c r="I341" t="n">
-        <v>23.1</v>
+        <v>22.78</v>
       </c>
       <c r="J341" t="n">
         <v>321.2</v>
@@ -17345,7 +17345,7 @@
         <v>0.09909999999999999</v>
       </c>
       <c r="I342" t="n">
-        <v>21.9</v>
+        <v>21.57</v>
       </c>
       <c r="J342" t="n">
         <v>342.1</v>
@@ -17390,7 +17390,7 @@
         <v>0.0917</v>
       </c>
       <c r="I343" t="n">
-        <v>20.78</v>
+        <v>20.54</v>
       </c>
       <c r="J343" t="n">
         <v>333</v>
@@ -17423,31 +17423,31 @@
         <v>-1</v>
       </c>
       <c r="E344" t="n">
-        <v>2.33</v>
+        <v>2.361</v>
       </c>
       <c r="F344" t="n">
-        <v>0.745</v>
+        <v>0.839</v>
       </c>
       <c r="G344" t="n">
-        <v>0.467</v>
+        <v>0.585</v>
       </c>
       <c r="H344" t="n">
-        <v>0.1283</v>
+        <v>0.143</v>
       </c>
       <c r="I344" t="n">
-        <v>22.55</v>
+        <v>22.61</v>
       </c>
       <c r="J344" t="n">
-        <v>321.8</v>
+        <v>324</v>
       </c>
       <c r="K344" t="n">
-        <v>5.524</v>
+        <v>6.067</v>
       </c>
       <c r="L344" t="n">
-        <v>-2.665</v>
+        <v>-2.477</v>
       </c>
       <c r="M344" t="n">
-        <v>20.907</v>
+        <v>21.957</v>
       </c>
     </row>
     <row r="345">
@@ -17468,31 +17468,31 @@
         <v>-1</v>
       </c>
       <c r="E345" t="n">
-        <v>2.503</v>
+        <v>2.331</v>
       </c>
       <c r="F345" t="n">
-        <v>0.68</v>
+        <v>0.704</v>
       </c>
       <c r="G345" t="n">
         <v>0.503</v>
       </c>
       <c r="H345" t="n">
-        <v>0.1081</v>
+        <v>0.1118</v>
       </c>
       <c r="I345" t="n">
-        <v>22.77</v>
+        <v>21.58</v>
       </c>
       <c r="J345" t="n">
-        <v>326.9</v>
+        <v>324.8</v>
       </c>
       <c r="K345" t="n">
-        <v>5.518</v>
+        <v>5.416</v>
       </c>
       <c r="L345" t="n">
-        <v>-2.667</v>
+        <v>-2.702</v>
       </c>
       <c r="M345" t="n">
-        <v>20.737</v>
+        <v>20.637</v>
       </c>
     </row>
     <row r="346">
@@ -17513,31 +17513,31 @@
         <v>1</v>
       </c>
       <c r="E346" t="n">
-        <v>2.454</v>
+        <v>2.425</v>
       </c>
       <c r="F346" t="n">
-        <v>0.777</v>
+        <v>0.839</v>
       </c>
       <c r="G346" t="n">
-        <v>0.458</v>
+        <v>0.585</v>
       </c>
       <c r="H346" t="n">
-        <v>0.1167</v>
+        <v>0.143</v>
       </c>
       <c r="I346" t="n">
-        <v>21.67</v>
+        <v>20.17</v>
       </c>
       <c r="J346" t="n">
-        <v>339.2</v>
+        <v>318.2</v>
       </c>
       <c r="K346" t="n">
-        <v>5.624</v>
+        <v>6.131</v>
       </c>
       <c r="L346" t="n">
-        <v>-3.938</v>
+        <v>-2.455</v>
       </c>
       <c r="M346" t="n">
-        <v>20.982</v>
+        <v>22.051</v>
       </c>
     </row>
     <row r="347">
@@ -17570,7 +17570,7 @@
         <v>0.0994</v>
       </c>
       <c r="I347" t="n">
-        <v>21.44</v>
+        <v>21.25</v>
       </c>
       <c r="J347" t="n">
         <v>338</v>
@@ -17615,7 +17615,7 @@
         <v>0.0985</v>
       </c>
       <c r="I348" t="n">
-        <v>22.9</v>
+        <v>22.68</v>
       </c>
       <c r="J348" t="n">
         <v>350.5</v>
@@ -17648,31 +17648,31 @@
         <v>-1</v>
       </c>
       <c r="E349" t="n">
-        <v>2.194</v>
+        <v>2.303</v>
       </c>
       <c r="F349" t="n">
-        <v>0.699</v>
+        <v>0.744</v>
       </c>
       <c r="G349" t="n">
-        <v>0.534</v>
+        <v>0.436</v>
       </c>
       <c r="H349" t="n">
-        <v>0.1075</v>
+        <v>0.1089</v>
       </c>
       <c r="I349" t="n">
-        <v>22.82</v>
+        <v>21.41</v>
       </c>
       <c r="J349" t="n">
-        <v>331.3</v>
+        <v>349.3</v>
       </c>
       <c r="K349" t="n">
-        <v>5.305</v>
+        <v>5.316</v>
       </c>
       <c r="L349" t="n">
-        <v>-2.741</v>
+        <v>-4.045</v>
       </c>
       <c r="M349" t="n">
-        <v>20.453</v>
+        <v>20.422</v>
       </c>
     </row>
     <row r="350">
@@ -17705,7 +17705,7 @@
         <v>0.1346</v>
       </c>
       <c r="I350" t="n">
-        <v>20.56</v>
+        <v>20.58</v>
       </c>
       <c r="J350" t="n">
         <v>305.8</v>
@@ -17750,7 +17750,7 @@
         <v>0.09909999999999999</v>
       </c>
       <c r="I351" t="n">
-        <v>20.76</v>
+        <v>20.48</v>
       </c>
       <c r="J351" t="n">
         <v>331.3</v>
@@ -18512,22 +18512,22 @@
         <v>0.493</v>
       </c>
       <c r="H368" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="I368" t="n">
-        <v>23.93</v>
+        <v>23.85</v>
       </c>
       <c r="J368" t="n">
         <v>346.1</v>
       </c>
       <c r="K368" t="n">
-        <v>5.579</v>
+        <v>5.58</v>
       </c>
       <c r="L368" t="n">
-        <v>-3.954</v>
+        <v>-3.953</v>
       </c>
       <c r="M368" t="n">
-        <v>20.834</v>
+        <v>20.839</v>
       </c>
     </row>
     <row r="369">
@@ -18557,22 +18557,22 @@
         <v>0.425</v>
       </c>
       <c r="H369" t="n">
-        <v>0.1288</v>
+        <v>0.1375</v>
       </c>
       <c r="I369" t="n">
-        <v>21.81</v>
+        <v>21.71</v>
       </c>
       <c r="J369" t="n">
         <v>309.5</v>
       </c>
       <c r="K369" t="n">
-        <v>5.872</v>
+        <v>5.924</v>
       </c>
       <c r="L369" t="n">
-        <v>-2.545</v>
+        <v>-2.527</v>
       </c>
       <c r="M369" t="n">
-        <v>21.447</v>
+        <v>21.591</v>
       </c>
     </row>
     <row r="370">
@@ -18602,22 +18602,22 @@
         <v>0.49</v>
       </c>
       <c r="H370" t="n">
-        <v>0.1097</v>
+        <v>0.113</v>
       </c>
       <c r="I370" t="n">
-        <v>20.36</v>
+        <v>20.24</v>
       </c>
       <c r="J370" t="n">
         <v>308.2</v>
       </c>
       <c r="K370" t="n">
-        <v>5.899</v>
+        <v>5.919</v>
       </c>
       <c r="L370" t="n">
-        <v>-2.535</v>
+        <v>-2.528</v>
       </c>
       <c r="M370" t="n">
-        <v>21.407</v>
+        <v>21.461</v>
       </c>
     </row>
     <row r="371">
@@ -18647,16 +18647,16 @@
         <v>0.514</v>
       </c>
       <c r="H371" t="n">
-        <v>0.0955</v>
+        <v>0.0956</v>
       </c>
       <c r="I371" t="n">
-        <v>25.08</v>
+        <v>25.03</v>
       </c>
       <c r="J371" t="n">
         <v>360.4</v>
       </c>
       <c r="K371" t="n">
-        <v>5.216</v>
+        <v>5.217</v>
       </c>
       <c r="L371" t="n">
         <v>-4.079</v>
@@ -18692,22 +18692,22 @@
         <v>0.449</v>
       </c>
       <c r="H372" t="n">
-        <v>0.1082</v>
+        <v>0.1095</v>
       </c>
       <c r="I372" t="n">
-        <v>22.21</v>
+        <v>22.07</v>
       </c>
       <c r="J372" t="n">
         <v>333.9</v>
       </c>
       <c r="K372" t="n">
-        <v>5.678</v>
+        <v>5.686</v>
       </c>
       <c r="L372" t="n">
-        <v>-2.612</v>
+        <v>-2.609</v>
       </c>
       <c r="M372" t="n">
-        <v>21.019</v>
+        <v>21.041</v>
       </c>
     </row>
     <row r="373">
@@ -18737,22 +18737,22 @@
         <v>0.538</v>
       </c>
       <c r="H373" t="n">
-        <v>0.1179</v>
+        <v>0.1211</v>
       </c>
       <c r="I373" t="n">
-        <v>24.59</v>
+        <v>24.52</v>
       </c>
       <c r="J373" t="n">
         <v>355</v>
       </c>
       <c r="K373" t="n">
-        <v>5.625</v>
+        <v>5.645</v>
       </c>
       <c r="L373" t="n">
-        <v>-3.938</v>
+        <v>-3.931</v>
       </c>
       <c r="M373" t="n">
-        <v>21.067</v>
+        <v>21.121</v>
       </c>
     </row>
     <row r="374">
@@ -18782,22 +18782,22 @@
         <v>0.473</v>
       </c>
       <c r="H374" t="n">
-        <v>0.1056</v>
+        <v>0.1076</v>
       </c>
       <c r="I374" t="n">
-        <v>24.85</v>
+        <v>24.76</v>
       </c>
       <c r="J374" t="n">
         <v>354.4</v>
       </c>
       <c r="K374" t="n">
-        <v>5.287</v>
+        <v>5.299</v>
       </c>
       <c r="L374" t="n">
-        <v>-4.055</v>
+        <v>-4.051</v>
       </c>
       <c r="M374" t="n">
-        <v>20.38</v>
+        <v>20.412</v>
       </c>
     </row>
     <row r="375">
@@ -18827,22 +18827,22 @@
         <v>0.514</v>
       </c>
       <c r="H375" t="n">
-        <v>0.0955</v>
+        <v>0.0956</v>
       </c>
       <c r="I375" t="n">
-        <v>22.13</v>
+        <v>22.11</v>
       </c>
       <c r="J375" t="n">
         <v>346.6</v>
       </c>
       <c r="K375" t="n">
-        <v>5.24</v>
+        <v>5.241</v>
       </c>
       <c r="L375" t="n">
         <v>-4.071</v>
       </c>
       <c r="M375" t="n">
-        <v>20.255</v>
+        <v>20.256</v>
       </c>
     </row>
     <row r="376">
@@ -18872,22 +18872,22 @@
         <v>0.536</v>
       </c>
       <c r="H376" t="n">
-        <v>0.1207</v>
+        <v>0.1282</v>
       </c>
       <c r="I376" t="n">
-        <v>21.01</v>
+        <v>20.66</v>
       </c>
       <c r="J376" t="n">
         <v>305.7</v>
       </c>
       <c r="K376" t="n">
-        <v>6.292</v>
+        <v>6.337</v>
       </c>
       <c r="L376" t="n">
-        <v>-2.399</v>
+        <v>-2.384</v>
       </c>
       <c r="M376" t="n">
-        <v>22.106</v>
+        <v>22.228</v>
       </c>
     </row>
     <row r="377">
@@ -18917,22 +18917,22 @@
         <v>0.455</v>
       </c>
       <c r="H377" t="n">
-        <v>0.1121</v>
+        <v>0.1142</v>
       </c>
       <c r="I377" t="n">
-        <v>25.18</v>
+        <v>24.96</v>
       </c>
       <c r="J377" t="n">
         <v>334.7</v>
       </c>
       <c r="K377" t="n">
-        <v>5.694</v>
+        <v>5.706</v>
       </c>
       <c r="L377" t="n">
-        <v>-2.606</v>
+        <v>-2.602</v>
       </c>
       <c r="M377" t="n">
-        <v>21.064</v>
+        <v>21.099</v>
       </c>
     </row>
     <row r="378">
@@ -18962,22 +18962,22 @@
         <v>0.436</v>
       </c>
       <c r="H378" t="n">
-        <v>0.0988</v>
+        <v>0.1001</v>
       </c>
       <c r="I378" t="n">
-        <v>22.72</v>
+        <v>22.86</v>
       </c>
       <c r="J378" t="n">
         <v>333.1</v>
       </c>
       <c r="K378" t="n">
-        <v>5.332</v>
+        <v>5.34</v>
       </c>
       <c r="L378" t="n">
-        <v>-2.731</v>
+        <v>-2.729</v>
       </c>
       <c r="M378" t="n">
-        <v>20.394</v>
+        <v>20.417</v>
       </c>
     </row>
     <row r="379">
@@ -19007,22 +19007,22 @@
         <v>0.436</v>
       </c>
       <c r="H379" t="n">
-        <v>0.1053</v>
+        <v>0.1067</v>
       </c>
       <c r="I379" t="n">
-        <v>23.87</v>
+        <v>23.8</v>
       </c>
       <c r="J379" t="n">
         <v>357.7</v>
       </c>
       <c r="K379" t="n">
-        <v>5.163</v>
+        <v>5.171</v>
       </c>
       <c r="L379" t="n">
-        <v>-4.098</v>
+        <v>-4.095</v>
       </c>
       <c r="M379" t="n">
-        <v>20.176</v>
+        <v>20.199</v>
       </c>
     </row>
     <row r="380">
@@ -19052,22 +19052,22 @@
         <v>0.45</v>
       </c>
       <c r="H380" t="n">
-        <v>0.1046</v>
+        <v>0.106</v>
       </c>
       <c r="I380" t="n">
-        <v>22.77</v>
+        <v>22.58</v>
       </c>
       <c r="J380" t="n">
         <v>335.9</v>
       </c>
       <c r="K380" t="n">
-        <v>5.504</v>
+        <v>5.512</v>
       </c>
       <c r="L380" t="n">
-        <v>-2.672</v>
+        <v>-2.669</v>
       </c>
       <c r="M380" t="n">
-        <v>20.701</v>
+        <v>20.724</v>
       </c>
     </row>
     <row r="381">
@@ -19088,31 +19088,31 @@
         <v>-1</v>
       </c>
       <c r="E381" t="n">
-        <v>2.268</v>
+        <v>2.338</v>
       </c>
       <c r="F381" t="n">
-        <v>0.822</v>
+        <v>0.904</v>
       </c>
       <c r="G381" t="n">
-        <v>0.441</v>
+        <v>0.535</v>
       </c>
       <c r="H381" t="n">
-        <v>0.1187</v>
+        <v>0.135</v>
       </c>
       <c r="I381" t="n">
-        <v>25.16</v>
+        <v>23.81</v>
       </c>
       <c r="J381" t="n">
-        <v>336.8</v>
+        <v>341.8</v>
       </c>
       <c r="K381" t="n">
-        <v>5.506</v>
+        <v>6.026</v>
       </c>
       <c r="L381" t="n">
-        <v>-3.979</v>
+        <v>-3.799</v>
       </c>
       <c r="M381" t="n">
-        <v>20.829</v>
+        <v>21.833</v>
       </c>
     </row>
     <row r="382">
@@ -19142,19 +19142,19 @@
         <v>0.395</v>
       </c>
       <c r="H382" t="n">
-        <v>0.0927</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="I382" t="n">
-        <v>24.9</v>
+        <v>24.82</v>
       </c>
       <c r="J382" t="n">
         <v>359.6</v>
       </c>
       <c r="K382" t="n">
-        <v>5.088</v>
+        <v>5.089</v>
       </c>
       <c r="L382" t="n">
-        <v>-4.124</v>
+        <v>-4.123</v>
       </c>
       <c r="M382" t="n">
         <v>19.898</v>
@@ -19187,22 +19187,22 @@
         <v>0.473</v>
       </c>
       <c r="H383" t="n">
-        <v>0.1056</v>
+        <v>0.1076</v>
       </c>
       <c r="I383" t="n">
-        <v>23.52</v>
+        <v>23.5</v>
       </c>
       <c r="J383" t="n">
         <v>340.3</v>
       </c>
       <c r="K383" t="n">
-        <v>5.321</v>
+        <v>5.333</v>
       </c>
       <c r="L383" t="n">
-        <v>-4.043</v>
+        <v>-4.039</v>
       </c>
       <c r="M383" t="n">
-        <v>20.425</v>
+        <v>20.456</v>
       </c>
     </row>
     <row r="384">
@@ -19268,31 +19268,31 @@
         <v>-1</v>
       </c>
       <c r="E385" t="n">
-        <v>2.081</v>
+        <v>2.261</v>
       </c>
       <c r="F385" t="n">
-        <v>0.711</v>
+        <v>0.806</v>
       </c>
       <c r="G385" t="n">
-        <v>0.408</v>
+        <v>0.51</v>
       </c>
       <c r="H385" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="I385" t="n">
-        <v>23.89</v>
+        <v>24.5</v>
       </c>
       <c r="J385" t="n">
-        <v>330.1</v>
+        <v>331.5</v>
       </c>
       <c r="K385" t="n">
-        <v>4.867</v>
+        <v>5.491</v>
       </c>
       <c r="L385" t="n">
-        <v>-4.2</v>
+        <v>-3.984</v>
       </c>
       <c r="M385" t="n">
-        <v>19.204</v>
+        <v>18.366</v>
       </c>
     </row>
     <row r="386">
@@ -19583,31 +19583,31 @@
         <v>1</v>
       </c>
       <c r="E392" t="n">
-        <v>2.354</v>
+        <v>2.371</v>
       </c>
       <c r="F392" t="n">
-        <v>0.749</v>
+        <v>0.806</v>
       </c>
       <c r="G392" t="n">
-        <v>0.477</v>
+        <v>0.51</v>
       </c>
       <c r="H392" t="n">
-        <v>0.1026</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="I392" t="n">
-        <v>25.22</v>
+        <v>24.21</v>
       </c>
       <c r="J392" t="n">
-        <v>329.6</v>
+        <v>312.9</v>
       </c>
       <c r="K392" t="n">
-        <v>5.422</v>
+        <v>5.601</v>
       </c>
       <c r="L392" t="n">
-        <v>-4.008</v>
+        <v>-2.638</v>
       </c>
       <c r="M392" t="n">
-        <v>18.222</v>
+        <v>18.522</v>
       </c>
     </row>
     <row r="393">
@@ -19628,31 +19628,31 @@
         <v>-1</v>
       </c>
       <c r="E393" t="n">
-        <v>2.317</v>
+        <v>2.076</v>
       </c>
       <c r="F393" t="n">
-        <v>0.646</v>
+        <v>0.678</v>
       </c>
       <c r="G393" t="n">
-        <v>0.473</v>
+        <v>0.422</v>
       </c>
       <c r="H393" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0818</v>
       </c>
       <c r="I393" t="n">
-        <v>23.91</v>
+        <v>24.27</v>
       </c>
       <c r="J393" t="n">
-        <v>334.4</v>
+        <v>332.2</v>
       </c>
       <c r="K393" t="n">
-        <v>5.079</v>
+        <v>4.767</v>
       </c>
       <c r="L393" t="n">
-        <v>-4.127</v>
+        <v>-4.235</v>
       </c>
       <c r="M393" t="n">
-        <v>19.49</v>
+        <v>16.996</v>
       </c>
     </row>
     <row r="394">
@@ -19898,31 +19898,31 @@
         <v>-1</v>
       </c>
       <c r="E399" t="n">
-        <v>2.14</v>
+        <v>2.261</v>
       </c>
       <c r="F399" t="n">
-        <v>0.744</v>
+        <v>0.806</v>
       </c>
       <c r="G399" t="n">
-        <v>0.477</v>
+        <v>0.51</v>
       </c>
       <c r="H399" t="n">
-        <v>0.1026</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="I399" t="n">
-        <v>23.89</v>
+        <v>24.5</v>
       </c>
       <c r="J399" t="n">
-        <v>341.8</v>
+        <v>331.5</v>
       </c>
       <c r="K399" t="n">
-        <v>5.198</v>
+        <v>5.491</v>
       </c>
       <c r="L399" t="n">
-        <v>-4.086</v>
+        <v>-3.984</v>
       </c>
       <c r="M399" t="n">
-        <v>19.858</v>
+        <v>18.366</v>
       </c>
     </row>
     <row r="400">
@@ -21473,31 +21473,31 @@
         <v>1</v>
       </c>
       <c r="E434" t="n">
-        <v>2.736</v>
+        <v>2.47</v>
       </c>
       <c r="F434" t="n">
-        <v>0.852</v>
+        <v>0.857</v>
       </c>
       <c r="G434" t="n">
-        <v>0.586</v>
+        <v>0.513</v>
       </c>
       <c r="H434" t="n">
-        <v>0.1513</v>
+        <v>0.1437</v>
       </c>
       <c r="I434" t="n">
-        <v>19.41</v>
+        <v>18.92</v>
       </c>
       <c r="J434" t="n">
-        <v>297.1</v>
+        <v>297.5</v>
       </c>
       <c r="K434" t="n">
-        <v>9.52</v>
+        <v>9.071999999999999</v>
       </c>
       <c r="L434" t="n">
-        <v>-1.282</v>
+        <v>-1.437</v>
       </c>
       <c r="M434" t="n">
-        <v>23.285</v>
+        <v>22.548</v>
       </c>
     </row>
     <row r="435">
@@ -22643,31 +22643,31 @@
         <v>-1</v>
       </c>
       <c r="E460" t="n">
-        <v>2.184</v>
+        <v>2.002</v>
       </c>
       <c r="F460" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.722</v>
       </c>
       <c r="G460" t="n">
-        <v>0.553</v>
+        <v>0.477</v>
       </c>
       <c r="H460" t="n">
-        <v>0.1053</v>
+        <v>0.1077</v>
       </c>
       <c r="I460" t="n">
-        <v>21.88</v>
+        <v>21.56</v>
       </c>
       <c r="J460" t="n">
-        <v>341.1</v>
+        <v>339</v>
       </c>
       <c r="K460" t="n">
-        <v>5.296</v>
+        <v>5.046</v>
       </c>
       <c r="L460" t="n">
-        <v>-4.052</v>
+        <v>-4.138</v>
       </c>
       <c r="M460" t="n">
-        <v>20.419</v>
+        <v>20.04</v>
       </c>
     </row>
     <row r="461">
@@ -23183,31 +23183,31 @@
         <v>-1</v>
       </c>
       <c r="E472" t="n">
-        <v>2.169</v>
+        <v>2.227</v>
       </c>
       <c r="F472" t="n">
-        <v>0.757</v>
+        <v>0.836</v>
       </c>
       <c r="G472" t="n">
-        <v>0.418</v>
+        <v>0.516</v>
       </c>
       <c r="H472" t="n">
-        <v>0.1388</v>
+        <v>0.2164</v>
       </c>
       <c r="I472" t="n">
-        <v>23.35</v>
+        <v>23.66</v>
       </c>
       <c r="J472" t="n">
-        <v>330.2</v>
+        <v>331.8</v>
       </c>
       <c r="K472" t="n">
-        <v>5.352</v>
+        <v>6.229</v>
       </c>
       <c r="L472" t="n">
-        <v>-2.725</v>
+        <v>-2.421</v>
       </c>
       <c r="M472" t="n">
-        <v>20.686</v>
+        <v>22.588</v>
       </c>
     </row>
     <row r="473">
@@ -23273,31 +23273,31 @@
         <v>1</v>
       </c>
       <c r="E474" t="n">
-        <v>2.469</v>
+        <v>2.253</v>
       </c>
       <c r="F474" t="n">
-        <v>0.679</v>
+        <v>0.719</v>
       </c>
       <c r="G474" t="n">
-        <v>0.457</v>
+        <v>0.418</v>
       </c>
       <c r="H474" t="n">
-        <v>0.1337</v>
+        <v>0.1233</v>
       </c>
       <c r="I474" t="n">
-        <v>21.85</v>
+        <v>22.11</v>
       </c>
       <c r="J474" t="n">
-        <v>321.8</v>
+        <v>320.1</v>
       </c>
       <c r="K474" t="n">
-        <v>5.543</v>
+        <v>5.267</v>
       </c>
       <c r="L474" t="n">
-        <v>-2.658</v>
+        <v>-2.754</v>
       </c>
       <c r="M474" t="n">
-        <v>20.926</v>
+        <v>20.427</v>
       </c>
     </row>
     <row r="475">
@@ -24038,31 +24038,31 @@
         <v>-1</v>
       </c>
       <c r="E491" t="n">
-        <v>2.252</v>
+        <v>2.333</v>
       </c>
       <c r="F491" t="n">
-        <v>0.677</v>
+        <v>0.775</v>
       </c>
       <c r="G491" t="n">
-        <v>0.466</v>
+        <v>0.574</v>
       </c>
       <c r="H491" t="n">
-        <v>0.0801</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="I491" t="n">
-        <v>25.46</v>
+        <v>25.61</v>
       </c>
       <c r="J491" t="n">
-        <v>334.3</v>
+        <v>334.9</v>
       </c>
       <c r="K491" t="n">
-        <v>5.019</v>
+        <v>5.626</v>
       </c>
       <c r="L491" t="n">
-        <v>-2.84</v>
+        <v>-2.63</v>
       </c>
       <c r="M491" t="n">
-        <v>17.74</v>
+        <v>18.957</v>
       </c>
     </row>
     <row r="492">

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -7265,7 +7265,7 @@
         <v>0.1796</v>
       </c>
       <c r="I118" t="n">
-        <v>23.89</v>
+        <v>23.98</v>
       </c>
       <c r="J118" t="n">
         <v>349</v>
@@ -11270,7 +11270,7 @@
         <v>0.201</v>
       </c>
       <c r="I207" t="n">
-        <v>19.47</v>
+        <v>19.53</v>
       </c>
       <c r="J207" t="n">
         <v>294.6</v>
@@ -12440,7 +12440,7 @@
         <v>0.1649</v>
       </c>
       <c r="I233" t="n">
-        <v>19.35</v>
+        <v>19.58</v>
       </c>
       <c r="J233" t="n">
         <v>303.7</v>
@@ -12452,7 +12452,7 @@
         <v>-2.074</v>
       </c>
       <c r="M233" t="n">
-        <v>24.583</v>
+        <v>22.621</v>
       </c>
     </row>
     <row r="234">
@@ -15500,7 +15500,7 @@
         <v>0.1281</v>
       </c>
       <c r="I301" t="n">
-        <v>20.75</v>
+        <v>20.61</v>
       </c>
       <c r="J301" t="n">
         <v>291.1</v>
@@ -18560,7 +18560,7 @@
         <v>0.1375</v>
       </c>
       <c r="I369" t="n">
-        <v>21.71</v>
+        <v>21.54</v>
       </c>
       <c r="J369" t="n">
         <v>309.5</v>

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -632,44 +632,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>37.06</v>
+        <v>37.88</v>
       </c>
       <c r="D5" t="n">
-        <v>12.1</v>
+        <v>13.16</v>
       </c>
       <c r="E5" t="n">
-        <v>7.65</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>2.35</v>
+        <v>1.71</v>
       </c>
       <c r="G5" t="n">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="H5" t="n">
-        <v>4813</v>
+        <v>4938</v>
       </c>
       <c r="I5" t="n">
-        <v>96.7</v>
+        <v>95.88</v>
       </c>
       <c r="J5" t="n">
-        <v>40.59</v>
+        <v>45.35</v>
       </c>
       <c r="K5" t="n">
-        <v>187.78</v>
+        <v>189.21</v>
       </c>
       <c r="L5" t="n">
-        <v>102.35</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.65</v>
+        <v>15.59</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -677,44 +677,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>37.88</v>
+        <v>36.92</v>
       </c>
       <c r="D6" t="n">
-        <v>13.16</v>
+        <v>12.05</v>
       </c>
       <c r="E6" t="n">
-        <v>9.199999999999999</v>
+        <v>7.63</v>
       </c>
       <c r="F6" t="n">
-        <v>1.71</v>
+        <v>2.35</v>
       </c>
       <c r="G6" t="n">
-        <v>332</v>
+        <v>303</v>
       </c>
       <c r="H6" t="n">
-        <v>4938</v>
+        <v>4828</v>
       </c>
       <c r="I6" t="n">
-        <v>95.88</v>
+        <v>93.36</v>
       </c>
       <c r="J6" t="n">
-        <v>45.35</v>
+        <v>40.59</v>
       </c>
       <c r="K6" t="n">
-        <v>189.21</v>
+        <v>187.78</v>
       </c>
       <c r="L6" t="n">
-        <v>80.29000000000001</v>
+        <v>102.35</v>
       </c>
       <c r="M6" t="n">
-        <v>15.59</v>
+        <v>-8.99</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -1764,25 +1764,25 @@
         <v>15</v>
       </c>
       <c r="C30" t="n">
-        <v>31.61</v>
+        <v>31.71</v>
       </c>
       <c r="D30" t="n">
-        <v>10.93</v>
+        <v>10.96</v>
       </c>
       <c r="E30" t="n">
-        <v>6.68</v>
+        <v>6.7</v>
       </c>
       <c r="F30" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G30" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H30" t="n">
-        <v>5075</v>
+        <v>5058</v>
       </c>
       <c r="I30" t="n">
-        <v>76.63</v>
+        <v>76.87</v>
       </c>
       <c r="J30" t="n">
         <v>34.06</v>
@@ -1794,7 +1794,7 @@
         <v>84.70999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>-8.08</v>
+        <v>-7.84</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -8108,31 +8108,31 @@
         <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>2.826</v>
+        <v>2.6847</v>
       </c>
       <c r="F137" t="n">
-        <v>0.903</v>
+        <v>0.85785</v>
       </c>
       <c r="G137" t="n">
-        <v>0.549</v>
+        <v>0.5215500000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>0.162</v>
+        <v>0.1539</v>
       </c>
       <c r="I137" t="n">
-        <v>19.56</v>
+        <v>20.538</v>
       </c>
       <c r="J137" t="n">
-        <v>295</v>
+        <v>309.75</v>
       </c>
       <c r="K137" t="n">
-        <v>9.702</v>
+        <v>6.367</v>
       </c>
       <c r="L137" t="n">
-        <v>-1.219</v>
+        <v>-2.373</v>
       </c>
       <c r="M137" t="n">
-        <v>24.049</v>
+        <v>22.895</v>
       </c>
     </row>
     <row r="138">
@@ -20933,31 +20933,31 @@
         <v>1</v>
       </c>
       <c r="E422" t="n">
-        <v>2.006</v>
+        <v>2.1063</v>
       </c>
       <c r="F422" t="n">
-        <v>0.661</v>
+        <v>0.6940500000000001</v>
       </c>
       <c r="G422" t="n">
-        <v>0.397</v>
+        <v>0.4168500000000001</v>
       </c>
       <c r="H422" t="n">
-        <v>0.0994</v>
+        <v>0.10437</v>
       </c>
       <c r="I422" t="n">
-        <v>21.67</v>
+        <v>20.5865</v>
       </c>
       <c r="J422" t="n">
-        <v>331.4</v>
+        <v>314.83</v>
       </c>
       <c r="K422" t="n">
-        <v>4.718</v>
+        <v>4.954</v>
       </c>
       <c r="L422" t="n">
-        <v>-2.944</v>
+        <v>-2.862</v>
       </c>
       <c r="M422" t="n">
-        <v>19.359</v>
+        <v>19.441</v>
       </c>
     </row>
     <row r="423">

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -1532,44 +1532,44 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>15</v>
       </c>
       <c r="C25" t="n">
-        <v>32.79</v>
+        <v>31.81</v>
       </c>
       <c r="D25" t="n">
-        <v>11.16</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>7.38</v>
+        <v>6.72</v>
       </c>
       <c r="F25" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="G25" t="n">
-        <v>369</v>
+        <v>316</v>
       </c>
       <c r="H25" t="n">
-        <v>5196</v>
+        <v>5042</v>
       </c>
       <c r="I25" t="n">
-        <v>80</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>20.21</v>
+        <v>34.06</v>
       </c>
       <c r="K25" t="n">
-        <v>127.38</v>
+        <v>170.15</v>
       </c>
       <c r="L25" t="n">
-        <v>82.06</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.06</v>
+        <v>-4.61</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -1577,44 +1577,44 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>15</v>
       </c>
       <c r="C26" t="n">
-        <v>34.26</v>
+        <v>32.79</v>
       </c>
       <c r="D26" t="n">
-        <v>11.22</v>
+        <v>11.16</v>
       </c>
       <c r="E26" t="n">
-        <v>7.04</v>
+        <v>7.38</v>
       </c>
       <c r="F26" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="G26" t="n">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="H26" t="n">
-        <v>4808</v>
+        <v>5196</v>
       </c>
       <c r="I26" t="n">
-        <v>79.72</v>
+        <v>80</v>
       </c>
       <c r="J26" t="n">
-        <v>21.71</v>
+        <v>20.21</v>
       </c>
       <c r="K26" t="n">
-        <v>172.13</v>
+        <v>127.38</v>
       </c>
       <c r="L26" t="n">
-        <v>81.18000000000001</v>
+        <v>82.06</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.46</v>
+        <v>-2.06</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -1622,44 +1622,44 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>15</v>
       </c>
       <c r="C27" t="n">
-        <v>34.43</v>
+        <v>34.26</v>
       </c>
       <c r="D27" t="n">
-        <v>11.52</v>
+        <v>11.22</v>
       </c>
       <c r="E27" t="n">
-        <v>6.14</v>
+        <v>7.04</v>
       </c>
       <c r="F27" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="G27" t="n">
-        <v>325</v>
+        <v>354</v>
       </c>
       <c r="H27" t="n">
-        <v>5027</v>
+        <v>4808</v>
       </c>
       <c r="I27" t="n">
-        <v>79.40000000000001</v>
+        <v>79.72</v>
       </c>
       <c r="J27" t="n">
-        <v>35.82</v>
+        <v>21.71</v>
       </c>
       <c r="K27" t="n">
-        <v>171.65</v>
+        <v>172.13</v>
       </c>
       <c r="L27" t="n">
-        <v>87.34999999999999</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-7.95</v>
+        <v>-1.46</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -1667,44 +1667,44 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>15</v>
       </c>
       <c r="C28" t="n">
-        <v>32.68</v>
+        <v>34.43</v>
       </c>
       <c r="D28" t="n">
-        <v>10.59</v>
+        <v>11.52</v>
       </c>
       <c r="E28" t="n">
-        <v>7.12</v>
+        <v>6.14</v>
       </c>
       <c r="F28" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="G28" t="n">
-        <v>374</v>
+        <v>325</v>
       </c>
       <c r="H28" t="n">
-        <v>5310</v>
+        <v>5027</v>
       </c>
       <c r="I28" t="n">
-        <v>77.89</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>19.06</v>
+        <v>35.82</v>
       </c>
       <c r="K28" t="n">
-        <v>124.46</v>
+        <v>171.65</v>
       </c>
       <c r="L28" t="n">
-        <v>84.70999999999999</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>-6.82</v>
+        <v>-7.95</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -1712,44 +1712,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>15</v>
       </c>
       <c r="C29" t="n">
-        <v>34.97</v>
+        <v>32.68</v>
       </c>
       <c r="D29" t="n">
-        <v>10.92</v>
+        <v>10.59</v>
       </c>
       <c r="E29" t="n">
-        <v>6.67</v>
+        <v>7.12</v>
       </c>
       <c r="F29" t="n">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="G29" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H29" t="n">
-        <v>5279</v>
+        <v>5310</v>
       </c>
       <c r="I29" t="n">
-        <v>76.90000000000001</v>
+        <v>77.89</v>
       </c>
       <c r="J29" t="n">
-        <v>21.26</v>
+        <v>19.06</v>
       </c>
       <c r="K29" t="n">
-        <v>122.45</v>
+        <v>124.46</v>
       </c>
       <c r="L29" t="n">
-        <v>78.53</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.63</v>
+        <v>-6.82</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -1757,44 +1757,44 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>15</v>
       </c>
       <c r="C30" t="n">
-        <v>31.71</v>
+        <v>34.97</v>
       </c>
       <c r="D30" t="n">
-        <v>10.96</v>
+        <v>10.92</v>
       </c>
       <c r="E30" t="n">
-        <v>6.7</v>
+        <v>6.67</v>
       </c>
       <c r="F30" t="n">
-        <v>1.64</v>
+        <v>1.13</v>
       </c>
       <c r="G30" t="n">
-        <v>317</v>
+        <v>376</v>
       </c>
       <c r="H30" t="n">
-        <v>5058</v>
+        <v>5279</v>
       </c>
       <c r="I30" t="n">
-        <v>76.87</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>34.06</v>
+        <v>21.26</v>
       </c>
       <c r="K30" t="n">
-        <v>170.15</v>
+        <v>122.45</v>
       </c>
       <c r="L30" t="n">
-        <v>84.70999999999999</v>
+        <v>78.53</v>
       </c>
       <c r="M30" t="n">
-        <v>-7.84</v>
+        <v>-1.63</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -20933,31 +20933,31 @@
         <v>1</v>
       </c>
       <c r="E422" t="n">
-        <v>2.1063</v>
+        <v>2.2066</v>
       </c>
       <c r="F422" t="n">
-        <v>0.6940500000000001</v>
+        <v>0.7271000000000001</v>
       </c>
       <c r="G422" t="n">
-        <v>0.4168500000000001</v>
+        <v>0.4367</v>
       </c>
       <c r="H422" t="n">
-        <v>0.10437</v>
+        <v>0.10934</v>
       </c>
       <c r="I422" t="n">
-        <v>20.5865</v>
+        <v>19.503</v>
       </c>
       <c r="J422" t="n">
-        <v>314.83</v>
+        <v>298.26</v>
       </c>
       <c r="K422" t="n">
-        <v>4.954</v>
+        <v>8.19</v>
       </c>
       <c r="L422" t="n">
-        <v>-2.862</v>
+        <v>-1.742</v>
       </c>
       <c r="M422" t="n">
-        <v>19.441</v>
+        <v>20.561</v>
       </c>
     </row>
     <row r="423">

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -567,7 +567,7 @@
         <v>4270</v>
       </c>
       <c r="I3" t="n">
-        <v>85.06999999999999</v>
+        <v>85.08</v>
       </c>
       <c r="J3" t="n">
         <v>35.1</v>
@@ -579,7 +579,7 @@
         <v>88.70999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.64</v>
+        <v>-3.63</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -684,37 +684,37 @@
         <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>30.71</v>
+        <v>30.81</v>
       </c>
       <c r="D6" t="n">
-        <v>11.48</v>
+        <v>11.38</v>
       </c>
       <c r="E6" t="n">
-        <v>6.73</v>
+        <v>6.68</v>
       </c>
       <c r="F6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="G6" t="n">
         <v>268</v>
       </c>
       <c r="H6" t="n">
-        <v>4344</v>
+        <v>4367</v>
       </c>
       <c r="I6" t="n">
-        <v>79.28</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>35.56</v>
+        <v>35.48</v>
       </c>
       <c r="K6" t="n">
-        <v>156.95</v>
+        <v>156.44</v>
       </c>
       <c r="L6" t="n">
         <v>78</v>
       </c>
       <c r="M6" t="n">
-        <v>1.28</v>
+        <v>0.9</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -729,37 +729,37 @@
         <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>32.39</v>
+        <v>32.62</v>
       </c>
       <c r="D7" t="n">
-        <v>10.98</v>
+        <v>10.84</v>
       </c>
       <c r="E7" t="n">
-        <v>6.12</v>
+        <v>5.94</v>
       </c>
       <c r="F7" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="G7" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H7" t="n">
-        <v>4170</v>
+        <v>4200</v>
       </c>
       <c r="I7" t="n">
-        <v>78.73</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>35.18</v>
+        <v>35.02</v>
       </c>
       <c r="K7" t="n">
-        <v>160.44</v>
+        <v>159.23</v>
       </c>
       <c r="L7" t="n">
         <v>80.29000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.56</v>
+        <v>-2.44</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -774,37 +774,37 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>31.33</v>
+        <v>31.48</v>
       </c>
       <c r="D8" t="n">
-        <v>11.05</v>
+        <v>10.98</v>
       </c>
       <c r="E8" t="n">
-        <v>7.57</v>
+        <v>7.46</v>
       </c>
       <c r="F8" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="G8" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H8" t="n">
-        <v>4288</v>
+        <v>4305</v>
       </c>
       <c r="I8" t="n">
-        <v>76.29000000000001</v>
+        <v>75.97</v>
       </c>
       <c r="J8" t="n">
-        <v>23.02</v>
+        <v>22.94</v>
       </c>
       <c r="K8" t="n">
-        <v>156.9</v>
+        <v>156.61</v>
       </c>
       <c r="L8" t="n">
         <v>75.70999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.58</v>
+        <v>0.26</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -812,44 +812,44 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>30.84</v>
+        <v>32.41</v>
       </c>
       <c r="D9" t="n">
-        <v>10.24</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>6.95</v>
+        <v>6.31</v>
       </c>
       <c r="F9" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="G9" t="n">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="H9" t="n">
-        <v>4267</v>
+        <v>4349</v>
       </c>
       <c r="I9" t="n">
-        <v>76.15000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="J9" t="n">
-        <v>33.72</v>
+        <v>34.03</v>
       </c>
       <c r="K9" t="n">
-        <v>156.61</v>
+        <v>157.41</v>
       </c>
       <c r="L9" t="n">
-        <v>82.59</v>
+        <v>94.06</v>
       </c>
       <c r="M9" t="n">
-        <v>-6.44</v>
+        <v>-18.36</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -857,44 +857,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>32.27</v>
+        <v>32.13</v>
       </c>
       <c r="D10" t="n">
-        <v>9.75</v>
+        <v>10.72</v>
       </c>
       <c r="E10" t="n">
-        <v>6.37</v>
+        <v>7.06</v>
       </c>
       <c r="F10" t="n">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="G10" t="n">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="H10" t="n">
-        <v>4333</v>
+        <v>4340</v>
       </c>
       <c r="I10" t="n">
-        <v>76.05</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>34.11</v>
+        <v>23.86</v>
       </c>
       <c r="K10" t="n">
-        <v>157.65</v>
+        <v>158.71</v>
       </c>
       <c r="L10" t="n">
-        <v>94.06</v>
+        <v>69.59</v>
       </c>
       <c r="M10" t="n">
-        <v>-18.01</v>
+        <v>5.92</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -902,44 +902,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>32.13</v>
+        <v>30.76</v>
       </c>
       <c r="D11" t="n">
-        <v>10.72</v>
+        <v>10.11</v>
       </c>
       <c r="E11" t="n">
-        <v>7.06</v>
+        <v>6.84</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="G11" t="n">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="H11" t="n">
-        <v>4340</v>
+        <v>4288</v>
       </c>
       <c r="I11" t="n">
-        <v>75.51000000000001</v>
+        <v>74.36</v>
       </c>
       <c r="J11" t="n">
-        <v>23.86</v>
+        <v>33.42</v>
       </c>
       <c r="K11" t="n">
-        <v>158.71</v>
+        <v>155.76</v>
       </c>
       <c r="L11" t="n">
-        <v>69.59</v>
+        <v>82.59</v>
       </c>
       <c r="M11" t="n">
-        <v>5.92</v>
+        <v>-8.23</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -947,44 +947,44 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>33.38</v>
+        <v>28.42</v>
       </c>
       <c r="D12" t="n">
-        <v>10.13</v>
+        <v>10.85</v>
       </c>
       <c r="E12" t="n">
-        <v>6.54</v>
+        <v>5.5</v>
       </c>
       <c r="F12" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="G12" t="n">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="H12" t="n">
-        <v>4403</v>
+        <v>4260</v>
       </c>
       <c r="I12" t="n">
-        <v>74.16</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>23.48</v>
+        <v>31.81</v>
       </c>
       <c r="K12" t="n">
-        <v>156.78</v>
+        <v>149.5</v>
       </c>
       <c r="L12" t="n">
-        <v>74.94</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.78</v>
+        <v>-1.89</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -992,44 +992,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>30.32</v>
+        <v>32.28</v>
       </c>
       <c r="D13" t="n">
-        <v>10.74</v>
+        <v>9.56</v>
       </c>
       <c r="E13" t="n">
-        <v>6.07</v>
+        <v>7.14</v>
       </c>
       <c r="F13" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="G13" t="n">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="H13" t="n">
-        <v>4317</v>
+        <v>4502</v>
       </c>
       <c r="I13" t="n">
-        <v>74.06999999999999</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="J13" t="n">
         <v>21.18</v>
       </c>
       <c r="K13" t="n">
-        <v>157.33</v>
+        <v>127.54</v>
       </c>
       <c r="L13" t="n">
-        <v>68.06</v>
+        <v>71.12</v>
       </c>
       <c r="M13" t="n">
-        <v>6.01</v>
+        <v>2.53</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1037,44 +1037,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>32.02</v>
+        <v>30.27</v>
       </c>
       <c r="D14" t="n">
-        <v>9.67</v>
+        <v>10.34</v>
       </c>
       <c r="E14" t="n">
-        <v>7.18</v>
+        <v>6.45</v>
       </c>
       <c r="F14" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="G14" t="n">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="H14" t="n">
-        <v>4480</v>
+        <v>4348</v>
       </c>
       <c r="I14" t="n">
-        <v>74.01000000000001</v>
+        <v>73.02</v>
       </c>
       <c r="J14" t="n">
-        <v>21.34</v>
+        <v>21.03</v>
       </c>
       <c r="K14" t="n">
-        <v>128.03</v>
+        <v>156.02</v>
       </c>
       <c r="L14" t="n">
-        <v>71.12</v>
+        <v>68.06</v>
       </c>
       <c r="M14" t="n">
-        <v>2.89</v>
+        <v>4.96</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1082,44 +1082,44 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>28.42</v>
+        <v>29.44</v>
       </c>
       <c r="D15" t="n">
-        <v>10.85</v>
+        <v>10.72</v>
       </c>
       <c r="E15" t="n">
-        <v>5.5</v>
+        <v>5.68</v>
       </c>
       <c r="F15" t="n">
         <v>1.28</v>
       </c>
       <c r="G15" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H15" t="n">
-        <v>4260</v>
+        <v>4301</v>
       </c>
       <c r="I15" t="n">
-        <v>73.81</v>
+        <v>72.94</v>
       </c>
       <c r="J15" t="n">
-        <v>31.81</v>
+        <v>32.58</v>
       </c>
       <c r="K15" t="n">
-        <v>149.5</v>
+        <v>150.49</v>
       </c>
       <c r="L15" t="n">
-        <v>75.70999999999999</v>
+        <v>76.47</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9</v>
+        <v>-3.53</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1127,44 +1127,44 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>31.41</v>
+        <v>33.08</v>
       </c>
       <c r="D16" t="n">
-        <v>10.51</v>
+        <v>9.84</v>
       </c>
       <c r="E16" t="n">
-        <v>5.96</v>
+        <v>6.23</v>
       </c>
       <c r="F16" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="G16" t="n">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="H16" t="n">
-        <v>4305</v>
+        <v>4414</v>
       </c>
       <c r="I16" t="n">
-        <v>72.95999999999999</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>33.49</v>
+        <v>22.71</v>
       </c>
       <c r="K16" t="n">
-        <v>153.14</v>
+        <v>129.11</v>
       </c>
       <c r="L16" t="n">
         <v>74.94</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.98</v>
+        <v>-2.4</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1172,44 +1172,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>29.44</v>
+        <v>30.86</v>
       </c>
       <c r="D17" t="n">
-        <v>10.72</v>
+        <v>10.01</v>
       </c>
       <c r="E17" t="n">
-        <v>5.68</v>
+        <v>7.27</v>
       </c>
       <c r="F17" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="G17" t="n">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="H17" t="n">
-        <v>4301</v>
+        <v>4491</v>
       </c>
       <c r="I17" t="n">
-        <v>72.94</v>
+        <v>72.45</v>
       </c>
       <c r="J17" t="n">
-        <v>32.58</v>
+        <v>34.18</v>
       </c>
       <c r="K17" t="n">
-        <v>150.49</v>
+        <v>126.27</v>
       </c>
       <c r="L17" t="n">
-        <v>76.47</v>
+        <v>82.59</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.53</v>
+        <v>-10.14</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1224,37 +1224,37 @@
         <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>30.6</v>
+        <v>30.82</v>
       </c>
       <c r="D18" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="E18" t="n">
-        <v>5.75</v>
+        <v>5.76</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="G18" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H18" t="n">
-        <v>4566</v>
+        <v>4598</v>
       </c>
       <c r="I18" t="n">
-        <v>72.73</v>
+        <v>72.22</v>
       </c>
       <c r="J18" t="n">
         <v>19.58</v>
       </c>
       <c r="K18" t="n">
-        <v>128.94</v>
+        <v>128.21</v>
       </c>
       <c r="L18" t="n">
         <v>77.23999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.51</v>
+        <v>-5.02</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1262,44 +1262,44 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>30.86</v>
+        <v>31.44</v>
       </c>
       <c r="D19" t="n">
-        <v>10.01</v>
+        <v>10.36</v>
       </c>
       <c r="E19" t="n">
-        <v>7.27</v>
+        <v>5.78</v>
       </c>
       <c r="F19" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="G19" t="n">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="H19" t="n">
-        <v>4491</v>
+        <v>4337</v>
       </c>
       <c r="I19" t="n">
-        <v>72.45999999999999</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>34.18</v>
+        <v>33.19</v>
       </c>
       <c r="K19" t="n">
-        <v>126.31</v>
+        <v>152.01</v>
       </c>
       <c r="L19" t="n">
-        <v>82.59</v>
+        <v>74.94</v>
       </c>
       <c r="M19" t="n">
-        <v>-10.13</v>
+        <v>-2.9</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1332,7 +1332,7 @@
         <v>4483</v>
       </c>
       <c r="I20" t="n">
-        <v>71.34999999999999</v>
+        <v>71.36</v>
       </c>
       <c r="J20" t="n">
         <v>19.35</v>
@@ -1344,7 +1344,7 @@
         <v>76.47</v>
       </c>
       <c r="M20" t="n">
-        <v>-5.12</v>
+        <v>-5.11</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1359,13 +1359,13 @@
         <v>13</v>
       </c>
       <c r="C21" t="n">
-        <v>29.83</v>
+        <v>29.75</v>
       </c>
       <c r="D21" t="n">
-        <v>10.12</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>6.41</v>
+        <v>6.29</v>
       </c>
       <c r="F21" t="n">
         <v>1.31</v>
@@ -1374,22 +1374,22 @@
         <v>322</v>
       </c>
       <c r="H21" t="n">
-        <v>4246</v>
+        <v>4255</v>
       </c>
       <c r="I21" t="n">
-        <v>70.78</v>
+        <v>70.09</v>
       </c>
       <c r="J21" t="n">
-        <v>19.27</v>
+        <v>18.96</v>
       </c>
       <c r="K21" t="n">
-        <v>137.33</v>
+        <v>136.59</v>
       </c>
       <c r="L21" t="n">
         <v>70.34999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>0.43</v>
+        <v>-0.26</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1404,37 +1404,37 @@
         <v>13</v>
       </c>
       <c r="C22" t="n">
-        <v>29.84</v>
+        <v>29.71</v>
       </c>
       <c r="D22" t="n">
-        <v>10.18</v>
+        <v>10.06</v>
       </c>
       <c r="E22" t="n">
-        <v>6.31</v>
+        <v>6.25</v>
       </c>
       <c r="F22" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="G22" t="n">
         <v>334</v>
       </c>
       <c r="H22" t="n">
-        <v>4536</v>
+        <v>4543</v>
       </c>
       <c r="I22" t="n">
-        <v>70.47</v>
+        <v>69.89</v>
       </c>
       <c r="J22" t="n">
-        <v>19.19</v>
+        <v>19.12</v>
       </c>
       <c r="K22" t="n">
-        <v>111.11</v>
+        <v>110.59</v>
       </c>
       <c r="L22" t="n">
         <v>68.06</v>
       </c>
       <c r="M22" t="n">
-        <v>2.41</v>
+        <v>1.83</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1442,44 +1442,44 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>13</v>
       </c>
       <c r="C23" t="n">
-        <v>30.68</v>
+        <v>28.79</v>
       </c>
       <c r="D23" t="n">
-        <v>9.630000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="F23" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="G23" t="n">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="H23" t="n">
-        <v>4374</v>
+        <v>4285</v>
       </c>
       <c r="I23" t="n">
-        <v>70.38</v>
+        <v>68.98</v>
       </c>
       <c r="J23" t="n">
-        <v>18.96</v>
+        <v>30.05</v>
       </c>
       <c r="K23" t="n">
-        <v>151.52</v>
+        <v>148.31</v>
       </c>
       <c r="L23" t="n">
-        <v>71.88</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5</v>
+        <v>-3.67</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1494,37 +1494,37 @@
         <v>13</v>
       </c>
       <c r="C24" t="n">
-        <v>30.19</v>
+        <v>30.06</v>
       </c>
       <c r="D24" t="n">
-        <v>10.07</v>
+        <v>9.93</v>
       </c>
       <c r="E24" t="n">
-        <v>5.53</v>
+        <v>5.37</v>
       </c>
       <c r="F24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="G24" t="n">
         <v>283</v>
       </c>
       <c r="H24" t="n">
-        <v>4445</v>
+        <v>4459</v>
       </c>
       <c r="I24" t="n">
-        <v>69.38</v>
+        <v>68.48</v>
       </c>
       <c r="J24" t="n">
-        <v>32.42</v>
+        <v>31.74</v>
       </c>
       <c r="K24" t="n">
-        <v>124.94</v>
+        <v>123.15</v>
       </c>
       <c r="L24" t="n">
         <v>75.70999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-6.33</v>
+        <v>-7.23</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -1532,44 +1532,44 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>13</v>
       </c>
       <c r="C25" t="n">
-        <v>28.7</v>
+        <v>28.34</v>
       </c>
       <c r="D25" t="n">
-        <v>9.93</v>
+        <v>10.06</v>
       </c>
       <c r="E25" t="n">
-        <v>5.86</v>
+        <v>6.05</v>
       </c>
       <c r="F25" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="G25" t="n">
-        <v>290</v>
+        <v>334</v>
       </c>
       <c r="H25" t="n">
-        <v>4266</v>
+        <v>4466</v>
       </c>
       <c r="I25" t="n">
-        <v>69.38</v>
+        <v>68.38</v>
       </c>
       <c r="J25" t="n">
-        <v>30.51</v>
+        <v>17.44</v>
       </c>
       <c r="K25" t="n">
-        <v>149.73</v>
+        <v>108.53</v>
       </c>
       <c r="L25" t="n">
-        <v>72.65000000000001</v>
+        <v>71.12</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.27</v>
+        <v>-2.74</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -1577,44 +1577,44 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>13</v>
       </c>
       <c r="C26" t="n">
-        <v>28.34</v>
+        <v>29.22</v>
       </c>
       <c r="D26" t="n">
-        <v>10.06</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>6.05</v>
+        <v>5.81</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="G26" t="n">
-        <v>334</v>
+        <v>297</v>
       </c>
       <c r="H26" t="n">
-        <v>4466</v>
+        <v>4359</v>
       </c>
       <c r="I26" t="n">
-        <v>68.38</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>17.44</v>
       </c>
       <c r="K26" t="n">
-        <v>108.53</v>
+        <v>146.32</v>
       </c>
       <c r="L26" t="n">
-        <v>71.12</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.74</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -1622,44 +1622,44 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>13</v>
       </c>
       <c r="C27" t="n">
-        <v>29.28</v>
+        <v>28.95</v>
       </c>
       <c r="D27" t="n">
-        <v>9.85</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>5.87</v>
+        <v>5.68</v>
       </c>
       <c r="F27" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="G27" t="n">
-        <v>297</v>
+        <v>333</v>
       </c>
       <c r="H27" t="n">
-        <v>4345</v>
+        <v>4468</v>
       </c>
       <c r="I27" t="n">
-        <v>68.02</v>
+        <v>66.89</v>
       </c>
       <c r="J27" t="n">
-        <v>17.97</v>
+        <v>16.9</v>
       </c>
       <c r="K27" t="n">
-        <v>147.5</v>
+        <v>107.96</v>
       </c>
       <c r="L27" t="n">
-        <v>75.70999999999999</v>
+        <v>71.88</v>
       </c>
       <c r="M27" t="n">
-        <v>-7.69</v>
+        <v>-4.99</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -1677,34 +1677,34 @@
         <v>26.64</v>
       </c>
       <c r="D28" t="n">
-        <v>9.5</v>
+        <v>9.31</v>
       </c>
       <c r="E28" t="n">
-        <v>5.97</v>
+        <v>5.84</v>
       </c>
       <c r="F28" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="G28" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H28" t="n">
-        <v>4715</v>
+        <v>4733</v>
       </c>
       <c r="I28" t="n">
-        <v>67.47</v>
+        <v>66.36</v>
       </c>
       <c r="J28" t="n">
-        <v>2.29</v>
+        <v>1.99</v>
       </c>
       <c r="K28" t="n">
-        <v>108.28</v>
+        <v>106.92</v>
       </c>
       <c r="L28" t="n">
         <v>69.59</v>
       </c>
       <c r="M28" t="n">
-        <v>-2.12</v>
+        <v>-3.23</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -1719,37 +1719,37 @@
         <v>13</v>
       </c>
       <c r="C29" t="n">
-        <v>29.51</v>
+        <v>29.39</v>
       </c>
       <c r="D29" t="n">
-        <v>9.34</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="F29" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="G29" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H29" t="n">
-        <v>4536</v>
+        <v>4547</v>
       </c>
       <c r="I29" t="n">
-        <v>66.73</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>17.74</v>
+        <v>17.59</v>
       </c>
       <c r="K29" t="n">
-        <v>120.72</v>
+        <v>119.92</v>
       </c>
       <c r="L29" t="n">
         <v>73.41</v>
       </c>
       <c r="M29" t="n">
-        <v>-6.68</v>
+        <v>-7.31</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -1757,44 +1757,44 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>13</v>
       </c>
       <c r="C30" t="n">
-        <v>26.63</v>
+        <v>29.04</v>
       </c>
       <c r="D30" t="n">
-        <v>9.44</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>5.72</v>
+        <v>5.53</v>
       </c>
       <c r="F30" t="n">
-        <v>1.33</v>
+        <v>0.99</v>
       </c>
       <c r="G30" t="n">
-        <v>276</v>
+        <v>331</v>
       </c>
       <c r="H30" t="n">
-        <v>4384</v>
+        <v>4474</v>
       </c>
       <c r="I30" t="n">
-        <v>64.90000000000001</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>28.68</v>
+        <v>17.21</v>
       </c>
       <c r="K30" t="n">
-        <v>145.39</v>
+        <v>104.05</v>
       </c>
       <c r="L30" t="n">
-        <v>73.41</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>-8.51</v>
+        <v>-8.08</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -1802,44 +1802,44 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>13</v>
       </c>
       <c r="C31" t="n">
-        <v>29.04</v>
+        <v>26.5</v>
       </c>
       <c r="D31" t="n">
         <v>9.279999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>5.53</v>
+        <v>5.58</v>
       </c>
       <c r="F31" t="n">
-        <v>0.99</v>
+        <v>1.31</v>
       </c>
       <c r="G31" t="n">
-        <v>331</v>
+        <v>277</v>
       </c>
       <c r="H31" t="n">
-        <v>4474</v>
+        <v>4400</v>
       </c>
       <c r="I31" t="n">
-        <v>64.56999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>17.05</v>
+        <v>28.29</v>
       </c>
       <c r="K31" t="n">
-        <v>104.21</v>
+        <v>144.48</v>
       </c>
       <c r="L31" t="n">
-        <v>72.65000000000001</v>
+        <v>73.41</v>
       </c>
       <c r="M31" t="n">
-        <v>-8.08</v>
+        <v>-9.31</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -1875,10 +1875,10 @@
         <v>63.71</v>
       </c>
       <c r="J32" t="n">
-        <v>15.52</v>
+        <v>15.14</v>
       </c>
       <c r="K32" t="n">
-        <v>103.71</v>
+        <v>103.05</v>
       </c>
       <c r="L32" t="n">
         <v>66.53</v>
@@ -1917,19 +1917,19 @@
         <v>4672</v>
       </c>
       <c r="I33" t="n">
-        <v>62.05</v>
+        <v>62.06</v>
       </c>
       <c r="J33" t="n">
-        <v>13.99</v>
+        <v>14.07</v>
       </c>
       <c r="K33" t="n">
-        <v>101.45</v>
+        <v>101.25</v>
       </c>
       <c r="L33" t="n">
         <v>71.88</v>
       </c>
       <c r="M33" t="n">
-        <v>-9.83</v>
+        <v>-9.82</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
         <v>1.7</v>
       </c>
       <c r="F6" t="n">
-        <v>0.671</v>
+        <v>0.673</v>
       </c>
       <c r="G6" t="n">
         <v>0.35</v>
@@ -2231,13 +2231,13 @@
         <v>348.1</v>
       </c>
       <c r="K6" t="n">
-        <v>4.296</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>-4.398</v>
+        <v>-4.396</v>
       </c>
       <c r="M6" t="n">
-        <v>16.693</v>
+        <v>16.695</v>
       </c>
     </row>
     <row r="7">
@@ -2618,31 +2618,31 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>2.508</v>
+        <v>2.631</v>
       </c>
       <c r="F15" t="n">
-        <v>0.903</v>
+        <v>0.84</v>
       </c>
       <c r="G15" t="n">
-        <v>0.526</v>
+        <v>0.496</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1563</v>
+        <v>0.117</v>
       </c>
       <c r="I15" t="n">
-        <v>21.78</v>
+        <v>21.99</v>
       </c>
       <c r="J15" t="n">
-        <v>316.2</v>
+        <v>334.3</v>
       </c>
       <c r="K15" t="n">
-        <v>6.304</v>
+        <v>6.005</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.395</v>
+        <v>-2.499</v>
       </c>
       <c r="M15" t="n">
-        <v>22.434</v>
+        <v>21.649</v>
       </c>
     </row>
     <row r="16">
@@ -2663,31 +2663,31 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>2.313</v>
+        <v>2.327</v>
       </c>
       <c r="F16" t="n">
-        <v>0.797</v>
+        <v>0.765</v>
       </c>
       <c r="G16" t="n">
-        <v>0.455</v>
+        <v>0.475</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0968</v>
+        <v>0.0905</v>
       </c>
       <c r="I16" t="n">
-        <v>21.14</v>
+        <v>21.13</v>
       </c>
       <c r="J16" t="n">
-        <v>332.5</v>
+        <v>332</v>
       </c>
       <c r="K16" t="n">
-        <v>5.398</v>
+        <v>5.35</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.709</v>
+        <v>-2.725</v>
       </c>
       <c r="M16" t="n">
-        <v>20.523</v>
+        <v>20.388</v>
       </c>
     </row>
     <row r="17">
@@ -2708,31 +2708,31 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.565</v>
+        <v>2.564</v>
       </c>
       <c r="F17" t="n">
-        <v>0.902</v>
+        <v>0.891</v>
       </c>
       <c r="G17" t="n">
-        <v>0.433</v>
+        <v>0.503</v>
       </c>
       <c r="H17" t="n">
-        <v>0.134</v>
+        <v>0.1262</v>
       </c>
       <c r="I17" t="n">
-        <v>20.58</v>
+        <v>20.33</v>
       </c>
       <c r="J17" t="n">
-        <v>313.3</v>
+        <v>312.8</v>
       </c>
       <c r="K17" t="n">
-        <v>6.039</v>
+        <v>6.109</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.487</v>
+        <v>-2.463</v>
       </c>
       <c r="M17" t="n">
-        <v>21.81</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="18">
@@ -2753,31 +2753,31 @@
         <v>-1</v>
       </c>
       <c r="E18" t="n">
-        <v>2.044</v>
+        <v>2.038</v>
       </c>
       <c r="F18" t="n">
-        <v>0.728</v>
+        <v>0.705</v>
       </c>
       <c r="G18" t="n">
-        <v>0.397</v>
+        <v>0.46</v>
       </c>
       <c r="H18" t="n">
-        <v>0.108</v>
+        <v>0.1023</v>
       </c>
       <c r="I18" t="n">
-        <v>24.31</v>
+        <v>24.32</v>
       </c>
       <c r="J18" t="n">
-        <v>352.6</v>
+        <v>352.7</v>
       </c>
       <c r="K18" t="n">
-        <v>4.942</v>
+        <v>4.982</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.174</v>
+        <v>-4.16</v>
       </c>
       <c r="M18" t="n">
-        <v>19.849</v>
+        <v>19.897</v>
       </c>
     </row>
     <row r="19">
@@ -2798,31 +2798,31 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>2.186</v>
+        <v>2.172</v>
       </c>
       <c r="F19" t="n">
-        <v>0.781</v>
+        <v>0.761</v>
       </c>
       <c r="G19" t="n">
-        <v>0.429</v>
+        <v>0.467</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1006</v>
+        <v>0.094</v>
       </c>
       <c r="I19" t="n">
-        <v>21.61</v>
+        <v>21.59</v>
       </c>
       <c r="J19" t="n">
-        <v>334.1</v>
+        <v>333.7</v>
       </c>
       <c r="K19" t="n">
-        <v>5.21</v>
+        <v>5.192</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.774</v>
+        <v>-2.78</v>
       </c>
       <c r="M19" t="n">
-        <v>20.236</v>
+        <v>20.176</v>
       </c>
     </row>
     <row r="20">
@@ -2843,31 +2843,31 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.508</v>
+        <v>2.505</v>
       </c>
       <c r="F20" t="n">
-        <v>0.903</v>
+        <v>0.888</v>
       </c>
       <c r="G20" t="n">
-        <v>0.526</v>
+        <v>0.553</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1563</v>
+        <v>0.1495</v>
       </c>
       <c r="I20" t="n">
-        <v>21.78</v>
+        <v>21.81</v>
       </c>
       <c r="J20" t="n">
-        <v>316.2</v>
+        <v>315.8</v>
       </c>
       <c r="K20" t="n">
-        <v>6.304</v>
+        <v>6.284</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.395</v>
+        <v>-2.402</v>
       </c>
       <c r="M20" t="n">
-        <v>22.434</v>
+        <v>22.369</v>
       </c>
     </row>
     <row r="21">
@@ -2888,31 +2888,31 @@
         <v>-1</v>
       </c>
       <c r="E21" t="n">
-        <v>2.47</v>
+        <v>2.364</v>
       </c>
       <c r="F21" t="n">
-        <v>0.903</v>
+        <v>0.752</v>
       </c>
       <c r="G21" t="n">
-        <v>0.526</v>
+        <v>0.453</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1563</v>
+        <v>0.1089</v>
       </c>
       <c r="I21" t="n">
-        <v>23.98</v>
+        <v>23.73</v>
       </c>
       <c r="J21" t="n">
-        <v>326.7</v>
+        <v>343.1</v>
       </c>
       <c r="K21" t="n">
-        <v>6.266</v>
+        <v>5.427</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.408</v>
+        <v>-4.006</v>
       </c>
       <c r="M21" t="n">
-        <v>22.375</v>
+        <v>20.643</v>
       </c>
     </row>
     <row r="22">
@@ -2933,31 +2933,31 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>2.187</v>
+        <v>2.165</v>
       </c>
       <c r="F22" t="n">
-        <v>0.754</v>
+        <v>0.749</v>
       </c>
       <c r="G22" t="n">
-        <v>0.419</v>
+        <v>0.479</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1156</v>
+        <v>0.1094</v>
       </c>
       <c r="I22" t="n">
-        <v>22.73</v>
+        <v>22.72</v>
       </c>
       <c r="J22" t="n">
-        <v>343.2</v>
+        <v>343.3</v>
       </c>
       <c r="K22" t="n">
-        <v>5.227</v>
+        <v>5.277</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.076</v>
+        <v>-4.058</v>
       </c>
       <c r="M22" t="n">
-        <v>20.379</v>
+        <v>20.459</v>
       </c>
     </row>
     <row r="23">
@@ -2978,31 +2978,31 @@
         <v>-1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.082</v>
+        <v>2.077</v>
       </c>
       <c r="F23" t="n">
-        <v>0.756</v>
+        <v>0.737</v>
       </c>
       <c r="G23" t="n">
-        <v>0.43</v>
+        <v>0.445</v>
       </c>
       <c r="H23" t="n">
-        <v>0.112</v>
+        <v>0.1057</v>
       </c>
       <c r="I23" t="n">
-        <v>24.11</v>
+        <v>24.12</v>
       </c>
       <c r="J23" t="n">
-        <v>346.1</v>
+        <v>345.6</v>
       </c>
       <c r="K23" t="n">
-        <v>5.126</v>
+        <v>5.075</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.11</v>
+        <v>-4.128</v>
       </c>
       <c r="M23" t="n">
-        <v>20.2</v>
+        <v>20.082</v>
       </c>
     </row>
     <row r="24">
@@ -3023,31 +3023,31 @@
         <v>-1</v>
       </c>
       <c r="E24" t="n">
-        <v>2.203</v>
+        <v>2.201</v>
       </c>
       <c r="F24" t="n">
-        <v>0.844</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.517</v>
+        <v>0.536</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1367</v>
+        <v>0.1311</v>
       </c>
       <c r="I24" t="n">
-        <v>24.26</v>
+        <v>24.23</v>
       </c>
       <c r="J24" t="n">
-        <v>344.9</v>
+        <v>344.4</v>
       </c>
       <c r="K24" t="n">
-        <v>5.745</v>
+        <v>5.696</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.896</v>
+        <v>-3.913</v>
       </c>
       <c r="M24" t="n">
-        <v>21.44</v>
+        <v>21.318</v>
       </c>
     </row>
     <row r="25">
@@ -3068,31 +3068,31 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>2.115</v>
+        <v>2.101</v>
       </c>
       <c r="F25" t="n">
-        <v>0.725</v>
+        <v>0.711</v>
       </c>
       <c r="G25" t="n">
-        <v>0.397</v>
+        <v>0.46</v>
       </c>
       <c r="H25" t="n">
-        <v>0.108</v>
+        <v>0.1023</v>
       </c>
       <c r="I25" t="n">
-        <v>21.59</v>
+        <v>21.57</v>
       </c>
       <c r="J25" t="n">
-        <v>345.8</v>
+        <v>346</v>
       </c>
       <c r="K25" t="n">
-        <v>5.007</v>
+        <v>5.057</v>
       </c>
       <c r="L25" t="n">
-        <v>-4.152</v>
+        <v>-4.134</v>
       </c>
       <c r="M25" t="n">
-        <v>19.956</v>
+        <v>20.021</v>
       </c>
     </row>
     <row r="26">
@@ -3113,31 +3113,31 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.672</v>
+        <v>2.667</v>
       </c>
       <c r="F26" t="n">
-        <v>0.842</v>
+        <v>0.84</v>
       </c>
       <c r="G26" t="n">
-        <v>0.488</v>
+        <v>0.573</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1507</v>
+        <v>0.1404</v>
       </c>
       <c r="I26" t="n">
-        <v>20.61</v>
+        <v>20.39</v>
       </c>
       <c r="J26" t="n">
-        <v>318.9</v>
+        <v>318.4</v>
       </c>
       <c r="K26" t="n">
-        <v>6.236</v>
+        <v>6.335</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.419</v>
+        <v>-2.384</v>
       </c>
       <c r="M26" t="n">
-        <v>22.231</v>
+        <v>22.379</v>
       </c>
     </row>
     <row r="27">
@@ -3158,31 +3158,31 @@
         <v>-1</v>
       </c>
       <c r="E27" t="n">
-        <v>2.47</v>
+        <v>2.455</v>
       </c>
       <c r="F27" t="n">
-        <v>0.903</v>
+        <v>0.888</v>
       </c>
       <c r="G27" t="n">
-        <v>0.526</v>
+        <v>0.553</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1563</v>
+        <v>0.1495</v>
       </c>
       <c r="I27" t="n">
-        <v>23.98</v>
+        <v>24.14</v>
       </c>
       <c r="J27" t="n">
-        <v>326.7</v>
+        <v>326.2</v>
       </c>
       <c r="K27" t="n">
-        <v>6.266</v>
+        <v>6.234</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.408</v>
+        <v>-2.419</v>
       </c>
       <c r="M27" t="n">
-        <v>22.375</v>
+        <v>22.299</v>
       </c>
     </row>
     <row r="28">
@@ -3878,31 +3878,31 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>2.445</v>
+        <v>2.592</v>
       </c>
       <c r="F43" t="n">
-        <v>0.85</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>0.511</v>
+        <v>0.442</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1276</v>
+        <v>0.1058</v>
       </c>
       <c r="I43" t="n">
-        <v>20.98</v>
+        <v>21.42</v>
       </c>
       <c r="J43" t="n">
-        <v>313.1</v>
+        <v>329.5</v>
       </c>
       <c r="K43" t="n">
-        <v>5.933</v>
+        <v>5.741</v>
       </c>
       <c r="L43" t="n">
-        <v>-2.523</v>
+        <v>-2.59</v>
       </c>
       <c r="M43" t="n">
-        <v>21.637</v>
+        <v>21.104</v>
       </c>
     </row>
     <row r="44">
@@ -3923,31 +3923,31 @@
         <v>-1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.399</v>
+        <v>2.282</v>
       </c>
       <c r="F44" t="n">
-        <v>0.85</v>
+        <v>0.731</v>
       </c>
       <c r="G44" t="n">
-        <v>0.511</v>
+        <v>0.391</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1276</v>
+        <v>0.1041</v>
       </c>
       <c r="I44" t="n">
-        <v>22.91</v>
+        <v>21.6</v>
       </c>
       <c r="J44" t="n">
-        <v>325.2</v>
+        <v>340.7</v>
       </c>
       <c r="K44" t="n">
-        <v>5.887</v>
+        <v>5.151</v>
       </c>
       <c r="L44" t="n">
-        <v>-2.539</v>
+        <v>-4.102</v>
       </c>
       <c r="M44" t="n">
-        <v>21.569</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="45">
@@ -4598,31 +4598,31 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.194</v>
+        <v>2.334</v>
       </c>
       <c r="F59" t="n">
-        <v>0.824</v>
+        <v>0.783</v>
       </c>
       <c r="G59" t="n">
-        <v>0.526</v>
+        <v>0.503</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1562</v>
+        <v>0.1231</v>
       </c>
       <c r="I59" t="n">
-        <v>24.68</v>
+        <v>25.4</v>
       </c>
       <c r="J59" t="n">
-        <v>348.6</v>
+        <v>357.9</v>
       </c>
       <c r="K59" t="n">
-        <v>5.831</v>
+        <v>5.645</v>
       </c>
       <c r="L59" t="n">
-        <v>-2.559</v>
+        <v>-3.931</v>
       </c>
       <c r="M59" t="n">
-        <v>22.131</v>
+        <v>21.578</v>
       </c>
     </row>
     <row r="60">
@@ -4688,31 +4688,31 @@
         <v>-1</v>
       </c>
       <c r="E61" t="n">
-        <v>2.155</v>
+        <v>2.012</v>
       </c>
       <c r="F61" t="n">
-        <v>0.824</v>
+        <v>0.67</v>
       </c>
       <c r="G61" t="n">
-        <v>0.526</v>
+        <v>0.414</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1562</v>
+        <v>0.1139</v>
       </c>
       <c r="I61" t="n">
-        <v>25.96</v>
+        <v>26.62</v>
       </c>
       <c r="J61" t="n">
-        <v>359.2</v>
+        <v>368</v>
       </c>
       <c r="K61" t="n">
-        <v>5.792</v>
+        <v>4.863</v>
       </c>
       <c r="L61" t="n">
-        <v>-3.88</v>
+        <v>-4.202</v>
       </c>
       <c r="M61" t="n">
-        <v>22.072</v>
+        <v>20.139</v>
       </c>
     </row>
     <row r="62">
@@ -4871,7 +4871,7 @@
         <v>1.772</v>
       </c>
       <c r="F65" t="n">
-        <v>0.653</v>
+        <v>0.655</v>
       </c>
       <c r="G65" t="n">
         <v>0.325</v>
@@ -4886,13 +4886,13 @@
         <v>356.9</v>
       </c>
       <c r="K65" t="n">
-        <v>4.348</v>
+        <v>4.352</v>
       </c>
       <c r="L65" t="n">
-        <v>-4.38</v>
+        <v>-4.378</v>
       </c>
       <c r="M65" t="n">
-        <v>19.145</v>
+        <v>19.159</v>
       </c>
     </row>
     <row r="66">
@@ -5096,7 +5096,7 @@
         <v>2.036</v>
       </c>
       <c r="F70" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G70" t="n">
         <v>0.361</v>
@@ -5111,13 +5111,13 @@
         <v>345.7</v>
       </c>
       <c r="K70" t="n">
-        <v>4.694</v>
+        <v>4.696</v>
       </c>
       <c r="L70" t="n">
-        <v>-4.26</v>
+        <v>-4.259</v>
       </c>
       <c r="M70" t="n">
-        <v>19.287</v>
+        <v>19.288</v>
       </c>
     </row>
     <row r="71">
@@ -5498,31 +5498,31 @@
         <v>-1</v>
       </c>
       <c r="E79" t="n">
-        <v>2.375</v>
+        <v>2.249</v>
       </c>
       <c r="F79" t="n">
-        <v>0.863</v>
+        <v>0.717</v>
       </c>
       <c r="G79" t="n">
-        <v>0.549</v>
+        <v>0.384</v>
       </c>
       <c r="H79" t="n">
-        <v>0.126</v>
+        <v>0.1001</v>
       </c>
       <c r="I79" t="n">
-        <v>23.16</v>
+        <v>22.88</v>
       </c>
       <c r="J79" t="n">
-        <v>332.6</v>
+        <v>346.6</v>
       </c>
       <c r="K79" t="n">
-        <v>5.955</v>
+        <v>5.052</v>
       </c>
       <c r="L79" t="n">
-        <v>-2.516</v>
+        <v>-4.136</v>
       </c>
       <c r="M79" t="n">
-        <v>21.699</v>
+        <v>19.918</v>
       </c>
     </row>
     <row r="80">
@@ -5588,31 +5588,31 @@
         <v>-1</v>
       </c>
       <c r="E81" t="n">
-        <v>2.503</v>
+        <v>2.623</v>
       </c>
       <c r="F81" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.747</v>
       </c>
       <c r="G81" t="n">
-        <v>0.57</v>
+        <v>0.551</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1251</v>
+        <v>0.0987</v>
       </c>
       <c r="I81" t="n">
-        <v>24.79</v>
+        <v>24.8</v>
       </c>
       <c r="J81" t="n">
-        <v>341.5</v>
+        <v>352.9</v>
       </c>
       <c r="K81" t="n">
-        <v>6.016</v>
+        <v>5.811</v>
       </c>
       <c r="L81" t="n">
-        <v>-3.802</v>
+        <v>-3.873</v>
       </c>
       <c r="M81" t="n">
-        <v>21.774</v>
+        <v>21.191</v>
       </c>
     </row>
     <row r="82">
@@ -6038,31 +6038,31 @@
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>2.524</v>
+        <v>2.663</v>
       </c>
       <c r="F91" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.761</v>
       </c>
       <c r="G91" t="n">
-        <v>0.57</v>
+        <v>0.551</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1251</v>
+        <v>0.0987</v>
       </c>
       <c r="I91" t="n">
-        <v>23.2</v>
+        <v>23.82</v>
       </c>
       <c r="J91" t="n">
-        <v>330.3</v>
+        <v>341.2</v>
       </c>
       <c r="K91" t="n">
-        <v>6.037</v>
+        <v>5.879</v>
       </c>
       <c r="L91" t="n">
-        <v>-2.487</v>
+        <v>-3.85</v>
       </c>
       <c r="M91" t="n">
-        <v>21.808</v>
+        <v>21.299</v>
       </c>
     </row>
     <row r="92">
@@ -6173,31 +6173,31 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>2.435</v>
+        <v>2.55</v>
       </c>
       <c r="F94" t="n">
-        <v>0.856</v>
+        <v>0.824</v>
       </c>
       <c r="G94" t="n">
-        <v>0.446</v>
+        <v>0.452</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1706</v>
+        <v>0.1244</v>
       </c>
       <c r="I94" t="n">
-        <v>22.43</v>
+        <v>23.76</v>
       </c>
       <c r="J94" t="n">
-        <v>331.1</v>
+        <v>347</v>
       </c>
       <c r="K94" t="n">
-        <v>6.063</v>
+        <v>5.848</v>
       </c>
       <c r="L94" t="n">
-        <v>-2.478</v>
+        <v>-2.553</v>
       </c>
       <c r="M94" t="n">
-        <v>22.536</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="95">
@@ -6578,31 +6578,31 @@
         <v>-1</v>
       </c>
       <c r="E103" t="n">
-        <v>2.369</v>
+        <v>2.483</v>
       </c>
       <c r="F103" t="n">
-        <v>0.856</v>
+        <v>0.789</v>
       </c>
       <c r="G103" t="n">
-        <v>0.446</v>
+        <v>0.452</v>
       </c>
       <c r="H103" t="n">
-        <v>0.1706</v>
+        <v>0.1244</v>
       </c>
       <c r="I103" t="n">
-        <v>24.58</v>
+        <v>25.36</v>
       </c>
       <c r="J103" t="n">
-        <v>345.1</v>
+        <v>360.8</v>
       </c>
       <c r="K103" t="n">
-        <v>5.997</v>
+        <v>5.711</v>
       </c>
       <c r="L103" t="n">
-        <v>-2.501</v>
+        <v>-3.908</v>
       </c>
       <c r="M103" t="n">
-        <v>22.435</v>
+        <v>21.64</v>
       </c>
     </row>
     <row r="104">
@@ -7076,7 +7076,7 @@
         <v>1.723</v>
       </c>
       <c r="F114" t="n">
-        <v>0.586</v>
+        <v>0.587</v>
       </c>
       <c r="G114" t="n">
         <v>0.32</v>
@@ -7091,13 +7091,13 @@
         <v>361</v>
       </c>
       <c r="K114" t="n">
-        <v>4.071</v>
+        <v>4.073</v>
       </c>
       <c r="L114" t="n">
-        <v>-4.476</v>
+        <v>-4.475</v>
       </c>
       <c r="M114" t="n">
-        <v>16.228</v>
+        <v>16.242</v>
       </c>
     </row>
     <row r="115">
@@ -7346,7 +7346,7 @@
         <v>2.09</v>
       </c>
       <c r="F120" t="n">
-        <v>0.758</v>
+        <v>0.76</v>
       </c>
       <c r="G120" t="n">
         <v>0.42</v>
@@ -7361,13 +7361,13 @@
         <v>328.2</v>
       </c>
       <c r="K120" t="n">
-        <v>5.285</v>
+        <v>5.289</v>
       </c>
       <c r="L120" t="n">
-        <v>-2.748</v>
+        <v>-2.746</v>
       </c>
       <c r="M120" t="n">
-        <v>20.657</v>
+        <v>20.658</v>
       </c>
     </row>
     <row r="121">
@@ -7973,31 +7973,31 @@
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>2.689</v>
+        <v>2.543</v>
       </c>
       <c r="F134" t="n">
-        <v>0.858</v>
+        <v>0.708</v>
       </c>
       <c r="G134" t="n">
-        <v>0.583</v>
+        <v>0.428</v>
       </c>
       <c r="H134" t="n">
-        <v>0.1087</v>
+        <v>0.1006</v>
       </c>
       <c r="I134" t="n">
-        <v>22.74</v>
+        <v>22.99</v>
       </c>
       <c r="J134" t="n">
-        <v>327.5</v>
+        <v>333.4</v>
       </c>
       <c r="K134" t="n">
-        <v>6.223</v>
+        <v>5.419</v>
       </c>
       <c r="L134" t="n">
-        <v>-3.731</v>
+        <v>-4.009</v>
       </c>
       <c r="M134" t="n">
-        <v>21.555</v>
+        <v>20.136</v>
       </c>
     </row>
     <row r="135">
@@ -8288,31 +8288,31 @@
         <v>-1</v>
       </c>
       <c r="E141" t="n">
-        <v>2.637</v>
+        <v>2.479</v>
       </c>
       <c r="F141" t="n">
-        <v>0.858</v>
+        <v>0.711</v>
       </c>
       <c r="G141" t="n">
-        <v>0.583</v>
+        <v>0.428</v>
       </c>
       <c r="H141" t="n">
-        <v>0.1087</v>
+        <v>0.1006</v>
       </c>
       <c r="I141" t="n">
-        <v>23.52</v>
+        <v>23.43</v>
       </c>
       <c r="J141" t="n">
-        <v>337.4</v>
+        <v>343.2</v>
       </c>
       <c r="K141" t="n">
-        <v>6.171</v>
+        <v>5.361</v>
       </c>
       <c r="L141" t="n">
-        <v>-3.749</v>
+        <v>-4.029</v>
       </c>
       <c r="M141" t="n">
-        <v>21.485</v>
+        <v>20.063</v>
       </c>
     </row>
     <row r="142">
@@ -8693,31 +8693,31 @@
         <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>2.365</v>
+        <v>2.305</v>
       </c>
       <c r="F150" t="n">
-        <v>0.841</v>
+        <v>0.701</v>
       </c>
       <c r="G150" t="n">
-        <v>0.472</v>
+        <v>0.411</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1043</v>
+        <v>0.0934</v>
       </c>
       <c r="I150" t="n">
-        <v>22.32</v>
+        <v>21.66</v>
       </c>
       <c r="J150" t="n">
-        <v>316.5</v>
+        <v>330.2</v>
       </c>
       <c r="K150" t="n">
-        <v>5.617</v>
+        <v>5.089</v>
       </c>
       <c r="L150" t="n">
-        <v>-2.633</v>
+        <v>-2.816</v>
       </c>
       <c r="M150" t="n">
-        <v>20.939</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="151">
@@ -9323,31 +9323,31 @@
         <v>1</v>
       </c>
       <c r="E164" t="n">
-        <v>2.554</v>
+        <v>2.696</v>
       </c>
       <c r="F164" t="n">
-        <v>0.831</v>
+        <v>0.778</v>
       </c>
       <c r="G164" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="H164" t="n">
-        <v>0.1809</v>
+        <v>0.1375</v>
       </c>
       <c r="I164" t="n">
-        <v>20.58</v>
+        <v>21.49</v>
       </c>
       <c r="J164" t="n">
-        <v>309.5</v>
+        <v>325.8</v>
       </c>
       <c r="K164" t="n">
-        <v>6.401</v>
+        <v>6.057</v>
       </c>
       <c r="L164" t="n">
-        <v>-2.361</v>
+        <v>-2.481</v>
       </c>
       <c r="M164" t="n">
-        <v>22.727</v>
+        <v>21.854</v>
       </c>
     </row>
     <row r="165">
@@ -9728,31 +9728,31 @@
         <v>-1</v>
       </c>
       <c r="E173" t="n">
-        <v>2.332</v>
+        <v>2.212</v>
       </c>
       <c r="F173" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="G173" t="n">
-        <v>0.483</v>
+        <v>0.399</v>
       </c>
       <c r="H173" t="n">
-        <v>0.103</v>
+        <v>0.0925</v>
       </c>
       <c r="I173" t="n">
-        <v>24.29</v>
+        <v>24.81</v>
       </c>
       <c r="J173" t="n">
-        <v>344.1</v>
+        <v>355.6</v>
       </c>
       <c r="K173" t="n">
-        <v>5.538</v>
+        <v>4.913</v>
       </c>
       <c r="L173" t="n">
-        <v>-3.968</v>
+        <v>-4.184</v>
       </c>
       <c r="M173" t="n">
-        <v>20.82</v>
+        <v>19.631</v>
       </c>
     </row>
     <row r="174">
@@ -10358,31 +10358,31 @@
         <v>-1</v>
       </c>
       <c r="E187" t="n">
-        <v>2.41</v>
+        <v>2.51</v>
       </c>
       <c r="F187" t="n">
-        <v>0.959</v>
+        <v>0.859</v>
       </c>
       <c r="G187" t="n">
-        <v>0.574</v>
+        <v>0.533</v>
       </c>
       <c r="H187" t="n">
-        <v>0.1461</v>
+        <v>0.1132</v>
       </c>
       <c r="I187" t="n">
-        <v>20.76</v>
+        <v>20.01</v>
       </c>
       <c r="J187" t="n">
-        <v>319.2</v>
+        <v>341.8</v>
       </c>
       <c r="K187" t="n">
-        <v>6.353</v>
+        <v>5.973</v>
       </c>
       <c r="L187" t="n">
-        <v>-2.378</v>
+        <v>-3.817</v>
       </c>
       <c r="M187" t="n">
-        <v>22.49</v>
+        <v>21.611</v>
       </c>
     </row>
     <row r="188">
@@ -10856,7 +10856,7 @@
         <v>1.787</v>
       </c>
       <c r="F198" t="n">
-        <v>0.743</v>
+        <v>0.745</v>
       </c>
       <c r="G198" t="n">
         <v>0.347</v>
@@ -10871,13 +10871,13 @@
         <v>338.6</v>
       </c>
       <c r="K198" t="n">
-        <v>4.499</v>
+        <v>4.503</v>
       </c>
       <c r="L198" t="n">
-        <v>-4.328</v>
+        <v>-4.326</v>
       </c>
       <c r="M198" t="n">
-        <v>18.954</v>
+        <v>18.968</v>
       </c>
     </row>
     <row r="199">
@@ -11846,7 +11846,7 @@
         <v>2.139</v>
       </c>
       <c r="F220" t="n">
-        <v>0.711</v>
+        <v>0.712</v>
       </c>
       <c r="G220" t="n">
         <v>0.35</v>
@@ -11861,13 +11861,13 @@
         <v>322.7</v>
       </c>
       <c r="K220" t="n">
-        <v>4.745</v>
+        <v>4.747</v>
       </c>
       <c r="L220" t="n">
         <v>-4.242</v>
       </c>
       <c r="M220" t="n">
-        <v>18.894</v>
+        <v>18.895</v>
       </c>
     </row>
     <row r="221">
@@ -11936,7 +11936,7 @@
         <v>2.254</v>
       </c>
       <c r="F222" t="n">
-        <v>0.711</v>
+        <v>0.712</v>
       </c>
       <c r="G222" t="n">
         <v>0.35</v>
@@ -11951,13 +11951,13 @@
         <v>309.9</v>
       </c>
       <c r="K222" t="n">
-        <v>4.86</v>
+        <v>4.862</v>
       </c>
       <c r="L222" t="n">
-        <v>-2.895</v>
+        <v>-2.894</v>
       </c>
       <c r="M222" t="n">
-        <v>19.058</v>
+        <v>19.059</v>
       </c>
     </row>
     <row r="223">
@@ -12158,31 +12158,31 @@
         <v>-1</v>
       </c>
       <c r="E227" t="n">
-        <v>2.402</v>
+        <v>2.552</v>
       </c>
       <c r="F227" t="n">
-        <v>0.895</v>
+        <v>0.829</v>
       </c>
       <c r="G227" t="n">
-        <v>0.666</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H227" t="n">
-        <v>0.1135</v>
+        <v>0.0927</v>
       </c>
       <c r="I227" t="n">
-        <v>23.94</v>
+        <v>24.33</v>
       </c>
       <c r="J227" t="n">
-        <v>326.9</v>
+        <v>343.8</v>
       </c>
       <c r="K227" t="n">
-        <v>6.205</v>
+        <v>5.882</v>
       </c>
       <c r="L227" t="n">
-        <v>-2.429</v>
+        <v>-3.849</v>
       </c>
       <c r="M227" t="n">
-        <v>22.053</v>
+        <v>21.291</v>
       </c>
     </row>
     <row r="228">
@@ -12791,7 +12791,7 @@
         <v>2.168</v>
       </c>
       <c r="F241" t="n">
-        <v>0.718</v>
+        <v>0.72</v>
       </c>
       <c r="G241" t="n">
         <v>0.419</v>
@@ -12806,13 +12806,13 @@
         <v>333.9</v>
       </c>
       <c r="K241" t="n">
-        <v>4.993</v>
+        <v>4.997</v>
       </c>
       <c r="L241" t="n">
-        <v>-2.849</v>
+        <v>-2.847</v>
       </c>
       <c r="M241" t="n">
-        <v>19.795</v>
+        <v>19.796</v>
       </c>
     </row>
     <row r="242">
@@ -13742,22 +13742,22 @@
         <v>0.526</v>
       </c>
       <c r="H262" t="n">
-        <v>0.1052</v>
+        <v>0.1045</v>
       </c>
       <c r="I262" t="n">
-        <v>23.31</v>
+        <v>23.26</v>
       </c>
       <c r="J262" t="n">
         <v>339.4</v>
       </c>
       <c r="K262" t="n">
-        <v>5.756</v>
+        <v>5.752</v>
       </c>
       <c r="L262" t="n">
-        <v>-2.585</v>
+        <v>-2.586</v>
       </c>
       <c r="M262" t="n">
-        <v>21.599</v>
+        <v>21.586</v>
       </c>
     </row>
     <row r="263">
@@ -13787,10 +13787,10 @@
         <v>0.521</v>
       </c>
       <c r="H263" t="n">
-        <v>0.0854</v>
+        <v>0.0853</v>
       </c>
       <c r="I263" t="n">
-        <v>21.98</v>
+        <v>21.84</v>
       </c>
       <c r="J263" t="n">
         <v>347.4</v>
@@ -13832,22 +13832,22 @@
         <v>0.549</v>
       </c>
       <c r="H264" t="n">
-        <v>0.0803</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="I264" t="n">
-        <v>22.61</v>
+        <v>22.47</v>
       </c>
       <c r="J264" t="n">
         <v>370.8</v>
       </c>
       <c r="K264" t="n">
-        <v>5.106</v>
+        <v>5.105</v>
       </c>
       <c r="L264" t="n">
-        <v>-4.117</v>
+        <v>-4.118</v>
       </c>
       <c r="M264" t="n">
-        <v>20.336</v>
+        <v>20.332</v>
       </c>
     </row>
     <row r="265">
@@ -13877,22 +13877,22 @@
         <v>0.498</v>
       </c>
       <c r="H265" t="n">
-        <v>0.0988</v>
+        <v>0.0983</v>
       </c>
       <c r="I265" t="n">
-        <v>20.62</v>
+        <v>20.57</v>
       </c>
       <c r="J265" t="n">
         <v>325.2</v>
       </c>
       <c r="K265" t="n">
-        <v>5.629</v>
+        <v>5.626</v>
       </c>
       <c r="L265" t="n">
-        <v>-2.629</v>
+        <v>-2.63</v>
       </c>
       <c r="M265" t="n">
-        <v>21.332</v>
+        <v>21.323</v>
       </c>
     </row>
     <row r="266">
@@ -13922,22 +13922,22 @@
         <v>0.525</v>
       </c>
       <c r="H266" t="n">
-        <v>0.075</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="I266" t="n">
-        <v>23.45</v>
+        <v>23.34</v>
       </c>
       <c r="J266" t="n">
         <v>356.4</v>
       </c>
       <c r="K266" t="n">
-        <v>5.418</v>
+        <v>5.417</v>
       </c>
       <c r="L266" t="n">
-        <v>-4.009</v>
+        <v>-4.01</v>
       </c>
       <c r="M266" t="n">
-        <v>20.784</v>
+        <v>20.783</v>
       </c>
     </row>
     <row r="267">
@@ -13967,22 +13967,22 @@
         <v>0.577</v>
       </c>
       <c r="H267" t="n">
-        <v>0.0961</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="I267" t="n">
-        <v>22.79</v>
+        <v>22.72</v>
       </c>
       <c r="J267" t="n">
         <v>339.3</v>
       </c>
       <c r="K267" t="n">
-        <v>5.788</v>
+        <v>5.785</v>
       </c>
       <c r="L267" t="n">
-        <v>-2.574</v>
+        <v>-2.575</v>
       </c>
       <c r="M267" t="n">
-        <v>21.621</v>
+        <v>21.616</v>
       </c>
     </row>
     <row r="268">
@@ -14012,22 +14012,22 @@
         <v>0.5679999999999999</v>
       </c>
       <c r="H268" t="n">
-        <v>0.0891</v>
+        <v>0.089</v>
       </c>
       <c r="I268" t="n">
-        <v>20.83</v>
+        <v>20.77</v>
       </c>
       <c r="J268" t="n">
         <v>339.4</v>
       </c>
       <c r="K268" t="n">
-        <v>5.573</v>
+        <v>5.572</v>
       </c>
       <c r="L268" t="n">
         <v>-2.648</v>
       </c>
       <c r="M268" t="n">
-        <v>21.174</v>
+        <v>21.173</v>
       </c>
     </row>
     <row r="269">
@@ -14057,10 +14057,10 @@
         <v>0.679</v>
       </c>
       <c r="H269" t="n">
-        <v>0.1112</v>
+        <v>0.1111</v>
       </c>
       <c r="I269" t="n">
-        <v>20.32</v>
+        <v>20.16</v>
       </c>
       <c r="J269" t="n">
         <v>320.8</v>
@@ -14102,22 +14102,22 @@
         <v>0.534</v>
       </c>
       <c r="H270" t="n">
-        <v>0.0886</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="I270" t="n">
-        <v>23.98</v>
+        <v>23.94</v>
       </c>
       <c r="J270" t="n">
         <v>354.8</v>
       </c>
       <c r="K270" t="n">
-        <v>5.616</v>
+        <v>5.614</v>
       </c>
       <c r="L270" t="n">
-        <v>-3.941</v>
+        <v>-3.942</v>
       </c>
       <c r="M270" t="n">
-        <v>21.239</v>
+        <v>21.235</v>
       </c>
     </row>
     <row r="271">
@@ -14147,22 +14147,22 @@
         <v>0.549</v>
       </c>
       <c r="H271" t="n">
-        <v>0.0803</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="I271" t="n">
-        <v>20.83</v>
+        <v>20.66</v>
       </c>
       <c r="J271" t="n">
         <v>360.6</v>
       </c>
       <c r="K271" t="n">
-        <v>5.193</v>
+        <v>5.192</v>
       </c>
       <c r="L271" t="n">
-        <v>-4.087</v>
+        <v>-4.088</v>
       </c>
       <c r="M271" t="n">
-        <v>20.477</v>
+        <v>20.473</v>
       </c>
     </row>
     <row r="272">
@@ -14192,19 +14192,19 @@
         <v>0.664</v>
       </c>
       <c r="H272" t="n">
-        <v>0.1055</v>
+        <v>0.1056</v>
       </c>
       <c r="I272" t="n">
-        <v>21.2</v>
+        <v>21.09</v>
       </c>
       <c r="J272" t="n">
         <v>339.4</v>
       </c>
       <c r="K272" t="n">
-        <v>5.886</v>
+        <v>5.887</v>
       </c>
       <c r="L272" t="n">
-        <v>-2.54</v>
+        <v>-2.539</v>
       </c>
       <c r="M272" t="n">
         <v>21.916</v>
@@ -14237,22 +14237,22 @@
         <v>0.594</v>
       </c>
       <c r="H273" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0804</v>
       </c>
       <c r="I273" t="n">
-        <v>23.16</v>
+        <v>23.02</v>
       </c>
       <c r="J273" t="n">
         <v>353.5</v>
       </c>
       <c r="K273" t="n">
-        <v>5.771</v>
+        <v>5.769</v>
       </c>
       <c r="L273" t="n">
         <v>-2.58</v>
       </c>
       <c r="M273" t="n">
-        <v>21.437</v>
+        <v>21.428</v>
       </c>
     </row>
     <row r="274">
@@ -14282,22 +14282,22 @@
         <v>0.488</v>
       </c>
       <c r="H274" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="I274" t="n">
-        <v>21.35</v>
+        <v>21.27</v>
       </c>
       <c r="J274" t="n">
         <v>344.3</v>
       </c>
       <c r="K274" t="n">
-        <v>5.079</v>
+        <v>5.078</v>
       </c>
       <c r="L274" t="n">
         <v>-2.819</v>
       </c>
       <c r="M274" t="n">
-        <v>20.224</v>
+        <v>20.22</v>
       </c>
     </row>
     <row r="275">
@@ -14327,10 +14327,10 @@
         <v>0.513</v>
       </c>
       <c r="H275" t="n">
-        <v>0.1251</v>
+        <v>0.1252</v>
       </c>
       <c r="I275" t="n">
-        <v>20.55</v>
+        <v>20.66</v>
       </c>
       <c r="J275" t="n">
         <v>312.1</v>
@@ -14375,7 +14375,7 @@
         <v>0.1119</v>
       </c>
       <c r="I276" t="n">
-        <v>21.14</v>
+        <v>21.28</v>
       </c>
       <c r="J276" t="n">
         <v>320.9</v>
@@ -14417,10 +14417,10 @@
         <v>0.495</v>
       </c>
       <c r="H277" t="n">
-        <v>0.0998</v>
+        <v>0.0999</v>
       </c>
       <c r="I277" t="n">
-        <v>20.95</v>
+        <v>21.49</v>
       </c>
       <c r="J277" t="n">
         <v>338.7</v>
@@ -14465,7 +14465,7 @@
         <v>0.1353</v>
       </c>
       <c r="I278" t="n">
-        <v>21.13</v>
+        <v>21.8</v>
       </c>
       <c r="J278" t="n">
         <v>348</v>
@@ -14510,7 +14510,7 @@
         <v>0.1032</v>
       </c>
       <c r="I279" t="n">
-        <v>21</v>
+        <v>21.06</v>
       </c>
       <c r="J279" t="n">
         <v>330.5</v>
@@ -14552,22 +14552,22 @@
         <v>0.52</v>
       </c>
       <c r="H280" t="n">
-        <v>0.1192</v>
+        <v>0.1193</v>
       </c>
       <c r="I280" t="n">
-        <v>21.35</v>
+        <v>21.94</v>
       </c>
       <c r="J280" t="n">
         <v>352.3</v>
       </c>
       <c r="K280" t="n">
-        <v>5.175</v>
+        <v>5.176</v>
       </c>
       <c r="L280" t="n">
-        <v>-4.094</v>
+        <v>-4.093</v>
       </c>
       <c r="M280" t="n">
-        <v>20.392</v>
+        <v>20.397</v>
       </c>
     </row>
     <row r="281">
@@ -14600,19 +14600,19 @@
         <v>0.125</v>
       </c>
       <c r="I281" t="n">
-        <v>19.93</v>
+        <v>20.43</v>
       </c>
       <c r="J281" t="n">
         <v>330.6</v>
       </c>
       <c r="K281" t="n">
-        <v>6.642</v>
+        <v>5.642</v>
       </c>
       <c r="L281" t="n">
-        <v>-2.278</v>
+        <v>-2.624</v>
       </c>
       <c r="M281" t="n">
-        <v>21.497</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="282">
@@ -14642,16 +14642,16 @@
         <v>0.427</v>
       </c>
       <c r="H282" t="n">
-        <v>0.144</v>
+        <v>0.1441</v>
       </c>
       <c r="I282" t="n">
-        <v>20.12</v>
+        <v>20.22</v>
       </c>
       <c r="J282" t="n">
         <v>310.8</v>
       </c>
       <c r="K282" t="n">
-        <v>5.781</v>
+        <v>5.782</v>
       </c>
       <c r="L282" t="n">
         <v>-2.576</v>
@@ -14678,31 +14678,31 @@
         <v>1</v>
       </c>
       <c r="E283" t="n">
-        <v>2.416</v>
+        <v>2.345</v>
       </c>
       <c r="F283" t="n">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="G283" t="n">
-        <v>0.583</v>
+        <v>0.471</v>
       </c>
       <c r="H283" t="n">
-        <v>0.1559</v>
+        <v>0.1149</v>
       </c>
       <c r="I283" t="n">
-        <v>20.31</v>
+        <v>20.7</v>
       </c>
       <c r="J283" t="n">
-        <v>309.1</v>
+        <v>329.4</v>
       </c>
       <c r="K283" t="n">
-        <v>6.237</v>
+        <v>5.436</v>
       </c>
       <c r="L283" t="n">
-        <v>-2.418</v>
+        <v>-2.695</v>
       </c>
       <c r="M283" t="n">
-        <v>22.354</v>
+        <v>20.721</v>
       </c>
     </row>
     <row r="284">
@@ -14732,16 +14732,16 @@
         <v>0.583</v>
       </c>
       <c r="H284" t="n">
-        <v>0.1559</v>
+        <v>0.156</v>
       </c>
       <c r="I284" t="n">
-        <v>22.31</v>
+        <v>22.48</v>
       </c>
       <c r="J284" t="n">
         <v>322.1</v>
       </c>
       <c r="K284" t="n">
-        <v>6.168</v>
+        <v>6.169</v>
       </c>
       <c r="L284" t="n">
         <v>-2.442</v>
@@ -14780,7 +14780,7 @@
         <v>0.1119</v>
       </c>
       <c r="I285" t="n">
-        <v>21.78</v>
+        <v>22.33</v>
       </c>
       <c r="J285" t="n">
         <v>337.1</v>
@@ -14822,19 +14822,19 @@
         <v>0.471</v>
       </c>
       <c r="H286" t="n">
-        <v>0.1324</v>
+        <v>0.1325</v>
       </c>
       <c r="I286" t="n">
-        <v>20.79</v>
+        <v>20.94</v>
       </c>
       <c r="J286" t="n">
         <v>316.3</v>
       </c>
       <c r="K286" t="n">
-        <v>5.964</v>
+        <v>5.965</v>
       </c>
       <c r="L286" t="n">
-        <v>-2.513</v>
+        <v>-2.512</v>
       </c>
       <c r="M286" t="n">
         <v>21.705</v>
@@ -14870,7 +14870,7 @@
         <v>0.1353</v>
       </c>
       <c r="I287" t="n">
-        <v>20.59</v>
+        <v>20.73</v>
       </c>
       <c r="J287" t="n">
         <v>338.7</v>
@@ -14903,31 +14903,31 @@
         <v>1</v>
       </c>
       <c r="E288" t="n">
-        <v>2.525</v>
+        <v>2.302</v>
       </c>
       <c r="F288" t="n">
-        <v>0.834</v>
+        <v>0.67</v>
       </c>
       <c r="G288" t="n">
-        <v>0.526</v>
+        <v>0.399</v>
       </c>
       <c r="H288" t="n">
-        <v>0.1422</v>
+        <v>0.1104</v>
       </c>
       <c r="I288" t="n">
-        <v>23.03</v>
+        <v>24.74</v>
       </c>
       <c r="J288" t="n">
-        <v>310.9</v>
+        <v>333.4</v>
       </c>
       <c r="K288" t="n">
-        <v>6.098</v>
+        <v>5.102</v>
       </c>
       <c r="L288" t="n">
-        <v>-2.466</v>
+        <v>-2.811</v>
       </c>
       <c r="M288" t="n">
-        <v>22.007</v>
+        <v>20.07</v>
       </c>
     </row>
     <row r="289">
@@ -14948,31 +14948,31 @@
         <v>-1</v>
       </c>
       <c r="E289" t="n">
-        <v>2.322</v>
+        <v>2.139</v>
       </c>
       <c r="F289" t="n">
-        <v>0.701</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G289" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="H289" t="n">
-        <v>0.1079</v>
+        <v>0.1028</v>
       </c>
       <c r="I289" t="n">
-        <v>25.9</v>
+        <v>26.3</v>
       </c>
       <c r="J289" t="n">
-        <v>351.7</v>
+        <v>355</v>
       </c>
       <c r="K289" t="n">
-        <v>5.269</v>
+        <v>5.018</v>
       </c>
       <c r="L289" t="n">
-        <v>-4.061</v>
+        <v>-4.148</v>
       </c>
       <c r="M289" t="n">
-        <v>18.408</v>
+        <v>17.968</v>
       </c>
     </row>
     <row r="290">
@@ -14993,31 +14993,31 @@
         <v>1</v>
       </c>
       <c r="E290" t="n">
-        <v>2.427</v>
+        <v>2.333</v>
       </c>
       <c r="F290" t="n">
-        <v>0.703</v>
+        <v>0.672</v>
       </c>
       <c r="G290" t="n">
         <v>0.459</v>
       </c>
       <c r="H290" t="n">
-        <v>0.1039</v>
+        <v>0.1007</v>
       </c>
       <c r="I290" t="n">
-        <v>23.71</v>
+        <v>25.76</v>
       </c>
       <c r="J290" t="n">
-        <v>342.3</v>
+        <v>348</v>
       </c>
       <c r="K290" t="n">
-        <v>5.374</v>
+        <v>5.199</v>
       </c>
       <c r="L290" t="n">
-        <v>-4.025</v>
+        <v>-4.085</v>
       </c>
       <c r="M290" t="n">
-        <v>20.504</v>
+        <v>18.235</v>
       </c>
     </row>
     <row r="291">
@@ -15038,31 +15038,31 @@
         <v>1</v>
       </c>
       <c r="E291" t="n">
-        <v>2.206</v>
+        <v>2.081</v>
       </c>
       <c r="F291" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.656</v>
       </c>
       <c r="G291" t="n">
-        <v>0.421</v>
+        <v>0.417</v>
       </c>
       <c r="H291" t="n">
-        <v>0.1028</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="I291" t="n">
-        <v>23.46</v>
+        <v>25.05</v>
       </c>
       <c r="J291" t="n">
-        <v>335.4</v>
+        <v>340.8</v>
       </c>
       <c r="K291" t="n">
-        <v>5.033</v>
+        <v>4.813</v>
       </c>
       <c r="L291" t="n">
-        <v>-2.835</v>
+        <v>-4.219</v>
       </c>
       <c r="M291" t="n">
-        <v>19.948</v>
+        <v>19.541</v>
       </c>
     </row>
     <row r="292">
@@ -15083,31 +15083,31 @@
         <v>1</v>
       </c>
       <c r="E292" t="n">
-        <v>2.525</v>
+        <v>2.432</v>
       </c>
       <c r="F292" t="n">
-        <v>0.834</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G292" t="n">
-        <v>0.526</v>
+        <v>0.505</v>
       </c>
       <c r="H292" t="n">
-        <v>0.1422</v>
+        <v>0.1323</v>
       </c>
       <c r="I292" t="n">
-        <v>23.03</v>
+        <v>24.48</v>
       </c>
       <c r="J292" t="n">
-        <v>310.9</v>
+        <v>321.7</v>
       </c>
       <c r="K292" t="n">
-        <v>6.098</v>
+        <v>5.86</v>
       </c>
       <c r="L292" t="n">
-        <v>-2.466</v>
+        <v>-2.549</v>
       </c>
       <c r="M292" t="n">
-        <v>22.007</v>
+        <v>21.548</v>
       </c>
     </row>
     <row r="293">
@@ -15128,31 +15128,31 @@
         <v>-1</v>
       </c>
       <c r="E293" t="n">
-        <v>2.283</v>
+        <v>2.123</v>
       </c>
       <c r="F293" t="n">
-        <v>0.715</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G293" t="n">
-        <v>0.455</v>
+        <v>0.451</v>
       </c>
       <c r="H293" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="I293" t="n">
-        <v>25.66</v>
+        <v>25.98</v>
       </c>
       <c r="J293" t="n">
-        <v>341.5</v>
+        <v>346.1</v>
       </c>
       <c r="K293" t="n">
-        <v>5.183</v>
+        <v>4.951</v>
       </c>
       <c r="L293" t="n">
-        <v>-4.091</v>
+        <v>-4.171</v>
       </c>
       <c r="M293" t="n">
-        <v>18.154</v>
+        <v>17.757</v>
       </c>
     </row>
     <row r="294">
@@ -15173,31 +15173,31 @@
         <v>-1</v>
       </c>
       <c r="E294" t="n">
-        <v>2.193</v>
+        <v>2.057</v>
       </c>
       <c r="F294" t="n">
-        <v>0.718</v>
+        <v>0.704</v>
       </c>
       <c r="G294" t="n">
-        <v>0.42</v>
+        <v>0.416</v>
       </c>
       <c r="H294" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="I294" t="n">
-        <v>25.83</v>
+        <v>26.02</v>
       </c>
       <c r="J294" t="n">
-        <v>346.4</v>
+        <v>351</v>
       </c>
       <c r="K294" t="n">
-        <v>5.029</v>
+        <v>4.827</v>
       </c>
       <c r="L294" t="n">
-        <v>-4.144</v>
+        <v>-4.214</v>
       </c>
       <c r="M294" t="n">
-        <v>17.911</v>
+        <v>17.553</v>
       </c>
     </row>
     <row r="295">
@@ -15218,31 +15218,31 @@
         <v>1</v>
       </c>
       <c r="E295" t="n">
-        <v>2.513</v>
+        <v>2.385</v>
       </c>
       <c r="F295" t="n">
-        <v>0.86</v>
+        <v>0.841</v>
       </c>
       <c r="G295" t="n">
-        <v>0.448</v>
+        <v>0.443</v>
       </c>
       <c r="H295" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.0961</v>
       </c>
       <c r="I295" t="n">
-        <v>22.27</v>
+        <v>24.43</v>
       </c>
       <c r="J295" t="n">
-        <v>330.2</v>
+        <v>335.6</v>
       </c>
       <c r="K295" t="n">
-        <v>5.712</v>
+        <v>5.53</v>
       </c>
       <c r="L295" t="n">
-        <v>-2.6</v>
+        <v>-2.663</v>
       </c>
       <c r="M295" t="n">
-        <v>21.002</v>
+        <v>20.714</v>
       </c>
     </row>
     <row r="296">
@@ -15263,31 +15263,31 @@
         <v>-1</v>
       </c>
       <c r="E296" t="n">
-        <v>2.484</v>
+        <v>2.396</v>
       </c>
       <c r="F296" t="n">
-        <v>0.834</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G296" t="n">
-        <v>0.526</v>
+        <v>0.505</v>
       </c>
       <c r="H296" t="n">
-        <v>0.1422</v>
+        <v>0.1323</v>
       </c>
       <c r="I296" t="n">
-        <v>24.57</v>
+        <v>25.36</v>
       </c>
       <c r="J296" t="n">
-        <v>325.5</v>
+        <v>335.4</v>
       </c>
       <c r="K296" t="n">
-        <v>6.057</v>
+        <v>5.824</v>
       </c>
       <c r="L296" t="n">
-        <v>-2.481</v>
+        <v>-2.561</v>
       </c>
       <c r="M296" t="n">
-        <v>21.947</v>
+        <v>21.496</v>
       </c>
     </row>
     <row r="297">
@@ -15308,31 +15308,31 @@
         <v>-1</v>
       </c>
       <c r="E297" t="n">
-        <v>2.116</v>
+        <v>1.997</v>
       </c>
       <c r="F297" t="n">
-        <v>0.664</v>
+        <v>0.65</v>
       </c>
       <c r="G297" t="n">
-        <v>0.379</v>
+        <v>0.381</v>
       </c>
       <c r="H297" t="n">
-        <v>0.0999</v>
+        <v>0.0969</v>
       </c>
       <c r="I297" t="n">
-        <v>25.6</v>
+        <v>26.02</v>
       </c>
       <c r="J297" t="n">
-        <v>354</v>
+        <v>359.7</v>
       </c>
       <c r="K297" t="n">
-        <v>4.801</v>
+        <v>4.64</v>
       </c>
       <c r="L297" t="n">
-        <v>-4.223</v>
+        <v>-4.279</v>
       </c>
       <c r="M297" t="n">
-        <v>17.545</v>
+        <v>17.279</v>
       </c>
     </row>
     <row r="298">
@@ -15353,31 +15353,31 @@
         <v>1</v>
       </c>
       <c r="E298" t="n">
-        <v>2.468</v>
+        <v>2.367</v>
       </c>
       <c r="F298" t="n">
-        <v>0.717</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G298" t="n">
-        <v>0.474</v>
+        <v>0.462</v>
       </c>
       <c r="H298" t="n">
-        <v>0.1131</v>
+        <v>0.1076</v>
       </c>
       <c r="I298" t="n">
-        <v>24.62</v>
+        <v>26.57</v>
       </c>
       <c r="J298" t="n">
-        <v>338.6</v>
+        <v>344.4</v>
       </c>
       <c r="K298" t="n">
-        <v>5.529</v>
+        <v>5.309</v>
       </c>
       <c r="L298" t="n">
-        <v>-3.971</v>
+        <v>-4.047</v>
       </c>
       <c r="M298" t="n">
-        <v>20.837</v>
+        <v>18.471</v>
       </c>
     </row>
     <row r="299">
@@ -15398,31 +15398,31 @@
         <v>-1</v>
       </c>
       <c r="E299" t="n">
-        <v>2.429</v>
+        <v>2.277</v>
       </c>
       <c r="F299" t="n">
-        <v>0.706</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="G299" t="n">
         <v>0.418</v>
       </c>
       <c r="H299" t="n">
-        <v>0.1088</v>
+        <v>0.1068</v>
       </c>
       <c r="I299" t="n">
-        <v>24.82</v>
+        <v>26.03</v>
       </c>
       <c r="J299" t="n">
-        <v>341.5</v>
+        <v>346.1</v>
       </c>
       <c r="K299" t="n">
-        <v>5.33</v>
+        <v>5.118</v>
       </c>
       <c r="L299" t="n">
-        <v>-4.04</v>
+        <v>-4.113</v>
       </c>
       <c r="M299" t="n">
-        <v>20.433</v>
+        <v>18.131</v>
       </c>
     </row>
     <row r="300">
@@ -15443,31 +15443,31 @@
         <v>1</v>
       </c>
       <c r="E300" t="n">
-        <v>2.188</v>
+        <v>2.059</v>
       </c>
       <c r="F300" t="n">
-        <v>0.662</v>
+        <v>0.648</v>
       </c>
       <c r="G300" t="n">
-        <v>0.379</v>
+        <v>0.381</v>
       </c>
       <c r="H300" t="n">
-        <v>0.0999</v>
+        <v>0.0969</v>
       </c>
       <c r="I300" t="n">
-        <v>23.78</v>
+        <v>26.14</v>
       </c>
       <c r="J300" t="n">
-        <v>344.9</v>
+        <v>350.7</v>
       </c>
       <c r="K300" t="n">
-        <v>4.869</v>
+        <v>4.698</v>
       </c>
       <c r="L300" t="n">
-        <v>-4.199</v>
+        <v>-4.259</v>
       </c>
       <c r="M300" t="n">
-        <v>19.616</v>
+        <v>17.371</v>
       </c>
     </row>
     <row r="301">
@@ -15851,7 +15851,7 @@
         <v>1.744</v>
       </c>
       <c r="F309" t="n">
-        <v>0.775</v>
+        <v>0.777</v>
       </c>
       <c r="G309" t="n">
         <v>0.41</v>
@@ -15866,13 +15866,13 @@
         <v>349</v>
       </c>
       <c r="K309" t="n">
-        <v>4.761</v>
+        <v>4.765</v>
       </c>
       <c r="L309" t="n">
-        <v>-4.237</v>
+        <v>-4.235</v>
       </c>
       <c r="M309" t="n">
-        <v>19.599</v>
+        <v>19.614</v>
       </c>
     </row>
     <row r="310">
@@ -16568,31 +16568,31 @@
         <v>1</v>
       </c>
       <c r="E325" t="n">
-        <v>2.376</v>
+        <v>2.294</v>
       </c>
       <c r="F325" t="n">
-        <v>0.851</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="G325" t="n">
-        <v>0.552</v>
+        <v>0.427</v>
       </c>
       <c r="H325" t="n">
-        <v>0.1</v>
+        <v>0.0936</v>
       </c>
       <c r="I325" t="n">
-        <v>24.1</v>
+        <v>24.19</v>
       </c>
       <c r="J325" t="n">
-        <v>314.4</v>
+        <v>322.8</v>
       </c>
       <c r="K325" t="n">
-        <v>5.782</v>
+        <v>5.094</v>
       </c>
       <c r="L325" t="n">
-        <v>-2.576</v>
+        <v>-4.122</v>
       </c>
       <c r="M325" t="n">
-        <v>20.831</v>
+        <v>17.631</v>
       </c>
     </row>
     <row r="326">
@@ -17066,7 +17066,7 @@
         <v>2.056</v>
       </c>
       <c r="F336" t="n">
-        <v>0.751</v>
+        <v>0.753</v>
       </c>
       <c r="G336" t="n">
         <v>0.352</v>
@@ -17081,13 +17081,13 @@
         <v>325.4</v>
       </c>
       <c r="K336" t="n">
-        <v>4.808</v>
+        <v>4.812</v>
       </c>
       <c r="L336" t="n">
-        <v>-2.913</v>
+        <v>-2.911</v>
       </c>
       <c r="M336" t="n">
-        <v>19.449</v>
+        <v>19.464</v>
       </c>
     </row>
     <row r="337">
@@ -17648,31 +17648,31 @@
         <v>1</v>
       </c>
       <c r="E349" t="n">
-        <v>2.606</v>
+        <v>2.739</v>
       </c>
       <c r="F349" t="n">
-        <v>0.926</v>
+        <v>0.871</v>
       </c>
       <c r="G349" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.466</v>
       </c>
       <c r="H349" t="n">
-        <v>0.1742</v>
+        <v>0.136</v>
       </c>
       <c r="I349" t="n">
-        <v>20.28</v>
+        <v>21.06</v>
       </c>
       <c r="J349" t="n">
-        <v>305.4</v>
+        <v>320.2</v>
       </c>
       <c r="K349" t="n">
-        <v>6.621</v>
+        <v>6.229</v>
       </c>
       <c r="L349" t="n">
-        <v>-2.285</v>
+        <v>-3.729</v>
       </c>
       <c r="M349" t="n">
-        <v>22.601</v>
+        <v>21.688</v>
       </c>
     </row>
     <row r="350">
@@ -17783,31 +17783,31 @@
         <v>-1</v>
       </c>
       <c r="E352" t="n">
-        <v>2.56</v>
+        <v>2.653</v>
       </c>
       <c r="F352" t="n">
-        <v>0.926</v>
+        <v>0.843</v>
       </c>
       <c r="G352" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.466</v>
       </c>
       <c r="H352" t="n">
-        <v>0.1742</v>
+        <v>0.136</v>
       </c>
       <c r="I352" t="n">
-        <v>22.17</v>
+        <v>22.06</v>
       </c>
       <c r="J352" t="n">
-        <v>315.9</v>
+        <v>331.2</v>
       </c>
       <c r="K352" t="n">
-        <v>6.575</v>
+        <v>6.087</v>
       </c>
       <c r="L352" t="n">
-        <v>-2.301</v>
+        <v>-3.778</v>
       </c>
       <c r="M352" t="n">
-        <v>22.539</v>
+        <v>21.469</v>
       </c>
     </row>
     <row r="353">
@@ -18416,7 +18416,7 @@
         <v>1.747</v>
       </c>
       <c r="F366" t="n">
-        <v>0.645</v>
+        <v>0.646</v>
       </c>
       <c r="G366" t="n">
         <v>0.365</v>
@@ -18431,10 +18431,10 @@
         <v>344</v>
       </c>
       <c r="K366" t="n">
-        <v>4.33</v>
+        <v>4.332</v>
       </c>
       <c r="L366" t="n">
-        <v>-4.386</v>
+        <v>-4.385</v>
       </c>
       <c r="M366" t="n">
         <v>18.727</v>
@@ -18638,31 +18638,31 @@
         <v>1</v>
       </c>
       <c r="E371" t="n">
-        <v>2.254</v>
+        <v>2.13</v>
       </c>
       <c r="F371" t="n">
-        <v>0.824</v>
+        <v>0.671</v>
       </c>
       <c r="G371" t="n">
-        <v>0.532</v>
+        <v>0.393</v>
       </c>
       <c r="H371" t="n">
-        <v>0.1171</v>
+        <v>0.1009</v>
       </c>
       <c r="I371" t="n">
-        <v>20.4</v>
+        <v>20.91</v>
       </c>
       <c r="J371" t="n">
-        <v>318.9</v>
+        <v>335.6</v>
       </c>
       <c r="K371" t="n">
-        <v>5.669</v>
+        <v>4.863</v>
       </c>
       <c r="L371" t="n">
-        <v>-2.615</v>
+        <v>-2.894</v>
       </c>
       <c r="M371" t="n">
-        <v>21.16</v>
+        <v>19.636</v>
       </c>
     </row>
     <row r="372">
@@ -18686,7 +18686,7 @@
         <v>1.864</v>
       </c>
       <c r="F372" t="n">
-        <v>0.643</v>
+        <v>0.644</v>
       </c>
       <c r="G372" t="n">
         <v>0.365</v>
@@ -18701,13 +18701,13 @@
         <v>333.7</v>
       </c>
       <c r="K372" t="n">
-        <v>4.443</v>
+        <v>4.445</v>
       </c>
       <c r="L372" t="n">
-        <v>-3.039</v>
+        <v>-3.038</v>
       </c>
       <c r="M372" t="n">
-        <v>18.89</v>
+        <v>18.904</v>
       </c>
     </row>
     <row r="373">
@@ -19358,31 +19358,31 @@
         <v>-1</v>
       </c>
       <c r="E387" t="n">
-        <v>2.238</v>
+        <v>2.329</v>
       </c>
       <c r="F387" t="n">
-        <v>0.848</v>
+        <v>0.774</v>
       </c>
       <c r="G387" t="n">
-        <v>0.536</v>
+        <v>0.446</v>
       </c>
       <c r="H387" t="n">
-        <v>0.1419</v>
+        <v>0.1139</v>
       </c>
       <c r="I387" t="n">
-        <v>23.5</v>
+        <v>22.97</v>
       </c>
       <c r="J387" t="n">
-        <v>324.2</v>
+        <v>343</v>
       </c>
       <c r="K387" t="n">
-        <v>5.857</v>
+        <v>5.452</v>
       </c>
       <c r="L387" t="n">
-        <v>-2.55</v>
+        <v>-3.998</v>
       </c>
       <c r="M387" t="n">
-        <v>21.658</v>
+        <v>20.73</v>
       </c>
     </row>
     <row r="388">
@@ -20618,31 +20618,31 @@
         <v>-1</v>
       </c>
       <c r="E415" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="F415" t="n">
-        <v>0.859</v>
+        <v>0.74</v>
       </c>
       <c r="G415" t="n">
-        <v>0.526</v>
+        <v>0.465</v>
       </c>
       <c r="H415" t="n">
-        <v>0.1184</v>
+        <v>0.1025</v>
       </c>
       <c r="I415" t="n">
-        <v>25.65</v>
+        <v>25.95</v>
       </c>
       <c r="J415" t="n">
-        <v>346.4</v>
+        <v>352.9</v>
       </c>
       <c r="K415" t="n">
-        <v>5.84</v>
+        <v>5.255</v>
       </c>
       <c r="L415" t="n">
-        <v>-3.863</v>
+        <v>-4.066</v>
       </c>
       <c r="M415" t="n">
-        <v>19.493</v>
+        <v>18.387</v>
       </c>
     </row>
     <row r="416">

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -497,44 +497,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>32.98</v>
+        <v>30.93</v>
       </c>
       <c r="D2" t="n">
-        <v>11.87</v>
+        <v>10.91</v>
       </c>
       <c r="E2" t="n">
-        <v>7.22</v>
+        <v>6.36</v>
       </c>
       <c r="F2" t="n">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="G2" t="n">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="H2" t="n">
-        <v>3976</v>
+        <v>4270</v>
       </c>
       <c r="I2" t="n">
-        <v>94.42</v>
+        <v>85.08</v>
       </c>
       <c r="J2" t="n">
-        <v>39.15</v>
+        <v>35.1</v>
       </c>
       <c r="K2" t="n">
-        <v>164.2</v>
+        <v>163.72</v>
       </c>
       <c r="L2" t="n">
-        <v>87.94</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>6.48</v>
+        <v>-3.63</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -542,44 +542,44 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>30.93</v>
+        <v>30.25</v>
       </c>
       <c r="D3" t="n">
-        <v>10.91</v>
+        <v>10.06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.36</v>
+        <v>6.56</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="G3" t="n">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H3" t="n">
-        <v>4270</v>
+        <v>4153</v>
       </c>
       <c r="I3" t="n">
-        <v>85.08</v>
+        <v>79.69</v>
       </c>
       <c r="J3" t="n">
-        <v>35.1</v>
+        <v>34.34</v>
       </c>
       <c r="K3" t="n">
-        <v>163.72</v>
+        <v>154.52</v>
       </c>
       <c r="L3" t="n">
-        <v>88.70999999999999</v>
+        <v>81.06</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.63</v>
+        <v>-1.37</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -587,44 +587,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>31.76</v>
+        <v>31.41</v>
       </c>
       <c r="D4" t="n">
-        <v>10.39</v>
+        <v>11.31</v>
       </c>
       <c r="E4" t="n">
-        <v>5.69</v>
+        <v>6.88</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="G4" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="H4" t="n">
-        <v>4030</v>
+        <v>4185</v>
       </c>
       <c r="I4" t="n">
-        <v>82.09999999999999</v>
+        <v>79.59</v>
       </c>
       <c r="J4" t="n">
-        <v>34.11</v>
+        <v>36.32</v>
       </c>
       <c r="K4" t="n">
-        <v>151.7</v>
+        <v>159.18</v>
       </c>
       <c r="L4" t="n">
-        <v>78.76000000000001</v>
+        <v>87.94</v>
       </c>
       <c r="M4" t="n">
-        <v>3.34</v>
+        <v>-8.35</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -632,44 +632,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>30.25</v>
+        <v>30.81</v>
       </c>
       <c r="D5" t="n">
-        <v>10.06</v>
+        <v>11.38</v>
       </c>
       <c r="E5" t="n">
-        <v>6.56</v>
+        <v>6.68</v>
       </c>
       <c r="F5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="G5" t="n">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="H5" t="n">
-        <v>4153</v>
+        <v>4367</v>
       </c>
       <c r="I5" t="n">
-        <v>79.69</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>34.34</v>
+        <v>35.48</v>
       </c>
       <c r="K5" t="n">
-        <v>154.52</v>
+        <v>156.44</v>
       </c>
       <c r="L5" t="n">
-        <v>81.06</v>
+        <v>78</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.37</v>
+        <v>0.9</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -677,44 +677,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>30.81</v>
+        <v>32.62</v>
       </c>
       <c r="D6" t="n">
-        <v>11.38</v>
+        <v>10.84</v>
       </c>
       <c r="E6" t="n">
-        <v>6.68</v>
+        <v>5.94</v>
       </c>
       <c r="F6" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="G6" t="n">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="H6" t="n">
-        <v>4367</v>
+        <v>4200</v>
       </c>
       <c r="I6" t="n">
-        <v>78.90000000000001</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>35.48</v>
+        <v>35.02</v>
       </c>
       <c r="K6" t="n">
-        <v>156.44</v>
+        <v>159.23</v>
       </c>
       <c r="L6" t="n">
-        <v>78</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9</v>
+        <v>-2.44</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -722,44 +722,44 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>32.62</v>
+        <v>31.48</v>
       </c>
       <c r="D7" t="n">
-        <v>10.84</v>
+        <v>10.98</v>
       </c>
       <c r="E7" t="n">
-        <v>5.94</v>
+        <v>7.46</v>
       </c>
       <c r="F7" t="n">
-        <v>1.78</v>
+        <v>1.27</v>
       </c>
       <c r="G7" t="n">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="H7" t="n">
-        <v>4200</v>
+        <v>4305</v>
       </c>
       <c r="I7" t="n">
-        <v>77.84999999999999</v>
+        <v>75.97</v>
       </c>
       <c r="J7" t="n">
-        <v>35.02</v>
+        <v>22.94</v>
       </c>
       <c r="K7" t="n">
-        <v>159.23</v>
+        <v>156.61</v>
       </c>
       <c r="L7" t="n">
-        <v>80.29000000000001</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.44</v>
+        <v>0.26</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -767,44 +767,44 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>31.48</v>
+        <v>32.41</v>
       </c>
       <c r="D8" t="n">
-        <v>10.98</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>7.46</v>
+        <v>6.31</v>
       </c>
       <c r="F8" t="n">
-        <v>1.27</v>
+        <v>1.71</v>
       </c>
       <c r="G8" t="n">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="H8" t="n">
-        <v>4305</v>
+        <v>4349</v>
       </c>
       <c r="I8" t="n">
-        <v>75.97</v>
+        <v>75.7</v>
       </c>
       <c r="J8" t="n">
-        <v>22.94</v>
+        <v>34.03</v>
       </c>
       <c r="K8" t="n">
-        <v>156.61</v>
+        <v>157.41</v>
       </c>
       <c r="L8" t="n">
-        <v>75.70999999999999</v>
+        <v>94.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0.26</v>
+        <v>-18.36</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -812,44 +812,44 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>32.41</v>
+        <v>32.13</v>
       </c>
       <c r="D9" t="n">
-        <v>9.699999999999999</v>
+        <v>10.72</v>
       </c>
       <c r="E9" t="n">
-        <v>6.31</v>
+        <v>7.06</v>
       </c>
       <c r="F9" t="n">
-        <v>1.71</v>
+        <v>1.3</v>
       </c>
       <c r="G9" t="n">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="H9" t="n">
-        <v>4349</v>
+        <v>4340</v>
       </c>
       <c r="I9" t="n">
-        <v>75.7</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>34.03</v>
+        <v>23.86</v>
       </c>
       <c r="K9" t="n">
-        <v>157.41</v>
+        <v>158.71</v>
       </c>
       <c r="L9" t="n">
-        <v>94.06</v>
+        <v>69.59</v>
       </c>
       <c r="M9" t="n">
-        <v>-18.36</v>
+        <v>5.92</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -857,44 +857,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>32.13</v>
+        <v>30.76</v>
       </c>
       <c r="D10" t="n">
-        <v>10.72</v>
+        <v>10.11</v>
       </c>
       <c r="E10" t="n">
-        <v>7.06</v>
+        <v>6.84</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="G10" t="n">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="H10" t="n">
-        <v>4340</v>
+        <v>4288</v>
       </c>
       <c r="I10" t="n">
-        <v>75.51000000000001</v>
+        <v>74.36</v>
       </c>
       <c r="J10" t="n">
-        <v>23.86</v>
+        <v>33.42</v>
       </c>
       <c r="K10" t="n">
-        <v>158.71</v>
+        <v>155.76</v>
       </c>
       <c r="L10" t="n">
-        <v>69.59</v>
+        <v>82.59</v>
       </c>
       <c r="M10" t="n">
-        <v>5.92</v>
+        <v>-8.23</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -902,44 +902,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>30.76</v>
+        <v>28.42</v>
       </c>
       <c r="D11" t="n">
-        <v>10.11</v>
+        <v>10.85</v>
       </c>
       <c r="E11" t="n">
-        <v>6.84</v>
+        <v>5.5</v>
       </c>
       <c r="F11" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="G11" t="n">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="H11" t="n">
-        <v>4288</v>
+        <v>4260</v>
       </c>
       <c r="I11" t="n">
-        <v>74.36</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>33.42</v>
+        <v>31.81</v>
       </c>
       <c r="K11" t="n">
-        <v>155.76</v>
+        <v>149.5</v>
       </c>
       <c r="L11" t="n">
-        <v>82.59</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-8.23</v>
+        <v>-1.89</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -947,44 +947,44 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>28.42</v>
+        <v>32.28</v>
       </c>
       <c r="D12" t="n">
-        <v>10.85</v>
+        <v>9.56</v>
       </c>
       <c r="E12" t="n">
-        <v>5.5</v>
+        <v>7.14</v>
       </c>
       <c r="F12" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="G12" t="n">
-        <v>264</v>
+        <v>314</v>
       </c>
       <c r="H12" t="n">
-        <v>4260</v>
+        <v>4502</v>
       </c>
       <c r="I12" t="n">
-        <v>73.81999999999999</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>31.81</v>
+        <v>21.18</v>
       </c>
       <c r="K12" t="n">
-        <v>149.5</v>
+        <v>127.54</v>
       </c>
       <c r="L12" t="n">
-        <v>75.70999999999999</v>
+        <v>71.12</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.89</v>
+        <v>2.53</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -992,44 +992,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>32.28</v>
+        <v>30.27</v>
       </c>
       <c r="D13" t="n">
-        <v>9.56</v>
+        <v>10.34</v>
       </c>
       <c r="E13" t="n">
-        <v>7.14</v>
+        <v>6.45</v>
       </c>
       <c r="F13" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="G13" t="n">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="H13" t="n">
-        <v>4502</v>
+        <v>4348</v>
       </c>
       <c r="I13" t="n">
-        <v>73.65000000000001</v>
+        <v>73.02</v>
       </c>
       <c r="J13" t="n">
-        <v>21.18</v>
+        <v>21.03</v>
       </c>
       <c r="K13" t="n">
-        <v>127.54</v>
+        <v>156.02</v>
       </c>
       <c r="L13" t="n">
-        <v>71.12</v>
+        <v>68.06</v>
       </c>
       <c r="M13" t="n">
-        <v>2.53</v>
+        <v>4.96</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1037,44 +1037,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.27</v>
+        <v>29.44</v>
       </c>
       <c r="D14" t="n">
-        <v>10.34</v>
+        <v>10.72</v>
       </c>
       <c r="E14" t="n">
-        <v>6.45</v>
+        <v>5.68</v>
       </c>
       <c r="F14" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="G14" t="n">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="H14" t="n">
-        <v>4348</v>
+        <v>4301</v>
       </c>
       <c r="I14" t="n">
-        <v>73.02</v>
+        <v>72.94</v>
       </c>
       <c r="J14" t="n">
-        <v>21.03</v>
+        <v>32.58</v>
       </c>
       <c r="K14" t="n">
-        <v>156.02</v>
+        <v>150.49</v>
       </c>
       <c r="L14" t="n">
-        <v>68.06</v>
+        <v>76.47</v>
       </c>
       <c r="M14" t="n">
-        <v>4.96</v>
+        <v>-3.53</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1082,44 +1082,44 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>29.44</v>
+        <v>33.08</v>
       </c>
       <c r="D15" t="n">
-        <v>10.72</v>
+        <v>9.84</v>
       </c>
       <c r="E15" t="n">
-        <v>5.68</v>
+        <v>6.23</v>
       </c>
       <c r="F15" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="G15" t="n">
-        <v>266</v>
+        <v>304</v>
       </c>
       <c r="H15" t="n">
-        <v>4301</v>
+        <v>4414</v>
       </c>
       <c r="I15" t="n">
-        <v>72.94</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>32.58</v>
+        <v>22.71</v>
       </c>
       <c r="K15" t="n">
-        <v>150.49</v>
+        <v>129.11</v>
       </c>
       <c r="L15" t="n">
-        <v>76.47</v>
+        <v>74.94</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.53</v>
+        <v>-2.4</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1127,44 +1127,44 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>33.08</v>
+        <v>30.86</v>
       </c>
       <c r="D16" t="n">
-        <v>9.84</v>
+        <v>10.01</v>
       </c>
       <c r="E16" t="n">
-        <v>6.23</v>
+        <v>7.27</v>
       </c>
       <c r="F16" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="G16" t="n">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="H16" t="n">
-        <v>4414</v>
+        <v>4491</v>
       </c>
       <c r="I16" t="n">
-        <v>72.54000000000001</v>
+        <v>72.45</v>
       </c>
       <c r="J16" t="n">
-        <v>22.71</v>
+        <v>34.18</v>
       </c>
       <c r="K16" t="n">
-        <v>129.11</v>
+        <v>126.27</v>
       </c>
       <c r="L16" t="n">
-        <v>74.94</v>
+        <v>82.59</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4</v>
+        <v>-10.14</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1172,44 +1172,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>30.86</v>
+        <v>30.82</v>
       </c>
       <c r="D17" t="n">
-        <v>10.01</v>
+        <v>10.1</v>
       </c>
       <c r="E17" t="n">
-        <v>7.27</v>
+        <v>5.76</v>
       </c>
       <c r="F17" t="n">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="G17" t="n">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="H17" t="n">
-        <v>4491</v>
+        <v>4598</v>
       </c>
       <c r="I17" t="n">
-        <v>72.45</v>
+        <v>72.22</v>
       </c>
       <c r="J17" t="n">
-        <v>34.18</v>
+        <v>19.58</v>
       </c>
       <c r="K17" t="n">
-        <v>126.27</v>
+        <v>128.21</v>
       </c>
       <c r="L17" t="n">
-        <v>82.59</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-10.14</v>
+        <v>-5.02</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1217,44 +1217,44 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>30.82</v>
+        <v>31.44</v>
       </c>
       <c r="D18" t="n">
-        <v>10.1</v>
+        <v>10.36</v>
       </c>
       <c r="E18" t="n">
-        <v>5.76</v>
+        <v>5.78</v>
       </c>
       <c r="F18" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="G18" t="n">
-        <v>316</v>
+        <v>276</v>
       </c>
       <c r="H18" t="n">
-        <v>4598</v>
+        <v>4337</v>
       </c>
       <c r="I18" t="n">
-        <v>72.22</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>19.58</v>
+        <v>33.19</v>
       </c>
       <c r="K18" t="n">
-        <v>128.21</v>
+        <v>152.01</v>
       </c>
       <c r="L18" t="n">
-        <v>77.23999999999999</v>
+        <v>74.94</v>
       </c>
       <c r="M18" t="n">
-        <v>-5.02</v>
+        <v>-2.9</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1262,44 +1262,44 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>31.44</v>
+        <v>26.92</v>
       </c>
       <c r="D19" t="n">
-        <v>10.36</v>
+        <v>11.36</v>
       </c>
       <c r="E19" t="n">
-        <v>5.78</v>
+        <v>6.15</v>
       </c>
       <c r="F19" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="G19" t="n">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="H19" t="n">
-        <v>4337</v>
+        <v>4483</v>
       </c>
       <c r="I19" t="n">
-        <v>72.04000000000001</v>
+        <v>71.36</v>
       </c>
       <c r="J19" t="n">
-        <v>33.19</v>
+        <v>19.35</v>
       </c>
       <c r="K19" t="n">
-        <v>152.01</v>
+        <v>127.89</v>
       </c>
       <c r="L19" t="n">
-        <v>74.94</v>
+        <v>76.47</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.9</v>
+        <v>-5.11</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1307,44 +1307,44 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>26.92</v>
+        <v>29.75</v>
       </c>
       <c r="D20" t="n">
-        <v>11.36</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>6.15</v>
+        <v>6.29</v>
       </c>
       <c r="F20" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="G20" t="n">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="H20" t="n">
-        <v>4483</v>
+        <v>4255</v>
       </c>
       <c r="I20" t="n">
-        <v>71.36</v>
+        <v>70.09</v>
       </c>
       <c r="J20" t="n">
-        <v>19.35</v>
+        <v>18.96</v>
       </c>
       <c r="K20" t="n">
-        <v>127.89</v>
+        <v>136.59</v>
       </c>
       <c r="L20" t="n">
-        <v>76.47</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-5.11</v>
+        <v>-0.26</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1352,44 +1352,44 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>13</v>
       </c>
       <c r="C21" t="n">
-        <v>29.75</v>
+        <v>29.71</v>
       </c>
       <c r="D21" t="n">
-        <v>9.960000000000001</v>
+        <v>10.06</v>
       </c>
       <c r="E21" t="n">
-        <v>6.29</v>
+        <v>6.25</v>
       </c>
       <c r="F21" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="G21" t="n">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="H21" t="n">
-        <v>4255</v>
+        <v>4543</v>
       </c>
       <c r="I21" t="n">
-        <v>70.09</v>
+        <v>69.89</v>
       </c>
       <c r="J21" t="n">
-        <v>18.96</v>
+        <v>19.12</v>
       </c>
       <c r="K21" t="n">
-        <v>136.59</v>
+        <v>110.59</v>
       </c>
       <c r="L21" t="n">
-        <v>70.34999999999999</v>
+        <v>68.06</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.26</v>
+        <v>1.83</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1397,44 +1397,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>13</v>
       </c>
       <c r="C22" t="n">
-        <v>29.71</v>
+        <v>28.79</v>
       </c>
       <c r="D22" t="n">
-        <v>10.06</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>6.25</v>
+        <v>5.78</v>
       </c>
       <c r="F22" t="n">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="G22" t="n">
-        <v>334</v>
+        <v>290</v>
       </c>
       <c r="H22" t="n">
-        <v>4543</v>
+        <v>4285</v>
       </c>
       <c r="I22" t="n">
-        <v>69.89</v>
+        <v>68.98</v>
       </c>
       <c r="J22" t="n">
-        <v>19.12</v>
+        <v>30.05</v>
       </c>
       <c r="K22" t="n">
-        <v>110.59</v>
+        <v>148.31</v>
       </c>
       <c r="L22" t="n">
-        <v>68.06</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>1.83</v>
+        <v>-3.67</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1442,44 +1442,44 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>13</v>
       </c>
       <c r="C23" t="n">
-        <v>28.79</v>
+        <v>30.06</v>
       </c>
       <c r="D23" t="n">
-        <v>9.859999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="E23" t="n">
-        <v>5.78</v>
+        <v>5.37</v>
       </c>
       <c r="F23" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="G23" t="n">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="H23" t="n">
-        <v>4285</v>
+        <v>4459</v>
       </c>
       <c r="I23" t="n">
-        <v>68.98</v>
+        <v>68.48</v>
       </c>
       <c r="J23" t="n">
-        <v>30.05</v>
+        <v>31.74</v>
       </c>
       <c r="K23" t="n">
-        <v>148.31</v>
+        <v>123.15</v>
       </c>
       <c r="L23" t="n">
-        <v>72.65000000000001</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.67</v>
+        <v>-7.23</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1487,44 +1487,44 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>13</v>
       </c>
       <c r="C24" t="n">
-        <v>30.06</v>
+        <v>28.34</v>
       </c>
       <c r="D24" t="n">
-        <v>9.93</v>
+        <v>10.06</v>
       </c>
       <c r="E24" t="n">
-        <v>5.37</v>
+        <v>6.05</v>
       </c>
       <c r="F24" t="n">
         <v>1.3</v>
       </c>
       <c r="G24" t="n">
-        <v>283</v>
+        <v>334</v>
       </c>
       <c r="H24" t="n">
-        <v>4459</v>
+        <v>4466</v>
       </c>
       <c r="I24" t="n">
-        <v>68.48</v>
+        <v>68.38</v>
       </c>
       <c r="J24" t="n">
-        <v>31.74</v>
+        <v>17.44</v>
       </c>
       <c r="K24" t="n">
-        <v>123.15</v>
+        <v>108.53</v>
       </c>
       <c r="L24" t="n">
-        <v>75.70999999999999</v>
+        <v>71.12</v>
       </c>
       <c r="M24" t="n">
-        <v>-7.23</v>
+        <v>-2.74</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -1532,44 +1532,44 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>13</v>
       </c>
       <c r="C25" t="n">
-        <v>28.34</v>
+        <v>30.25</v>
       </c>
       <c r="D25" t="n">
-        <v>10.06</v>
+        <v>9.9</v>
       </c>
       <c r="E25" t="n">
-        <v>6.05</v>
+        <v>5.42</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="G25" t="n">
-        <v>334</v>
+        <v>277</v>
       </c>
       <c r="H25" t="n">
-        <v>4466</v>
+        <v>4242</v>
       </c>
       <c r="I25" t="n">
-        <v>68.38</v>
+        <v>67.72</v>
       </c>
       <c r="J25" t="n">
-        <v>17.44</v>
+        <v>31.81</v>
       </c>
       <c r="K25" t="n">
-        <v>108.53</v>
+        <v>147.28</v>
       </c>
       <c r="L25" t="n">
-        <v>71.12</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.74</v>
+        <v>-11.04</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -11393,31 +11393,31 @@
         <v>1</v>
       </c>
       <c r="E210" t="n">
-        <v>2.573</v>
+        <v>2.451</v>
       </c>
       <c r="F210" t="n">
-        <v>0.836</v>
+        <v>0.797</v>
       </c>
       <c r="G210" t="n">
-        <v>0.424</v>
+        <v>0.404</v>
       </c>
       <c r="H210" t="n">
-        <v>0.0964</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="I210" t="n">
-        <v>19.86</v>
+        <v>20.91</v>
       </c>
       <c r="J210" t="n">
-        <v>290.3</v>
+        <v>305.5</v>
       </c>
       <c r="K210" t="n">
-        <v>8.670999999999999</v>
+        <v>5.404</v>
       </c>
       <c r="L210" t="n">
-        <v>-1.576</v>
+        <v>-2.707</v>
       </c>
       <c r="M210" t="n">
-        <v>21.567</v>
+        <v>20.436</v>
       </c>
     </row>
     <row r="211">
@@ -11438,31 +11438,31 @@
         <v>1</v>
       </c>
       <c r="E211" t="n">
-        <v>2.548</v>
+        <v>2.427</v>
       </c>
       <c r="F211" t="n">
-        <v>0.777</v>
+        <v>0.74</v>
       </c>
       <c r="G211" t="n">
-        <v>0.471</v>
+        <v>0.449</v>
       </c>
       <c r="H211" t="n">
-        <v>0.1081</v>
+        <v>0.103</v>
       </c>
       <c r="I211" t="n">
-        <v>20.15</v>
+        <v>21.21</v>
       </c>
       <c r="J211" t="n">
-        <v>322.1</v>
+        <v>339.1</v>
       </c>
       <c r="K211" t="n">
-        <v>5.693</v>
+        <v>5.423</v>
       </c>
       <c r="L211" t="n">
-        <v>-3.914</v>
+        <v>-4.008</v>
       </c>
       <c r="M211" t="n">
-        <v>20.678</v>
+        <v>20.584</v>
       </c>
     </row>
     <row r="212">
@@ -11483,31 +11483,31 @@
         <v>-1</v>
       </c>
       <c r="E212" t="n">
-        <v>2.448</v>
+        <v>2.331</v>
       </c>
       <c r="F212" t="n">
-        <v>0.763</v>
+        <v>0.726</v>
       </c>
       <c r="G212" t="n">
-        <v>0.438</v>
+        <v>0.417</v>
       </c>
       <c r="H212" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0796</v>
       </c>
       <c r="I212" t="n">
-        <v>20.07</v>
+        <v>21.12</v>
       </c>
       <c r="J212" t="n">
-        <v>305.8</v>
+        <v>321.9</v>
       </c>
       <c r="K212" t="n">
-        <v>5.352</v>
+        <v>5.095</v>
       </c>
       <c r="L212" t="n">
-        <v>-2.725</v>
+        <v>-2.813</v>
       </c>
       <c r="M212" t="n">
-        <v>19.927</v>
+        <v>19.838</v>
       </c>
     </row>
     <row r="213">
@@ -11528,31 +11528,31 @@
         <v>1</v>
       </c>
       <c r="E213" t="n">
-        <v>2.601</v>
+        <v>2.478</v>
       </c>
       <c r="F213" t="n">
-        <v>0.799</v>
+        <v>0.761</v>
       </c>
       <c r="G213" t="n">
-        <v>0.386</v>
+        <v>0.367</v>
       </c>
       <c r="H213" t="n">
-        <v>0.0866</v>
+        <v>0.0825</v>
       </c>
       <c r="I213" t="n">
-        <v>19.87</v>
+        <v>20.92</v>
       </c>
       <c r="J213" t="n">
-        <v>295.4</v>
+        <v>311</v>
       </c>
       <c r="K213" t="n">
-        <v>8.491</v>
+        <v>5.229</v>
       </c>
       <c r="L213" t="n">
-        <v>-1.638</v>
+        <v>-2.767</v>
       </c>
       <c r="M213" t="n">
-        <v>21.145</v>
+        <v>20.016</v>
       </c>
     </row>
     <row r="214">
@@ -11573,31 +11573,31 @@
         <v>-1</v>
       </c>
       <c r="E214" t="n">
-        <v>2.298</v>
+        <v>2.189</v>
       </c>
       <c r="F214" t="n">
-        <v>0.849</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="G214" t="n">
-        <v>0.492</v>
+        <v>0.469</v>
       </c>
       <c r="H214" t="n">
-        <v>0.1128</v>
+        <v>0.1074</v>
       </c>
       <c r="I214" t="n">
-        <v>20.94</v>
+        <v>22.04</v>
       </c>
       <c r="J214" t="n">
-        <v>318.3</v>
+        <v>335</v>
       </c>
       <c r="K214" t="n">
-        <v>5.657</v>
+        <v>5.387</v>
       </c>
       <c r="L214" t="n">
-        <v>-2.619</v>
+        <v>-2.712</v>
       </c>
       <c r="M214" t="n">
-        <v>20.699</v>
+        <v>20.606</v>
       </c>
     </row>
     <row r="215">
@@ -11618,31 +11618,31 @@
         <v>-1</v>
       </c>
       <c r="E215" t="n">
-        <v>2.461</v>
+        <v>2.344</v>
       </c>
       <c r="F215" t="n">
-        <v>0.769</v>
+        <v>0.733</v>
       </c>
       <c r="G215" t="n">
-        <v>0.471</v>
+        <v>0.449</v>
       </c>
       <c r="H215" t="n">
-        <v>0.1081</v>
+        <v>0.103</v>
       </c>
       <c r="I215" t="n">
-        <v>20.34</v>
+        <v>21.41</v>
       </c>
       <c r="J215" t="n">
-        <v>333.6</v>
+        <v>351.2</v>
       </c>
       <c r="K215" t="n">
-        <v>5.59</v>
+        <v>5.326</v>
       </c>
       <c r="L215" t="n">
-        <v>-3.95</v>
+        <v>-4.041</v>
       </c>
       <c r="M215" t="n">
-        <v>20.524</v>
+        <v>20.433</v>
       </c>
     </row>
     <row r="216">
@@ -11663,31 +11663,31 @@
         <v>1</v>
       </c>
       <c r="E216" t="n">
-        <v>2.555</v>
+        <v>2.433</v>
       </c>
       <c r="F216" t="n">
-        <v>0.888</v>
+        <v>0.845</v>
       </c>
       <c r="G216" t="n">
-        <v>0.474</v>
+        <v>0.452</v>
       </c>
       <c r="H216" t="n">
-        <v>0.0755</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="I216" t="n">
-        <v>20.48</v>
+        <v>21.55</v>
       </c>
       <c r="J216" t="n">
-        <v>308.3</v>
+        <v>324.6</v>
       </c>
       <c r="K216" t="n">
-        <v>5.732</v>
+        <v>5.458</v>
       </c>
       <c r="L216" t="n">
-        <v>-2.593</v>
+        <v>-2.688</v>
       </c>
       <c r="M216" t="n">
-        <v>20.46</v>
+        <v>20.365</v>
       </c>
     </row>
     <row r="217">
@@ -11708,31 +11708,31 @@
         <v>1</v>
       </c>
       <c r="E217" t="n">
-        <v>2.589</v>
+        <v>2.466</v>
       </c>
       <c r="F217" t="n">
-        <v>0.879</v>
+        <v>0.837</v>
       </c>
       <c r="G217" t="n">
-        <v>0.569</v>
+        <v>0.542</v>
       </c>
       <c r="H217" t="n">
-        <v>0.1129</v>
+        <v>0.1075</v>
       </c>
       <c r="I217" t="n">
-        <v>19.41</v>
+        <v>20.43</v>
       </c>
       <c r="J217" t="n">
-        <v>286.2</v>
+        <v>301.3</v>
       </c>
       <c r="K217" t="n">
-        <v>9.162000000000001</v>
+        <v>5.869</v>
       </c>
       <c r="L217" t="n">
-        <v>-1.406</v>
+        <v>-2.546</v>
       </c>
       <c r="M217" t="n">
-        <v>22.544</v>
+        <v>21.404</v>
       </c>
     </row>
     <row r="218">
@@ -11753,31 +11753,31 @@
         <v>-1</v>
       </c>
       <c r="E218" t="n">
-        <v>2.632</v>
+        <v>2.507</v>
       </c>
       <c r="F218" t="n">
-        <v>0.882</v>
+        <v>0.84</v>
       </c>
       <c r="G218" t="n">
-        <v>0.431</v>
+        <v>0.411</v>
       </c>
       <c r="H218" t="n">
-        <v>0.0946</v>
+        <v>0.0901</v>
       </c>
       <c r="I218" t="n">
-        <v>20.46</v>
+        <v>21.54</v>
       </c>
       <c r="J218" t="n">
-        <v>301.9</v>
+        <v>317.8</v>
       </c>
       <c r="K218" t="n">
-        <v>5.826</v>
+        <v>5.55</v>
       </c>
       <c r="L218" t="n">
-        <v>-2.56</v>
+        <v>-2.656</v>
       </c>
       <c r="M218" t="n">
-        <v>20.751</v>
+        <v>20.656</v>
       </c>
     </row>
     <row r="219">
@@ -11798,31 +11798,31 @@
         <v>1</v>
       </c>
       <c r="E219" t="n">
-        <v>2.551</v>
+        <v>2.429</v>
       </c>
       <c r="F219" t="n">
-        <v>0.793</v>
+        <v>0.755</v>
       </c>
       <c r="G219" t="n">
-        <v>0.441</v>
+        <v>0.42</v>
       </c>
       <c r="H219" t="n">
-        <v>0.0844</v>
+        <v>0.0804</v>
       </c>
       <c r="I219" t="n">
-        <v>20.11</v>
+        <v>21.16</v>
       </c>
       <c r="J219" t="n">
-        <v>298.4</v>
+        <v>314.1</v>
       </c>
       <c r="K219" t="n">
-        <v>7.525</v>
+        <v>5.261</v>
       </c>
       <c r="L219" t="n">
-        <v>-1.972</v>
+        <v>-2.756</v>
       </c>
       <c r="M219" t="n">
-        <v>20.874</v>
+        <v>20.09</v>
       </c>
     </row>
     <row r="220">
@@ -11843,31 +11843,31 @@
         <v>-1</v>
       </c>
       <c r="E220" t="n">
-        <v>2.139</v>
+        <v>2.037</v>
       </c>
       <c r="F220" t="n">
-        <v>0.712</v>
+        <v>0.679</v>
       </c>
       <c r="G220" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="H220" t="n">
-        <v>0.0806</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="I220" t="n">
-        <v>20.4</v>
+        <v>21.47</v>
       </c>
       <c r="J220" t="n">
-        <v>322.7</v>
+        <v>339.7</v>
       </c>
       <c r="K220" t="n">
-        <v>4.747</v>
+        <v>4.522</v>
       </c>
       <c r="L220" t="n">
-        <v>-4.242</v>
+        <v>-4.32</v>
       </c>
       <c r="M220" t="n">
-        <v>18.895</v>
+        <v>18.817</v>
       </c>
     </row>
     <row r="221">
@@ -11888,31 +11888,31 @@
         <v>-1</v>
       </c>
       <c r="E221" t="n">
-        <v>2.116</v>
+        <v>2.015</v>
       </c>
       <c r="F221" t="n">
-        <v>0.731</v>
+        <v>0.697</v>
       </c>
       <c r="G221" t="n">
-        <v>0.39</v>
+        <v>0.371</v>
       </c>
       <c r="H221" t="n">
-        <v>0.0728</v>
+        <v>0.0693</v>
       </c>
       <c r="I221" t="n">
-        <v>20.67</v>
+        <v>21.75</v>
       </c>
       <c r="J221" t="n">
-        <v>337.3</v>
+        <v>355.1</v>
       </c>
       <c r="K221" t="n">
-        <v>4.795</v>
+        <v>4.567</v>
       </c>
       <c r="L221" t="n">
-        <v>-4.225</v>
+        <v>-4.304</v>
       </c>
       <c r="M221" t="n">
-        <v>18.935</v>
+        <v>18.856</v>
       </c>
     </row>
     <row r="222">
@@ -11933,31 +11933,31 @@
         <v>1</v>
       </c>
       <c r="E222" t="n">
-        <v>2.254</v>
+        <v>2.147</v>
       </c>
       <c r="F222" t="n">
-        <v>0.712</v>
+        <v>0.679</v>
       </c>
       <c r="G222" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="H222" t="n">
-        <v>0.0806</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="I222" t="n">
-        <v>20.23</v>
+        <v>21.29</v>
       </c>
       <c r="J222" t="n">
-        <v>309.9</v>
+        <v>326.2</v>
       </c>
       <c r="K222" t="n">
-        <v>4.862</v>
+        <v>4.632</v>
       </c>
       <c r="L222" t="n">
-        <v>-2.894</v>
+        <v>-2.974</v>
       </c>
       <c r="M222" t="n">
-        <v>19.059</v>
+        <v>18.979</v>
       </c>
     </row>
     <row r="223">
@@ -17828,31 +17828,31 @@
         <v>1</v>
       </c>
       <c r="E353" t="n">
-        <v>2.709</v>
+        <v>2.58</v>
       </c>
       <c r="F353" t="n">
-        <v>1.009</v>
+        <v>0.961</v>
       </c>
       <c r="G353" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.538</v>
       </c>
       <c r="H353" t="n">
-        <v>0.1268</v>
+        <v>0.1207</v>
       </c>
       <c r="I353" t="n">
-        <v>18.6</v>
+        <v>19.57</v>
       </c>
       <c r="J353" t="n">
-        <v>286.9</v>
+        <v>302</v>
       </c>
       <c r="K353" t="n">
-        <v>9.618</v>
+        <v>7.302</v>
       </c>
       <c r="L353" t="n">
-        <v>-1.248</v>
+        <v>-2.05</v>
       </c>
       <c r="M353" t="n">
-        <v>23.353</v>
+        <v>22.551</v>
       </c>
     </row>
     <row r="354">
@@ -17873,31 +17873,31 @@
         <v>-1</v>
       </c>
       <c r="E354" t="n">
-        <v>2.608</v>
+        <v>2.484</v>
       </c>
       <c r="F354" t="n">
-        <v>0.963</v>
+        <v>0.918</v>
       </c>
       <c r="G354" t="n">
-        <v>0.498</v>
+        <v>0.475</v>
       </c>
       <c r="H354" t="n">
-        <v>0.1279</v>
+        <v>0.1218</v>
       </c>
       <c r="I354" t="n">
-        <v>20.12</v>
+        <v>21.18</v>
       </c>
       <c r="J354" t="n">
-        <v>310.4</v>
+        <v>326.7</v>
       </c>
       <c r="K354" t="n">
-        <v>6.297</v>
+        <v>6.001</v>
       </c>
       <c r="L354" t="n">
-        <v>-2.397</v>
+        <v>-2.5</v>
       </c>
       <c r="M354" t="n">
-        <v>21.801</v>
+        <v>21.698</v>
       </c>
     </row>
     <row r="355">
@@ -17918,31 +17918,31 @@
         <v>1</v>
       </c>
       <c r="E355" t="n">
-        <v>2.605</v>
+        <v>2.481</v>
       </c>
       <c r="F355" t="n">
-        <v>0.989</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="G355" t="n">
-        <v>0.65</v>
+        <v>0.619</v>
       </c>
       <c r="H355" t="n">
-        <v>0.1504</v>
+        <v>0.1433</v>
       </c>
       <c r="I355" t="n">
-        <v>17.79</v>
+        <v>18.73</v>
       </c>
       <c r="J355" t="n">
-        <v>286.6</v>
+        <v>301.6</v>
       </c>
       <c r="K355" t="n">
-        <v>9.785</v>
+        <v>7.463</v>
       </c>
       <c r="L355" t="n">
-        <v>-1.19</v>
+        <v>-1.994</v>
       </c>
       <c r="M355" t="n">
-        <v>25.77</v>
+        <v>24.966</v>
       </c>
     </row>
     <row r="356">
@@ -17963,31 +17963,31 @@
         <v>1</v>
       </c>
       <c r="E356" t="n">
-        <v>2.421</v>
+        <v>2.306</v>
       </c>
       <c r="F356" t="n">
-        <v>0.872</v>
+        <v>0.831</v>
       </c>
       <c r="G356" t="n">
-        <v>0.511</v>
+        <v>0.486</v>
       </c>
       <c r="H356" t="n">
-        <v>0.0968</v>
+        <v>0.0922</v>
       </c>
       <c r="I356" t="n">
-        <v>19.08</v>
+        <v>20.08</v>
       </c>
       <c r="J356" t="n">
-        <v>307.9</v>
+        <v>324.1</v>
       </c>
       <c r="K356" t="n">
-        <v>6.768</v>
+        <v>5.493</v>
       </c>
       <c r="L356" t="n">
-        <v>-2.234</v>
+        <v>-2.676</v>
       </c>
       <c r="M356" t="n">
-        <v>21.106</v>
+        <v>20.665</v>
       </c>
     </row>
     <row r="357">
@@ -18008,31 +18008,31 @@
         <v>1</v>
       </c>
       <c r="E357" t="n">
-        <v>2.577</v>
+        <v>2.455</v>
       </c>
       <c r="F357" t="n">
-        <v>0.854</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G357" t="n">
-        <v>0.577</v>
+        <v>0.55</v>
       </c>
       <c r="H357" t="n">
-        <v>0.1156</v>
+        <v>0.1101</v>
       </c>
       <c r="I357" t="n">
-        <v>18.58</v>
+        <v>19.55</v>
       </c>
       <c r="J357" t="n">
-        <v>320.2</v>
+        <v>337.1</v>
       </c>
       <c r="K357" t="n">
-        <v>7.133</v>
+        <v>6.842</v>
       </c>
       <c r="L357" t="n">
-        <v>-3.416</v>
+        <v>-3.517</v>
       </c>
       <c r="M357" t="n">
-        <v>21.829</v>
+        <v>21.728</v>
       </c>
     </row>
     <row r="358">
@@ -18053,31 +18053,31 @@
         <v>-1</v>
       </c>
       <c r="E358" t="n">
-        <v>2.47</v>
+        <v>2.352</v>
       </c>
       <c r="F358" t="n">
-        <v>0.843</v>
+        <v>0.803</v>
       </c>
       <c r="G358" t="n">
-        <v>0.538</v>
+        <v>0.512</v>
       </c>
       <c r="H358" t="n">
-        <v>0.1114</v>
+        <v>0.1061</v>
       </c>
       <c r="I358" t="n">
-        <v>19.68</v>
+        <v>20.71</v>
       </c>
       <c r="J358" t="n">
-        <v>303.9</v>
+        <v>319.9</v>
       </c>
       <c r="K358" t="n">
-        <v>6.9</v>
+        <v>5.619</v>
       </c>
       <c r="L358" t="n">
-        <v>-2.189</v>
+        <v>-2.632</v>
       </c>
       <c r="M358" t="n">
-        <v>21.424</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="359">
@@ -18098,31 +18098,31 @@
         <v>-1</v>
       </c>
       <c r="E359" t="n">
-        <v>2.649</v>
+        <v>2.523</v>
       </c>
       <c r="F359" t="n">
-        <v>0.965</v>
+        <v>0.919</v>
       </c>
       <c r="G359" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.538</v>
       </c>
       <c r="H359" t="n">
-        <v>0.1268</v>
+        <v>0.1207</v>
       </c>
       <c r="I359" t="n">
-        <v>20.68</v>
+        <v>21.77</v>
       </c>
       <c r="J359" t="n">
-        <v>301.5</v>
+        <v>317.3</v>
       </c>
       <c r="K359" t="n">
-        <v>6.47</v>
+        <v>6.161</v>
       </c>
       <c r="L359" t="n">
-        <v>-2.338</v>
+        <v>-2.445</v>
       </c>
       <c r="M359" t="n">
-        <v>22.08</v>
+        <v>21.973</v>
       </c>
     </row>
     <row r="360">
@@ -18143,31 +18143,31 @@
         <v>1</v>
       </c>
       <c r="E360" t="n">
-        <v>2.574</v>
+        <v>2.451</v>
       </c>
       <c r="F360" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.896</v>
       </c>
       <c r="G360" t="n">
-        <v>0.493</v>
+        <v>0.47</v>
       </c>
       <c r="H360" t="n">
-        <v>0.1047</v>
+        <v>0.0997</v>
       </c>
       <c r="I360" t="n">
-        <v>19.31</v>
+        <v>20.32</v>
       </c>
       <c r="J360" t="n">
-        <v>296.5</v>
+        <v>312.1</v>
       </c>
       <c r="K360" t="n">
-        <v>9.07</v>
+        <v>5.781</v>
       </c>
       <c r="L360" t="n">
-        <v>-1.438</v>
+        <v>-2.576</v>
       </c>
       <c r="M360" t="n">
-        <v>22.306</v>
+        <v>21.167</v>
       </c>
     </row>
     <row r="361">
@@ -18188,31 +18188,31 @@
         <v>1</v>
       </c>
       <c r="E361" t="n">
-        <v>2.431</v>
+        <v>2.315</v>
       </c>
       <c r="F361" t="n">
-        <v>0.849</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="G361" t="n">
-        <v>0.584</v>
+        <v>0.556</v>
       </c>
       <c r="H361" t="n">
-        <v>0.1043</v>
+        <v>0.0993</v>
       </c>
       <c r="I361" t="n">
-        <v>19.39</v>
+        <v>20.41</v>
       </c>
       <c r="J361" t="n">
-        <v>321.9</v>
+        <v>338.8</v>
       </c>
       <c r="K361" t="n">
-        <v>6.923</v>
+        <v>5.639</v>
       </c>
       <c r="L361" t="n">
-        <v>-3.488</v>
+        <v>-3.933</v>
       </c>
       <c r="M361" t="n">
-        <v>21.43</v>
+        <v>20.986</v>
       </c>
     </row>
     <row r="362">
@@ -18233,31 +18233,31 @@
         <v>-1</v>
       </c>
       <c r="E362" t="n">
-        <v>2.362</v>
+        <v>2.25</v>
       </c>
       <c r="F362" t="n">
-        <v>0.854</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G362" t="n">
-        <v>0.517</v>
+        <v>0.493</v>
       </c>
       <c r="H362" t="n">
-        <v>0.1021</v>
+        <v>0.0973</v>
       </c>
       <c r="I362" t="n">
-        <v>21.1</v>
+        <v>22.21</v>
       </c>
       <c r="J362" t="n">
-        <v>320.9</v>
+        <v>337.8</v>
       </c>
       <c r="K362" t="n">
-        <v>5.717</v>
+        <v>5.448</v>
       </c>
       <c r="L362" t="n">
-        <v>-3.906</v>
+        <v>-3.999</v>
       </c>
       <c r="M362" t="n">
-        <v>20.72</v>
+        <v>20.627</v>
       </c>
     </row>
     <row r="363">
@@ -18278,31 +18278,31 @@
         <v>1</v>
       </c>
       <c r="E363" t="n">
-        <v>2.534</v>
+        <v>2.413</v>
       </c>
       <c r="F363" t="n">
-        <v>0.889</v>
+        <v>0.847</v>
       </c>
       <c r="G363" t="n">
-        <v>0.536</v>
+        <v>0.51</v>
       </c>
       <c r="H363" t="n">
-        <v>0.1122</v>
+        <v>0.1069</v>
       </c>
       <c r="I363" t="n">
-        <v>19.32</v>
+        <v>20.34</v>
       </c>
       <c r="J363" t="n">
-        <v>301.9</v>
+        <v>317.8</v>
       </c>
       <c r="K363" t="n">
-        <v>7.057</v>
+        <v>5.768</v>
       </c>
       <c r="L363" t="n">
-        <v>-2.134</v>
+        <v>-2.581</v>
       </c>
       <c r="M363" t="n">
-        <v>21.666</v>
+        <v>21.22</v>
       </c>
     </row>
     <row r="364">
@@ -18323,31 +18323,31 @@
         <v>-1</v>
       </c>
       <c r="E364" t="n">
-        <v>2.564</v>
+        <v>2.442</v>
       </c>
       <c r="F364" t="n">
-        <v>0.976</v>
+        <v>0.929</v>
       </c>
       <c r="G364" t="n">
-        <v>0.65</v>
+        <v>0.619</v>
       </c>
       <c r="H364" t="n">
-        <v>0.1504</v>
+        <v>0.1433</v>
       </c>
       <c r="I364" t="n">
-        <v>20.73</v>
+        <v>21.82</v>
       </c>
       <c r="J364" t="n">
-        <v>301.2</v>
+        <v>317</v>
       </c>
       <c r="K364" t="n">
-        <v>6.718</v>
+        <v>6.398</v>
       </c>
       <c r="L364" t="n">
-        <v>-2.252</v>
+        <v>-2.362</v>
       </c>
       <c r="M364" t="n">
-        <v>22.668</v>
+        <v>22.558</v>
       </c>
     </row>
     <row r="365">
@@ -18368,31 +18368,31 @@
         <v>-1</v>
       </c>
       <c r="E365" t="n">
-        <v>2.48</v>
+        <v>2.362</v>
       </c>
       <c r="F365" t="n">
-        <v>0.87</v>
+        <v>0.828</v>
       </c>
       <c r="G365" t="n">
-        <v>0.536</v>
+        <v>0.51</v>
       </c>
       <c r="H365" t="n">
-        <v>0.1122</v>
+        <v>0.1069</v>
       </c>
       <c r="I365" t="n">
-        <v>20.53</v>
+        <v>21.61</v>
       </c>
       <c r="J365" t="n">
-        <v>316.2</v>
+        <v>332.9</v>
       </c>
       <c r="K365" t="n">
-        <v>5.965</v>
+        <v>5.679</v>
       </c>
       <c r="L365" t="n">
-        <v>-2.512</v>
+        <v>-2.611</v>
       </c>
       <c r="M365" t="n">
-        <v>21.177</v>
+        <v>21.078</v>
       </c>
     </row>
     <row r="366">

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -1269,13 +1269,13 @@
         <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>26.92</v>
+        <v>26.93</v>
       </c>
       <c r="D19" t="n">
         <v>11.36</v>
       </c>
       <c r="E19" t="n">
-        <v>6.15</v>
+        <v>6.19</v>
       </c>
       <c r="F19" t="n">
         <v>1.57</v>
@@ -1287,10 +1287,10 @@
         <v>4483</v>
       </c>
       <c r="I19" t="n">
-        <v>71.36</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>19.35</v>
+        <v>19.5</v>
       </c>
       <c r="K19" t="n">
         <v>127.89</v>
@@ -1299,7 +1299,7 @@
         <v>76.47</v>
       </c>
       <c r="M19" t="n">
-        <v>-5.11</v>
+        <v>-5.01</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1635,7 +1635,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>5.68</v>
+        <v>5.7</v>
       </c>
       <c r="F27" t="n">
         <v>1.36</v>
@@ -1647,7 +1647,7 @@
         <v>4468</v>
       </c>
       <c r="I27" t="n">
-        <v>66.89</v>
+        <v>66.92</v>
       </c>
       <c r="J27" t="n">
         <v>16.9</v>
@@ -1659,7 +1659,7 @@
         <v>71.88</v>
       </c>
       <c r="M27" t="n">
-        <v>-4.99</v>
+        <v>-4.96</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -1680,7 +1680,7 @@
         <v>9.31</v>
       </c>
       <c r="E28" t="n">
-        <v>5.84</v>
+        <v>5.85</v>
       </c>
       <c r="F28" t="n">
         <v>1.57</v>
@@ -1692,7 +1692,7 @@
         <v>4733</v>
       </c>
       <c r="I28" t="n">
-        <v>66.36</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J28" t="n">
         <v>1.99</v>
@@ -1704,7 +1704,7 @@
         <v>69.59</v>
       </c>
       <c r="M28" t="n">
-        <v>-3.23</v>
+        <v>-3.19</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
         <v>0.1294</v>
       </c>
       <c r="I32" t="n">
-        <v>19.31</v>
+        <v>19.28</v>
       </c>
       <c r="J32" t="n">
         <v>301.1</v>
@@ -4424,7 +4424,7 @@
         <v>0.641</v>
       </c>
       <c r="G55" t="n">
-        <v>0.43</v>
+        <v>0.438</v>
       </c>
       <c r="H55" t="n">
         <v>0.1181</v>
@@ -4436,13 +4436,13 @@
         <v>372.1</v>
       </c>
       <c r="K55" t="n">
-        <v>4.685</v>
+        <v>4.701</v>
       </c>
       <c r="L55" t="n">
-        <v>-4.263</v>
+        <v>-4.258</v>
       </c>
       <c r="M55" t="n">
-        <v>19.902</v>
+        <v>19.921</v>
       </c>
     </row>
     <row r="56">
@@ -4649,7 +4649,7 @@
         <v>0.643</v>
       </c>
       <c r="G60" t="n">
-        <v>0.43</v>
+        <v>0.438</v>
       </c>
       <c r="H60" t="n">
         <v>0.1181</v>
@@ -4661,13 +4661,13 @@
         <v>378.9</v>
       </c>
       <c r="K60" t="n">
-        <v>4.642</v>
+        <v>4.658</v>
       </c>
       <c r="L60" t="n">
-        <v>-4.278</v>
+        <v>-4.272</v>
       </c>
       <c r="M60" t="n">
-        <v>17.88</v>
+        <v>17.899</v>
       </c>
     </row>
     <row r="61">
@@ -5285,7 +5285,7 @@
         <v>0.1229</v>
       </c>
       <c r="I74" t="n">
-        <v>20.11</v>
+        <v>20.08</v>
       </c>
       <c r="J74" t="n">
         <v>324.3</v>
@@ -9110,7 +9110,7 @@
         <v>0.1537</v>
       </c>
       <c r="I159" t="n">
-        <v>21.82</v>
+        <v>21.84</v>
       </c>
       <c r="J159" t="n">
         <v>331.2</v>
@@ -9470,7 +9470,7 @@
         <v>0.1537</v>
       </c>
       <c r="I167" t="n">
-        <v>19.68</v>
+        <v>19.65</v>
       </c>
       <c r="J167" t="n">
         <v>313</v>
@@ -10190,7 +10190,7 @@
         <v>0.1056</v>
       </c>
       <c r="I183" t="n">
-        <v>22.81</v>
+        <v>22.77</v>
       </c>
       <c r="J183" t="n">
         <v>335.2</v>
@@ -15314,7 +15314,7 @@
         <v>0.65</v>
       </c>
       <c r="G297" t="n">
-        <v>0.381</v>
+        <v>0.388</v>
       </c>
       <c r="H297" t="n">
         <v>0.0969</v>
@@ -15326,13 +15326,13 @@
         <v>359.7</v>
       </c>
       <c r="K297" t="n">
-        <v>4.64</v>
+        <v>4.654</v>
       </c>
       <c r="L297" t="n">
-        <v>-4.279</v>
+        <v>-4.274</v>
       </c>
       <c r="M297" t="n">
-        <v>17.279</v>
+        <v>17.297</v>
       </c>
     </row>
     <row r="298">
@@ -15449,7 +15449,7 @@
         <v>0.648</v>
       </c>
       <c r="G300" t="n">
-        <v>0.381</v>
+        <v>0.388</v>
       </c>
       <c r="H300" t="n">
         <v>0.0969</v>
@@ -15461,13 +15461,13 @@
         <v>350.7</v>
       </c>
       <c r="K300" t="n">
-        <v>4.698</v>
+        <v>4.712</v>
       </c>
       <c r="L300" t="n">
-        <v>-4.259</v>
+        <v>-4.254</v>
       </c>
       <c r="M300" t="n">
-        <v>17.371</v>
+        <v>17.389</v>
       </c>
     </row>
     <row r="301">
@@ -15494,7 +15494,7 @@
         <v>0.904</v>
       </c>
       <c r="G301" t="n">
-        <v>0.521</v>
+        <v>0.518</v>
       </c>
       <c r="H301" t="n">
         <v>0.1342</v>
@@ -15506,13 +15506,13 @@
         <v>351.9</v>
       </c>
       <c r="K301" t="n">
-        <v>5.561</v>
+        <v>5.555</v>
       </c>
       <c r="L301" t="n">
-        <v>-3.96</v>
+        <v>-3.962</v>
       </c>
       <c r="M301" t="n">
-        <v>21.171</v>
+        <v>21.156</v>
       </c>
     </row>
     <row r="302">
@@ -15533,13 +15533,13 @@
         <v>1</v>
       </c>
       <c r="E302" t="n">
-        <v>2.491</v>
+        <v>2.495</v>
       </c>
       <c r="F302" t="n">
         <v>0.873</v>
       </c>
       <c r="G302" t="n">
-        <v>0.55</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H302" t="n">
         <v>0.1534</v>
@@ -15551,13 +15551,13 @@
         <v>331.3</v>
       </c>
       <c r="K302" t="n">
-        <v>6.257</v>
+        <v>6.279</v>
       </c>
       <c r="L302" t="n">
-        <v>-2.411</v>
+        <v>-2.404</v>
       </c>
       <c r="M302" t="n">
-        <v>22.358</v>
+        <v>22.386</v>
       </c>
     </row>
     <row r="303">
@@ -15584,7 +15584,7 @@
         <v>0.82</v>
       </c>
       <c r="G303" t="n">
-        <v>0.487</v>
+        <v>0.495</v>
       </c>
       <c r="H303" t="n">
         <v>0.116</v>
@@ -15596,13 +15596,13 @@
         <v>352.3</v>
       </c>
       <c r="K303" t="n">
-        <v>5.296</v>
+        <v>5.312</v>
       </c>
       <c r="L303" t="n">
-        <v>-4.052</v>
+        <v>-4.046</v>
       </c>
       <c r="M303" t="n">
-        <v>20.577</v>
+        <v>20.609</v>
       </c>
     </row>
     <row r="304">
@@ -15629,7 +15629,7 @@
         <v>0.848</v>
       </c>
       <c r="G304" t="n">
-        <v>0.456</v>
+        <v>0.461</v>
       </c>
       <c r="H304" t="n">
         <v>0.098</v>
@@ -15641,13 +15641,13 @@
         <v>354.5</v>
       </c>
       <c r="K304" t="n">
-        <v>5.116</v>
+        <v>5.126</v>
       </c>
       <c r="L304" t="n">
-        <v>-4.114</v>
+        <v>-4.11</v>
       </c>
       <c r="M304" t="n">
-        <v>20.131</v>
+        <v>20.161</v>
       </c>
     </row>
     <row r="305">
@@ -15674,7 +15674,7 @@
         <v>1</v>
       </c>
       <c r="G305" t="n">
-        <v>0.521</v>
+        <v>0.518</v>
       </c>
       <c r="H305" t="n">
         <v>0.1342</v>
@@ -15686,13 +15686,13 @@
         <v>339.4</v>
       </c>
       <c r="K305" t="n">
-        <v>5.895</v>
+        <v>5.889</v>
       </c>
       <c r="L305" t="n">
-        <v>-3.844</v>
+        <v>-3.846</v>
       </c>
       <c r="M305" t="n">
-        <v>21.698</v>
+        <v>21.683</v>
       </c>
     </row>
     <row r="306">
@@ -15713,13 +15713,13 @@
         <v>1</v>
       </c>
       <c r="E306" t="n">
-        <v>2.293</v>
+        <v>2.297</v>
       </c>
       <c r="F306" t="n">
         <v>0.889</v>
       </c>
       <c r="G306" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="H306" t="n">
         <v>0.1428</v>
@@ -15731,13 +15731,13 @@
         <v>330</v>
       </c>
       <c r="K306" t="n">
-        <v>5.88</v>
+        <v>5.886</v>
       </c>
       <c r="L306" t="n">
-        <v>-2.542</v>
+        <v>-2.54</v>
       </c>
       <c r="M306" t="n">
-        <v>21.664</v>
+        <v>21.673</v>
       </c>
     </row>
     <row r="307">
@@ -15764,7 +15764,7 @@
         <v>0.896</v>
       </c>
       <c r="G307" t="n">
-        <v>0.442</v>
+        <v>0.447</v>
       </c>
       <c r="H307" t="n">
         <v>0.1103</v>
@@ -15776,13 +15776,13 @@
         <v>352.3</v>
       </c>
       <c r="K307" t="n">
-        <v>5.593</v>
+        <v>5.603</v>
       </c>
       <c r="L307" t="n">
-        <v>-3.949</v>
+        <v>-3.945</v>
       </c>
       <c r="M307" t="n">
-        <v>20.953</v>
+        <v>20.969</v>
       </c>
     </row>
     <row r="308">
@@ -15803,13 +15803,13 @@
         <v>1</v>
       </c>
       <c r="E308" t="n">
-        <v>2.409</v>
+        <v>2.413</v>
       </c>
       <c r="F308" t="n">
         <v>0.982</v>
       </c>
       <c r="G308" t="n">
-        <v>0.492</v>
+        <v>0.498</v>
       </c>
       <c r="H308" t="n">
         <v>0.1375</v>
@@ -15821,13 +15821,13 @@
         <v>325.1</v>
       </c>
       <c r="K308" t="n">
-        <v>6.182</v>
+        <v>6.198</v>
       </c>
       <c r="L308" t="n">
-        <v>-2.437</v>
+        <v>-2.432</v>
       </c>
       <c r="M308" t="n">
-        <v>22.126</v>
+        <v>22.151</v>
       </c>
     </row>
     <row r="309">
@@ -15899,7 +15899,7 @@
         <v>0.8139999999999999</v>
       </c>
       <c r="G310" t="n">
-        <v>0.431</v>
+        <v>0.436</v>
       </c>
       <c r="H310" t="n">
         <v>0.1109</v>
@@ -15911,13 +15911,13 @@
         <v>345.5</v>
       </c>
       <c r="K310" t="n">
-        <v>5.011</v>
+        <v>5.021</v>
       </c>
       <c r="L310" t="n">
-        <v>-4.15</v>
+        <v>-4.147</v>
       </c>
       <c r="M310" t="n">
-        <v>20.04</v>
+        <v>20.057</v>
       </c>
     </row>
     <row r="311">
@@ -15944,7 +15944,7 @@
         <v>0.819</v>
       </c>
       <c r="G311" t="n">
-        <v>0.444</v>
+        <v>0.449</v>
       </c>
       <c r="H311" t="n">
         <v>0.1134</v>
@@ -15956,13 +15956,13 @@
         <v>358.9</v>
       </c>
       <c r="K311" t="n">
-        <v>5.021</v>
+        <v>5.031</v>
       </c>
       <c r="L311" t="n">
-        <v>-4.147</v>
+        <v>-4.143</v>
       </c>
       <c r="M311" t="n">
-        <v>20.096</v>
+        <v>20.112</v>
       </c>
     </row>
     <row r="312">
@@ -16034,7 +16034,7 @@
         <v>0.894</v>
       </c>
       <c r="G313" t="n">
-        <v>0.456</v>
+        <v>0.461</v>
       </c>
       <c r="H313" t="n">
         <v>0.098</v>
@@ -16046,13 +16046,13 @@
         <v>345.5</v>
       </c>
       <c r="K313" t="n">
-        <v>5.359</v>
+        <v>5.369</v>
       </c>
       <c r="L313" t="n">
-        <v>-4.03</v>
+        <v>-4.026</v>
       </c>
       <c r="M313" t="n">
-        <v>20.51</v>
+        <v>20.539</v>
       </c>
     </row>
     <row r="314">
@@ -16670,7 +16670,7 @@
         <v>0.1184</v>
       </c>
       <c r="I327" t="n">
-        <v>19.65</v>
+        <v>19.68</v>
       </c>
       <c r="J327" t="n">
         <v>328.2</v>
@@ -17615,7 +17615,7 @@
         <v>0.1513</v>
       </c>
       <c r="I348" t="n">
-        <v>21.07</v>
+        <v>21.08</v>
       </c>
       <c r="J348" t="n">
         <v>320.4</v>
@@ -19775,7 +19775,7 @@
         <v>0.08890000000000001</v>
       </c>
       <c r="I396" t="n">
-        <v>24</v>
+        <v>23.96</v>
       </c>
       <c r="J396" t="n">
         <v>328</v>

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -612,7 +612,7 @@
         <v>3817</v>
       </c>
       <c r="I4" t="n">
-        <v>75.12</v>
+        <v>75.13</v>
       </c>
       <c r="J4" t="n">
         <v>34.02</v>
@@ -624,7 +624,7 @@
         <v>74.81999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -888,7 +888,7 @@
         <v>22.09</v>
       </c>
       <c r="K10" t="n">
-        <v>146.91</v>
+        <v>146.77</v>
       </c>
       <c r="L10" t="n">
         <v>64.94</v>
@@ -902,44 +902,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>28.35</v>
+        <v>28.21</v>
       </c>
       <c r="D11" t="n">
-        <v>10.83</v>
+        <v>10.06</v>
       </c>
       <c r="E11" t="n">
-        <v>6.21</v>
+        <v>6.73</v>
       </c>
       <c r="F11" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="G11" t="n">
-        <v>261</v>
+        <v>330</v>
       </c>
       <c r="H11" t="n">
-        <v>3933</v>
+        <v>4711</v>
       </c>
       <c r="I11" t="n">
-        <v>70.73</v>
+        <v>70.69</v>
       </c>
       <c r="J11" t="n">
-        <v>33.39</v>
+        <v>5.66</v>
       </c>
       <c r="K11" t="n">
-        <v>144.58</v>
+        <v>114.66</v>
       </c>
       <c r="L11" t="n">
-        <v>69.88</v>
+        <v>69.59</v>
       </c>
       <c r="M11" t="n">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -947,44 +947,44 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>28.21</v>
+        <v>28.58</v>
       </c>
       <c r="D12" t="n">
-        <v>10.06</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>6.73</v>
+        <v>6.35</v>
       </c>
       <c r="F12" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="G12" t="n">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="H12" t="n">
-        <v>4711</v>
+        <v>4227</v>
       </c>
       <c r="I12" t="n">
-        <v>70.69</v>
+        <v>70.61</v>
       </c>
       <c r="J12" t="n">
-        <v>5.66</v>
+        <v>19.62</v>
       </c>
       <c r="K12" t="n">
-        <v>114.66</v>
+        <v>122.53</v>
       </c>
       <c r="L12" t="n">
-        <v>69.59</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1</v>
+        <v>-0.68</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -992,44 +992,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>28.58</v>
+        <v>28.72</v>
       </c>
       <c r="D13" t="n">
-        <v>9.470000000000001</v>
+        <v>10.06</v>
       </c>
       <c r="E13" t="n">
-        <v>6.35</v>
+        <v>6.76</v>
       </c>
       <c r="F13" t="n">
-        <v>1.73</v>
+        <v>1.28</v>
       </c>
       <c r="G13" t="n">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="H13" t="n">
-        <v>4227</v>
+        <v>3950</v>
       </c>
       <c r="I13" t="n">
-        <v>70.61</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>19.62</v>
+        <v>33.25</v>
       </c>
       <c r="K13" t="n">
-        <v>122.53</v>
+        <v>145.92</v>
       </c>
       <c r="L13" t="n">
-        <v>71.29000000000001</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.68</v>
+        <v>-11.14</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1037,44 +1037,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>28.72</v>
+        <v>28.14</v>
       </c>
       <c r="D14" t="n">
-        <v>10.06</v>
+        <v>10.03</v>
       </c>
       <c r="E14" t="n">
-        <v>6.76</v>
+        <v>5.31</v>
       </c>
       <c r="F14" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="G14" t="n">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="H14" t="n">
-        <v>3950</v>
+        <v>3939</v>
       </c>
       <c r="I14" t="n">
-        <v>70.03</v>
+        <v>69.98</v>
       </c>
       <c r="J14" t="n">
-        <v>33.25</v>
+        <v>30.28</v>
       </c>
       <c r="K14" t="n">
-        <v>145.92</v>
+        <v>139.14</v>
       </c>
       <c r="L14" t="n">
-        <v>81.18000000000001</v>
+        <v>70.59</v>
       </c>
       <c r="M14" t="n">
-        <v>-11.15</v>
+        <v>-0.61</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1082,44 +1082,44 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>28.14</v>
+        <v>28.35</v>
       </c>
       <c r="D15" t="n">
-        <v>10.03</v>
+        <v>10.83</v>
       </c>
       <c r="E15" t="n">
-        <v>5.31</v>
+        <v>6.21</v>
       </c>
       <c r="F15" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="G15" t="n">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="H15" t="n">
-        <v>3939</v>
+        <v>3933</v>
       </c>
       <c r="I15" t="n">
-        <v>69.98</v>
+        <v>69.73</v>
       </c>
       <c r="J15" t="n">
-        <v>30.28</v>
+        <v>33.39</v>
       </c>
       <c r="K15" t="n">
-        <v>139.14</v>
+        <v>144.58</v>
       </c>
       <c r="L15" t="n">
-        <v>70.59</v>
+        <v>69.88</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.61</v>
+        <v>-0.15</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1377,7 +1377,7 @@
         <v>4072</v>
       </c>
       <c r="I21" t="n">
-        <v>67.54000000000001</v>
+        <v>67.55</v>
       </c>
       <c r="J21" t="n">
         <v>18.56</v>
@@ -1389,7 +1389,7 @@
         <v>66.34999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1602,7 +1602,7 @@
         <v>4015</v>
       </c>
       <c r="I26" t="n">
-        <v>64.43000000000001</v>
+        <v>64.44</v>
       </c>
       <c r="J26" t="n">
         <v>29.01</v>
@@ -1614,7 +1614,7 @@
         <v>67.06</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.63</v>
+        <v>-2.62</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -3077,7 +3077,7 @@
         <v>0.533</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1406</v>
+        <v>0.141</v>
       </c>
       <c r="I25" t="n">
         <v>23.32</v>
@@ -3086,13 +3086,13 @@
         <v>343.6</v>
       </c>
       <c r="K25" t="n">
-        <v>5.983</v>
+        <v>5.985</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.814</v>
+        <v>-3.813</v>
       </c>
       <c r="M25" t="n">
-        <v>21.806</v>
+        <v>21.814</v>
       </c>
     </row>
     <row r="26">
@@ -3347,7 +3347,7 @@
         <v>0.503</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1167</v>
+        <v>0.1171</v>
       </c>
       <c r="I31" t="n">
         <v>19.56</v>
@@ -3356,13 +3356,13 @@
         <v>325.4</v>
       </c>
       <c r="K31" t="n">
-        <v>6.87</v>
+        <v>6.873</v>
       </c>
       <c r="L31" t="n">
-        <v>-3.507</v>
+        <v>-3.506</v>
       </c>
       <c r="M31" t="n">
-        <v>21.4</v>
+        <v>21.409</v>
       </c>
     </row>
     <row r="32">
@@ -5690,7 +5690,7 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>23.7</v>
+        <v>23.76</v>
       </c>
       <c r="J83" t="n">
         <v>348.6</v>
@@ -7082,7 +7082,7 @@
         <v>0.59</v>
       </c>
       <c r="H114" t="n">
-        <v>0.1614</v>
+        <v>0.1618</v>
       </c>
       <c r="I114" t="n">
         <v>19.76</v>
@@ -7091,13 +7091,13 @@
         <v>336.7</v>
       </c>
       <c r="K114" t="n">
-        <v>7.394</v>
+        <v>7.397</v>
       </c>
       <c r="L114" t="n">
-        <v>-2.018</v>
+        <v>-2.017</v>
       </c>
       <c r="M114" t="n">
-        <v>22.98</v>
+        <v>22.984</v>
       </c>
     </row>
     <row r="115">
@@ -8120,19 +8120,19 @@
         <v>0.101</v>
       </c>
       <c r="I137" t="n">
-        <v>20</v>
+        <v>20.06</v>
       </c>
       <c r="J137" t="n">
         <v>325.9</v>
       </c>
       <c r="K137" t="n">
-        <v>6.796</v>
+        <v>5.796</v>
       </c>
       <c r="L137" t="n">
-        <v>-2.225</v>
+        <v>-2.571</v>
       </c>
       <c r="M137" t="n">
-        <v>21.551</v>
+        <v>21.205</v>
       </c>
     </row>
     <row r="138">
@@ -13202,7 +13202,7 @@
         <v>0.484</v>
       </c>
       <c r="H250" t="n">
-        <v>0.0864</v>
+        <v>0.0868</v>
       </c>
       <c r="I250" t="n">
         <v>20.58</v>
@@ -13211,13 +13211,13 @@
         <v>333.2</v>
       </c>
       <c r="K250" t="n">
-        <v>5.559</v>
+        <v>5.562</v>
       </c>
       <c r="L250" t="n">
-        <v>-2.653</v>
+        <v>-2.652</v>
       </c>
       <c r="M250" t="n">
-        <v>21.115</v>
+        <v>21.124</v>
       </c>
     </row>
     <row r="251">
@@ -14147,22 +14147,22 @@
         <v>0.54</v>
       </c>
       <c r="H271" t="n">
-        <v>0.1384</v>
+        <v>0.1388</v>
       </c>
       <c r="I271" t="n">
-        <v>23.27</v>
+        <v>23.33</v>
       </c>
       <c r="J271" t="n">
         <v>332.8</v>
       </c>
       <c r="K271" t="n">
-        <v>5.846</v>
+        <v>5.849</v>
       </c>
       <c r="L271" t="n">
-        <v>-2.554</v>
+        <v>-2.553</v>
       </c>
       <c r="M271" t="n">
-        <v>21.564</v>
+        <v>21.572</v>
       </c>
     </row>
     <row r="272">
@@ -14327,22 +14327,22 @@
         <v>0.54</v>
       </c>
       <c r="H275" t="n">
-        <v>0.1384</v>
+        <v>0.1388</v>
       </c>
       <c r="I275" t="n">
-        <v>25.24</v>
+        <v>25.29</v>
       </c>
       <c r="J275" t="n">
         <v>343.8</v>
       </c>
       <c r="K275" t="n">
-        <v>5.756</v>
+        <v>5.759</v>
       </c>
       <c r="L275" t="n">
-        <v>-3.892</v>
+        <v>-3.891</v>
       </c>
       <c r="M275" t="n">
-        <v>21.421</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="276">
@@ -15632,22 +15632,22 @@
         <v>0.432</v>
       </c>
       <c r="H304" t="n">
-        <v>0.1065</v>
+        <v>0.107</v>
       </c>
       <c r="I304" t="n">
-        <v>19.81</v>
+        <v>19.8</v>
       </c>
       <c r="J304" t="n">
         <v>322.8</v>
       </c>
       <c r="K304" t="n">
-        <v>6.608</v>
+        <v>6.611</v>
       </c>
       <c r="L304" t="n">
-        <v>-2.29</v>
+        <v>-2.289</v>
       </c>
       <c r="M304" t="n">
-        <v>21.272</v>
+        <v>21.28</v>
       </c>
     </row>
     <row r="305">
@@ -16577,7 +16577,7 @@
         <v>0.444</v>
       </c>
       <c r="H325" t="n">
-        <v>0.1388</v>
+        <v>0.1392</v>
       </c>
       <c r="I325" t="n">
         <v>19.4</v>
@@ -16586,13 +16586,13 @@
         <v>316.5</v>
       </c>
       <c r="K325" t="n">
-        <v>6.958</v>
+        <v>6.96</v>
       </c>
       <c r="L325" t="n">
-        <v>-2.169</v>
+        <v>-2.168</v>
       </c>
       <c r="M325" t="n">
-        <v>21.64</v>
+        <v>21.644</v>
       </c>
     </row>
     <row r="326">
@@ -17162,7 +17162,7 @@
         <v>0.546</v>
       </c>
       <c r="H338" t="n">
-        <v>0.1159</v>
+        <v>0.1165</v>
       </c>
       <c r="I338" t="n">
         <v>20.93</v>
@@ -17171,13 +17171,13 @@
         <v>330.6</v>
       </c>
       <c r="K338" t="n">
-        <v>5.954</v>
+        <v>5.958</v>
       </c>
       <c r="L338" t="n">
-        <v>-2.516</v>
+        <v>-2.515</v>
       </c>
       <c r="M338" t="n">
-        <v>21.609</v>
+        <v>21.618</v>
       </c>
     </row>
     <row r="339">
@@ -17837,7 +17837,7 @@
         <v>0.427</v>
       </c>
       <c r="H353" t="n">
-        <v>0.1188</v>
+        <v>0.1195</v>
       </c>
       <c r="I353" t="n">
         <v>21.99</v>
@@ -17846,13 +17846,13 @@
         <v>340.9</v>
       </c>
       <c r="K353" t="n">
-        <v>5.342</v>
+        <v>5.346</v>
       </c>
       <c r="L353" t="n">
-        <v>-4.036</v>
+        <v>-4.034</v>
       </c>
       <c r="M353" t="n">
-        <v>20.61</v>
+        <v>20.619</v>
       </c>
     </row>
     <row r="354">
@@ -18017,7 +18017,7 @@
         <v>0.427</v>
       </c>
       <c r="H357" t="n">
-        <v>0.1188</v>
+        <v>0.1195</v>
       </c>
       <c r="I357" t="n">
         <v>20.99</v>
@@ -18026,13 +18026,13 @@
         <v>325.4</v>
       </c>
       <c r="K357" t="n">
-        <v>5.48</v>
+        <v>5.484</v>
       </c>
       <c r="L357" t="n">
-        <v>-2.68</v>
+        <v>-2.679</v>
       </c>
       <c r="M357" t="n">
-        <v>20.821</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="358">

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -528,7 +528,7 @@
         <v>34.42</v>
       </c>
       <c r="K2" t="n">
-        <v>146.68</v>
+        <v>146.71</v>
       </c>
       <c r="L2" t="n">
         <v>75.06</v>
@@ -612,7 +612,7 @@
         <v>3817</v>
       </c>
       <c r="I4" t="n">
-        <v>75.12</v>
+        <v>75.13</v>
       </c>
       <c r="J4" t="n">
         <v>34.02</v>
@@ -624,7 +624,7 @@
         <v>74.81999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -902,44 +902,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>28.35</v>
+        <v>28.58</v>
       </c>
       <c r="D11" t="n">
-        <v>10.83</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>6.21</v>
+        <v>6.35</v>
       </c>
       <c r="F11" t="n">
-        <v>1.22</v>
+        <v>1.74</v>
       </c>
       <c r="G11" t="n">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="H11" t="n">
-        <v>3933</v>
+        <v>4227</v>
       </c>
       <c r="I11" t="n">
-        <v>70.73</v>
+        <v>70.63</v>
       </c>
       <c r="J11" t="n">
-        <v>33.39</v>
+        <v>19.62</v>
       </c>
       <c r="K11" t="n">
-        <v>144.58</v>
+        <v>122.57</v>
       </c>
       <c r="L11" t="n">
-        <v>69.88</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.85</v>
+        <v>-0.66</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -947,44 +947,44 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>28.58</v>
+        <v>27.72</v>
       </c>
       <c r="D12" t="n">
-        <v>9.470000000000001</v>
+        <v>10.06</v>
       </c>
       <c r="E12" t="n">
-        <v>6.35</v>
+        <v>6.74</v>
       </c>
       <c r="F12" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="G12" t="n">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="H12" t="n">
-        <v>4227</v>
+        <v>4715</v>
       </c>
       <c r="I12" t="n">
-        <v>70.63</v>
+        <v>70.38</v>
       </c>
       <c r="J12" t="n">
-        <v>19.62</v>
+        <v>5.35</v>
       </c>
       <c r="K12" t="n">
-        <v>122.53</v>
+        <v>114.38</v>
       </c>
       <c r="L12" t="n">
-        <v>71.29000000000001</v>
+        <v>69.59</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.66</v>
+        <v>0.79</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -992,44 +992,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>27.72</v>
+        <v>28.16</v>
       </c>
       <c r="D13" t="n">
         <v>10.06</v>
       </c>
       <c r="E13" t="n">
-        <v>6.74</v>
+        <v>5.41</v>
       </c>
       <c r="F13" t="n">
-        <v>1.68</v>
+        <v>1.2</v>
       </c>
       <c r="G13" t="n">
-        <v>333</v>
+        <v>245</v>
       </c>
       <c r="H13" t="n">
-        <v>4715</v>
+        <v>3929</v>
       </c>
       <c r="I13" t="n">
-        <v>70.38</v>
+        <v>70.27</v>
       </c>
       <c r="J13" t="n">
-        <v>5.35</v>
+        <v>30.42</v>
       </c>
       <c r="K13" t="n">
-        <v>114.38</v>
+        <v>139.33</v>
       </c>
       <c r="L13" t="n">
-        <v>69.59</v>
+        <v>70.59</v>
       </c>
       <c r="M13" t="n">
-        <v>0.79</v>
+        <v>-0.32</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1037,44 +1037,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>28.16</v>
+        <v>28.35</v>
       </c>
       <c r="D14" t="n">
-        <v>10.06</v>
+        <v>10.83</v>
       </c>
       <c r="E14" t="n">
-        <v>5.41</v>
+        <v>6.21</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="G14" t="n">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="H14" t="n">
-        <v>3929</v>
+        <v>3933</v>
       </c>
       <c r="I14" t="n">
-        <v>70.27</v>
+        <v>69.73</v>
       </c>
       <c r="J14" t="n">
-        <v>30.42</v>
+        <v>33.39</v>
       </c>
       <c r="K14" t="n">
-        <v>139.33</v>
+        <v>144.58</v>
       </c>
       <c r="L14" t="n">
-        <v>70.59</v>
+        <v>69.88</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.32</v>
+        <v>-0.15</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1287,7 +1287,7 @@
         <v>4066</v>
       </c>
       <c r="I19" t="n">
-        <v>68.34</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="J19" t="n">
         <v>19.06</v>
@@ -1299,7 +1299,7 @@
         <v>66.34999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1602,7 +1602,7 @@
         <v>4015</v>
       </c>
       <c r="I26" t="n">
-        <v>64.43000000000001</v>
+        <v>64.44</v>
       </c>
       <c r="J26" t="n">
         <v>29.01</v>
@@ -1614,7 +1614,7 @@
         <v>67.06</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.63</v>
+        <v>-2.62</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -3077,7 +3077,7 @@
         <v>0.533</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1404</v>
+        <v>0.1407</v>
       </c>
       <c r="I25" t="n">
         <v>23.34</v>
@@ -3086,13 +3086,13 @@
         <v>343.6</v>
       </c>
       <c r="K25" t="n">
-        <v>5.981</v>
+        <v>5.983</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.815</v>
+        <v>-3.814</v>
       </c>
       <c r="M25" t="n">
-        <v>21.801</v>
+        <v>21.81</v>
       </c>
     </row>
     <row r="26">
@@ -3347,7 +3347,7 @@
         <v>0.503</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1167</v>
+        <v>0.1171</v>
       </c>
       <c r="I31" t="n">
         <v>19.59</v>
@@ -3356,13 +3356,13 @@
         <v>325.4</v>
       </c>
       <c r="K31" t="n">
-        <v>6.87</v>
+        <v>6.873</v>
       </c>
       <c r="L31" t="n">
-        <v>-3.507</v>
+        <v>-3.506</v>
       </c>
       <c r="M31" t="n">
-        <v>21.4</v>
+        <v>21.409</v>
       </c>
     </row>
     <row r="32">
@@ -5690,7 +5690,7 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>23.7</v>
+        <v>23.76</v>
       </c>
       <c r="J83" t="n">
         <v>348.6</v>
@@ -7037,7 +7037,7 @@
         <v>0.645</v>
       </c>
       <c r="H113" t="n">
-        <v>0.1632</v>
+        <v>0.1636</v>
       </c>
       <c r="I113" t="n">
         <v>19.44</v>
@@ -7046,13 +7046,13 @@
         <v>336.7</v>
       </c>
       <c r="K113" t="n">
-        <v>7.604</v>
+        <v>7.607</v>
       </c>
       <c r="L113" t="n">
-        <v>-1.945</v>
+        <v>-1.944</v>
       </c>
       <c r="M113" t="n">
-        <v>23.344</v>
+        <v>23.353</v>
       </c>
     </row>
     <row r="114">
@@ -8075,19 +8075,19 @@
         <v>0.101</v>
       </c>
       <c r="I136" t="n">
-        <v>20</v>
+        <v>20.06</v>
       </c>
       <c r="J136" t="n">
         <v>325.9</v>
       </c>
       <c r="K136" t="n">
-        <v>6.796</v>
+        <v>5.796</v>
       </c>
       <c r="L136" t="n">
-        <v>-2.225</v>
+        <v>-2.571</v>
       </c>
       <c r="M136" t="n">
-        <v>21.551</v>
+        <v>21.205</v>
       </c>
     </row>
     <row r="137">
@@ -13157,7 +13157,7 @@
         <v>0.484</v>
       </c>
       <c r="H249" t="n">
-        <v>0.0863</v>
+        <v>0.0867</v>
       </c>
       <c r="I249" t="n">
         <v>20.62</v>
@@ -13166,13 +13166,13 @@
         <v>332.2</v>
       </c>
       <c r="K249" t="n">
-        <v>5.559</v>
+        <v>5.561</v>
       </c>
       <c r="L249" t="n">
-        <v>-2.653</v>
+        <v>-2.652</v>
       </c>
       <c r="M249" t="n">
-        <v>21.115</v>
+        <v>21.124</v>
       </c>
     </row>
     <row r="250">
@@ -14102,22 +14102,22 @@
         <v>0.54</v>
       </c>
       <c r="H270" t="n">
-        <v>0.1384</v>
+        <v>0.1388</v>
       </c>
       <c r="I270" t="n">
-        <v>23.32</v>
+        <v>23.38</v>
       </c>
       <c r="J270" t="n">
         <v>332.8</v>
       </c>
       <c r="K270" t="n">
-        <v>5.846</v>
+        <v>5.849</v>
       </c>
       <c r="L270" t="n">
-        <v>-2.554</v>
+        <v>-2.553</v>
       </c>
       <c r="M270" t="n">
-        <v>21.564</v>
+        <v>21.572</v>
       </c>
     </row>
     <row r="271">
@@ -14282,22 +14282,22 @@
         <v>0.54</v>
       </c>
       <c r="H274" t="n">
-        <v>0.1384</v>
+        <v>0.1388</v>
       </c>
       <c r="I274" t="n">
-        <v>25.25</v>
+        <v>25.31</v>
       </c>
       <c r="J274" t="n">
         <v>343.8</v>
       </c>
       <c r="K274" t="n">
-        <v>5.756</v>
+        <v>5.759</v>
       </c>
       <c r="L274" t="n">
-        <v>-3.892</v>
+        <v>-3.891</v>
       </c>
       <c r="M274" t="n">
-        <v>21.421</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="275">
@@ -15587,22 +15587,22 @@
         <v>0.432</v>
       </c>
       <c r="H303" t="n">
-        <v>0.1065</v>
+        <v>0.1071</v>
       </c>
       <c r="I303" t="n">
-        <v>19.87</v>
+        <v>19.86</v>
       </c>
       <c r="J303" t="n">
         <v>322.8</v>
       </c>
       <c r="K303" t="n">
-        <v>6.608</v>
+        <v>6.612</v>
       </c>
       <c r="L303" t="n">
-        <v>-2.29</v>
+        <v>-2.288</v>
       </c>
       <c r="M303" t="n">
-        <v>21.272</v>
+        <v>21.281</v>
       </c>
     </row>
     <row r="304">
@@ -16532,7 +16532,7 @@
         <v>0.444</v>
       </c>
       <c r="H324" t="n">
-        <v>0.1387</v>
+        <v>0.1391</v>
       </c>
       <c r="I324" t="n">
         <v>19.4</v>
@@ -16541,13 +16541,13 @@
         <v>316.5</v>
       </c>
       <c r="K324" t="n">
-        <v>6.957</v>
+        <v>6.96</v>
       </c>
       <c r="L324" t="n">
-        <v>-2.169</v>
+        <v>-2.168</v>
       </c>
       <c r="M324" t="n">
-        <v>21.64</v>
+        <v>21.644</v>
       </c>
     </row>
     <row r="325">
@@ -17072,7 +17072,7 @@
         <v>0.526</v>
       </c>
       <c r="H336" t="n">
-        <v>0.1131</v>
+        <v>0.1137</v>
       </c>
       <c r="I336" t="n">
         <v>20.76</v>
@@ -17081,13 +17081,13 @@
         <v>330</v>
       </c>
       <c r="K336" t="n">
-        <v>5.817</v>
+        <v>5.82</v>
       </c>
       <c r="L336" t="n">
-        <v>-2.564</v>
+        <v>-2.563</v>
       </c>
       <c r="M336" t="n">
-        <v>21.348</v>
+        <v>21.357</v>
       </c>
     </row>
     <row r="337">
@@ -17747,7 +17747,7 @@
         <v>0.427</v>
       </c>
       <c r="H351" t="n">
-        <v>0.1188</v>
+        <v>0.1195</v>
       </c>
       <c r="I351" t="n">
         <v>21.99</v>
@@ -17756,13 +17756,13 @@
         <v>340.9</v>
       </c>
       <c r="K351" t="n">
-        <v>5.342</v>
+        <v>5.346</v>
       </c>
       <c r="L351" t="n">
-        <v>-4.036</v>
+        <v>-4.034</v>
       </c>
       <c r="M351" t="n">
-        <v>20.61</v>
+        <v>20.619</v>
       </c>
     </row>
     <row r="352">
@@ -17927,7 +17927,7 @@
         <v>0.427</v>
       </c>
       <c r="H355" t="n">
-        <v>0.1188</v>
+        <v>0.1195</v>
       </c>
       <c r="I355" t="n">
         <v>20.99</v>
@@ -17936,13 +17936,13 @@
         <v>325.4</v>
       </c>
       <c r="K355" t="n">
-        <v>5.48</v>
+        <v>5.484</v>
       </c>
       <c r="L355" t="n">
-        <v>-2.68</v>
+        <v>-2.679</v>
       </c>
       <c r="M355" t="n">
-        <v>20.821</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="356">

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -497,44 +497,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>29.12</v>
+        <v>27.77</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.28</v>
+        <v>7.78</v>
       </c>
       <c r="F2" t="n">
-        <v>1.27</v>
+        <v>1.84</v>
       </c>
       <c r="G2" t="n">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="H2" t="n">
-        <v>3917</v>
+        <v>3613</v>
       </c>
       <c r="I2" t="n">
-        <v>81.31999999999999</v>
+        <v>81.14</v>
       </c>
       <c r="J2" t="n">
-        <v>34.66</v>
+        <v>35.46</v>
       </c>
       <c r="K2" t="n">
-        <v>148.45</v>
+        <v>148.8</v>
       </c>
       <c r="L2" t="n">
-        <v>69.88</v>
+        <v>75.06</v>
       </c>
       <c r="M2" t="n">
-        <v>11.44</v>
+        <v>6.08</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -542,44 +542,44 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>27.77</v>
+        <v>28.92</v>
       </c>
       <c r="D3" t="n">
-        <v>9.880000000000001</v>
+        <v>10.36</v>
       </c>
       <c r="E3" t="n">
-        <v>7.78</v>
+        <v>7.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="G3" t="n">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="H3" t="n">
-        <v>3613</v>
+        <v>3937</v>
       </c>
       <c r="I3" t="n">
-        <v>81.14</v>
+        <v>79.31</v>
       </c>
       <c r="J3" t="n">
-        <v>35.46</v>
+        <v>34.24</v>
       </c>
       <c r="K3" t="n">
-        <v>148.8</v>
+        <v>147.43</v>
       </c>
       <c r="L3" t="n">
-        <v>75.06</v>
+        <v>69.88</v>
       </c>
       <c r="M3" t="n">
-        <v>6.08</v>
+        <v>9.43</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -615,10 +615,10 @@
         <v>72.31</v>
       </c>
       <c r="J4" t="n">
-        <v>31.25</v>
+        <v>30.86</v>
       </c>
       <c r="K4" t="n">
-        <v>134.07</v>
+        <v>133.23</v>
       </c>
       <c r="L4" t="n">
         <v>68.59</v>
@@ -642,13 +642,13 @@
         <v>28.07</v>
       </c>
       <c r="D5" t="n">
-        <v>9.75</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="E5" t="n">
         <v>6.47</v>
       </c>
       <c r="F5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
         <v>255</v>
@@ -657,19 +657,19 @@
         <v>4084</v>
       </c>
       <c r="I5" t="n">
-        <v>68.94</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>31.55</v>
       </c>
       <c r="K5" t="n">
-        <v>116.71</v>
+        <v>116.88</v>
       </c>
       <c r="L5" t="n">
         <v>76.23999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-7.3</v>
+        <v>-7.14</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -677,44 +677,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>28.22</v>
+        <v>29.96</v>
       </c>
       <c r="D6" t="n">
-        <v>9.51</v>
+        <v>9.18</v>
       </c>
       <c r="E6" t="n">
-        <v>6.83</v>
+        <v>6.16</v>
       </c>
       <c r="F6" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="G6" t="n">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="H6" t="n">
-        <v>4202</v>
+        <v>4120</v>
       </c>
       <c r="I6" t="n">
-        <v>68.52</v>
+        <v>67.55</v>
       </c>
       <c r="J6" t="n">
-        <v>20.05</v>
+        <v>20.4</v>
       </c>
       <c r="K6" t="n">
-        <v>107.59</v>
+        <v>118.8</v>
       </c>
       <c r="L6" t="n">
-        <v>62.82</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -729,37 +729,37 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>31.74</v>
+        <v>31.56</v>
       </c>
       <c r="D7" t="n">
-        <v>9.050000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>5.55</v>
+        <v>5.42</v>
       </c>
       <c r="F7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
         <v>275</v>
       </c>
       <c r="H7" t="n">
-        <v>4012</v>
+        <v>4002</v>
       </c>
       <c r="I7" t="n">
-        <v>68.27</v>
+        <v>67.42</v>
       </c>
       <c r="J7" t="n">
-        <v>21.39</v>
+        <v>20.89</v>
       </c>
       <c r="K7" t="n">
-        <v>144.21</v>
+        <v>143.24</v>
       </c>
       <c r="L7" t="n">
         <v>69.18000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.91</v>
+        <v>-1.76</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -767,44 +767,44 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>27.45</v>
+        <v>27.44</v>
       </c>
       <c r="D8" t="n">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="E8" t="n">
-        <v>6.08</v>
+        <v>5.9</v>
       </c>
       <c r="F8" t="n">
-        <v>1.51</v>
+        <v>1.13</v>
       </c>
       <c r="G8" t="n">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="H8" t="n">
-        <v>3907</v>
+        <v>3522</v>
       </c>
       <c r="I8" t="n">
-        <v>67.68000000000001</v>
+        <v>66.23</v>
       </c>
       <c r="J8" t="n">
-        <v>30.42</v>
+        <v>31.25</v>
       </c>
       <c r="K8" t="n">
-        <v>143.6</v>
+        <v>134.72</v>
       </c>
       <c r="L8" t="n">
-        <v>67.76000000000001</v>
+        <v>74.41</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.08</v>
+        <v>-8.18</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -812,44 +812,44 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>29.89</v>
+        <v>26.55</v>
       </c>
       <c r="D9" t="n">
-        <v>9.16</v>
+        <v>8.85</v>
       </c>
       <c r="E9" t="n">
-        <v>6.16</v>
+        <v>7.19</v>
       </c>
       <c r="F9" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="G9" t="n">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="H9" t="n">
-        <v>4120</v>
+        <v>3561</v>
       </c>
       <c r="I9" t="n">
-        <v>67.42</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>20.33</v>
+        <v>20.45</v>
       </c>
       <c r="K9" t="n">
-        <v>118.69</v>
+        <v>135.35</v>
       </c>
       <c r="L9" t="n">
-        <v>65.65000000000001</v>
+        <v>59.53</v>
       </c>
       <c r="M9" t="n">
-        <v>1.77</v>
+        <v>6.43</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -857,44 +857,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>27.22</v>
+        <v>27.63</v>
       </c>
       <c r="D10" t="n">
-        <v>9.119999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>5.91</v>
+        <v>4.99</v>
       </c>
       <c r="F10" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="G10" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H10" t="n">
-        <v>3523</v>
+        <v>3538</v>
       </c>
       <c r="I10" t="n">
-        <v>66</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>30.74</v>
+        <v>30.09</v>
       </c>
       <c r="K10" t="n">
-        <v>133.7</v>
+        <v>134.24</v>
       </c>
       <c r="L10" t="n">
-        <v>74.41</v>
+        <v>67.94</v>
       </c>
       <c r="M10" t="n">
-        <v>-8.41</v>
+        <v>-2.68</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -902,44 +902,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>26.55</v>
+        <v>25.77</v>
       </c>
       <c r="D11" t="n">
-        <v>8.85</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>7.19</v>
+        <v>4.94</v>
       </c>
       <c r="F11" t="n">
         <v>1.22</v>
       </c>
       <c r="G11" t="n">
-        <v>265</v>
+        <v>225</v>
       </c>
       <c r="H11" t="n">
-        <v>3561</v>
+        <v>3631</v>
       </c>
       <c r="I11" t="n">
+        <v>65.09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>130.33</v>
+      </c>
+      <c r="L11" t="n">
         <v>66</v>
       </c>
-      <c r="J11" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="K11" t="n">
-        <v>135.43</v>
-      </c>
-      <c r="L11" t="n">
-        <v>59.53</v>
-      </c>
       <c r="M11" t="n">
-        <v>6.47</v>
+        <v>-0.91</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -947,7 +947,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -957,34 +957,34 @@
         <v>27.4</v>
       </c>
       <c r="D12" t="n">
-        <v>9.210000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>5.01</v>
+        <v>5.52</v>
       </c>
       <c r="F12" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="G12" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="H12" t="n">
-        <v>3541</v>
+        <v>3619</v>
       </c>
       <c r="I12" t="n">
-        <v>65.06</v>
+        <v>64.87</v>
       </c>
       <c r="J12" t="n">
-        <v>30.48</v>
+        <v>30.02</v>
       </c>
       <c r="K12" t="n">
-        <v>134.87</v>
+        <v>136.41</v>
       </c>
       <c r="L12" t="n">
-        <v>67.94</v>
+        <v>79.59</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.88</v>
+        <v>-14.72</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -992,44 +992,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>26.92</v>
+        <v>27.63</v>
       </c>
       <c r="D13" t="n">
-        <v>8.380000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="E13" t="n">
-        <v>5.44</v>
+        <v>6.05</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="G13" t="n">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="H13" t="n">
-        <v>3636</v>
+        <v>3711</v>
       </c>
       <c r="I13" t="n">
-        <v>63.54</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>29.51</v>
+        <v>18.7</v>
       </c>
       <c r="K13" t="n">
-        <v>135.16</v>
+        <v>111.57</v>
       </c>
       <c r="L13" t="n">
-        <v>79.59</v>
+        <v>57.59</v>
       </c>
       <c r="M13" t="n">
-        <v>-16.05</v>
+        <v>6.56</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1037,44 +1037,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>26.46</v>
+        <v>26.58</v>
       </c>
       <c r="D14" t="n">
-        <v>8.5</v>
+        <v>9.06</v>
       </c>
       <c r="E14" t="n">
-        <v>5.78</v>
+        <v>4.87</v>
       </c>
       <c r="F14" t="n">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="G14" t="n">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="H14" t="n">
-        <v>3815</v>
+        <v>3648</v>
       </c>
       <c r="I14" t="n">
-        <v>63.5</v>
+        <v>63.05</v>
       </c>
       <c r="J14" t="n">
-        <v>17.6</v>
+        <v>28.79</v>
       </c>
       <c r="K14" t="n">
-        <v>110.75</v>
+        <v>129.28</v>
       </c>
       <c r="L14" t="n">
-        <v>65.34999999999999</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.85</v>
+        <v>-1.66</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1082,44 +1082,44 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>27.29</v>
+        <v>25.98</v>
       </c>
       <c r="D15" t="n">
-        <v>8.51</v>
+        <v>8.15</v>
       </c>
       <c r="E15" t="n">
-        <v>5.5</v>
+        <v>6.03</v>
       </c>
       <c r="F15" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="G15" t="n">
-        <v>274</v>
+        <v>228</v>
       </c>
       <c r="H15" t="n">
-        <v>3748</v>
+        <v>3614</v>
       </c>
       <c r="I15" t="n">
-        <v>63.44</v>
+        <v>62.89</v>
       </c>
       <c r="J15" t="n">
-        <v>18.31</v>
+        <v>29.12</v>
       </c>
       <c r="K15" t="n">
-        <v>100.51</v>
+        <v>132.26</v>
       </c>
       <c r="L15" t="n">
-        <v>60.82</v>
+        <v>69.88</v>
       </c>
       <c r="M15" t="n">
-        <v>2.62</v>
+        <v>-6.99</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1127,44 +1127,44 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>25.56</v>
+        <v>27.12</v>
       </c>
       <c r="D16" t="n">
-        <v>9.390000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>4.86</v>
+        <v>5.44</v>
       </c>
       <c r="F16" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="G16" t="n">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="H16" t="n">
-        <v>3653</v>
+        <v>3758</v>
       </c>
       <c r="I16" t="n">
-        <v>63.12</v>
+        <v>62.57</v>
       </c>
       <c r="J16" t="n">
-        <v>28.21</v>
+        <v>17.86</v>
       </c>
       <c r="K16" t="n">
-        <v>129.3</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>66</v>
+        <v>60.82</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.88</v>
+        <v>1.75</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1172,44 +1172,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>27.42</v>
+        <v>26.28</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="F17" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="G17" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H17" t="n">
-        <v>3724</v>
+        <v>3833</v>
       </c>
       <c r="I17" t="n">
-        <v>62.94</v>
+        <v>62.49</v>
       </c>
       <c r="J17" t="n">
-        <v>18.31</v>
+        <v>17.21</v>
       </c>
       <c r="K17" t="n">
-        <v>110.43</v>
+        <v>109.91</v>
       </c>
       <c r="L17" t="n">
-        <v>57.59</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>5.35</v>
+        <v>-2.86</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1217,44 +1217,44 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>25.98</v>
+        <v>27.08</v>
       </c>
       <c r="D18" t="n">
-        <v>8.15</v>
+        <v>8.51</v>
       </c>
       <c r="E18" t="n">
-        <v>6.03</v>
+        <v>5.12</v>
       </c>
       <c r="F18" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="G18" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="H18" t="n">
-        <v>3614</v>
+        <v>3579</v>
       </c>
       <c r="I18" t="n">
-        <v>62.89</v>
+        <v>62.28</v>
       </c>
       <c r="J18" t="n">
-        <v>29.12</v>
+        <v>28.79</v>
       </c>
       <c r="K18" t="n">
-        <v>132.26</v>
+        <v>131.9</v>
       </c>
       <c r="L18" t="n">
-        <v>69.88</v>
+        <v>62.12</v>
       </c>
       <c r="M18" t="n">
-        <v>-6.99</v>
+        <v>0.16</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
         <v>62.23</v>
       </c>
       <c r="J19" t="n">
-        <v>29.51</v>
+        <v>29.31</v>
       </c>
       <c r="K19" t="n">
-        <v>130.07</v>
+        <v>129.57</v>
       </c>
       <c r="L19" t="n">
         <v>64.06</v>
@@ -1307,44 +1307,44 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>26.33</v>
+        <v>26.58</v>
       </c>
       <c r="D20" t="n">
-        <v>8.91</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>4.74</v>
+        <v>6.1</v>
       </c>
       <c r="F20" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="G20" t="n">
-        <v>232</v>
+        <v>273</v>
       </c>
       <c r="H20" t="n">
-        <v>3663</v>
+        <v>3739</v>
       </c>
       <c r="I20" t="n">
-        <v>62.02</v>
+        <v>61.59</v>
       </c>
       <c r="J20" t="n">
-        <v>28.02</v>
+        <v>18.25</v>
       </c>
       <c r="K20" t="n">
-        <v>127.42</v>
+        <v>95.67</v>
       </c>
       <c r="L20" t="n">
-        <v>64.70999999999999</v>
+        <v>61.47</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.69</v>
+        <v>0.12</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1352,44 +1352,44 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>11</v>
       </c>
       <c r="C21" t="n">
-        <v>25.52</v>
+        <v>25.72</v>
       </c>
       <c r="D21" t="n">
-        <v>9.52</v>
+        <v>8.26</v>
       </c>
       <c r="E21" t="n">
-        <v>5.03</v>
+        <v>6.65</v>
       </c>
       <c r="F21" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="G21" t="n">
-        <v>244</v>
+        <v>285</v>
       </c>
       <c r="H21" t="n">
-        <v>3587</v>
+        <v>3777</v>
       </c>
       <c r="I21" t="n">
-        <v>61.41</v>
+        <v>60.98</v>
       </c>
       <c r="J21" t="n">
-        <v>28.34</v>
+        <v>18.64</v>
       </c>
       <c r="K21" t="n">
-        <v>129.14</v>
+        <v>98.25</v>
       </c>
       <c r="L21" t="n">
-        <v>61.47</v>
+        <v>60.18</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.06</v>
+        <v>0.8</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1397,44 +1397,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C22" t="n">
-        <v>26.05</v>
+        <v>25.44</v>
       </c>
       <c r="D22" t="n">
-        <v>8.619999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>5.19</v>
+        <v>6.08</v>
       </c>
       <c r="F22" t="n">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="G22" t="n">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="H22" t="n">
-        <v>4346</v>
+        <v>3845</v>
       </c>
       <c r="I22" t="n">
-        <v>60.87</v>
+        <v>60.96</v>
       </c>
       <c r="J22" t="n">
-        <v>2.96</v>
+        <v>17.47</v>
       </c>
       <c r="K22" t="n">
-        <v>100.25</v>
+        <v>96.86</v>
       </c>
       <c r="L22" t="n">
-        <v>64.23999999999999</v>
+        <v>57.59</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.37</v>
+        <v>3.37</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1442,44 +1442,44 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>11</v>
       </c>
       <c r="C23" t="n">
-        <v>26.43</v>
+        <v>24.16</v>
       </c>
       <c r="D23" t="n">
-        <v>8.44</v>
+        <v>9.1</v>
       </c>
       <c r="E23" t="n">
-        <v>5.98</v>
+        <v>5.42</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9</v>
+        <v>1.29</v>
       </c>
       <c r="G23" t="n">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="H23" t="n">
-        <v>3750</v>
+        <v>3785</v>
       </c>
       <c r="I23" t="n">
-        <v>60.66</v>
+        <v>60.92</v>
       </c>
       <c r="J23" t="n">
-        <v>17.86</v>
+        <v>17.34</v>
       </c>
       <c r="K23" t="n">
-        <v>94.73</v>
+        <v>109.48</v>
       </c>
       <c r="L23" t="n">
-        <v>61.47</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3.79</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1487,44 +1487,44 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>26.62</v>
+        <v>25.91</v>
       </c>
       <c r="D24" t="n">
-        <v>8.27</v>
+        <v>8.48</v>
       </c>
       <c r="E24" t="n">
-        <v>4.98</v>
+        <v>5.14</v>
       </c>
       <c r="F24" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="G24" t="n">
-        <v>243</v>
+        <v>300</v>
       </c>
       <c r="H24" t="n">
-        <v>3736</v>
+        <v>4353</v>
       </c>
       <c r="I24" t="n">
-        <v>59.81</v>
+        <v>60.05</v>
       </c>
       <c r="J24" t="n">
-        <v>27.5</v>
+        <v>2.4</v>
       </c>
       <c r="K24" t="n">
-        <v>105.25</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>64.06</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.25</v>
+        <v>-4.19</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -1532,44 +1532,44 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>25.46</v>
+        <v>26.62</v>
       </c>
       <c r="D25" t="n">
-        <v>8.08</v>
+        <v>8.27</v>
       </c>
       <c r="E25" t="n">
-        <v>6.47</v>
+        <v>4.98</v>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G25" t="n">
-        <v>286</v>
+        <v>243</v>
       </c>
       <c r="H25" t="n">
-        <v>3786</v>
+        <v>3736</v>
       </c>
       <c r="I25" t="n">
-        <v>59.8</v>
+        <v>59.81</v>
       </c>
       <c r="J25" t="n">
-        <v>18.12</v>
+        <v>27.11</v>
       </c>
       <c r="K25" t="n">
-        <v>97.14</v>
+        <v>104.45</v>
       </c>
       <c r="L25" t="n">
-        <v>60.18</v>
+        <v>64.06</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.38</v>
+        <v>-4.25</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -1602,19 +1602,19 @@
         <v>3808</v>
       </c>
       <c r="I26" t="n">
-        <v>59.77</v>
+        <v>59.74</v>
       </c>
       <c r="J26" t="n">
         <v>17.21</v>
       </c>
       <c r="K26" t="n">
-        <v>95.75</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>58.88</v>
       </c>
       <c r="M26" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -1622,44 +1622,44 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>11</v>
       </c>
       <c r="C27" t="n">
-        <v>23.63</v>
+        <v>25.14</v>
       </c>
       <c r="D27" t="n">
-        <v>8.949999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="E27" t="n">
-        <v>5.39</v>
+        <v>4.87</v>
       </c>
       <c r="F27" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="G27" t="n">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="H27" t="n">
-        <v>3795</v>
+        <v>3629</v>
       </c>
       <c r="I27" t="n">
-        <v>59.71</v>
+        <v>59.72</v>
       </c>
       <c r="J27" t="n">
-        <v>16.69</v>
+        <v>27.76</v>
       </c>
       <c r="K27" t="n">
-        <v>107.46</v>
+        <v>127.41</v>
       </c>
       <c r="L27" t="n">
-        <v>64.70999999999999</v>
+        <v>61.47</v>
       </c>
       <c r="M27" t="n">
-        <v>-5</v>
+        <v>-1.75</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -1683,28 +1683,28 @@
         <v>6.28</v>
       </c>
       <c r="F28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="G28" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H28" t="n">
         <v>3710</v>
       </c>
       <c r="I28" t="n">
-        <v>59.19</v>
+        <v>59.08</v>
       </c>
       <c r="J28" t="n">
         <v>17.21</v>
       </c>
       <c r="K28" t="n">
-        <v>128.96</v>
+        <v>128.76</v>
       </c>
       <c r="L28" t="n">
         <v>64.06</v>
       </c>
       <c r="M28" t="n">
-        <v>-4.87</v>
+        <v>-4.98</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -1719,37 +1719,37 @@
         <v>11</v>
       </c>
       <c r="C29" t="n">
-        <v>24.67</v>
+        <v>24.84</v>
       </c>
       <c r="D29" t="n">
-        <v>8.82</v>
+        <v>8.99</v>
       </c>
       <c r="E29" t="n">
-        <v>4.93</v>
+        <v>5.05</v>
       </c>
       <c r="F29" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="G29" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H29" t="n">
-        <v>3588</v>
+        <v>3571</v>
       </c>
       <c r="I29" t="n">
-        <v>57.76</v>
+        <v>58.7</v>
       </c>
       <c r="J29" t="n">
-        <v>26.92</v>
+        <v>27.37</v>
       </c>
       <c r="K29" t="n">
-        <v>125.04</v>
+        <v>125.96</v>
       </c>
       <c r="L29" t="n">
         <v>66.65000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>-8.890000000000001</v>
+        <v>-7.95</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -1776,13 +1776,13 @@
         <v>1.08</v>
       </c>
       <c r="G30" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H30" t="n">
         <v>4292</v>
       </c>
       <c r="I30" t="n">
-        <v>56.74</v>
+        <v>56.73</v>
       </c>
       <c r="J30" t="n">
         <v>13.13</v>
@@ -1794,7 +1794,7 @@
         <v>61.41</v>
       </c>
       <c r="M30" t="n">
-        <v>-4.67</v>
+        <v>-4.68</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -1802,44 +1802,44 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>11</v>
       </c>
       <c r="C31" t="n">
-        <v>24.06</v>
+        <v>25.13</v>
       </c>
       <c r="D31" t="n">
-        <v>7.94</v>
+        <v>7.88</v>
       </c>
       <c r="E31" t="n">
-        <v>5.1</v>
+        <v>4.66</v>
       </c>
       <c r="F31" t="n">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="G31" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="H31" t="n">
-        <v>3780</v>
+        <v>3867</v>
       </c>
       <c r="I31" t="n">
-        <v>55.98</v>
+        <v>56.69</v>
       </c>
       <c r="J31" t="n">
-        <v>14.24</v>
+        <v>14.3</v>
       </c>
       <c r="K31" t="n">
-        <v>100.68</v>
+        <v>90.3</v>
       </c>
       <c r="L31" t="n">
-        <v>62.12</v>
+        <v>60.82</v>
       </c>
       <c r="M31" t="n">
-        <v>-6.14</v>
+        <v>-4.13</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -1847,44 +1847,44 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>11</v>
       </c>
       <c r="C32" t="n">
-        <v>24.57</v>
+        <v>24.24</v>
       </c>
       <c r="D32" t="n">
-        <v>7.71</v>
+        <v>7.93</v>
       </c>
       <c r="E32" t="n">
-        <v>4.49</v>
+        <v>5.07</v>
       </c>
       <c r="F32" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="G32" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="H32" t="n">
-        <v>3874</v>
+        <v>3779</v>
       </c>
       <c r="I32" t="n">
-        <v>55.16</v>
+        <v>56.15</v>
       </c>
       <c r="J32" t="n">
-        <v>13.2</v>
+        <v>14.56</v>
       </c>
       <c r="K32" t="n">
-        <v>88.05</v>
+        <v>101.63</v>
       </c>
       <c r="L32" t="n">
-        <v>60.82</v>
+        <v>62.12</v>
       </c>
       <c r="M32" t="n">
-        <v>-5.66</v>
+        <v>-5.97</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -1911,7 +1911,7 @@
         <v>1.13</v>
       </c>
       <c r="G33" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H33" t="n">
         <v>3774</v>
@@ -1945,7 +1945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M361"/>
+  <dimension ref="A1:M359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2258,31 +2258,31 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>2.233</v>
+        <v>2.389</v>
       </c>
       <c r="F7" t="n">
-        <v>0.64</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.52</v>
+        <v>0.655</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0844</v>
+        <v>0.1107</v>
       </c>
       <c r="I7" t="n">
-        <v>25.44</v>
+        <v>25.19</v>
       </c>
       <c r="J7" t="n">
-        <v>339.1</v>
+        <v>331.7</v>
       </c>
       <c r="K7" t="n">
-        <v>5.059</v>
+        <v>5.997</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.134</v>
+        <v>-2.501</v>
       </c>
       <c r="M7" t="n">
-        <v>17.896</v>
+        <v>21.685</v>
       </c>
     </row>
     <row r="8">
@@ -2303,31 +2303,31 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>2.116</v>
+        <v>2.219</v>
       </c>
       <c r="F8" t="n">
-        <v>0.656</v>
+        <v>0.654</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.605</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0795</v>
+        <v>0.0893</v>
       </c>
       <c r="I8" t="n">
-        <v>26.64</v>
+        <v>26.04</v>
       </c>
       <c r="J8" t="n">
-        <v>354.7</v>
+        <v>353</v>
       </c>
       <c r="K8" t="n">
-        <v>5.029</v>
+        <v>5.273</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.144</v>
+        <v>-4.06</v>
       </c>
       <c r="M8" t="n">
-        <v>17.836</v>
+        <v>18.338</v>
       </c>
     </row>
     <row r="9">
@@ -2843,31 +2843,31 @@
         <v>-1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.256</v>
+        <v>2.468</v>
       </c>
       <c r="F20" t="n">
-        <v>0.658</v>
+        <v>0.822</v>
       </c>
       <c r="G20" t="n">
-        <v>0.473</v>
+        <v>0.618</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1065</v>
+        <v>0.169</v>
       </c>
       <c r="I20" t="n">
-        <v>24.64</v>
+        <v>24.2</v>
       </c>
       <c r="J20" t="n">
-        <v>343.9</v>
+        <v>330.7</v>
       </c>
       <c r="K20" t="n">
-        <v>5.157</v>
+        <v>6.362</v>
       </c>
       <c r="L20" t="n">
-        <v>-4.1</v>
+        <v>-2.375</v>
       </c>
       <c r="M20" t="n">
-        <v>20.187</v>
+        <v>22.633</v>
       </c>
     </row>
     <row r="21">
@@ -3077,22 +3077,22 @@
         <v>0.573</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1277</v>
+        <v>0.1273</v>
       </c>
       <c r="I25" t="n">
-        <v>20.76</v>
+        <v>20.74</v>
       </c>
       <c r="J25" t="n">
         <v>304.4</v>
       </c>
       <c r="K25" t="n">
-        <v>6.277</v>
+        <v>6.275</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.404</v>
+        <v>-2.405</v>
       </c>
       <c r="M25" t="n">
-        <v>21.8</v>
+        <v>21.792</v>
       </c>
     </row>
     <row r="26">
@@ -3122,7 +3122,7 @@
         <v>0.573</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1277</v>
+        <v>0.1273</v>
       </c>
       <c r="I26" t="n">
         <v>19.22</v>
@@ -3131,13 +3131,13 @@
         <v>294.9</v>
       </c>
       <c r="K26" t="n">
-        <v>9.33</v>
+        <v>9.327999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>-1.348</v>
       </c>
       <c r="M26" t="n">
-        <v>22.909</v>
+        <v>22.901</v>
       </c>
     </row>
     <row r="27">
@@ -3167,7 +3167,7 @@
         <v>0.573</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1277</v>
+        <v>0.1273</v>
       </c>
       <c r="I27" t="n">
         <v>19.22</v>
@@ -3176,13 +3176,13 @@
         <v>294.9</v>
       </c>
       <c r="K27" t="n">
-        <v>9.33</v>
+        <v>9.327999999999999</v>
       </c>
       <c r="L27" t="n">
         <v>-1.348</v>
       </c>
       <c r="M27" t="n">
-        <v>22.909</v>
+        <v>22.901</v>
       </c>
     </row>
     <row r="28">
@@ -3215,7 +3215,7 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>20.58</v>
+        <v>20.57</v>
       </c>
       <c r="J28" t="n">
         <v>314.7</v>
@@ -3260,7 +3260,7 @@
         <v>0.1087</v>
       </c>
       <c r="I29" t="n">
-        <v>20.46</v>
+        <v>20.43</v>
       </c>
       <c r="J29" t="n">
         <v>321.3</v>
@@ -3350,7 +3350,7 @@
         <v>0.0921</v>
       </c>
       <c r="I31" t="n">
-        <v>20.13</v>
+        <v>20.1</v>
       </c>
       <c r="J31" t="n">
         <v>322.3</v>
@@ -3440,7 +3440,7 @@
         <v>0.1072</v>
       </c>
       <c r="I33" t="n">
-        <v>19.33</v>
+        <v>19.29</v>
       </c>
       <c r="J33" t="n">
         <v>320</v>
@@ -3530,7 +3530,7 @@
         <v>0.1132</v>
       </c>
       <c r="I35" t="n">
-        <v>23.31</v>
+        <v>23.37</v>
       </c>
       <c r="J35" t="n">
         <v>340.9</v>
@@ -3575,7 +3575,7 @@
         <v>0.0939</v>
       </c>
       <c r="I36" t="n">
-        <v>23.32</v>
+        <v>23.47</v>
       </c>
       <c r="J36" t="n">
         <v>351.5</v>
@@ -3620,7 +3620,7 @@
         <v>0.0837</v>
       </c>
       <c r="I37" t="n">
-        <v>22.65</v>
+        <v>22.74</v>
       </c>
       <c r="J37" t="n">
         <v>350.8</v>
@@ -3665,7 +3665,7 @@
         <v>0.1201</v>
       </c>
       <c r="I38" t="n">
-        <v>22.81</v>
+        <v>22.86</v>
       </c>
       <c r="J38" t="n">
         <v>338.5</v>
@@ -3710,7 +3710,7 @@
         <v>0.1054</v>
       </c>
       <c r="I39" t="n">
-        <v>22.11</v>
+        <v>22.12</v>
       </c>
       <c r="J39" t="n">
         <v>320.4</v>
@@ -3755,7 +3755,7 @@
         <v>0.1045</v>
       </c>
       <c r="I40" t="n">
-        <v>23.05</v>
+        <v>23.2</v>
       </c>
       <c r="J40" t="n">
         <v>350.3</v>
@@ -3800,7 +3800,7 @@
         <v>0.108</v>
       </c>
       <c r="I41" t="n">
-        <v>23.09</v>
+        <v>23.21</v>
       </c>
       <c r="J41" t="n">
         <v>353.9</v>
@@ -3845,7 +3845,7 @@
         <v>0.096</v>
       </c>
       <c r="I42" t="n">
-        <v>23.38</v>
+        <v>23.45</v>
       </c>
       <c r="J42" t="n">
         <v>326.4</v>
@@ -3890,7 +3890,7 @@
         <v>0.101</v>
       </c>
       <c r="I43" t="n">
-        <v>23.15</v>
+        <v>23.27</v>
       </c>
       <c r="J43" t="n">
         <v>354.6</v>
@@ -3935,7 +3935,7 @@
         <v>0.1201</v>
       </c>
       <c r="I44" t="n">
-        <v>22.9</v>
+        <v>23.05</v>
       </c>
       <c r="J44" t="n">
         <v>350.8</v>
@@ -3980,7 +3980,7 @@
         <v>0.0837</v>
       </c>
       <c r="I45" t="n">
-        <v>22.68</v>
+        <v>22.69</v>
       </c>
       <c r="J45" t="n">
         <v>335.9</v>
@@ -4115,7 +4115,7 @@
         <v>0.1279</v>
       </c>
       <c r="I48" t="n">
-        <v>25.86</v>
+        <v>25.88</v>
       </c>
       <c r="J48" t="n">
         <v>362.8</v>
@@ -4160,7 +4160,7 @@
         <v>0.0998</v>
       </c>
       <c r="I49" t="n">
-        <v>26.93</v>
+        <v>26.94</v>
       </c>
       <c r="J49" t="n">
         <v>366.9</v>
@@ -4250,7 +4250,7 @@
         <v>0.0963</v>
       </c>
       <c r="I51" t="n">
-        <v>27.09</v>
+        <v>27.11</v>
       </c>
       <c r="J51" t="n">
         <v>371.7</v>
@@ -4295,7 +4295,7 @@
         <v>0.1043</v>
       </c>
       <c r="I52" t="n">
-        <v>26.25</v>
+        <v>26.23</v>
       </c>
       <c r="J52" t="n">
         <v>373</v>
@@ -4430,7 +4430,7 @@
         <v>0.1027</v>
       </c>
       <c r="I55" t="n">
-        <v>26.77</v>
+        <v>26.78</v>
       </c>
       <c r="J55" t="n">
         <v>370.9</v>
@@ -4508,31 +4508,31 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>2.267</v>
+        <v>2.125</v>
       </c>
       <c r="F57" t="n">
-        <v>0.806</v>
+        <v>0.662</v>
       </c>
       <c r="G57" t="n">
-        <v>0.486</v>
+        <v>0.434</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1536</v>
+        <v>0.1072</v>
       </c>
       <c r="I57" t="n">
-        <v>24.02</v>
+        <v>23.59</v>
       </c>
       <c r="J57" t="n">
-        <v>345.9</v>
+        <v>353.6</v>
       </c>
       <c r="K57" t="n">
-        <v>5.773</v>
+        <v>4.96</v>
       </c>
       <c r="L57" t="n">
-        <v>-2.579</v>
+        <v>-4.168</v>
       </c>
       <c r="M57" t="n">
-        <v>22.004</v>
+        <v>20.257</v>
       </c>
     </row>
     <row r="58">
@@ -5060,7 +5060,7 @@
         <v>0.1051</v>
       </c>
       <c r="I69" t="n">
-        <v>23.89</v>
+        <v>23.91</v>
       </c>
       <c r="J69" t="n">
         <v>357.7</v>
@@ -5105,7 +5105,7 @@
         <v>0.1045</v>
       </c>
       <c r="I70" t="n">
-        <v>23.15</v>
+        <v>23.13</v>
       </c>
       <c r="J70" t="n">
         <v>330.4</v>
@@ -5138,31 +5138,31 @@
         <v>-1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.503</v>
+        <v>2.347</v>
       </c>
       <c r="F71" t="n">
-        <v>0.847</v>
+        <v>0.697</v>
       </c>
       <c r="G71" t="n">
-        <v>0.599</v>
+        <v>0.475</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1224</v>
+        <v>0.0895</v>
       </c>
       <c r="I71" t="n">
-        <v>24.67</v>
+        <v>24.57</v>
       </c>
       <c r="J71" t="n">
-        <v>341.6</v>
+        <v>349.4</v>
       </c>
       <c r="K71" t="n">
-        <v>6.129</v>
+        <v>5.228</v>
       </c>
       <c r="L71" t="n">
-        <v>-3.763</v>
+        <v>-4.075</v>
       </c>
       <c r="M71" t="n">
-        <v>21.953</v>
+        <v>20.153</v>
       </c>
     </row>
     <row r="72">
@@ -5195,7 +5195,7 @@
         <v>0.0873</v>
       </c>
       <c r="I72" t="n">
-        <v>22.36</v>
+        <v>22.38</v>
       </c>
       <c r="J72" t="n">
         <v>344.1</v>
@@ -5228,31 +5228,31 @@
         <v>-1</v>
       </c>
       <c r="E73" t="n">
-        <v>2.276</v>
+        <v>2.503</v>
       </c>
       <c r="F73" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.847</v>
       </c>
       <c r="G73" t="n">
-        <v>0.479</v>
+        <v>0.599</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0835</v>
+        <v>0.1224</v>
       </c>
       <c r="I73" t="n">
-        <v>24.53</v>
+        <v>24.72</v>
       </c>
       <c r="J73" t="n">
-        <v>349.4</v>
+        <v>341.6</v>
       </c>
       <c r="K73" t="n">
-        <v>5.101</v>
+        <v>6.129</v>
       </c>
       <c r="L73" t="n">
-        <v>-4.119</v>
+        <v>-3.763</v>
       </c>
       <c r="M73" t="n">
-        <v>19.906</v>
+        <v>21.953</v>
       </c>
     </row>
     <row r="74">
@@ -5285,7 +5285,7 @@
         <v>0.0827</v>
       </c>
       <c r="I74" t="n">
-        <v>22.02</v>
+        <v>22.04</v>
       </c>
       <c r="J74" t="n">
         <v>337.4</v>
@@ -5330,7 +5330,7 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>24.74</v>
+        <v>24.8</v>
       </c>
       <c r="J75" t="n">
         <v>352.5</v>
@@ -5375,7 +5375,7 @@
         <v>0.097</v>
       </c>
       <c r="I76" t="n">
-        <v>21.76</v>
+        <v>21.77</v>
       </c>
       <c r="J76" t="n">
         <v>325.4</v>
@@ -5420,7 +5420,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>24.93</v>
+        <v>24.98</v>
       </c>
       <c r="J77" t="n">
         <v>348.2</v>
@@ -5465,7 +5465,7 @@
         <v>0.1002</v>
       </c>
       <c r="I78" t="n">
-        <v>24.04</v>
+        <v>24.06</v>
       </c>
       <c r="J78" t="n">
         <v>347.5</v>
@@ -5510,7 +5510,7 @@
         <v>0.1051</v>
       </c>
       <c r="I79" t="n">
-        <v>23.16</v>
+        <v>23.15</v>
       </c>
       <c r="J79" t="n">
         <v>347.1</v>
@@ -5555,7 +5555,7 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>23.74</v>
+        <v>23.78</v>
       </c>
       <c r="J80" t="n">
         <v>338.7</v>
@@ -5597,7 +5597,7 @@
         <v>0.524</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1201</v>
+        <v>0.1204</v>
       </c>
       <c r="I81" t="n">
         <v>24.75</v>
@@ -5606,13 +5606,13 @@
         <v>346.6</v>
       </c>
       <c r="K81" t="n">
-        <v>5.801</v>
+        <v>5.802</v>
       </c>
       <c r="L81" t="n">
         <v>-2.569</v>
       </c>
       <c r="M81" t="n">
-        <v>21.798</v>
+        <v>21.802</v>
       </c>
     </row>
     <row r="82">
@@ -5642,7 +5642,7 @@
         <v>0.488</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1182</v>
+        <v>0.1184</v>
       </c>
       <c r="I82" t="n">
         <v>25.3</v>
@@ -5651,13 +5651,13 @@
         <v>365</v>
       </c>
       <c r="K82" t="n">
-        <v>5.491</v>
+        <v>5.492</v>
       </c>
       <c r="L82" t="n">
         <v>-3.984</v>
       </c>
       <c r="M82" t="n">
-        <v>21.247</v>
+        <v>21.251</v>
       </c>
     </row>
     <row r="83">
@@ -5687,7 +5687,7 @@
         <v>0.508</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1151</v>
+        <v>0.1153</v>
       </c>
       <c r="I83" t="n">
         <v>24.78</v>
@@ -5696,13 +5696,13 @@
         <v>355.7</v>
       </c>
       <c r="K83" t="n">
-        <v>5.746</v>
+        <v>5.747</v>
       </c>
       <c r="L83" t="n">
         <v>-3.896</v>
       </c>
       <c r="M83" t="n">
-        <v>21.655</v>
+        <v>21.659</v>
       </c>
     </row>
     <row r="84">
@@ -5732,7 +5732,7 @@
         <v>0.636</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1293</v>
+        <v>0.1296</v>
       </c>
       <c r="I84" t="n">
         <v>22.47</v>
@@ -5741,13 +5741,13 @@
         <v>341.9</v>
       </c>
       <c r="K84" t="n">
-        <v>5.832</v>
+        <v>5.834</v>
       </c>
       <c r="L84" t="n">
         <v>-2.558</v>
       </c>
       <c r="M84" t="n">
-        <v>21.992</v>
+        <v>21.996</v>
       </c>
     </row>
     <row r="85">
@@ -5777,7 +5777,7 @@
         <v>0.495</v>
       </c>
       <c r="H85" t="n">
-        <v>0.1428</v>
+        <v>0.1431</v>
       </c>
       <c r="I85" t="n">
         <v>20.86</v>
@@ -5786,13 +5786,13 @@
         <v>333.9</v>
       </c>
       <c r="K85" t="n">
-        <v>5.873</v>
+        <v>5.875</v>
       </c>
       <c r="L85" t="n">
         <v>-2.544</v>
       </c>
       <c r="M85" t="n">
-        <v>22.088</v>
+        <v>22.093</v>
       </c>
     </row>
     <row r="86">
@@ -5822,7 +5822,7 @@
         <v>0.497</v>
       </c>
       <c r="H86" t="n">
-        <v>0.117</v>
+        <v>0.1172</v>
       </c>
       <c r="I86" t="n">
         <v>21.68</v>
@@ -5831,13 +5831,13 @@
         <v>341.1</v>
       </c>
       <c r="K86" t="n">
-        <v>5.663</v>
+        <v>5.664</v>
       </c>
       <c r="L86" t="n">
         <v>-2.617</v>
       </c>
       <c r="M86" t="n">
-        <v>21.503</v>
+        <v>21.507</v>
       </c>
     </row>
     <row r="87">
@@ -5858,31 +5858,31 @@
         <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>2.443</v>
+        <v>2.261</v>
       </c>
       <c r="F87" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="G87" t="n">
-        <v>0.625</v>
+        <v>0.45</v>
       </c>
       <c r="H87" t="n">
-        <v>0.1615</v>
+        <v>0.1243</v>
       </c>
       <c r="I87" t="n">
-        <v>21.46</v>
+        <v>22.07</v>
       </c>
       <c r="J87" t="n">
-        <v>329.4</v>
+        <v>347.2</v>
       </c>
       <c r="K87" t="n">
-        <v>6.322</v>
+        <v>5.307</v>
       </c>
       <c r="L87" t="n">
-        <v>-2.389</v>
+        <v>-2.74</v>
       </c>
       <c r="M87" t="n">
-        <v>23.01</v>
+        <v>20.977</v>
       </c>
     </row>
     <row r="88">
@@ -5912,7 +5912,7 @@
         <v>0.517</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1089</v>
+        <v>0.1091</v>
       </c>
       <c r="I88" t="n">
         <v>24.7</v>
@@ -5921,13 +5921,13 @@
         <v>348.8</v>
       </c>
       <c r="K88" t="n">
-        <v>5.751</v>
+        <v>5.753</v>
       </c>
       <c r="L88" t="n">
         <v>-2.586</v>
       </c>
       <c r="M88" t="n">
-        <v>21.61</v>
+        <v>21.615</v>
       </c>
     </row>
     <row r="89">
@@ -5957,7 +5957,7 @@
         <v>0.473</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1327</v>
+        <v>0.1329</v>
       </c>
       <c r="I89" t="n">
         <v>23.44</v>
@@ -5966,13 +5966,13 @@
         <v>361.1</v>
       </c>
       <c r="K89" t="n">
-        <v>5.273</v>
+        <v>5.274</v>
       </c>
       <c r="L89" t="n">
-        <v>-4.06</v>
+        <v>-4.059</v>
       </c>
       <c r="M89" t="n">
-        <v>21.025</v>
+        <v>21.03</v>
       </c>
     </row>
     <row r="90">
@@ -6002,7 +6002,7 @@
         <v>0.519</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1509</v>
+        <v>0.1512</v>
       </c>
       <c r="I90" t="n">
         <v>21.49</v>
@@ -6011,13 +6011,13 @@
         <v>336.5</v>
       </c>
       <c r="K90" t="n">
-        <v>6.146</v>
+        <v>6.148</v>
       </c>
       <c r="L90" t="n">
-        <v>-2.45</v>
+        <v>-2.449</v>
       </c>
       <c r="M90" t="n">
-        <v>22.604</v>
+        <v>22.608</v>
       </c>
     </row>
     <row r="91">
@@ -6047,7 +6047,7 @@
         <v>0.497</v>
       </c>
       <c r="H91" t="n">
-        <v>0.117</v>
+        <v>0.1172</v>
       </c>
       <c r="I91" t="n">
         <v>24.15</v>
@@ -6056,13 +6056,13 @@
         <v>354.9</v>
       </c>
       <c r="K91" t="n">
-        <v>5.597</v>
+        <v>5.598</v>
       </c>
       <c r="L91" t="n">
         <v>-3.947</v>
       </c>
       <c r="M91" t="n">
-        <v>21.408</v>
+        <v>21.412</v>
       </c>
     </row>
     <row r="92">
@@ -6083,31 +6083,31 @@
         <v>-1</v>
       </c>
       <c r="E92" t="n">
-        <v>1.835</v>
+        <v>2.01</v>
       </c>
       <c r="F92" t="n">
-        <v>0.614</v>
+        <v>0.608</v>
       </c>
       <c r="G92" t="n">
-        <v>0.368</v>
+        <v>0.407</v>
       </c>
       <c r="H92" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0862</v>
       </c>
       <c r="I92" t="n">
-        <v>25.42</v>
+        <v>25.78</v>
       </c>
       <c r="J92" t="n">
-        <v>367.8</v>
+        <v>365</v>
       </c>
       <c r="K92" t="n">
-        <v>4.248</v>
+        <v>4.557</v>
       </c>
       <c r="L92" t="n">
-        <v>-4.414</v>
+        <v>-4.307</v>
       </c>
       <c r="M92" t="n">
-        <v>15.77</v>
+        <v>16.381</v>
       </c>
     </row>
     <row r="93">
@@ -6140,7 +6140,7 @@
         <v>0.1225</v>
       </c>
       <c r="I93" t="n">
-        <v>24.01</v>
+        <v>23.96</v>
       </c>
       <c r="J93" t="n">
         <v>338.9</v>
@@ -6185,7 +6185,7 @@
         <v>0.1123</v>
       </c>
       <c r="I94" t="n">
-        <v>25.58</v>
+        <v>25.53</v>
       </c>
       <c r="J94" t="n">
         <v>361</v>
@@ -6230,7 +6230,7 @@
         <v>0.08890000000000001</v>
       </c>
       <c r="I95" t="n">
-        <v>25.55</v>
+        <v>25.49</v>
       </c>
       <c r="J95" t="n">
         <v>350.5</v>
@@ -6275,7 +6275,7 @@
         <v>0.09909999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>25.16</v>
+        <v>25.11</v>
       </c>
       <c r="J96" t="n">
         <v>345.2</v>
@@ -6308,31 +6308,31 @@
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>1.901</v>
+        <v>2.065</v>
       </c>
       <c r="F97" t="n">
-        <v>0.612</v>
+        <v>0.606</v>
       </c>
       <c r="G97" t="n">
-        <v>0.368</v>
+        <v>0.407</v>
       </c>
       <c r="H97" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0862</v>
       </c>
       <c r="I97" t="n">
-        <v>25.69</v>
+        <v>25.21</v>
       </c>
       <c r="J97" t="n">
-        <v>361.4</v>
+        <v>357.7</v>
       </c>
       <c r="K97" t="n">
-        <v>4.31</v>
+        <v>4.608</v>
       </c>
       <c r="L97" t="n">
-        <v>-4.393</v>
+        <v>-4.29</v>
       </c>
       <c r="M97" t="n">
-        <v>15.87</v>
+        <v>19.079</v>
       </c>
     </row>
     <row r="98">
@@ -6365,7 +6365,7 @@
         <v>0.107</v>
       </c>
       <c r="I98" t="n">
-        <v>25.51</v>
+        <v>25.45</v>
       </c>
       <c r="J98" t="n">
         <v>352.2</v>
@@ -6410,7 +6410,7 @@
         <v>0.0834</v>
       </c>
       <c r="I99" t="n">
-        <v>25.23</v>
+        <v>25.2</v>
       </c>
       <c r="J99" t="n">
         <v>354.4</v>
@@ -6455,7 +6455,7 @@
         <v>0.1056</v>
       </c>
       <c r="I100" t="n">
-        <v>24.54</v>
+        <v>24.51</v>
       </c>
       <c r="J100" t="n">
         <v>343.4</v>
@@ -6500,7 +6500,7 @@
         <v>0.0833</v>
       </c>
       <c r="I101" t="n">
-        <v>25.3</v>
+        <v>25.26</v>
       </c>
       <c r="J101" t="n">
         <v>345.2</v>
@@ -6533,31 +6533,31 @@
         <v>-1</v>
       </c>
       <c r="E102" t="n">
-        <v>1.992</v>
+        <v>2.213</v>
       </c>
       <c r="F102" t="n">
-        <v>0.589</v>
+        <v>0.768</v>
       </c>
       <c r="G102" t="n">
-        <v>0.381</v>
+        <v>0.478</v>
       </c>
       <c r="H102" t="n">
-        <v>0.081</v>
+        <v>0.1056</v>
       </c>
       <c r="I102" t="n">
-        <v>25.75</v>
+        <v>25.33</v>
       </c>
       <c r="J102" t="n">
-        <v>354.5</v>
+        <v>353.6</v>
       </c>
       <c r="K102" t="n">
-        <v>4.418</v>
+        <v>5.339</v>
       </c>
       <c r="L102" t="n">
-        <v>-4.356</v>
+        <v>-4.037</v>
       </c>
       <c r="M102" t="n">
-        <v>16.746</v>
+        <v>20.526</v>
       </c>
     </row>
     <row r="103">
@@ -6590,7 +6590,7 @@
         <v>0.1679</v>
       </c>
       <c r="I103" t="n">
-        <v>19.68</v>
+        <v>19.64</v>
       </c>
       <c r="J103" t="n">
         <v>328.7</v>
@@ -6635,7 +6635,7 @@
         <v>0.2096</v>
       </c>
       <c r="I104" t="n">
-        <v>19.36</v>
+        <v>19.34</v>
       </c>
       <c r="J104" t="n">
         <v>309.1</v>
@@ -6680,7 +6680,7 @@
         <v>0.1399</v>
       </c>
       <c r="I105" t="n">
-        <v>20.37</v>
+        <v>20.3</v>
       </c>
       <c r="J105" t="n">
         <v>337.7</v>
@@ -6725,7 +6725,7 @@
         <v>0.1715</v>
       </c>
       <c r="I106" t="n">
-        <v>19.4</v>
+        <v>19.34</v>
       </c>
       <c r="J106" t="n">
         <v>314.9</v>
@@ -6737,7 +6737,7 @@
         <v>-1.852</v>
       </c>
       <c r="M106" t="n">
-        <v>23.848</v>
+        <v>25.809</v>
       </c>
     </row>
     <row r="107">
@@ -6770,7 +6770,7 @@
         <v>0.1489</v>
       </c>
       <c r="I107" t="n">
-        <v>21.01</v>
+        <v>20.98</v>
       </c>
       <c r="J107" t="n">
         <v>347.8</v>
@@ -6815,7 +6815,7 @@
         <v>0.1551</v>
       </c>
       <c r="I108" t="n">
-        <v>19.85</v>
+        <v>19.81</v>
       </c>
       <c r="J108" t="n">
         <v>330.7</v>
@@ -6860,7 +6860,7 @@
         <v>0.1604</v>
       </c>
       <c r="I109" t="n">
-        <v>20.48</v>
+        <v>20.46</v>
       </c>
       <c r="J109" t="n">
         <v>347</v>
@@ -6905,7 +6905,7 @@
         <v>0.1715</v>
       </c>
       <c r="I110" t="n">
-        <v>19.64</v>
+        <v>19.6</v>
       </c>
       <c r="J110" t="n">
         <v>332.3</v>
@@ -6950,7 +6950,7 @@
         <v>0.1904</v>
       </c>
       <c r="I111" t="n">
-        <v>19.42</v>
+        <v>19.39</v>
       </c>
       <c r="J111" t="n">
         <v>308.5</v>
@@ -6995,7 +6995,7 @@
         <v>0.1347</v>
       </c>
       <c r="I112" t="n">
-        <v>20.58</v>
+        <v>20.51</v>
       </c>
       <c r="J112" t="n">
         <v>347.8</v>
@@ -7040,7 +7040,7 @@
         <v>0.1904</v>
       </c>
       <c r="I113" t="n">
-        <v>19.42</v>
+        <v>19.39</v>
       </c>
       <c r="J113" t="n">
         <v>308.5</v>
@@ -7082,22 +7082,22 @@
         <v>0.461</v>
       </c>
       <c r="H114" t="n">
-        <v>0.1128</v>
+        <v>0.1133</v>
       </c>
       <c r="I114" t="n">
         <v>23.29</v>
       </c>
       <c r="J114" t="n">
-        <v>338.6</v>
+        <v>337.5</v>
       </c>
       <c r="K114" t="n">
-        <v>5.696</v>
+        <v>5.699</v>
       </c>
       <c r="L114" t="n">
-        <v>-3.913</v>
+        <v>-3.912</v>
       </c>
       <c r="M114" t="n">
-        <v>20.671</v>
+        <v>20.676</v>
       </c>
     </row>
     <row r="115">
@@ -7133,7 +7133,7 @@
         <v>23.06</v>
       </c>
       <c r="J115" t="n">
-        <v>332.2</v>
+        <v>331.1</v>
       </c>
       <c r="K115" t="n">
         <v>5.421</v>
@@ -7172,22 +7172,22 @@
         <v>0.449</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1166</v>
+        <v>0.1171</v>
       </c>
       <c r="I116" t="n">
         <v>22.91</v>
       </c>
       <c r="J116" t="n">
-        <v>343</v>
+        <v>341.8</v>
       </c>
       <c r="K116" t="n">
-        <v>5.388</v>
+        <v>5.391</v>
       </c>
       <c r="L116" t="n">
-        <v>-4.02</v>
+        <v>-4.019</v>
       </c>
       <c r="M116" t="n">
-        <v>20.24</v>
+        <v>20.249</v>
       </c>
     </row>
     <row r="117">
@@ -7223,7 +7223,7 @@
         <v>22.66</v>
       </c>
       <c r="J117" t="n">
-        <v>326.5</v>
+        <v>325.3</v>
       </c>
       <c r="K117" t="n">
         <v>5.907</v>
@@ -7262,16 +7262,16 @@
         <v>0.477</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0861</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I118" t="n">
         <v>21.76</v>
       </c>
       <c r="J118" t="n">
-        <v>333</v>
+        <v>331.8</v>
       </c>
       <c r="K118" t="n">
-        <v>5.567</v>
+        <v>5.566</v>
       </c>
       <c r="L118" t="n">
         <v>-3.958</v>
@@ -7313,7 +7313,7 @@
         <v>22.94</v>
       </c>
       <c r="J119" t="n">
-        <v>324.6</v>
+        <v>323.4</v>
       </c>
       <c r="K119" t="n">
         <v>5.649</v>
@@ -7343,31 +7343,31 @@
         <v>-1</v>
       </c>
       <c r="E120" t="n">
-        <v>2.689</v>
+        <v>2.514</v>
       </c>
       <c r="F120" t="n">
-        <v>0.86</v>
+        <v>0.698</v>
       </c>
       <c r="G120" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.439</v>
       </c>
       <c r="H120" t="n">
-        <v>0.1112</v>
+        <v>0.0941</v>
       </c>
       <c r="I120" t="n">
-        <v>23.03</v>
+        <v>22.57</v>
       </c>
       <c r="J120" t="n">
-        <v>336</v>
+        <v>339.3</v>
       </c>
       <c r="K120" t="n">
-        <v>6.21</v>
+        <v>5.353</v>
       </c>
       <c r="L120" t="n">
-        <v>-3.735</v>
+        <v>-4.032</v>
       </c>
       <c r="M120" t="n">
-        <v>21.538</v>
+        <v>19.978</v>
       </c>
     </row>
     <row r="121">
@@ -7403,7 +7403,7 @@
         <v>22.85</v>
       </c>
       <c r="J121" t="n">
-        <v>324.5</v>
+        <v>323.4</v>
       </c>
       <c r="K121" t="n">
         <v>5.93</v>
@@ -7448,7 +7448,7 @@
         <v>23.6</v>
       </c>
       <c r="J122" t="n">
-        <v>342.7</v>
+        <v>341.5</v>
       </c>
       <c r="K122" t="n">
         <v>5.331</v>
@@ -7493,7 +7493,7 @@
         <v>22.95</v>
       </c>
       <c r="J123" t="n">
-        <v>324.5</v>
+        <v>323.4</v>
       </c>
       <c r="K123" t="n">
         <v>5.936</v>
@@ -7538,7 +7538,7 @@
         <v>22.91</v>
       </c>
       <c r="J124" t="n">
-        <v>337.3</v>
+        <v>336.1</v>
       </c>
       <c r="K124" t="n">
         <v>5.597</v>
@@ -7577,22 +7577,22 @@
         <v>0.461</v>
       </c>
       <c r="H125" t="n">
-        <v>0.1128</v>
+        <v>0.1133</v>
       </c>
       <c r="I125" t="n">
         <v>23.02</v>
       </c>
       <c r="J125" t="n">
-        <v>348.9</v>
+        <v>347.7</v>
       </c>
       <c r="K125" t="n">
-        <v>5.635</v>
+        <v>5.638</v>
       </c>
       <c r="L125" t="n">
-        <v>-3.934</v>
+        <v>-3.933</v>
       </c>
       <c r="M125" t="n">
-        <v>19.944</v>
+        <v>19.948</v>
       </c>
     </row>
     <row r="126">
@@ -7622,22 +7622,22 @@
         <v>0.456</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0897</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>21.99</v>
+        <v>21.93</v>
       </c>
       <c r="J126" t="n">
         <v>331.5</v>
       </c>
       <c r="K126" t="n">
-        <v>5.64</v>
+        <v>5.638</v>
       </c>
       <c r="L126" t="n">
-        <v>-2.625</v>
+        <v>-2.626</v>
       </c>
       <c r="M126" t="n">
-        <v>20.855</v>
+        <v>20.851</v>
       </c>
     </row>
     <row r="127">
@@ -7667,7 +7667,7 @@
         <v>0.521</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0833</v>
+        <v>0.0834</v>
       </c>
       <c r="I127" t="n">
         <v>22.06</v>
@@ -7712,22 +7712,22 @@
         <v>0.419</v>
       </c>
       <c r="H128" t="n">
-        <v>0.102</v>
+        <v>0.1022</v>
       </c>
       <c r="I128" t="n">
-        <v>23.22</v>
+        <v>23.15</v>
       </c>
       <c r="J128" t="n">
         <v>347.4</v>
       </c>
       <c r="K128" t="n">
-        <v>5.656</v>
+        <v>5.657</v>
       </c>
       <c r="L128" t="n">
         <v>-3.927</v>
       </c>
       <c r="M128" t="n">
-        <v>20.963</v>
+        <v>20.967</v>
       </c>
     </row>
     <row r="129">
@@ -7757,10 +7757,10 @@
         <v>0.434</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0861</v>
+        <v>0.0862</v>
       </c>
       <c r="I129" t="n">
-        <v>21.33</v>
+        <v>21.34</v>
       </c>
       <c r="J129" t="n">
         <v>335.2</v>
@@ -7802,22 +7802,22 @@
         <v>0.437</v>
       </c>
       <c r="H130" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>22.15</v>
+        <v>22.1</v>
       </c>
       <c r="J130" t="n">
         <v>331.4</v>
       </c>
       <c r="K130" t="n">
-        <v>5.514</v>
+        <v>5.516</v>
       </c>
       <c r="L130" t="n">
         <v>-2.668</v>
       </c>
       <c r="M130" t="n">
-        <v>20.607</v>
+        <v>20.615</v>
       </c>
     </row>
     <row r="131">
@@ -7847,22 +7847,22 @@
         <v>0.429</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0805</v>
+        <v>0.0808</v>
       </c>
       <c r="I131" t="n">
-        <v>22.16</v>
+        <v>22.09</v>
       </c>
       <c r="J131" t="n">
         <v>334.8</v>
       </c>
       <c r="K131" t="n">
-        <v>5.631</v>
+        <v>5.633</v>
       </c>
       <c r="L131" t="n">
-        <v>-2.628</v>
+        <v>-2.627</v>
       </c>
       <c r="M131" t="n">
-        <v>20.719</v>
+        <v>20.724</v>
       </c>
     </row>
     <row r="132">
@@ -7892,22 +7892,22 @@
         <v>0.483</v>
       </c>
       <c r="H132" t="n">
-        <v>0.11</v>
+        <v>0.1099</v>
       </c>
       <c r="I132" t="n">
-        <v>20.85</v>
+        <v>20.84</v>
       </c>
       <c r="J132" t="n">
         <v>307.6</v>
       </c>
       <c r="K132" t="n">
-        <v>6.034</v>
+        <v>6.033</v>
       </c>
       <c r="L132" t="n">
-        <v>-2.488</v>
+        <v>-2.489</v>
       </c>
       <c r="M132" t="n">
-        <v>21.684</v>
+        <v>21.679</v>
       </c>
     </row>
     <row r="133">
@@ -7937,7 +7937,7 @@
         <v>0.451</v>
       </c>
       <c r="H133" t="n">
-        <v>0.1101</v>
+        <v>0.1103</v>
       </c>
       <c r="I133" t="n">
         <v>20.94</v>
@@ -7946,13 +7946,13 @@
         <v>332.4</v>
       </c>
       <c r="K133" t="n">
-        <v>5.363</v>
+        <v>5.364</v>
       </c>
       <c r="L133" t="n">
-        <v>-2.721</v>
+        <v>-2.72</v>
       </c>
       <c r="M133" t="n">
-        <v>20.569</v>
+        <v>20.573</v>
       </c>
     </row>
     <row r="134">
@@ -7985,7 +7985,7 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I134" t="n">
-        <v>21.92</v>
+        <v>21.85</v>
       </c>
       <c r="J134" t="n">
         <v>323.5</v>
@@ -8027,22 +8027,22 @@
         <v>0.518</v>
       </c>
       <c r="H135" t="n">
-        <v>0.1043</v>
+        <v>0.1045</v>
       </c>
       <c r="I135" t="n">
-        <v>21.94</v>
+        <v>21.96</v>
       </c>
       <c r="J135" t="n">
         <v>323.5</v>
       </c>
       <c r="K135" t="n">
-        <v>5.85</v>
+        <v>5.851</v>
       </c>
       <c r="L135" t="n">
         <v>-2.552</v>
       </c>
       <c r="M135" t="n">
-        <v>21.379</v>
+        <v>21.384</v>
       </c>
     </row>
     <row r="136">
@@ -8072,22 +8072,22 @@
         <v>0.456</v>
       </c>
       <c r="H136" t="n">
-        <v>0.0897</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>20.73</v>
+        <v>20.72</v>
       </c>
       <c r="J136" t="n">
         <v>317.2</v>
       </c>
       <c r="K136" t="n">
-        <v>5.831</v>
+        <v>5.829</v>
       </c>
       <c r="L136" t="n">
         <v>-2.559</v>
       </c>
       <c r="M136" t="n">
-        <v>21.157</v>
+        <v>21.152</v>
       </c>
     </row>
     <row r="137">
@@ -8165,7 +8165,7 @@
         <v>0.1745</v>
       </c>
       <c r="I138" t="n">
-        <v>22.78</v>
+        <v>22.85</v>
       </c>
       <c r="J138" t="n">
         <v>325</v>
@@ -8210,7 +8210,7 @@
         <v>0.1247</v>
       </c>
       <c r="I139" t="n">
-        <v>22.16</v>
+        <v>22.27</v>
       </c>
       <c r="J139" t="n">
         <v>344.8</v>
@@ -8255,7 +8255,7 @@
         <v>0.1644</v>
       </c>
       <c r="I140" t="n">
-        <v>20.48</v>
+        <v>20.51</v>
       </c>
       <c r="J140" t="n">
         <v>319.1</v>
@@ -8300,7 +8300,7 @@
         <v>0.1351</v>
       </c>
       <c r="I141" t="n">
-        <v>21</v>
+        <v>21.01</v>
       </c>
       <c r="J141" t="n">
         <v>331.1</v>
@@ -8345,7 +8345,7 @@
         <v>0.1132</v>
       </c>
       <c r="I142" t="n">
-        <v>22.4</v>
+        <v>22.56</v>
       </c>
       <c r="J142" t="n">
         <v>343.4</v>
@@ -8378,31 +8378,31 @@
         <v>-1</v>
       </c>
       <c r="E143" t="n">
-        <v>2.22</v>
+        <v>2.468</v>
       </c>
       <c r="F143" t="n">
-        <v>0.661</v>
+        <v>0.843</v>
       </c>
       <c r="G143" t="n">
-        <v>0.474</v>
+        <v>0.538</v>
       </c>
       <c r="H143" t="n">
-        <v>0.1114</v>
+        <v>0.1745</v>
       </c>
       <c r="I143" t="n">
-        <v>22.18</v>
+        <v>22.85</v>
       </c>
       <c r="J143" t="n">
-        <v>340.4</v>
+        <v>325</v>
       </c>
       <c r="K143" t="n">
-        <v>5.158</v>
+        <v>6.277</v>
       </c>
       <c r="L143" t="n">
-        <v>-4.099</v>
+        <v>-2.404</v>
       </c>
       <c r="M143" t="n">
-        <v>20.23</v>
+        <v>22.491</v>
       </c>
     </row>
     <row r="144">
@@ -8435,7 +8435,7 @@
         <v>0.1745</v>
       </c>
       <c r="I144" t="n">
-        <v>20.13</v>
+        <v>20.12</v>
       </c>
       <c r="J144" t="n">
         <v>309.5</v>
@@ -8468,31 +8468,31 @@
         <v>-1</v>
       </c>
       <c r="E145" t="n">
-        <v>2.093</v>
+        <v>2.327</v>
       </c>
       <c r="F145" t="n">
-        <v>0.708</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G145" t="n">
-        <v>0.463</v>
+        <v>0.485</v>
       </c>
       <c r="H145" t="n">
-        <v>0.1257</v>
+        <v>0.1201</v>
       </c>
       <c r="I145" t="n">
-        <v>22.55</v>
+        <v>22.24</v>
       </c>
       <c r="J145" t="n">
-        <v>349.9</v>
+        <v>348.4</v>
       </c>
       <c r="K145" t="n">
-        <v>5.189</v>
+        <v>5.404</v>
       </c>
       <c r="L145" t="n">
-        <v>-4.089</v>
+        <v>-4.014</v>
       </c>
       <c r="M145" t="n">
-        <v>20.417</v>
+        <v>20.703</v>
       </c>
     </row>
     <row r="146">
@@ -8525,7 +8525,7 @@
         <v>0.1342</v>
       </c>
       <c r="I146" t="n">
-        <v>22.36</v>
+        <v>22.45</v>
       </c>
       <c r="J146" t="n">
         <v>346</v>
@@ -8570,7 +8570,7 @@
         <v>0.1258</v>
       </c>
       <c r="I147" t="n">
-        <v>21.03</v>
+        <v>20.99</v>
       </c>
       <c r="J147" t="n">
         <v>313.3</v>
@@ -8615,7 +8615,7 @@
         <v>0.0791</v>
       </c>
       <c r="I148" t="n">
-        <v>24.89</v>
+        <v>24.86</v>
       </c>
       <c r="J148" t="n">
         <v>356.7</v>
@@ -8660,7 +8660,7 @@
         <v>0.1006</v>
       </c>
       <c r="I149" t="n">
-        <v>24.28</v>
+        <v>24.26</v>
       </c>
       <c r="J149" t="n">
         <v>339.4</v>
@@ -8705,7 +8705,7 @@
         <v>0.093</v>
       </c>
       <c r="I150" t="n">
-        <v>23.04</v>
+        <v>23.07</v>
       </c>
       <c r="J150" t="n">
         <v>337.2</v>
@@ -8750,7 +8750,7 @@
         <v>0.0982</v>
       </c>
       <c r="I151" t="n">
-        <v>23.56</v>
+        <v>23.57</v>
       </c>
       <c r="J151" t="n">
         <v>341.1</v>
@@ -8795,7 +8795,7 @@
         <v>0.0987</v>
       </c>
       <c r="I152" t="n">
-        <v>24.48</v>
+        <v>24.45</v>
       </c>
       <c r="J152" t="n">
         <v>352.9</v>
@@ -8840,7 +8840,7 @@
         <v>0.07920000000000001</v>
       </c>
       <c r="I153" t="n">
-        <v>24.11</v>
+        <v>24.16</v>
       </c>
       <c r="J153" t="n">
         <v>331</v>
@@ -8873,31 +8873,31 @@
         <v>-1</v>
       </c>
       <c r="E154" t="n">
-        <v>1.844</v>
+        <v>2.029</v>
       </c>
       <c r="F154" t="n">
-        <v>0.667</v>
+        <v>0.658</v>
       </c>
       <c r="G154" t="n">
-        <v>0.461</v>
+        <v>0.433</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0711</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="I154" t="n">
-        <v>24.53</v>
+        <v>24.91</v>
       </c>
       <c r="J154" t="n">
-        <v>359.2</v>
+        <v>358.6</v>
       </c>
       <c r="K154" t="n">
-        <v>4.527</v>
+        <v>4.695</v>
       </c>
       <c r="L154" t="n">
-        <v>-4.318</v>
+        <v>-4.26</v>
       </c>
       <c r="M154" t="n">
-        <v>18.893</v>
+        <v>19.225</v>
       </c>
     </row>
     <row r="155">
@@ -8930,7 +8930,7 @@
         <v>0.0915</v>
       </c>
       <c r="I155" t="n">
-        <v>24.95</v>
+        <v>24.92</v>
       </c>
       <c r="J155" t="n">
         <v>344.6</v>
@@ -8975,7 +8975,7 @@
         <v>0.0907</v>
       </c>
       <c r="I156" t="n">
-        <v>23.82</v>
+        <v>23.85</v>
       </c>
       <c r="J156" t="n">
         <v>337.2</v>
@@ -9020,7 +9020,7 @@
         <v>0.0735</v>
       </c>
       <c r="I157" t="n">
-        <v>24.56</v>
+        <v>24.52</v>
       </c>
       <c r="J157" t="n">
         <v>353.3</v>
@@ -9065,7 +9065,7 @@
         <v>0.1006</v>
       </c>
       <c r="I158" t="n">
-        <v>23.12</v>
+        <v>23.13</v>
       </c>
       <c r="J158" t="n">
         <v>327</v>
@@ -9107,22 +9107,22 @@
         <v>0.459</v>
       </c>
       <c r="H159" t="n">
-        <v>0.119</v>
+        <v>0.1193</v>
       </c>
       <c r="I159" t="n">
-        <v>19.71</v>
+        <v>19.76</v>
       </c>
       <c r="J159" t="n">
         <v>321.7</v>
       </c>
       <c r="K159" t="n">
-        <v>7</v>
+        <v>7.002</v>
       </c>
       <c r="L159" t="n">
-        <v>-2.154</v>
+        <v>-2.153</v>
       </c>
       <c r="M159" t="n">
-        <v>22.034</v>
+        <v>22.042</v>
       </c>
     </row>
     <row r="160">
@@ -9152,22 +9152,22 @@
         <v>0.406</v>
       </c>
       <c r="H160" t="n">
-        <v>0.1224</v>
+        <v>0.1225</v>
       </c>
       <c r="I160" t="n">
-        <v>20.4</v>
+        <v>20.37</v>
       </c>
       <c r="J160" t="n">
         <v>344.3</v>
       </c>
       <c r="K160" t="n">
-        <v>5.16</v>
+        <v>5.161</v>
       </c>
       <c r="L160" t="n">
-        <v>-4.099</v>
+        <v>-4.098</v>
       </c>
       <c r="M160" t="n">
-        <v>20.343</v>
+        <v>20.347</v>
       </c>
     </row>
     <row r="161">
@@ -9197,16 +9197,16 @@
         <v>0.419</v>
       </c>
       <c r="H161" t="n">
-        <v>0.1065</v>
+        <v>0.1066</v>
       </c>
       <c r="I161" t="n">
-        <v>21.88</v>
+        <v>21.85</v>
       </c>
       <c r="J161" t="n">
         <v>330.8</v>
       </c>
       <c r="K161" t="n">
-        <v>5.618</v>
+        <v>5.619</v>
       </c>
       <c r="L161" t="n">
         <v>-2.632</v>
@@ -9242,22 +9242,22 @@
         <v>0.435</v>
       </c>
       <c r="H162" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0896</v>
       </c>
       <c r="I162" t="n">
-        <v>20.66</v>
+        <v>20.63</v>
       </c>
       <c r="J162" t="n">
         <v>332.8</v>
       </c>
       <c r="K162" t="n">
-        <v>5.606</v>
+        <v>5.608</v>
       </c>
       <c r="L162" t="n">
-        <v>-2.637</v>
+        <v>-2.636</v>
       </c>
       <c r="M162" t="n">
-        <v>20.761</v>
+        <v>20.766</v>
       </c>
     </row>
     <row r="163">
@@ -9287,16 +9287,16 @@
         <v>0.419</v>
       </c>
       <c r="H163" t="n">
-        <v>0.1065</v>
+        <v>0.1066</v>
       </c>
       <c r="I163" t="n">
-        <v>20.6</v>
+        <v>20.65</v>
       </c>
       <c r="J163" t="n">
         <v>316.8</v>
       </c>
       <c r="K163" t="n">
-        <v>5.806</v>
+        <v>5.807</v>
       </c>
       <c r="L163" t="n">
         <v>-2.567</v>
@@ -9332,22 +9332,22 @@
         <v>0.443</v>
       </c>
       <c r="H164" t="n">
-        <v>0.1022</v>
+        <v>0.1025</v>
       </c>
       <c r="I164" t="n">
-        <v>20.28</v>
+        <v>20.25</v>
       </c>
       <c r="J164" t="n">
         <v>325.6</v>
       </c>
       <c r="K164" t="n">
-        <v>5.391</v>
+        <v>5.393</v>
       </c>
       <c r="L164" t="n">
-        <v>-2.711</v>
+        <v>-2.71</v>
       </c>
       <c r="M164" t="n">
-        <v>20.548</v>
+        <v>20.553</v>
       </c>
     </row>
     <row r="165">
@@ -9380,7 +9380,7 @@
         <v>0.0951</v>
       </c>
       <c r="I165" t="n">
-        <v>20.83</v>
+        <v>20.88</v>
       </c>
       <c r="J165" t="n">
         <v>332.8</v>
@@ -9422,7 +9422,7 @@
         <v>0.527</v>
       </c>
       <c r="H166" t="n">
-        <v>0.1131</v>
+        <v>0.1134</v>
       </c>
       <c r="I166" t="n">
         <v>21.8</v>
@@ -9431,13 +9431,13 @@
         <v>343.1</v>
       </c>
       <c r="K166" t="n">
-        <v>5.589</v>
+        <v>5.59</v>
       </c>
       <c r="L166" t="n">
         <v>-3.95</v>
       </c>
       <c r="M166" t="n">
-        <v>21.027</v>
+        <v>21.032</v>
       </c>
     </row>
     <row r="167">
@@ -9467,22 +9467,22 @@
         <v>0.444</v>
       </c>
       <c r="H167" t="n">
-        <v>0.1124</v>
+        <v>0.1125</v>
       </c>
       <c r="I167" t="n">
-        <v>20.95</v>
+        <v>20.92</v>
       </c>
       <c r="J167" t="n">
         <v>340.9</v>
       </c>
       <c r="K167" t="n">
-        <v>5.548</v>
+        <v>5.549</v>
       </c>
       <c r="L167" t="n">
         <v>-3.964</v>
       </c>
       <c r="M167" t="n">
-        <v>20.884</v>
+        <v>20.888</v>
       </c>
     </row>
     <row r="168">
@@ -9503,31 +9503,31 @@
         <v>1</v>
       </c>
       <c r="E168" t="n">
-        <v>2.203</v>
+        <v>2.414</v>
       </c>
       <c r="F168" t="n">
-        <v>0.767</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="G168" t="n">
-        <v>0.434</v>
+        <v>0.509</v>
       </c>
       <c r="H168" t="n">
-        <v>0.092</v>
+        <v>0.1355</v>
       </c>
       <c r="I168" t="n">
-        <v>20.81</v>
+        <v>18.71</v>
       </c>
       <c r="J168" t="n">
-        <v>327.7</v>
+        <v>306.4</v>
       </c>
       <c r="K168" t="n">
-        <v>5.157</v>
+        <v>7.113</v>
       </c>
       <c r="L168" t="n">
-        <v>-2.792</v>
+        <v>-2.115</v>
       </c>
       <c r="M168" t="n">
-        <v>20.074</v>
+        <v>24.31</v>
       </c>
     </row>
     <row r="169">
@@ -9557,22 +9557,22 @@
         <v>0.459</v>
       </c>
       <c r="H169" t="n">
-        <v>0.119</v>
+        <v>0.1193</v>
       </c>
       <c r="I169" t="n">
-        <v>19.58</v>
+        <v>19.55</v>
       </c>
       <c r="J169" t="n">
         <v>336.2</v>
       </c>
       <c r="K169" t="n">
-        <v>6.765</v>
+        <v>6.767</v>
       </c>
       <c r="L169" t="n">
         <v>-2.235</v>
       </c>
       <c r="M169" t="n">
-        <v>21.658</v>
+        <v>21.667</v>
       </c>
     </row>
     <row r="170">
@@ -9602,22 +9602,22 @@
         <v>0.5659999999999999</v>
       </c>
       <c r="H170" t="n">
-        <v>0.1026</v>
+        <v>0.1028</v>
       </c>
       <c r="I170" t="n">
-        <v>19.48</v>
+        <v>19.47</v>
       </c>
       <c r="J170" t="n">
         <v>323.4</v>
       </c>
       <c r="K170" t="n">
-        <v>6.861</v>
+        <v>6.862</v>
       </c>
       <c r="L170" t="n">
         <v>-2.202</v>
       </c>
       <c r="M170" t="n">
-        <v>21.708</v>
+        <v>21.713</v>
       </c>
     </row>
     <row r="171">
@@ -9647,22 +9647,22 @@
         <v>0.5679999999999999</v>
       </c>
       <c r="H171" t="n">
-        <v>0.1019</v>
+        <v>0.1017</v>
       </c>
       <c r="I171" t="n">
-        <v>19.75</v>
+        <v>19.76</v>
       </c>
       <c r="J171" t="n">
         <v>346.6</v>
       </c>
       <c r="K171" t="n">
-        <v>6.553</v>
+        <v>6.552</v>
       </c>
       <c r="L171" t="n">
         <v>-3.617</v>
       </c>
       <c r="M171" t="n">
-        <v>21.237</v>
+        <v>21.236</v>
       </c>
     </row>
     <row r="172">
@@ -9692,7 +9692,7 @@
         <v>0.619</v>
       </c>
       <c r="H172" t="n">
-        <v>0.0907</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="I172" t="n">
         <v>19.24</v>
@@ -9701,13 +9701,13 @@
         <v>330.2</v>
       </c>
       <c r="K172" t="n">
-        <v>6.526</v>
+        <v>6.527</v>
       </c>
       <c r="L172" t="n">
         <v>-2.318</v>
       </c>
       <c r="M172" t="n">
-        <v>23.074</v>
+        <v>23.078</v>
       </c>
     </row>
     <row r="173">
@@ -9728,31 +9728,31 @@
         <v>-1</v>
       </c>
       <c r="E173" t="n">
-        <v>2.434</v>
+        <v>2.228</v>
       </c>
       <c r="F173" t="n">
-        <v>0.92</v>
+        <v>0.777</v>
       </c>
       <c r="G173" t="n">
-        <v>0.674</v>
+        <v>0.492</v>
       </c>
       <c r="H173" t="n">
-        <v>0.1194</v>
+        <v>0.0965</v>
       </c>
       <c r="I173" t="n">
         <v>20.24</v>
       </c>
       <c r="J173" t="n">
-        <v>321</v>
+        <v>340.6</v>
       </c>
       <c r="K173" t="n">
-        <v>6.338</v>
+        <v>5.345</v>
       </c>
       <c r="L173" t="n">
-        <v>-2.383</v>
+        <v>-4.035</v>
       </c>
       <c r="M173" t="n">
-        <v>22.309</v>
+        <v>20.468</v>
       </c>
     </row>
     <row r="174">
@@ -9782,7 +9782,7 @@
         <v>0.634</v>
       </c>
       <c r="H174" t="n">
-        <v>0.1175</v>
+        <v>0.1178</v>
       </c>
       <c r="I174" t="n">
         <v>19.29</v>
@@ -9791,13 +9791,13 @@
         <v>311.4</v>
       </c>
       <c r="K174" t="n">
-        <v>7.52</v>
+        <v>7.522</v>
       </c>
       <c r="L174" t="n">
-        <v>-1.974</v>
+        <v>-1.973</v>
       </c>
       <c r="M174" t="n">
-        <v>24.842</v>
+        <v>24.847</v>
       </c>
     </row>
     <row r="175">
@@ -9827,22 +9827,22 @@
         <v>0.674</v>
       </c>
       <c r="H175" t="n">
-        <v>0.1194</v>
+        <v>0.1179</v>
       </c>
       <c r="I175" t="n">
-        <v>20.24</v>
+        <v>20.28</v>
       </c>
       <c r="J175" t="n">
         <v>321</v>
       </c>
       <c r="K175" t="n">
-        <v>6.338</v>
+        <v>6.329</v>
       </c>
       <c r="L175" t="n">
-        <v>-2.383</v>
+        <v>-2.386</v>
       </c>
       <c r="M175" t="n">
-        <v>22.309</v>
+        <v>22.287</v>
       </c>
     </row>
     <row r="176">
@@ -9872,22 +9872,22 @@
         <v>0.553</v>
       </c>
       <c r="H176" t="n">
-        <v>0.0868</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="I176" t="n">
-        <v>19.99</v>
+        <v>20.03</v>
       </c>
       <c r="J176" t="n">
         <v>331.3</v>
       </c>
       <c r="K176" t="n">
-        <v>6.704</v>
+        <v>5.705</v>
       </c>
       <c r="L176" t="n">
-        <v>-2.257</v>
+        <v>-2.602</v>
       </c>
       <c r="M176" t="n">
-        <v>21.334</v>
+        <v>20.992</v>
       </c>
     </row>
     <row r="177">
@@ -9917,22 +9917,22 @@
         <v>0.5610000000000001</v>
       </c>
       <c r="H177" t="n">
-        <v>0.1</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="I177" t="n">
-        <v>19.63</v>
+        <v>19.62</v>
       </c>
       <c r="J177" t="n">
         <v>336.6</v>
       </c>
       <c r="K177" t="n">
-        <v>6.847</v>
+        <v>6.845</v>
       </c>
       <c r="L177" t="n">
-        <v>-2.207</v>
+        <v>-2.208</v>
       </c>
       <c r="M177" t="n">
-        <v>21.645</v>
+        <v>21.636</v>
       </c>
     </row>
     <row r="178">
@@ -9962,19 +9962,19 @@
         <v>0.592</v>
       </c>
       <c r="H178" t="n">
-        <v>0.1022</v>
+        <v>0.1024</v>
       </c>
       <c r="I178" t="n">
-        <v>19.76</v>
+        <v>19.79</v>
       </c>
       <c r="J178" t="n">
         <v>332</v>
       </c>
       <c r="K178" t="n">
-        <v>7.102</v>
+        <v>7.103</v>
       </c>
       <c r="L178" t="n">
-        <v>-2.119</v>
+        <v>-2.118</v>
       </c>
       <c r="M178" t="n">
         <v>22.115</v>
@@ -10007,7 +10007,7 @@
         <v>0.645</v>
       </c>
       <c r="H179" t="n">
-        <v>0.0945</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="I179" t="n">
         <v>19.15</v>
@@ -10016,13 +10016,13 @@
         <v>329</v>
       </c>
       <c r="K179" t="n">
-        <v>7.201</v>
+        <v>7.202</v>
       </c>
       <c r="L179" t="n">
-        <v>-2.085</v>
+        <v>-2.084</v>
       </c>
       <c r="M179" t="n">
-        <v>24.162</v>
+        <v>24.166</v>
       </c>
     </row>
     <row r="180">
@@ -10052,22 +10052,22 @@
         <v>0.674</v>
       </c>
       <c r="H180" t="n">
-        <v>0.1194</v>
+        <v>0.1179</v>
       </c>
       <c r="I180" t="n">
-        <v>20.24</v>
+        <v>20.28</v>
       </c>
       <c r="J180" t="n">
         <v>321</v>
       </c>
       <c r="K180" t="n">
-        <v>6.338</v>
+        <v>6.329</v>
       </c>
       <c r="L180" t="n">
-        <v>-2.383</v>
+        <v>-2.386</v>
       </c>
       <c r="M180" t="n">
-        <v>22.309</v>
+        <v>22.287</v>
       </c>
     </row>
     <row r="181">
@@ -10097,22 +10097,22 @@
         <v>0.523</v>
       </c>
       <c r="H181" t="n">
-        <v>0.1168</v>
+        <v>0.117</v>
       </c>
       <c r="I181" t="n">
-        <v>19.59</v>
+        <v>19.62</v>
       </c>
       <c r="J181" t="n">
         <v>313.8</v>
       </c>
       <c r="K181" t="n">
-        <v>6.988</v>
+        <v>6.989</v>
       </c>
       <c r="L181" t="n">
         <v>-2.158</v>
       </c>
       <c r="M181" t="n">
-        <v>22.018</v>
+        <v>22.022</v>
       </c>
     </row>
     <row r="182">
@@ -10145,7 +10145,7 @@
         <v>0.0917</v>
       </c>
       <c r="I182" t="n">
-        <v>21.6</v>
+        <v>21.61</v>
       </c>
       <c r="J182" t="n">
         <v>331</v>
@@ -10190,7 +10190,7 @@
         <v>0.0975</v>
       </c>
       <c r="I183" t="n">
-        <v>22.08</v>
+        <v>22.06</v>
       </c>
       <c r="J183" t="n">
         <v>307.9</v>
@@ -10223,31 +10223,31 @@
         <v>-1</v>
       </c>
       <c r="E184" t="n">
-        <v>2</v>
+        <v>2.174</v>
       </c>
       <c r="F184" t="n">
-        <v>0.695</v>
+        <v>0.869</v>
       </c>
       <c r="G184" t="n">
-        <v>0.421</v>
+        <v>0.539</v>
       </c>
       <c r="H184" t="n">
-        <v>0.0663</v>
+        <v>0.0975</v>
       </c>
       <c r="I184" t="n">
-        <v>22.15</v>
+        <v>23.32</v>
       </c>
       <c r="J184" t="n">
-        <v>338.4</v>
+        <v>320.9</v>
       </c>
       <c r="K184" t="n">
-        <v>4.63</v>
+        <v>5.575</v>
       </c>
       <c r="L184" t="n">
-        <v>-4.282</v>
+        <v>-2.647</v>
       </c>
       <c r="M184" t="n">
-        <v>18.969</v>
+        <v>20.89</v>
       </c>
     </row>
     <row r="185">
@@ -10280,7 +10280,7 @@
         <v>0.09229999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>21.73</v>
+        <v>21.76</v>
       </c>
       <c r="J185" t="n">
         <v>321.2</v>
@@ -10415,7 +10415,7 @@
         <v>0.0828</v>
       </c>
       <c r="I188" t="n">
-        <v>22.06</v>
+        <v>22.07</v>
       </c>
       <c r="J188" t="n">
         <v>341.3</v>
@@ -10505,7 +10505,7 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I190" t="n">
-        <v>21.43</v>
+        <v>21.46</v>
       </c>
       <c r="J190" t="n">
         <v>322.9</v>
@@ -10637,22 +10637,22 @@
         <v>0.536</v>
       </c>
       <c r="H193" t="n">
-        <v>0.0798</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="I193" t="n">
-        <v>24.71</v>
+        <v>24.64</v>
       </c>
       <c r="J193" t="n">
         <v>338</v>
       </c>
       <c r="K193" t="n">
-        <v>5.289</v>
+        <v>5.279</v>
       </c>
       <c r="L193" t="n">
-        <v>-4.054</v>
+        <v>-4.058</v>
       </c>
       <c r="M193" t="n">
-        <v>20.251</v>
+        <v>20.22</v>
       </c>
     </row>
     <row r="194">
@@ -10682,22 +10682,22 @@
         <v>0.681</v>
       </c>
       <c r="H194" t="n">
-        <v>0.1066</v>
+        <v>0.1056</v>
       </c>
       <c r="I194" t="n">
-        <v>23.23</v>
+        <v>23.21</v>
       </c>
       <c r="J194" t="n">
         <v>330.9</v>
       </c>
       <c r="K194" t="n">
-        <v>5.774</v>
+        <v>5.768</v>
       </c>
       <c r="L194" t="n">
-        <v>-2.578</v>
+        <v>-2.581</v>
       </c>
       <c r="M194" t="n">
-        <v>21.329</v>
+        <v>21.316</v>
       </c>
     </row>
     <row r="195">
@@ -10727,22 +10727,22 @@
         <v>0.482</v>
       </c>
       <c r="H195" t="n">
-        <v>0.107</v>
+        <v>0.1053</v>
       </c>
       <c r="I195" t="n">
-        <v>23.36</v>
+        <v>23.27</v>
       </c>
       <c r="J195" t="n">
         <v>349.2</v>
       </c>
       <c r="K195" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="L195" t="n">
-        <v>-4.14</v>
+        <v>-4.144</v>
       </c>
       <c r="M195" t="n">
-        <v>20.07</v>
+        <v>20.039</v>
       </c>
     </row>
     <row r="196">
@@ -10772,22 +10772,22 @@
         <v>0.604</v>
       </c>
       <c r="H196" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0779</v>
       </c>
       <c r="I196" t="n">
-        <v>23.02</v>
+        <v>22.99</v>
       </c>
       <c r="J196" t="n">
         <v>333.9</v>
       </c>
       <c r="K196" t="n">
-        <v>5.076</v>
+        <v>5.071</v>
       </c>
       <c r="L196" t="n">
-        <v>-2.82</v>
+        <v>-2.822</v>
       </c>
       <c r="M196" t="n">
-        <v>19.929</v>
+        <v>19.916</v>
       </c>
     </row>
     <row r="197">
@@ -10817,22 +10817,22 @@
         <v>0.6</v>
       </c>
       <c r="H197" t="n">
-        <v>0.0945</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="I197" t="n">
-        <v>22.52</v>
+        <v>22.44</v>
       </c>
       <c r="J197" t="n">
         <v>334.7</v>
       </c>
       <c r="K197" t="n">
-        <v>5.727</v>
+        <v>5.719</v>
       </c>
       <c r="L197" t="n">
-        <v>-2.595</v>
+        <v>-2.598</v>
       </c>
       <c r="M197" t="n">
-        <v>21.095</v>
+        <v>21.072</v>
       </c>
     </row>
     <row r="198">
@@ -10862,22 +10862,22 @@
         <v>0.581</v>
       </c>
       <c r="H198" t="n">
-        <v>0.0774</v>
+        <v>0.0756</v>
       </c>
       <c r="I198" t="n">
-        <v>25.36</v>
+        <v>25.27</v>
       </c>
       <c r="J198" t="n">
         <v>349</v>
       </c>
       <c r="K198" t="n">
-        <v>5.177</v>
+        <v>5.167</v>
       </c>
       <c r="L198" t="n">
-        <v>-4.093</v>
+        <v>-4.096</v>
       </c>
       <c r="M198" t="n">
-        <v>20.056</v>
+        <v>20.017</v>
       </c>
     </row>
     <row r="199">
@@ -10907,22 +10907,22 @@
         <v>0.537</v>
       </c>
       <c r="H199" t="n">
-        <v>0.1062</v>
+        <v>0.1034</v>
       </c>
       <c r="I199" t="n">
-        <v>23.72</v>
+        <v>23.65</v>
       </c>
       <c r="J199" t="n">
         <v>335.6</v>
       </c>
       <c r="K199" t="n">
-        <v>5.491</v>
+        <v>5.474</v>
       </c>
       <c r="L199" t="n">
-        <v>-2.676</v>
+        <v>-2.682</v>
       </c>
       <c r="M199" t="n">
-        <v>20.809</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="200">
@@ -10952,22 +10952,22 @@
         <v>0.594</v>
       </c>
       <c r="H200" t="n">
-        <v>0.0897</v>
+        <v>0.0886</v>
       </c>
       <c r="I200" t="n">
-        <v>22.81</v>
+        <v>22.73</v>
       </c>
       <c r="J200" t="n">
         <v>330.9</v>
       </c>
       <c r="K200" t="n">
-        <v>5.684</v>
+        <v>5.678</v>
       </c>
       <c r="L200" t="n">
-        <v>-2.61</v>
+        <v>-2.612</v>
       </c>
       <c r="M200" t="n">
-        <v>20.949</v>
+        <v>20.931</v>
       </c>
     </row>
     <row r="201">
@@ -10997,22 +10997,22 @@
         <v>0.539</v>
       </c>
       <c r="H201" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>24.69</v>
+        <v>24.62</v>
       </c>
       <c r="J201" t="n">
         <v>346.1</v>
       </c>
       <c r="K201" t="n">
-        <v>4.96</v>
+        <v>4.942</v>
       </c>
       <c r="L201" t="n">
-        <v>-4.168</v>
+        <v>-4.174</v>
       </c>
       <c r="M201" t="n">
-        <v>19.855</v>
+        <v>19.798</v>
       </c>
     </row>
     <row r="202">
@@ -11042,7 +11042,7 @@
         <v>0.595</v>
       </c>
       <c r="H202" t="n">
-        <v>0.0948</v>
+        <v>0.0929</v>
       </c>
       <c r="I202" t="n">
         <v>20.9</v>
@@ -11051,13 +11051,13 @@
         <v>309.9</v>
       </c>
       <c r="K202" t="n">
-        <v>5.923</v>
+        <v>5.911</v>
       </c>
       <c r="L202" t="n">
-        <v>-2.527</v>
+        <v>-2.531</v>
       </c>
       <c r="M202" t="n">
-        <v>21.393</v>
+        <v>21.357</v>
       </c>
     </row>
     <row r="203">
@@ -11087,22 +11087,22 @@
         <v>0.533</v>
       </c>
       <c r="H203" t="n">
-        <v>0.095</v>
+        <v>0.0939</v>
       </c>
       <c r="I203" t="n">
-        <v>24.37</v>
+        <v>24.26</v>
       </c>
       <c r="J203" t="n">
         <v>351.6</v>
       </c>
       <c r="K203" t="n">
-        <v>5.052</v>
+        <v>5.045</v>
       </c>
       <c r="L203" t="n">
-        <v>-4.136</v>
+        <v>-4.139</v>
       </c>
       <c r="M203" t="n">
-        <v>20.012</v>
+        <v>19.994</v>
       </c>
     </row>
     <row r="204">
@@ -11132,22 +11132,22 @@
         <v>0.489</v>
       </c>
       <c r="H204" t="n">
-        <v>0.0859</v>
+        <v>0.0857</v>
       </c>
       <c r="I204" t="n">
-        <v>25.27</v>
+        <v>25.28</v>
       </c>
       <c r="J204" t="n">
         <v>338</v>
       </c>
       <c r="K204" t="n">
-        <v>5.424</v>
+        <v>5.423</v>
       </c>
       <c r="L204" t="n">
-        <v>-4.007</v>
+        <v>-4.008</v>
       </c>
       <c r="M204" t="n">
-        <v>20.483</v>
+        <v>20.478</v>
       </c>
     </row>
     <row r="205">
@@ -11177,22 +11177,22 @@
         <v>0.505</v>
       </c>
       <c r="H205" t="n">
-        <v>0.0814</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>25.9</v>
+        <v>25.94</v>
       </c>
       <c r="J205" t="n">
         <v>350.7</v>
       </c>
       <c r="K205" t="n">
-        <v>4.804</v>
+        <v>4.803</v>
       </c>
       <c r="L205" t="n">
         <v>-4.222</v>
       </c>
       <c r="M205" t="n">
-        <v>17.502</v>
+        <v>17.498</v>
       </c>
     </row>
     <row r="206">
@@ -11222,22 +11222,22 @@
         <v>0.504</v>
       </c>
       <c r="H206" t="n">
-        <v>0.0929</v>
+        <v>0.0927</v>
       </c>
       <c r="I206" t="n">
-        <v>26.11</v>
+        <v>26.17</v>
       </c>
       <c r="J206" t="n">
         <v>355.2</v>
       </c>
       <c r="K206" t="n">
-        <v>5.447</v>
+        <v>5.446</v>
       </c>
       <c r="L206" t="n">
-        <v>-3.999</v>
+        <v>-4</v>
       </c>
       <c r="M206" t="n">
-        <v>18.581</v>
+        <v>18.577</v>
       </c>
     </row>
     <row r="207">
@@ -11267,22 +11267,22 @@
         <v>0.52</v>
       </c>
       <c r="H207" t="n">
-        <v>0.1101</v>
+        <v>0.1093</v>
       </c>
       <c r="I207" t="n">
-        <v>24.98</v>
+        <v>24.99</v>
       </c>
       <c r="J207" t="n">
         <v>335.8</v>
       </c>
       <c r="K207" t="n">
-        <v>5.662</v>
+        <v>5.657</v>
       </c>
       <c r="L207" t="n">
-        <v>-2.617</v>
+        <v>-2.619</v>
       </c>
       <c r="M207" t="n">
-        <v>21.071</v>
+        <v>21.057</v>
       </c>
     </row>
     <row r="208">
@@ -11312,22 +11312,22 @@
         <v>0.486</v>
       </c>
       <c r="H208" t="n">
-        <v>0.0898</v>
+        <v>0.0895</v>
       </c>
       <c r="I208" t="n">
-        <v>26.26</v>
+        <v>26.3</v>
       </c>
       <c r="J208" t="n">
         <v>359.5</v>
       </c>
       <c r="K208" t="n">
-        <v>4.978</v>
+        <v>4.976</v>
       </c>
       <c r="L208" t="n">
         <v>-4.162</v>
       </c>
       <c r="M208" t="n">
-        <v>17.825</v>
+        <v>17.817</v>
       </c>
     </row>
     <row r="209">
@@ -11357,22 +11357,22 @@
         <v>0.496</v>
       </c>
       <c r="H209" t="n">
-        <v>0.0833</v>
+        <v>0.083</v>
       </c>
       <c r="I209" t="n">
-        <v>25.94</v>
+        <v>25.98</v>
       </c>
       <c r="J209" t="n">
         <v>355.4</v>
       </c>
       <c r="K209" t="n">
-        <v>5.102</v>
+        <v>5.1</v>
       </c>
       <c r="L209" t="n">
         <v>-4.119</v>
       </c>
       <c r="M209" t="n">
-        <v>17.941</v>
+        <v>17.933</v>
       </c>
     </row>
     <row r="210">
@@ -11402,7 +11402,7 @@
         <v>0.533</v>
       </c>
       <c r="H210" t="n">
-        <v>0.1064</v>
+        <v>0.1062</v>
       </c>
       <c r="I210" t="n">
         <v>25.15</v>
@@ -11411,13 +11411,13 @@
         <v>338.5</v>
       </c>
       <c r="K210" t="n">
-        <v>5.751</v>
+        <v>5.75</v>
       </c>
       <c r="L210" t="n">
-        <v>-3.894</v>
+        <v>-3.895</v>
       </c>
       <c r="M210" t="n">
-        <v>21.197</v>
+        <v>21.193</v>
       </c>
     </row>
     <row r="211">
@@ -11447,7 +11447,7 @@
         <v>0.486</v>
       </c>
       <c r="H211" t="n">
-        <v>0.0898</v>
+        <v>0.0895</v>
       </c>
       <c r="I211" t="n">
         <v>26.99</v>
@@ -11456,13 +11456,13 @@
         <v>352</v>
       </c>
       <c r="K211" t="n">
-        <v>5.012</v>
+        <v>5.01</v>
       </c>
       <c r="L211" t="n">
-        <v>-4.15</v>
+        <v>-4.151</v>
       </c>
       <c r="M211" t="n">
-        <v>17.863</v>
+        <v>17.855</v>
       </c>
     </row>
     <row r="212">
@@ -11492,7 +11492,7 @@
         <v>0.521</v>
       </c>
       <c r="H212" t="n">
-        <v>0.0993</v>
+        <v>0.0992</v>
       </c>
       <c r="I212" t="n">
         <v>25.49</v>
@@ -11501,13 +11501,13 @@
         <v>339.5</v>
       </c>
       <c r="K212" t="n">
-        <v>5.702</v>
+        <v>5.701</v>
       </c>
       <c r="L212" t="n">
         <v>-3.911</v>
       </c>
       <c r="M212" t="n">
-        <v>19.053</v>
+        <v>19.048</v>
       </c>
     </row>
     <row r="213">
@@ -11537,22 +11537,22 @@
         <v>0.5570000000000001</v>
       </c>
       <c r="H213" t="n">
-        <v>0.12</v>
+        <v>0.1189</v>
       </c>
       <c r="I213" t="n">
-        <v>25.92</v>
+        <v>25.98</v>
       </c>
       <c r="J213" t="n">
         <v>345</v>
       </c>
       <c r="K213" t="n">
-        <v>6.11</v>
+        <v>6.103</v>
       </c>
       <c r="L213" t="n">
-        <v>-3.77</v>
+        <v>-3.772</v>
       </c>
       <c r="M213" t="n">
-        <v>19.917</v>
+        <v>19.899</v>
       </c>
     </row>
     <row r="214">
@@ -11582,22 +11582,22 @@
         <v>0.5610000000000001</v>
       </c>
       <c r="H214" t="n">
-        <v>0.1035</v>
+        <v>0.1026</v>
       </c>
       <c r="I214" t="n">
-        <v>25.73</v>
+        <v>25.79</v>
       </c>
       <c r="J214" t="n">
         <v>338.7</v>
       </c>
       <c r="K214" t="n">
-        <v>5.775</v>
+        <v>5.77</v>
       </c>
       <c r="L214" t="n">
-        <v>-3.886</v>
+        <v>-3.888</v>
       </c>
       <c r="M214" t="n">
-        <v>19.262</v>
+        <v>19.245</v>
       </c>
     </row>
     <row r="215">
@@ -11627,22 +11627,22 @@
         <v>0.396</v>
       </c>
       <c r="H215" t="n">
-        <v>0.0738</v>
+        <v>0.0737</v>
       </c>
       <c r="I215" t="n">
-        <v>27.36</v>
+        <v>27.35</v>
       </c>
       <c r="J215" t="n">
         <v>368.4</v>
       </c>
       <c r="K215" t="n">
-        <v>3.21</v>
+        <v>3.209</v>
       </c>
       <c r="L215" t="n">
         <v>-4.774</v>
       </c>
       <c r="M215" t="n">
-        <v>16.417</v>
+        <v>16.412</v>
       </c>
     </row>
     <row r="216">
@@ -11672,22 +11672,22 @@
         <v>0.403</v>
       </c>
       <c r="H216" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="I216" t="n">
-        <v>24.95</v>
+        <v>24.96</v>
       </c>
       <c r="J216" t="n">
         <v>355.4</v>
       </c>
       <c r="K216" t="n">
-        <v>5.009</v>
+        <v>5.007</v>
       </c>
       <c r="L216" t="n">
-        <v>-4.151</v>
+        <v>-4.152</v>
       </c>
       <c r="M216" t="n">
-        <v>20.253</v>
+        <v>20.244</v>
       </c>
     </row>
     <row r="217">
@@ -11717,22 +11717,22 @@
         <v>0.428</v>
       </c>
       <c r="H217" t="n">
-        <v>0.0833</v>
+        <v>0.0838</v>
       </c>
       <c r="I217" t="n">
-        <v>25.23</v>
+        <v>25.16</v>
       </c>
       <c r="J217" t="n">
         <v>348.6</v>
       </c>
       <c r="K217" t="n">
-        <v>4.919</v>
+        <v>4.922</v>
       </c>
       <c r="L217" t="n">
-        <v>-2.874</v>
+        <v>-2.873</v>
       </c>
       <c r="M217" t="n">
-        <v>20.012</v>
+        <v>20.021</v>
       </c>
     </row>
     <row r="218">
@@ -11762,22 +11762,22 @@
         <v>0.425</v>
       </c>
       <c r="H218" t="n">
-        <v>0.0984</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="I218" t="n">
-        <v>26.38</v>
+        <v>26.31</v>
       </c>
       <c r="J218" t="n">
         <v>363.1</v>
       </c>
       <c r="K218" t="n">
-        <v>5.016</v>
+        <v>5.018</v>
       </c>
       <c r="L218" t="n">
-        <v>-4.149</v>
+        <v>-4.148</v>
       </c>
       <c r="M218" t="n">
-        <v>20.314</v>
+        <v>20.318</v>
       </c>
     </row>
     <row r="219">
@@ -11807,22 +11807,22 @@
         <v>0.486</v>
       </c>
       <c r="H219" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0964</v>
       </c>
       <c r="I219" t="n">
-        <v>26.2</v>
+        <v>26.15</v>
       </c>
       <c r="J219" t="n">
         <v>354.6</v>
       </c>
       <c r="K219" t="n">
-        <v>5.163</v>
+        <v>5.161</v>
       </c>
       <c r="L219" t="n">
         <v>-4.098</v>
       </c>
       <c r="M219" t="n">
-        <v>20.586</v>
+        <v>20.581</v>
       </c>
     </row>
     <row r="220">
@@ -11852,22 +11852,22 @@
         <v>0.396</v>
       </c>
       <c r="H220" t="n">
-        <v>0.0738</v>
+        <v>0.0737</v>
       </c>
       <c r="I220" t="n">
-        <v>26.2</v>
+        <v>26.17</v>
       </c>
       <c r="J220" t="n">
         <v>353.9</v>
       </c>
       <c r="K220" t="n">
-        <v>4.292</v>
+        <v>4.291</v>
       </c>
       <c r="L220" t="n">
-        <v>-4.399</v>
+        <v>-4.4</v>
       </c>
       <c r="M220" t="n">
-        <v>18.857</v>
+        <v>18.853</v>
       </c>
     </row>
     <row r="221">
@@ -11900,7 +11900,7 @@
         <v>0.0873</v>
       </c>
       <c r="I221" t="n">
-        <v>26.86</v>
+        <v>26.8</v>
       </c>
       <c r="J221" t="n">
         <v>374.4</v>
@@ -11912,7 +11912,7 @@
         <v>-4.384</v>
       </c>
       <c r="M221" t="n">
-        <v>17.105</v>
+        <v>17.109</v>
       </c>
     </row>
     <row r="222">
@@ -11945,7 +11945,7 @@
         <v>0.0877</v>
       </c>
       <c r="I222" t="n">
-        <v>26.48</v>
+        <v>26.47</v>
       </c>
       <c r="J222" t="n">
         <v>343.9</v>
@@ -11987,22 +11987,22 @@
         <v>0.427</v>
       </c>
       <c r="H223" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.0988</v>
       </c>
       <c r="I223" t="n">
-        <v>26.89</v>
+        <v>26.82</v>
       </c>
       <c r="J223" t="n">
         <v>374.7</v>
       </c>
       <c r="K223" t="n">
-        <v>4.702</v>
+        <v>4.706</v>
       </c>
       <c r="L223" t="n">
-        <v>-4.257</v>
+        <v>-4.256</v>
       </c>
       <c r="M223" t="n">
-        <v>17.815</v>
+        <v>17.828</v>
       </c>
     </row>
     <row r="224">
@@ -12032,22 +12032,22 @@
         <v>0.486</v>
       </c>
       <c r="H224" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0964</v>
       </c>
       <c r="I224" t="n">
-        <v>24.66</v>
+        <v>24.59</v>
       </c>
       <c r="J224" t="n">
         <v>341.9</v>
       </c>
       <c r="K224" t="n">
-        <v>5.267</v>
+        <v>5.265</v>
       </c>
       <c r="L224" t="n">
-        <v>-2.754</v>
+        <v>-2.755</v>
       </c>
       <c r="M224" t="n">
-        <v>20.752</v>
+        <v>20.748</v>
       </c>
     </row>
     <row r="225">
@@ -12077,22 +12077,22 @@
         <v>0.486</v>
       </c>
       <c r="H225" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0964</v>
       </c>
       <c r="I225" t="n">
-        <v>24.66</v>
+        <v>24.59</v>
       </c>
       <c r="J225" t="n">
         <v>341.9</v>
       </c>
       <c r="K225" t="n">
-        <v>5.267</v>
+        <v>5.265</v>
       </c>
       <c r="L225" t="n">
-        <v>-2.754</v>
+        <v>-2.755</v>
       </c>
       <c r="M225" t="n">
-        <v>20.752</v>
+        <v>20.748</v>
       </c>
     </row>
     <row r="226">
@@ -12122,22 +12122,22 @@
         <v>0.403</v>
       </c>
       <c r="H226" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>26.87</v>
+        <v>26.82</v>
       </c>
       <c r="J226" t="n">
         <v>370.7</v>
       </c>
       <c r="K226" t="n">
-        <v>4.825</v>
+        <v>4.823</v>
       </c>
       <c r="L226" t="n">
         <v>-4.215</v>
       </c>
       <c r="M226" t="n">
-        <v>18.005</v>
+        <v>17.996</v>
       </c>
     </row>
     <row r="227">
@@ -12167,7 +12167,7 @@
         <v>0.602</v>
       </c>
       <c r="H227" t="n">
-        <v>0.0934</v>
+        <v>0.0941</v>
       </c>
       <c r="I227" t="n">
         <v>20.28</v>
@@ -12176,13 +12176,13 @@
         <v>329.7</v>
       </c>
       <c r="K227" t="n">
-        <v>6.044</v>
+        <v>6.049</v>
       </c>
       <c r="L227" t="n">
-        <v>-2.485</v>
+        <v>-2.483</v>
       </c>
       <c r="M227" t="n">
-        <v>24.007</v>
+        <v>24.02</v>
       </c>
     </row>
     <row r="228">
@@ -12212,7 +12212,7 @@
         <v>0.519</v>
       </c>
       <c r="H228" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0781</v>
       </c>
       <c r="I228" t="n">
         <v>22.33</v>
@@ -12221,13 +12221,13 @@
         <v>347.2</v>
       </c>
       <c r="K228" t="n">
-        <v>5.452</v>
+        <v>5.457</v>
       </c>
       <c r="L228" t="n">
-        <v>-2.69</v>
+        <v>-2.688</v>
       </c>
       <c r="M228" t="n">
-        <v>20.878</v>
+        <v>20.895</v>
       </c>
     </row>
     <row r="229">
@@ -12257,7 +12257,7 @@
         <v>0.604</v>
       </c>
       <c r="H229" t="n">
-        <v>0.1097</v>
+        <v>0.1108</v>
       </c>
       <c r="I229" t="n">
         <v>19.82</v>
@@ -12266,13 +12266,13 @@
         <v>317.7</v>
       </c>
       <c r="K229" t="n">
-        <v>6.97</v>
+        <v>6.977</v>
       </c>
       <c r="L229" t="n">
-        <v>-2.164</v>
+        <v>-2.162</v>
       </c>
       <c r="M229" t="n">
-        <v>24.378</v>
+        <v>24.397</v>
       </c>
     </row>
     <row r="230">
@@ -12302,7 +12302,7 @@
         <v>0.571</v>
       </c>
       <c r="H230" t="n">
-        <v>0.1081</v>
+        <v>0.109</v>
       </c>
       <c r="I230" t="n">
         <v>21.11</v>
@@ -12311,13 +12311,13 @@
         <v>368.1</v>
       </c>
       <c r="K230" t="n">
-        <v>5.632</v>
+        <v>5.637</v>
       </c>
       <c r="L230" t="n">
-        <v>-3.935</v>
+        <v>-3.934</v>
       </c>
       <c r="M230" t="n">
-        <v>21.475</v>
+        <v>21.493</v>
       </c>
     </row>
     <row r="231">
@@ -12347,7 +12347,7 @@
         <v>0.547</v>
       </c>
       <c r="H231" t="n">
-        <v>0.0842</v>
+        <v>0.0851</v>
       </c>
       <c r="I231" t="n">
         <v>21.43</v>
@@ -12356,13 +12356,13 @@
         <v>359.3</v>
       </c>
       <c r="K231" t="n">
-        <v>5.587</v>
+        <v>5.593</v>
       </c>
       <c r="L231" t="n">
-        <v>-3.951</v>
+        <v>-3.949</v>
       </c>
       <c r="M231" t="n">
-        <v>21.155</v>
+        <v>21.169</v>
       </c>
     </row>
     <row r="232">
@@ -12383,31 +12383,31 @@
         <v>1</v>
       </c>
       <c r="E232" t="n">
-        <v>2.38</v>
+        <v>2.254</v>
       </c>
       <c r="F232" t="n">
-        <v>0.862</v>
+        <v>0.746</v>
       </c>
       <c r="G232" t="n">
-        <v>0.604</v>
+        <v>0.473</v>
       </c>
       <c r="H232" t="n">
-        <v>0.1097</v>
+        <v>0.0848</v>
       </c>
       <c r="I232" t="n">
-        <v>19.82</v>
+        <v>21.65</v>
       </c>
       <c r="J232" t="n">
-        <v>317.7</v>
+        <v>340.5</v>
       </c>
       <c r="K232" t="n">
-        <v>6.97</v>
+        <v>5.201</v>
       </c>
       <c r="L232" t="n">
-        <v>-2.164</v>
+        <v>-2.777</v>
       </c>
       <c r="M232" t="n">
-        <v>24.378</v>
+        <v>20.486</v>
       </c>
     </row>
     <row r="233">
@@ -12437,7 +12437,7 @@
         <v>0.482</v>
       </c>
       <c r="H233" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="I233" t="n">
         <v>21.88</v>
@@ -12446,13 +12446,13 @@
         <v>331.1</v>
       </c>
       <c r="K233" t="n">
-        <v>5.527</v>
+        <v>5.533</v>
       </c>
       <c r="L233" t="n">
-        <v>-2.664</v>
+        <v>-2.662</v>
       </c>
       <c r="M233" t="n">
-        <v>20.941</v>
+        <v>20.958</v>
       </c>
     </row>
     <row r="234">
@@ -12482,7 +12482,7 @@
         <v>0.51</v>
       </c>
       <c r="H234" t="n">
-        <v>0.0877</v>
+        <v>0.0881</v>
       </c>
       <c r="I234" t="n">
         <v>22.7</v>
@@ -12491,13 +12491,13 @@
         <v>363.9</v>
       </c>
       <c r="K234" t="n">
-        <v>5.495</v>
+        <v>5.498</v>
       </c>
       <c r="L234" t="n">
-        <v>-3.983</v>
+        <v>-3.982</v>
       </c>
       <c r="M234" t="n">
-        <v>21.031</v>
+        <v>21.04</v>
       </c>
     </row>
     <row r="235">
@@ -12527,7 +12527,7 @@
         <v>0.519</v>
       </c>
       <c r="H235" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0781</v>
       </c>
       <c r="I235" t="n">
         <v>21.16</v>
@@ -12536,13 +12536,13 @@
         <v>327.8</v>
       </c>
       <c r="K235" t="n">
-        <v>5.594</v>
+        <v>5.599</v>
       </c>
       <c r="L235" t="n">
-        <v>-2.641</v>
+        <v>-2.639</v>
       </c>
       <c r="M235" t="n">
-        <v>21.123</v>
+        <v>21.141</v>
       </c>
     </row>
     <row r="236">
@@ -12563,31 +12563,31 @@
         <v>1</v>
       </c>
       <c r="E236" t="n">
-        <v>2.258</v>
+        <v>2.38</v>
       </c>
       <c r="F236" t="n">
-        <v>0.718</v>
+        <v>0.862</v>
       </c>
       <c r="G236" t="n">
-        <v>0.473</v>
+        <v>0.604</v>
       </c>
       <c r="H236" t="n">
-        <v>0.0765</v>
+        <v>0.1108</v>
       </c>
       <c r="I236" t="n">
-        <v>21.8</v>
+        <v>19.82</v>
       </c>
       <c r="J236" t="n">
-        <v>340.5</v>
+        <v>317.7</v>
       </c>
       <c r="K236" t="n">
-        <v>5.099</v>
+        <v>6.977</v>
       </c>
       <c r="L236" t="n">
-        <v>-2.812</v>
+        <v>-2.162</v>
       </c>
       <c r="M236" t="n">
-        <v>20.227</v>
+        <v>24.397</v>
       </c>
     </row>
     <row r="237">
@@ -12617,7 +12617,7 @@
         <v>0.506</v>
       </c>
       <c r="H237" t="n">
-        <v>0.0784</v>
+        <v>0.0793</v>
       </c>
       <c r="I237" t="n">
         <v>22.5</v>
@@ -12626,13 +12626,13 @@
         <v>360</v>
       </c>
       <c r="K237" t="n">
-        <v>5.013</v>
+        <v>5.019</v>
       </c>
       <c r="L237" t="n">
-        <v>-4.15</v>
+        <v>-4.148</v>
       </c>
       <c r="M237" t="n">
-        <v>20.177</v>
+        <v>20.195</v>
       </c>
     </row>
     <row r="238">
@@ -12662,7 +12662,7 @@
         <v>0.535</v>
       </c>
       <c r="H238" t="n">
-        <v>0.0927</v>
+        <v>0.0934</v>
       </c>
       <c r="I238" t="n">
         <v>20.43</v>
@@ -12671,13 +12671,13 @@
         <v>320.5</v>
       </c>
       <c r="K238" t="n">
-        <v>5.558</v>
+        <v>5.562</v>
       </c>
       <c r="L238" t="n">
-        <v>-2.653</v>
+        <v>-2.652</v>
       </c>
       <c r="M238" t="n">
-        <v>21.172</v>
+        <v>21.185</v>
       </c>
     </row>
     <row r="239">
@@ -12707,22 +12707,22 @@
         <v>0.541</v>
       </c>
       <c r="H239" t="n">
-        <v>0.1019</v>
+        <v>0.1021</v>
       </c>
       <c r="I239" t="n">
-        <v>20.3</v>
+        <v>20.33</v>
       </c>
       <c r="J239" t="n">
         <v>323.3</v>
       </c>
       <c r="K239" t="n">
-        <v>5.523</v>
+        <v>5.525</v>
       </c>
       <c r="L239" t="n">
         <v>-2.665</v>
       </c>
       <c r="M239" t="n">
-        <v>20.76</v>
+        <v>20.765</v>
       </c>
     </row>
     <row r="240">
@@ -12755,7 +12755,7 @@
         <v>0.1281</v>
       </c>
       <c r="I240" t="n">
-        <v>21.06</v>
+        <v>21.09</v>
       </c>
       <c r="J240" t="n">
         <v>337.2</v>
@@ -12797,22 +12797,22 @@
         <v>0.51</v>
       </c>
       <c r="H241" t="n">
-        <v>0.1105</v>
+        <v>0.1108</v>
       </c>
       <c r="I241" t="n">
-        <v>20.03</v>
+        <v>20.1</v>
       </c>
       <c r="J241" t="n">
         <v>334.7</v>
       </c>
       <c r="K241" t="n">
-        <v>5.604</v>
+        <v>5.606</v>
       </c>
       <c r="L241" t="n">
         <v>-2.637</v>
       </c>
       <c r="M241" t="n">
-        <v>20.961</v>
+        <v>20.965</v>
       </c>
     </row>
     <row r="242">
@@ -12845,7 +12845,7 @@
         <v>0.1013</v>
       </c>
       <c r="I242" t="n">
-        <v>20.34</v>
+        <v>20.35</v>
       </c>
       <c r="J242" t="n">
         <v>330.3</v>
@@ -12890,7 +12890,7 @@
         <v>0.1381</v>
       </c>
       <c r="I243" t="n">
-        <v>21.98</v>
+        <v>22.04</v>
       </c>
       <c r="J243" t="n">
         <v>320.4</v>
@@ -12935,7 +12935,7 @@
         <v>0.1381</v>
       </c>
       <c r="I244" t="n">
-        <v>19.71</v>
+        <v>19.76</v>
       </c>
       <c r="J244" t="n">
         <v>308</v>
@@ -12980,7 +12980,7 @@
         <v>0.1019</v>
       </c>
       <c r="I245" t="n">
-        <v>21.14</v>
+        <v>21.23</v>
       </c>
       <c r="J245" t="n">
         <v>335.4</v>
@@ -13025,7 +13025,7 @@
         <v>0.1131</v>
       </c>
       <c r="I246" t="n">
-        <v>20.87</v>
+        <v>20.88</v>
       </c>
       <c r="J246" t="n">
         <v>322.4</v>
@@ -13067,22 +13067,22 @@
         <v>0.59</v>
       </c>
       <c r="H247" t="n">
-        <v>0.0896</v>
+        <v>0.0898</v>
       </c>
       <c r="I247" t="n">
-        <v>20.8</v>
+        <v>20.83</v>
       </c>
       <c r="J247" t="n">
         <v>340.7</v>
       </c>
       <c r="K247" t="n">
-        <v>5.254</v>
+        <v>5.255</v>
       </c>
       <c r="L247" t="n">
         <v>-4.066</v>
       </c>
       <c r="M247" t="n">
-        <v>20.303</v>
+        <v>20.304</v>
       </c>
     </row>
     <row r="248">
@@ -13112,22 +13112,22 @@
         <v>0.533</v>
       </c>
       <c r="H248" t="n">
-        <v>0.1066</v>
+        <v>0.1068</v>
       </c>
       <c r="I248" t="n">
-        <v>20.32</v>
+        <v>20.39</v>
       </c>
       <c r="J248" t="n">
         <v>335.4</v>
       </c>
       <c r="K248" t="n">
-        <v>5.346</v>
+        <v>5.347</v>
       </c>
       <c r="L248" t="n">
-        <v>-2.727</v>
+        <v>-2.726</v>
       </c>
       <c r="M248" t="n">
-        <v>20.547</v>
+        <v>20.551</v>
       </c>
     </row>
     <row r="249">
@@ -13160,7 +13160,7 @@
         <v>0.1281</v>
       </c>
       <c r="I249" t="n">
-        <v>20.68</v>
+        <v>20.78</v>
       </c>
       <c r="J249" t="n">
         <v>326.2</v>
@@ -13205,7 +13205,7 @@
         <v>0.1102</v>
       </c>
       <c r="I250" t="n">
-        <v>23.65</v>
+        <v>23.7</v>
       </c>
       <c r="J250" t="n">
         <v>343</v>
@@ -13250,7 +13250,7 @@
         <v>0.1223</v>
       </c>
       <c r="I251" t="n">
-        <v>25.41</v>
+        <v>25.43</v>
       </c>
       <c r="J251" t="n">
         <v>339.9</v>
@@ -13295,7 +13295,7 @@
         <v>0.111</v>
       </c>
       <c r="I252" t="n">
-        <v>23.69</v>
+        <v>23.74</v>
       </c>
       <c r="J252" t="n">
         <v>333.3</v>
@@ -13340,7 +13340,7 @@
         <v>0.1262</v>
       </c>
       <c r="I253" t="n">
-        <v>26.13</v>
+        <v>26.15</v>
       </c>
       <c r="J253" t="n">
         <v>338.3</v>
@@ -13385,7 +13385,7 @@
         <v>0.1211</v>
       </c>
       <c r="I254" t="n">
-        <v>25.43</v>
+        <v>25.44</v>
       </c>
       <c r="J254" t="n">
         <v>346.6</v>
@@ -13430,7 +13430,7 @@
         <v>0.132</v>
       </c>
       <c r="I255" t="n">
-        <v>25.72</v>
+        <v>25.74</v>
       </c>
       <c r="J255" t="n">
         <v>350.1</v>
@@ -13475,7 +13475,7 @@
         <v>0.111</v>
       </c>
       <c r="I256" t="n">
-        <v>26.03</v>
+        <v>26.06</v>
       </c>
       <c r="J256" t="n">
         <v>344.8</v>
@@ -13520,7 +13520,7 @@
         <v>0.1024</v>
       </c>
       <c r="I257" t="n">
-        <v>26.08</v>
+        <v>26.09</v>
       </c>
       <c r="J257" t="n">
         <v>352</v>
@@ -13565,7 +13565,7 @@
         <v>0.1515</v>
       </c>
       <c r="I258" t="n">
-        <v>23.27</v>
+        <v>23.36</v>
       </c>
       <c r="J258" t="n">
         <v>321.4</v>
@@ -13598,31 +13598,31 @@
         <v>-1</v>
       </c>
       <c r="E259" t="n">
-        <v>2.459</v>
+        <v>2.287</v>
       </c>
       <c r="F259" t="n">
-        <v>0.86</v>
+        <v>0.714</v>
       </c>
       <c r="G259" t="n">
-        <v>0.528</v>
+        <v>0.475</v>
       </c>
       <c r="H259" t="n">
-        <v>0.1642</v>
+        <v>0.1148</v>
       </c>
       <c r="I259" t="n">
-        <v>25.22</v>
+        <v>25.8</v>
       </c>
       <c r="J259" t="n">
-        <v>335.7</v>
+        <v>346</v>
       </c>
       <c r="K259" t="n">
-        <v>6.22</v>
+        <v>5.354</v>
       </c>
       <c r="L259" t="n">
-        <v>-2.424</v>
+        <v>-4.032</v>
       </c>
       <c r="M259" t="n">
-        <v>22.353</v>
+        <v>18.622</v>
       </c>
     </row>
     <row r="260">
@@ -13655,7 +13655,7 @@
         <v>0.1024</v>
       </c>
       <c r="I260" t="n">
-        <v>23.26</v>
+        <v>23.3</v>
       </c>
       <c r="J260" t="n">
         <v>343</v>
@@ -13700,7 +13700,7 @@
         <v>0.1158</v>
       </c>
       <c r="I261" t="n">
-        <v>25.07</v>
+        <v>25.06</v>
       </c>
       <c r="J261" t="n">
         <v>351.9</v>
@@ -13733,31 +13733,31 @@
         <v>-1</v>
       </c>
       <c r="E262" t="n">
-        <v>1.856</v>
+        <v>2.017</v>
       </c>
       <c r="F262" t="n">
-        <v>0.752</v>
+        <v>0.748</v>
       </c>
       <c r="G262" t="n">
-        <v>0.482</v>
+        <v>0.471</v>
       </c>
       <c r="H262" t="n">
-        <v>0.1014</v>
+        <v>0.1042</v>
       </c>
       <c r="I262" t="n">
-        <v>25.36</v>
+        <v>25.67</v>
       </c>
       <c r="J262" t="n">
-        <v>360.4</v>
+        <v>359.6</v>
       </c>
       <c r="K262" t="n">
-        <v>4.932</v>
+        <v>5.08</v>
       </c>
       <c r="L262" t="n">
-        <v>-4.178</v>
+        <v>-4.126</v>
       </c>
       <c r="M262" t="n">
-        <v>19.864</v>
+        <v>18.144</v>
       </c>
     </row>
     <row r="263">
@@ -13778,31 +13778,31 @@
         <v>1</v>
       </c>
       <c r="E263" t="n">
-        <v>2.094</v>
+        <v>2.314</v>
       </c>
       <c r="F263" t="n">
-        <v>0.746</v>
+        <v>0.896</v>
       </c>
       <c r="G263" t="n">
-        <v>0.469</v>
+        <v>0.528</v>
       </c>
       <c r="H263" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.1442</v>
       </c>
       <c r="I263" t="n">
-        <v>22.56</v>
+        <v>23.4</v>
       </c>
       <c r="J263" t="n">
-        <v>336.7</v>
+        <v>329.3</v>
       </c>
       <c r="K263" t="n">
-        <v>5.098</v>
+        <v>6.027</v>
       </c>
       <c r="L263" t="n">
-        <v>-2.812</v>
+        <v>-2.491</v>
       </c>
       <c r="M263" t="n">
-        <v>20.04</v>
+        <v>21.944</v>
       </c>
     </row>
     <row r="264">
@@ -13835,7 +13835,7 @@
         <v>0.1442</v>
       </c>
       <c r="I264" t="n">
-        <v>23.38</v>
+        <v>23.4</v>
       </c>
       <c r="J264" t="n">
         <v>329.3</v>
@@ -13880,7 +13880,7 @@
         <v>0.1277</v>
       </c>
       <c r="I265" t="n">
-        <v>24.74</v>
+        <v>24.76</v>
       </c>
       <c r="J265" t="n">
         <v>346.5</v>
@@ -13922,19 +13922,19 @@
         <v>0.495</v>
       </c>
       <c r="H266" t="n">
-        <v>0.1035</v>
+        <v>0.1034</v>
       </c>
       <c r="I266" t="n">
-        <v>23.78</v>
+        <v>23.8</v>
       </c>
       <c r="J266" t="n">
         <v>340.8</v>
       </c>
       <c r="K266" t="n">
-        <v>5.699</v>
+        <v>5.698</v>
       </c>
       <c r="L266" t="n">
-        <v>-3.912</v>
+        <v>-3.913</v>
       </c>
       <c r="M266" t="n">
         <v>21.073</v>
@@ -13970,7 +13970,7 @@
         <v>0.1181</v>
       </c>
       <c r="I267" t="n">
-        <v>24.37</v>
+        <v>24.38</v>
       </c>
       <c r="J267" t="n">
         <v>342.3</v>
@@ -14012,7 +14012,7 @@
         <v>0.451</v>
       </c>
       <c r="H268" t="n">
-        <v>0.1002</v>
+        <v>0.1</v>
       </c>
       <c r="I268" t="n">
         <v>24.26</v>
@@ -14021,13 +14021,13 @@
         <v>340.9</v>
       </c>
       <c r="K268" t="n">
-        <v>5.147</v>
+        <v>5.146</v>
       </c>
       <c r="L268" t="n">
-        <v>-4.103</v>
+        <v>-4.104</v>
       </c>
       <c r="M268" t="n">
-        <v>20.151</v>
+        <v>20.147</v>
       </c>
     </row>
     <row r="269">
@@ -14057,22 +14057,22 @@
         <v>0.506</v>
       </c>
       <c r="H269" t="n">
-        <v>0.1065</v>
+        <v>0.1062</v>
       </c>
       <c r="I269" t="n">
-        <v>25.33</v>
+        <v>25.34</v>
       </c>
       <c r="J269" t="n">
         <v>345.7</v>
       </c>
       <c r="K269" t="n">
-        <v>5.526</v>
+        <v>5.524</v>
       </c>
       <c r="L269" t="n">
-        <v>-3.972</v>
+        <v>-3.973</v>
       </c>
       <c r="M269" t="n">
-        <v>20.864</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="270">
@@ -14105,7 +14105,7 @@
         <v>0.1202</v>
       </c>
       <c r="I270" t="n">
-        <v>24.78</v>
+        <v>24.79</v>
       </c>
       <c r="J270" t="n">
         <v>349</v>
@@ -14138,31 +14138,31 @@
         <v>1</v>
       </c>
       <c r="E271" t="n">
-        <v>1.91</v>
+        <v>2.059</v>
       </c>
       <c r="F271" t="n">
-        <v>0.75</v>
+        <v>0.746</v>
       </c>
       <c r="G271" t="n">
-        <v>0.482</v>
+        <v>0.471</v>
       </c>
       <c r="H271" t="n">
-        <v>0.1014</v>
+        <v>0.1042</v>
       </c>
       <c r="I271" t="n">
-        <v>24.23</v>
+        <v>23.45</v>
       </c>
       <c r="J271" t="n">
-        <v>351.4</v>
+        <v>349.4</v>
       </c>
       <c r="K271" t="n">
-        <v>4.982</v>
+        <v>5.118</v>
       </c>
       <c r="L271" t="n">
-        <v>-4.16</v>
+        <v>-4.113</v>
       </c>
       <c r="M271" t="n">
-        <v>19.94</v>
+        <v>20.158</v>
       </c>
     </row>
     <row r="272">
@@ -14192,7 +14192,7 @@
         <v>0.577</v>
       </c>
       <c r="H272" t="n">
-        <v>0.117</v>
+        <v>0.1162</v>
       </c>
       <c r="I272" t="n">
         <v>23.58</v>
@@ -14201,13 +14201,13 @@
         <v>324.1</v>
       </c>
       <c r="K272" t="n">
-        <v>5.494</v>
+        <v>5.489</v>
       </c>
       <c r="L272" t="n">
-        <v>-3.983</v>
+        <v>-3.985</v>
       </c>
       <c r="M272" t="n">
-        <v>20.483</v>
+        <v>20.47</v>
       </c>
     </row>
     <row r="273">
@@ -14237,7 +14237,7 @@
         <v>0.614</v>
       </c>
       <c r="H273" t="n">
-        <v>0.1232</v>
+        <v>0.1222</v>
       </c>
       <c r="I273" t="n">
         <v>22.71</v>
@@ -14246,13 +14246,13 @@
         <v>316.9</v>
       </c>
       <c r="K273" t="n">
-        <v>6.176</v>
+        <v>6.17</v>
       </c>
       <c r="L273" t="n">
-        <v>-2.439</v>
+        <v>-2.441</v>
       </c>
       <c r="M273" t="n">
-        <v>21.62</v>
+        <v>21.606</v>
       </c>
     </row>
     <row r="274">
@@ -14282,7 +14282,7 @@
         <v>0.66</v>
       </c>
       <c r="H274" t="n">
-        <v>0.1101</v>
+        <v>0.1084</v>
       </c>
       <c r="I274" t="n">
         <v>24.62</v>
@@ -14291,13 +14291,13 @@
         <v>318.9</v>
       </c>
       <c r="K274" t="n">
-        <v>6.169</v>
+        <v>6.158</v>
       </c>
       <c r="L274" t="n">
-        <v>-2.442</v>
+        <v>-2.446</v>
       </c>
       <c r="M274" t="n">
-        <v>19.569</v>
+        <v>19.541</v>
       </c>
     </row>
     <row r="275">
@@ -14327,7 +14327,7 @@
         <v>0.706</v>
       </c>
       <c r="H275" t="n">
-        <v>0.1113</v>
+        <v>0.1114</v>
       </c>
       <c r="I275" t="n">
         <v>23.44</v>
@@ -14372,7 +14372,7 @@
         <v>0.706</v>
       </c>
       <c r="H276" t="n">
-        <v>0.1113</v>
+        <v>0.1114</v>
       </c>
       <c r="I276" t="n">
         <v>24.47</v>
@@ -14417,7 +14417,7 @@
         <v>0.577</v>
       </c>
       <c r="H277" t="n">
-        <v>0.117</v>
+        <v>0.1162</v>
       </c>
       <c r="I277" t="n">
         <v>24.77</v>
@@ -14426,13 +14426,13 @@
         <v>333.9</v>
       </c>
       <c r="K277" t="n">
-        <v>5.401</v>
+        <v>5.396</v>
       </c>
       <c r="L277" t="n">
-        <v>-4.015</v>
+        <v>-4.017</v>
       </c>
       <c r="M277" t="n">
-        <v>18.385</v>
+        <v>18.371</v>
       </c>
     </row>
     <row r="278">
@@ -14462,7 +14462,7 @@
         <v>0.656</v>
       </c>
       <c r="H278" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.094</v>
       </c>
       <c r="I278" t="n">
         <v>25.57</v>
@@ -14471,13 +14471,13 @@
         <v>332.6</v>
       </c>
       <c r="K278" t="n">
-        <v>5.563</v>
+        <v>5.559</v>
       </c>
       <c r="L278" t="n">
-        <v>-3.959</v>
+        <v>-3.961</v>
       </c>
       <c r="M278" t="n">
-        <v>18.496</v>
+        <v>18.487</v>
       </c>
     </row>
     <row r="279">
@@ -14507,7 +14507,7 @@
         <v>0.722</v>
       </c>
       <c r="H279" t="n">
-        <v>0.1283</v>
+        <v>0.1269</v>
       </c>
       <c r="I279" t="n">
         <v>24.6</v>
@@ -14516,13 +14516,13 @@
         <v>321.3</v>
       </c>
       <c r="K279" t="n">
-        <v>6.69</v>
+        <v>6.681</v>
       </c>
       <c r="L279" t="n">
-        <v>-3.569</v>
+        <v>-3.572</v>
       </c>
       <c r="M279" t="n">
-        <v>20.513</v>
+        <v>20.486</v>
       </c>
     </row>
     <row r="280">
@@ -14552,7 +14552,7 @@
         <v>0.6889999999999999</v>
       </c>
       <c r="H280" t="n">
-        <v>0.1088</v>
+        <v>0.1083</v>
       </c>
       <c r="I280" t="n">
         <v>23.44</v>
@@ -14561,13 +14561,13 @@
         <v>323.9</v>
       </c>
       <c r="K280" t="n">
-        <v>6.21</v>
+        <v>6.207</v>
       </c>
       <c r="L280" t="n">
-        <v>-3.735</v>
+        <v>-3.736</v>
       </c>
       <c r="M280" t="n">
-        <v>21.59</v>
+        <v>21.585</v>
       </c>
     </row>
     <row r="281">
@@ -14597,7 +14597,7 @@
         <v>0.581</v>
       </c>
       <c r="H281" t="n">
-        <v>0.0919</v>
+        <v>0.0916</v>
       </c>
       <c r="I281" t="n">
         <v>23.8</v>
@@ -14606,13 +14606,13 @@
         <v>329.6</v>
       </c>
       <c r="K281" t="n">
-        <v>5.504</v>
+        <v>5.503</v>
       </c>
       <c r="L281" t="n">
         <v>-3.98</v>
       </c>
       <c r="M281" t="n">
-        <v>20.302</v>
+        <v>20.298</v>
       </c>
     </row>
     <row r="282">
@@ -14642,7 +14642,7 @@
         <v>0.706</v>
       </c>
       <c r="H282" t="n">
-        <v>0.1113</v>
+        <v>0.1114</v>
       </c>
       <c r="I282" t="n">
         <v>24.47</v>
@@ -14687,16 +14687,16 @@
         <v>0.443</v>
       </c>
       <c r="H283" t="n">
-        <v>0.101</v>
+        <v>0.1011</v>
       </c>
       <c r="I283" t="n">
-        <v>19.91</v>
+        <v>19.88</v>
       </c>
       <c r="J283" t="n">
         <v>333.3</v>
       </c>
       <c r="K283" t="n">
-        <v>6.491</v>
+        <v>6.492</v>
       </c>
       <c r="L283" t="n">
         <v>-2.33</v>
@@ -14723,31 +14723,31 @@
         <v>-1</v>
       </c>
       <c r="E284" t="n">
-        <v>2.094</v>
+        <v>2.347</v>
       </c>
       <c r="F284" t="n">
-        <v>0.714</v>
+        <v>0.867</v>
       </c>
       <c r="G284" t="n">
-        <v>0.373</v>
+        <v>0.498</v>
       </c>
       <c r="H284" t="n">
-        <v>0.0775</v>
+        <v>0.1136</v>
       </c>
       <c r="I284" t="n">
-        <v>21.85</v>
+        <v>22.27</v>
       </c>
       <c r="J284" t="n">
-        <v>339.7</v>
+        <v>324.3</v>
       </c>
       <c r="K284" t="n">
-        <v>4.733</v>
+        <v>5.759</v>
       </c>
       <c r="L284" t="n">
-        <v>-4.247</v>
+        <v>-2.584</v>
       </c>
       <c r="M284" t="n">
-        <v>19.215</v>
+        <v>21.258</v>
       </c>
     </row>
     <row r="285">
@@ -14780,7 +14780,7 @@
         <v>0.0808</v>
       </c>
       <c r="I285" t="n">
-        <v>21.21</v>
+        <v>21.1</v>
       </c>
       <c r="J285" t="n">
         <v>323.1</v>
@@ -14825,7 +14825,7 @@
         <v>0.0815</v>
       </c>
       <c r="I286" t="n">
-        <v>21.14</v>
+        <v>21.06</v>
       </c>
       <c r="J286" t="n">
         <v>339.9</v>
@@ -14867,22 +14867,22 @@
         <v>0.443</v>
       </c>
       <c r="H287" t="n">
-        <v>0.101</v>
+        <v>0.1011</v>
       </c>
       <c r="I287" t="n">
-        <v>21.49</v>
+        <v>21.21</v>
       </c>
       <c r="J287" t="n">
         <v>342.2</v>
       </c>
       <c r="K287" t="n">
-        <v>5.421</v>
+        <v>5.422</v>
       </c>
       <c r="L287" t="n">
         <v>-4.008</v>
       </c>
       <c r="M287" t="n">
-        <v>20.578</v>
+        <v>20.579</v>
       </c>
     </row>
     <row r="288">
@@ -14915,7 +14915,7 @@
         <v>0.1238</v>
       </c>
       <c r="I288" t="n">
-        <v>20.87</v>
+        <v>20.77</v>
       </c>
       <c r="J288" t="n">
         <v>326.6</v>
@@ -14957,7 +14957,7 @@
         <v>0.409</v>
       </c>
       <c r="H289" t="n">
-        <v>0.1151</v>
+        <v>0.1152</v>
       </c>
       <c r="I289" t="n">
         <v>20.39</v>
@@ -15002,10 +15002,10 @@
         <v>0.445</v>
       </c>
       <c r="H290" t="n">
-        <v>0.1073</v>
+        <v>0.1074</v>
       </c>
       <c r="I290" t="n">
-        <v>19.76</v>
+        <v>19.75</v>
       </c>
       <c r="J290" t="n">
         <v>317.8</v>
@@ -15050,7 +15050,7 @@
         <v>0.1078</v>
       </c>
       <c r="I291" t="n">
-        <v>21.61</v>
+        <v>21.64</v>
       </c>
       <c r="J291" t="n">
         <v>334.6</v>
@@ -15095,7 +15095,7 @@
         <v>0.0895</v>
       </c>
       <c r="I292" t="n">
-        <v>21.73</v>
+        <v>21.4</v>
       </c>
       <c r="J292" t="n">
         <v>343.6</v>
@@ -15140,7 +15140,7 @@
         <v>0.0808</v>
       </c>
       <c r="I293" t="n">
-        <v>22</v>
+        <v>21.73</v>
       </c>
       <c r="J293" t="n">
         <v>335.6</v>
@@ -15185,7 +15185,7 @@
         <v>0.102</v>
       </c>
       <c r="I294" t="n">
-        <v>22.08</v>
+        <v>22.04</v>
       </c>
       <c r="J294" t="n">
         <v>326.5</v>
@@ -15227,22 +15227,22 @@
         <v>0.422</v>
       </c>
       <c r="H295" t="n">
-        <v>0.1155</v>
+        <v>0.1158</v>
       </c>
       <c r="I295" t="n">
-        <v>19.78</v>
+        <v>19.75</v>
       </c>
       <c r="J295" t="n">
         <v>319.4</v>
       </c>
       <c r="K295" t="n">
-        <v>6.664</v>
+        <v>6.666</v>
       </c>
       <c r="L295" t="n">
         <v>-2.27</v>
       </c>
       <c r="M295" t="n">
-        <v>20.986</v>
+        <v>20.991</v>
       </c>
     </row>
     <row r="296">
@@ -15275,7 +15275,7 @@
         <v>0.1228</v>
       </c>
       <c r="I296" t="n">
-        <v>21.3</v>
+        <v>21.31</v>
       </c>
       <c r="J296" t="n">
         <v>325.8</v>
@@ -15308,31 +15308,31 @@
         <v>-1</v>
       </c>
       <c r="E297" t="n">
-        <v>2.193</v>
+        <v>2.418</v>
       </c>
       <c r="F297" t="n">
-        <v>0.777</v>
+        <v>0.77</v>
       </c>
       <c r="G297" t="n">
-        <v>0.46</v>
+        <v>0.446</v>
       </c>
       <c r="H297" t="n">
-        <v>0.1138</v>
+        <v>0.1145</v>
       </c>
       <c r="I297" t="n">
-        <v>21.98</v>
+        <v>21.92</v>
       </c>
       <c r="J297" t="n">
-        <v>339</v>
+        <v>336.3</v>
       </c>
       <c r="K297" t="n">
-        <v>5.35</v>
+        <v>5.537</v>
       </c>
       <c r="L297" t="n">
-        <v>-4.033</v>
+        <v>-3.968</v>
       </c>
       <c r="M297" t="n">
-        <v>20.216</v>
+        <v>20.476</v>
       </c>
     </row>
     <row r="298">
@@ -15365,7 +15365,7 @@
         <v>0.1287</v>
       </c>
       <c r="I298" t="n">
-        <v>20.43</v>
+        <v>20.4</v>
       </c>
       <c r="J298" t="n">
         <v>325.9</v>
@@ -15410,7 +15410,7 @@
         <v>0.1283</v>
       </c>
       <c r="I299" t="n">
-        <v>20.65</v>
+        <v>20.53</v>
       </c>
       <c r="J299" t="n">
         <v>314.4</v>
@@ -15452,7 +15452,7 @@
         <v>0.491</v>
       </c>
       <c r="H300" t="n">
-        <v>0.1633</v>
+        <v>0.1637</v>
       </c>
       <c r="I300" t="n">
         <v>21.85</v>
@@ -15461,13 +15461,13 @@
         <v>310.5</v>
       </c>
       <c r="K300" t="n">
-        <v>6.41</v>
+        <v>6.412</v>
       </c>
       <c r="L300" t="n">
         <v>-2.358</v>
       </c>
       <c r="M300" t="n">
-        <v>22.181</v>
+        <v>22.186</v>
       </c>
     </row>
     <row r="301">
@@ -15497,22 +15497,22 @@
         <v>0.416</v>
       </c>
       <c r="H301" t="n">
-        <v>0.1339</v>
+        <v>0.1343</v>
       </c>
       <c r="I301" t="n">
-        <v>20.3</v>
+        <v>20.23</v>
       </c>
       <c r="J301" t="n">
         <v>322.4</v>
       </c>
       <c r="K301" t="n">
-        <v>5.635</v>
+        <v>5.638</v>
       </c>
       <c r="L301" t="n">
-        <v>-3.934</v>
+        <v>-3.933</v>
       </c>
       <c r="M301" t="n">
-        <v>20.769</v>
+        <v>20.774</v>
       </c>
     </row>
     <row r="302">
@@ -15545,7 +15545,7 @@
         <v>0.106</v>
       </c>
       <c r="I302" t="n">
-        <v>20.48</v>
+        <v>20.36</v>
       </c>
       <c r="J302" t="n">
         <v>306.7</v>
@@ -15632,7 +15632,7 @@
         <v>0.416</v>
       </c>
       <c r="H304" t="n">
-        <v>0.1339</v>
+        <v>0.1343</v>
       </c>
       <c r="I304" t="n">
         <v>20.84</v>
@@ -15641,13 +15641,13 @@
         <v>332.5</v>
       </c>
       <c r="K304" t="n">
-        <v>5.529</v>
+        <v>5.532</v>
       </c>
       <c r="L304" t="n">
-        <v>-3.971</v>
+        <v>-3.97</v>
       </c>
       <c r="M304" t="n">
-        <v>20.608</v>
+        <v>20.613</v>
       </c>
     </row>
     <row r="305">
@@ -15677,7 +15677,7 @@
         <v>0.5659999999999999</v>
       </c>
       <c r="H305" t="n">
-        <v>0.1129</v>
+        <v>0.1136</v>
       </c>
       <c r="I305" t="n">
         <v>20.25</v>
@@ -15686,13 +15686,13 @@
         <v>303</v>
       </c>
       <c r="K305" t="n">
-        <v>6.174</v>
+        <v>6.179</v>
       </c>
       <c r="L305" t="n">
-        <v>-2.44</v>
+        <v>-2.438</v>
       </c>
       <c r="M305" t="n">
-        <v>21.926</v>
+        <v>21.939</v>
       </c>
     </row>
     <row r="306">
@@ -15722,7 +15722,7 @@
         <v>0.545</v>
       </c>
       <c r="H306" t="n">
-        <v>0.1003</v>
+        <v>0.1002</v>
       </c>
       <c r="I306" t="n">
         <v>20.07</v>
@@ -15731,13 +15731,13 @@
         <v>303.9</v>
       </c>
       <c r="K306" t="n">
-        <v>5.718</v>
+        <v>5.717</v>
       </c>
       <c r="L306" t="n">
         <v>-2.598</v>
       </c>
       <c r="M306" t="n">
-        <v>21.075</v>
+        <v>21.074</v>
       </c>
     </row>
     <row r="307">
@@ -15767,7 +15767,7 @@
         <v>0.609</v>
       </c>
       <c r="H307" t="n">
-        <v>0.1243</v>
+        <v>0.1252</v>
       </c>
       <c r="I307" t="n">
         <v>19.61</v>
@@ -15776,13 +15776,13 @@
         <v>306.9</v>
       </c>
       <c r="K307" t="n">
-        <v>7.499</v>
+        <v>7.504</v>
       </c>
       <c r="L307" t="n">
-        <v>-1.981</v>
+        <v>-1.98</v>
       </c>
       <c r="M307" t="n">
-        <v>22.884</v>
+        <v>22.897</v>
       </c>
     </row>
     <row r="308">
@@ -15812,7 +15812,7 @@
         <v>0.528</v>
       </c>
       <c r="H308" t="n">
-        <v>0.1265</v>
+        <v>0.1282</v>
       </c>
       <c r="I308" t="n">
         <v>21.04</v>
@@ -15821,13 +15821,13 @@
         <v>324.8</v>
       </c>
       <c r="K308" t="n">
-        <v>5.894</v>
+        <v>5.904</v>
       </c>
       <c r="L308" t="n">
-        <v>-2.537</v>
+        <v>-2.533</v>
       </c>
       <c r="M308" t="n">
-        <v>21.588</v>
+        <v>21.615</v>
       </c>
     </row>
     <row r="309">
@@ -15857,7 +15857,7 @@
         <v>0.585</v>
       </c>
       <c r="H309" t="n">
-        <v>0.097</v>
+        <v>0.0968</v>
       </c>
       <c r="I309" t="n">
         <v>20.37</v>
@@ -15866,7 +15866,7 @@
         <v>338.9</v>
       </c>
       <c r="K309" t="n">
-        <v>5.906</v>
+        <v>5.905</v>
       </c>
       <c r="L309" t="n">
         <v>-3.841</v>
@@ -15902,7 +15902,7 @@
         <v>0.529</v>
       </c>
       <c r="H310" t="n">
-        <v>0.1104</v>
+        <v>0.1108</v>
       </c>
       <c r="I310" t="n">
         <v>19.85</v>
@@ -15911,13 +15911,13 @@
         <v>317.9</v>
       </c>
       <c r="K310" t="n">
-        <v>6.858</v>
+        <v>6.861</v>
       </c>
       <c r="L310" t="n">
-        <v>-2.203</v>
+        <v>-2.202</v>
       </c>
       <c r="M310" t="n">
-        <v>21.737</v>
+        <v>21.746</v>
       </c>
     </row>
     <row r="311">
@@ -15947,7 +15947,7 @@
         <v>0.529</v>
       </c>
       <c r="H311" t="n">
-        <v>0.0887</v>
+        <v>0.0886</v>
       </c>
       <c r="I311" t="n">
         <v>20.7</v>
@@ -15962,7 +15962,7 @@
         <v>-2.509</v>
       </c>
       <c r="M311" t="n">
-        <v>21.387</v>
+        <v>21.383</v>
       </c>
     </row>
     <row r="312">
@@ -15983,31 +15983,31 @@
         <v>-1</v>
       </c>
       <c r="E312" t="n">
-        <v>2.069</v>
+        <v>2.285</v>
       </c>
       <c r="F312" t="n">
-        <v>0.757</v>
+        <v>0.743</v>
       </c>
       <c r="G312" t="n">
-        <v>0.537</v>
+        <v>0.532</v>
       </c>
       <c r="H312" t="n">
-        <v>0.0911</v>
+        <v>0.0963</v>
       </c>
       <c r="I312" t="n">
-        <v>21.67</v>
+        <v>21.1</v>
       </c>
       <c r="J312" t="n">
-        <v>350.2</v>
+        <v>348.8</v>
       </c>
       <c r="K312" t="n">
-        <v>5.204</v>
+        <v>5.413</v>
       </c>
       <c r="L312" t="n">
-        <v>-4.083</v>
+        <v>-4.011</v>
       </c>
       <c r="M312" t="n">
-        <v>20.212</v>
+        <v>20.566</v>
       </c>
     </row>
     <row r="313">
@@ -16037,7 +16037,7 @@
         <v>0.485</v>
       </c>
       <c r="H313" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0887</v>
       </c>
       <c r="I313" t="n">
         <v>20.47</v>
@@ -16046,13 +16046,13 @@
         <v>311.3</v>
       </c>
       <c r="K313" t="n">
-        <v>5.589</v>
+        <v>5.588</v>
       </c>
       <c r="L313" t="n">
         <v>-2.643</v>
       </c>
       <c r="M313" t="n">
-        <v>20.767</v>
+        <v>20.763</v>
       </c>
     </row>
     <row r="314">
@@ -16082,7 +16082,7 @@
         <v>0.512</v>
       </c>
       <c r="H314" t="n">
-        <v>0.0917</v>
+        <v>0.0916</v>
       </c>
       <c r="I314" t="n">
         <v>22.03</v>
@@ -16097,7 +16097,7 @@
         <v>-2.611</v>
       </c>
       <c r="M314" t="n">
-        <v>20.943</v>
+        <v>20.94</v>
       </c>
     </row>
     <row r="315">
@@ -16127,7 +16127,7 @@
         <v>0.485</v>
       </c>
       <c r="H315" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0887</v>
       </c>
       <c r="I315" t="n">
         <v>21.2</v>
@@ -16136,13 +16136,13 @@
         <v>327.2</v>
       </c>
       <c r="K315" t="n">
-        <v>5.502</v>
+        <v>5.501</v>
       </c>
       <c r="L315" t="n">
         <v>-2.673</v>
       </c>
       <c r="M315" t="n">
-        <v>20.632</v>
+        <v>20.628</v>
       </c>
     </row>
     <row r="316">
@@ -16152,42 +16152,42 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E316" t="n">
-        <v>2.199</v>
+        <v>2.302</v>
       </c>
       <c r="F316" t="n">
-        <v>0.68</v>
+        <v>0.676</v>
       </c>
       <c r="G316" t="n">
-        <v>0.445</v>
+        <v>0.448</v>
       </c>
       <c r="H316" t="n">
-        <v>0.1024</v>
+        <v>0.106</v>
       </c>
       <c r="I316" t="n">
-        <v>21.39</v>
+        <v>21.16</v>
       </c>
       <c r="J316" t="n">
-        <v>325.3</v>
+        <v>336.3</v>
       </c>
       <c r="K316" t="n">
-        <v>5.063</v>
+        <v>5.186</v>
       </c>
       <c r="L316" t="n">
-        <v>-2.825</v>
+        <v>-2.782</v>
       </c>
       <c r="M316" t="n">
-        <v>20.01</v>
+        <v>20.209</v>
       </c>
     </row>
     <row r="317">
@@ -16197,42 +16197,42 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E317" t="n">
-        <v>2.293</v>
+        <v>2.482</v>
       </c>
       <c r="F317" t="n">
-        <v>0.849</v>
+        <v>0.833</v>
       </c>
       <c r="G317" t="n">
-        <v>0.544</v>
+        <v>0.43</v>
       </c>
       <c r="H317" t="n">
-        <v>0.1542</v>
+        <v>0.1435</v>
       </c>
       <c r="I317" t="n">
-        <v>22.48</v>
+        <v>20.75</v>
       </c>
       <c r="J317" t="n">
-        <v>321</v>
+        <v>315.3</v>
       </c>
       <c r="K317" t="n">
-        <v>6.004</v>
+        <v>5.869</v>
       </c>
       <c r="L317" t="n">
-        <v>-2.499</v>
+        <v>-2.546</v>
       </c>
       <c r="M317" t="n">
-        <v>21.969</v>
+        <v>21.581</v>
       </c>
     </row>
     <row r="318">
@@ -16242,42 +16242,42 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E318" t="n">
-        <v>2.329</v>
+        <v>2.467</v>
       </c>
       <c r="F318" t="n">
-        <v>0.849</v>
+        <v>0.765</v>
       </c>
       <c r="G318" t="n">
-        <v>0.49</v>
+        <v>0.455</v>
       </c>
       <c r="H318" t="n">
-        <v>0.1458</v>
+        <v>0.1212</v>
       </c>
       <c r="I318" t="n">
-        <v>20.61</v>
+        <v>21.18</v>
       </c>
       <c r="J318" t="n">
-        <v>316.7</v>
+        <v>335.9</v>
       </c>
       <c r="K318" t="n">
-        <v>5.882</v>
+        <v>5.634</v>
       </c>
       <c r="L318" t="n">
-        <v>-2.541</v>
+        <v>-2.627</v>
       </c>
       <c r="M318" t="n">
-        <v>21.682</v>
+        <v>21.06</v>
       </c>
     </row>
     <row r="319">
@@ -16287,42 +16287,42 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E319" t="n">
-        <v>2.261</v>
+        <v>2.387</v>
       </c>
       <c r="F319" t="n">
-        <v>0.775</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G319" t="n">
-        <v>0.506</v>
+        <v>0.45</v>
       </c>
       <c r="H319" t="n">
-        <v>0.1227</v>
+        <v>0.1055</v>
       </c>
       <c r="I319" t="n">
-        <v>21.4</v>
+        <v>21.19</v>
       </c>
       <c r="J319" t="n">
-        <v>337.3</v>
+        <v>335.4</v>
       </c>
       <c r="K319" t="n">
-        <v>5.559</v>
+        <v>5.306</v>
       </c>
       <c r="L319" t="n">
-        <v>-3.961</v>
+        <v>-2.74</v>
       </c>
       <c r="M319" t="n">
-        <v>21.005</v>
+        <v>20.406</v>
       </c>
     </row>
     <row r="320">
@@ -16332,42 +16332,42 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D320" t="n">
         <v>1</v>
       </c>
       <c r="E320" t="n">
-        <v>2.232</v>
+        <v>2.549</v>
       </c>
       <c r="F320" t="n">
-        <v>0.712</v>
+        <v>0.802</v>
       </c>
       <c r="G320" t="n">
-        <v>0.428</v>
+        <v>0.441</v>
       </c>
       <c r="H320" t="n">
-        <v>0.1087</v>
+        <v>0.1191</v>
       </c>
       <c r="I320" t="n">
-        <v>21.47</v>
+        <v>20.4</v>
       </c>
       <c r="J320" t="n">
-        <v>339</v>
+        <v>309.9</v>
       </c>
       <c r="K320" t="n">
-        <v>5.164</v>
+        <v>5.75</v>
       </c>
       <c r="L320" t="n">
-        <v>-4.097</v>
+        <v>-2.587</v>
       </c>
       <c r="M320" t="n">
-        <v>20.206</v>
+        <v>21.226</v>
       </c>
     </row>
     <row r="321">
@@ -16377,42 +16377,42 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E321" t="n">
-        <v>2.355</v>
+        <v>2.569</v>
       </c>
       <c r="F321" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.758</v>
       </c>
       <c r="G321" t="n">
-        <v>0.514</v>
+        <v>0.463</v>
       </c>
       <c r="H321" t="n">
-        <v>0.1221</v>
+        <v>0.1007</v>
       </c>
       <c r="I321" t="n">
-        <v>20.44</v>
+        <v>21.12</v>
       </c>
       <c r="J321" t="n">
-        <v>311.3</v>
+        <v>329.9</v>
       </c>
       <c r="K321" t="n">
-        <v>5.74</v>
+        <v>5.615</v>
       </c>
       <c r="L321" t="n">
-        <v>-2.59</v>
+        <v>-2.634</v>
       </c>
       <c r="M321" t="n">
-        <v>21.298</v>
+        <v>20.864</v>
       </c>
     </row>
     <row r="322">
@@ -16422,42 +16422,42 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E322" t="n">
-        <v>2.393</v>
+        <v>2.429</v>
       </c>
       <c r="F322" t="n">
-        <v>0.777</v>
+        <v>0.788</v>
       </c>
       <c r="G322" t="n">
-        <v>0.533</v>
+        <v>0.445</v>
       </c>
       <c r="H322" t="n">
-        <v>0.1053</v>
+        <v>0.1071</v>
       </c>
       <c r="I322" t="n">
-        <v>21.44</v>
+        <v>20.64</v>
       </c>
       <c r="J322" t="n">
-        <v>331.3</v>
+        <v>318.3</v>
       </c>
       <c r="K322" t="n">
-        <v>5.645</v>
+        <v>5.538</v>
       </c>
       <c r="L322" t="n">
-        <v>-2.623</v>
+        <v>-2.66</v>
       </c>
       <c r="M322" t="n">
-        <v>21.023</v>
+        <v>20.804</v>
       </c>
     </row>
     <row r="323">
@@ -16467,42 +16467,42 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E323" t="n">
-        <v>2.244</v>
+        <v>2.421</v>
       </c>
       <c r="F323" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.839</v>
       </c>
       <c r="G323" t="n">
-        <v>0.493</v>
+        <v>0.52</v>
       </c>
       <c r="H323" t="n">
-        <v>0.1141</v>
+        <v>0.1486</v>
       </c>
       <c r="I323" t="n">
-        <v>20.9</v>
+        <v>22.13</v>
       </c>
       <c r="J323" t="n">
-        <v>319.7</v>
+        <v>320.4</v>
       </c>
       <c r="K323" t="n">
-        <v>5.539</v>
+        <v>6.031</v>
       </c>
       <c r="L323" t="n">
-        <v>-2.66</v>
+        <v>-2.49</v>
       </c>
       <c r="M323" t="n">
-        <v>20.921</v>
+        <v>21.956</v>
       </c>
     </row>
     <row r="324">
@@ -16512,42 +16512,42 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D324" t="n">
         <v>-1</v>
       </c>
       <c r="E324" t="n">
-        <v>2.293</v>
+        <v>2.531</v>
       </c>
       <c r="F324" t="n">
-        <v>0.849</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G324" t="n">
-        <v>0.544</v>
+        <v>0.477</v>
       </c>
       <c r="H324" t="n">
-        <v>0.1542</v>
+        <v>0.1259</v>
       </c>
       <c r="I324" t="n">
-        <v>22.48</v>
+        <v>21.28</v>
       </c>
       <c r="J324" t="n">
-        <v>321</v>
+        <v>317.7</v>
       </c>
       <c r="K324" t="n">
-        <v>6.004</v>
+        <v>5.86</v>
       </c>
       <c r="L324" t="n">
-        <v>-2.499</v>
+        <v>-2.549</v>
       </c>
       <c r="M324" t="n">
-        <v>21.969</v>
+        <v>21.477</v>
       </c>
     </row>
     <row r="325">
@@ -16557,42 +16557,42 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E325" t="n">
-        <v>2.32</v>
+        <v>2.341</v>
       </c>
       <c r="F325" t="n">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="G325" t="n">
-        <v>0.526</v>
+        <v>0.454</v>
       </c>
       <c r="H325" t="n">
-        <v>0.1336</v>
+        <v>0.1076</v>
       </c>
       <c r="I325" t="n">
-        <v>21.11</v>
+        <v>20.69</v>
       </c>
       <c r="J325" t="n">
-        <v>317.7</v>
+        <v>338.4</v>
       </c>
       <c r="K325" t="n">
-        <v>5.814</v>
+        <v>5.255</v>
       </c>
       <c r="L325" t="n">
-        <v>-2.565</v>
+        <v>-4.066</v>
       </c>
       <c r="M325" t="n">
-        <v>21.519</v>
+        <v>20.346</v>
       </c>
     </row>
     <row r="326">
@@ -16602,87 +16602,87 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E326" t="n">
-        <v>2.074</v>
+        <v>2.6</v>
       </c>
       <c r="F326" t="n">
-        <v>0.7</v>
+        <v>0.87</v>
       </c>
       <c r="G326" t="n">
-        <v>0.444</v>
+        <v>0.534</v>
       </c>
       <c r="H326" t="n">
-        <v>0.1108</v>
+        <v>0.1381</v>
       </c>
       <c r="I326" t="n">
-        <v>21.02</v>
+        <v>21.24</v>
       </c>
       <c r="J326" t="n">
-        <v>344.7</v>
+        <v>321.2</v>
       </c>
       <c r="K326" t="n">
-        <v>5.027</v>
+        <v>6.237</v>
       </c>
       <c r="L326" t="n">
-        <v>-4.145</v>
+        <v>-2.418</v>
       </c>
       <c r="M326" t="n">
-        <v>20.039</v>
+        <v>22.192</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="D327" t="n">
         <v>-1</v>
       </c>
       <c r="E327" t="n">
-        <v>2.454</v>
+        <v>2.287</v>
       </c>
       <c r="F327" t="n">
-        <v>0.862</v>
+        <v>0.852</v>
       </c>
       <c r="G327" t="n">
-        <v>0.609</v>
+        <v>0.507</v>
       </c>
       <c r="H327" t="n">
-        <v>0.1404</v>
+        <v>0.0898</v>
       </c>
       <c r="I327" t="n">
-        <v>21.26</v>
+        <v>23.82</v>
       </c>
       <c r="J327" t="n">
-        <v>322</v>
+        <v>337.6</v>
       </c>
       <c r="K327" t="n">
-        <v>6.238</v>
+        <v>5.544</v>
       </c>
       <c r="L327" t="n">
-        <v>-2.418</v>
+        <v>-3.966</v>
       </c>
       <c r="M327" t="n">
-        <v>22.263</v>
+        <v>20.737</v>
       </c>
     </row>
     <row r="328">
@@ -16692,42 +16692,42 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E328" t="n">
-        <v>2.287</v>
+        <v>2.213</v>
       </c>
       <c r="F328" t="n">
-        <v>0.852</v>
+        <v>0.771</v>
       </c>
       <c r="G328" t="n">
-        <v>0.507</v>
+        <v>0.415</v>
       </c>
       <c r="H328" t="n">
-        <v>0.0898</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="I328" t="n">
-        <v>23.95</v>
+        <v>20.82</v>
       </c>
       <c r="J328" t="n">
-        <v>337.6</v>
+        <v>325.9</v>
       </c>
       <c r="K328" t="n">
-        <v>5.544</v>
+        <v>5.144</v>
       </c>
       <c r="L328" t="n">
-        <v>-3.966</v>
+        <v>-2.797</v>
       </c>
       <c r="M328" t="n">
-        <v>20.737</v>
+        <v>20.05</v>
       </c>
     </row>
     <row r="329">
@@ -16737,42 +16737,42 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E329" t="n">
-        <v>2.386</v>
+        <v>2.296</v>
       </c>
       <c r="F329" t="n">
-        <v>0.905</v>
+        <v>0.765</v>
       </c>
       <c r="G329" t="n">
-        <v>0.495</v>
+        <v>0.446</v>
       </c>
       <c r="H329" t="n">
-        <v>0.1285</v>
+        <v>0.098</v>
       </c>
       <c r="I329" t="n">
-        <v>21.37</v>
+        <v>22.76</v>
       </c>
       <c r="J329" t="n">
-        <v>304.6</v>
+        <v>327</v>
       </c>
       <c r="K329" t="n">
-        <v>5.957</v>
+        <v>5.306</v>
       </c>
       <c r="L329" t="n">
-        <v>-2.515</v>
+        <v>-2.74</v>
       </c>
       <c r="M329" t="n">
-        <v>21.696</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="330">
@@ -16782,42 +16782,42 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D330" t="n">
         <v>-1</v>
       </c>
       <c r="E330" t="n">
-        <v>2.296</v>
+        <v>2.286</v>
       </c>
       <c r="F330" t="n">
-        <v>0.765</v>
+        <v>0.866</v>
       </c>
       <c r="G330" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="H330" t="n">
-        <v>0.098</v>
+        <v>0.0958</v>
       </c>
       <c r="I330" t="n">
-        <v>22.81</v>
+        <v>22.78</v>
       </c>
       <c r="J330" t="n">
-        <v>327</v>
+        <v>336.7</v>
       </c>
       <c r="K330" t="n">
-        <v>5.306</v>
+        <v>5.483</v>
       </c>
       <c r="L330" t="n">
-        <v>-2.74</v>
+        <v>-3.987</v>
       </c>
       <c r="M330" t="n">
-        <v>20.37</v>
+        <v>20.657</v>
       </c>
     </row>
     <row r="331">
@@ -16827,42 +16827,42 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E331" t="n">
-        <v>2.286</v>
+        <v>2.351</v>
       </c>
       <c r="F331" t="n">
-        <v>0.866</v>
+        <v>0.87</v>
       </c>
       <c r="G331" t="n">
-        <v>0.445</v>
+        <v>0.507</v>
       </c>
       <c r="H331" t="n">
-        <v>0.0958</v>
+        <v>0.0898</v>
       </c>
       <c r="I331" t="n">
-        <v>22.95</v>
+        <v>21.47</v>
       </c>
       <c r="J331" t="n">
-        <v>336.7</v>
+        <v>319.9</v>
       </c>
       <c r="K331" t="n">
-        <v>5.483</v>
+        <v>5.644</v>
       </c>
       <c r="L331" t="n">
-        <v>-3.987</v>
+        <v>-2.623</v>
       </c>
       <c r="M331" t="n">
-        <v>20.657</v>
+        <v>20.896</v>
       </c>
     </row>
     <row r="332">
@@ -16872,42 +16872,42 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D332" t="n">
         <v>1</v>
       </c>
       <c r="E332" t="n">
-        <v>2.351</v>
+        <v>2.386</v>
       </c>
       <c r="F332" t="n">
-        <v>0.87</v>
+        <v>0.905</v>
       </c>
       <c r="G332" t="n">
-        <v>0.507</v>
+        <v>0.495</v>
       </c>
       <c r="H332" t="n">
-        <v>0.0898</v>
+        <v>0.1285</v>
       </c>
       <c r="I332" t="n">
-        <v>21.41</v>
+        <v>21.44</v>
       </c>
       <c r="J332" t="n">
-        <v>319.9</v>
+        <v>304.6</v>
       </c>
       <c r="K332" t="n">
-        <v>5.644</v>
+        <v>5.957</v>
       </c>
       <c r="L332" t="n">
-        <v>-2.623</v>
+        <v>-2.515</v>
       </c>
       <c r="M332" t="n">
-        <v>20.896</v>
+        <v>21.696</v>
       </c>
     </row>
     <row r="333">
@@ -16917,42 +16917,42 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E333" t="n">
-        <v>2.386</v>
+        <v>1.963</v>
       </c>
       <c r="F333" t="n">
-        <v>0.905</v>
+        <v>0.825</v>
       </c>
       <c r="G333" t="n">
-        <v>0.495</v>
+        <v>0.401</v>
       </c>
       <c r="H333" t="n">
-        <v>0.1285</v>
+        <v>0.1158</v>
       </c>
       <c r="I333" t="n">
-        <v>21.37</v>
+        <v>22.02</v>
       </c>
       <c r="J333" t="n">
-        <v>304.6</v>
+        <v>345.7</v>
       </c>
       <c r="K333" t="n">
-        <v>5.957</v>
+        <v>5.11</v>
       </c>
       <c r="L333" t="n">
-        <v>-2.515</v>
+        <v>-4.116</v>
       </c>
       <c r="M333" t="n">
-        <v>21.696</v>
+        <v>20.221</v>
       </c>
     </row>
     <row r="334">
@@ -16962,42 +16962,42 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E334" t="n">
-        <v>1.963</v>
+        <v>2.511</v>
       </c>
       <c r="F334" t="n">
-        <v>0.825</v>
+        <v>0.872</v>
       </c>
       <c r="G334" t="n">
-        <v>0.401</v>
+        <v>0.408</v>
       </c>
       <c r="H334" t="n">
-        <v>0.1158</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="I334" t="n">
-        <v>22.05</v>
+        <v>21.07</v>
       </c>
       <c r="J334" t="n">
-        <v>345.7</v>
+        <v>326.5</v>
       </c>
       <c r="K334" t="n">
-        <v>5.11</v>
+        <v>5.584</v>
       </c>
       <c r="L334" t="n">
-        <v>-4.116</v>
+        <v>-2.644</v>
       </c>
       <c r="M334" t="n">
-        <v>20.221</v>
+        <v>20.68</v>
       </c>
     </row>
     <row r="335">
@@ -17007,42 +17007,42 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E335" t="n">
-        <v>2.511</v>
+        <v>2.122</v>
       </c>
       <c r="F335" t="n">
-        <v>0.872</v>
+        <v>0.757</v>
       </c>
       <c r="G335" t="n">
-        <v>0.408</v>
+        <v>0.415</v>
       </c>
       <c r="H335" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="I335" t="n">
-        <v>21.02</v>
+        <v>23.03</v>
       </c>
       <c r="J335" t="n">
-        <v>326.5</v>
+        <v>341.7</v>
       </c>
       <c r="K335" t="n">
-        <v>5.584</v>
+        <v>5.025</v>
       </c>
       <c r="L335" t="n">
-        <v>-2.644</v>
+        <v>-4.145</v>
       </c>
       <c r="M335" t="n">
-        <v>20.68</v>
+        <v>19.864</v>
       </c>
     </row>
     <row r="336">
@@ -17052,42 +17052,42 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E336" t="n">
-        <v>2.329</v>
+        <v>2.294</v>
       </c>
       <c r="F336" t="n">
-        <v>0.905</v>
+        <v>0.908</v>
       </c>
       <c r="G336" t="n">
-        <v>0.495</v>
+        <v>0.42</v>
       </c>
       <c r="H336" t="n">
-        <v>0.1285</v>
+        <v>0.0886</v>
       </c>
       <c r="I336" t="n">
-        <v>23.28</v>
+        <v>21</v>
       </c>
       <c r="J336" t="n">
-        <v>320.6</v>
+        <v>320.4</v>
       </c>
       <c r="K336" t="n">
-        <v>5.9</v>
+        <v>5.482</v>
       </c>
       <c r="L336" t="n">
-        <v>-2.535</v>
+        <v>-2.68</v>
       </c>
       <c r="M336" t="n">
-        <v>21.611</v>
+        <v>20.589</v>
       </c>
     </row>
     <row r="337">
@@ -17097,87 +17097,87 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E337" t="n">
-        <v>2.294</v>
+        <v>2.427</v>
       </c>
       <c r="F337" t="n">
-        <v>0.908</v>
+        <v>0.843</v>
       </c>
       <c r="G337" t="n">
-        <v>0.42</v>
+        <v>0.408</v>
       </c>
       <c r="H337" t="n">
-        <v>0.0886</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="I337" t="n">
-        <v>21.01</v>
+        <v>22.94</v>
       </c>
       <c r="J337" t="n">
-        <v>320.4</v>
+        <v>343.1</v>
       </c>
       <c r="K337" t="n">
-        <v>5.482</v>
+        <v>5.442</v>
       </c>
       <c r="L337" t="n">
-        <v>-2.68</v>
+        <v>-4.001</v>
       </c>
       <c r="M337" t="n">
-        <v>20.589</v>
+        <v>20.461</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E338" t="n">
-        <v>2.427</v>
+        <v>2.365</v>
       </c>
       <c r="F338" t="n">
-        <v>0.843</v>
+        <v>0.67</v>
       </c>
       <c r="G338" t="n">
-        <v>0.408</v>
+        <v>0.506</v>
       </c>
       <c r="H338" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="I338" t="n">
-        <v>23.09</v>
+        <v>25.25</v>
       </c>
       <c r="J338" t="n">
-        <v>343.1</v>
+        <v>339.4</v>
       </c>
       <c r="K338" t="n">
-        <v>5.442</v>
+        <v>5.125</v>
       </c>
       <c r="L338" t="n">
-        <v>-4.001</v>
+        <v>-4.111</v>
       </c>
       <c r="M338" t="n">
-        <v>20.461</v>
+        <v>19.791</v>
       </c>
     </row>
     <row r="339">
@@ -17187,42 +17187,42 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E339" t="n">
-        <v>2.365</v>
+        <v>2.491</v>
       </c>
       <c r="F339" t="n">
-        <v>0.67</v>
+        <v>0.715</v>
       </c>
       <c r="G339" t="n">
-        <v>0.506</v>
+        <v>0.548</v>
       </c>
       <c r="H339" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0804</v>
       </c>
       <c r="I339" t="n">
-        <v>25.25</v>
+        <v>25.21</v>
       </c>
       <c r="J339" t="n">
-        <v>339.4</v>
+        <v>348.7</v>
       </c>
       <c r="K339" t="n">
-        <v>5.126</v>
+        <v>5.499</v>
       </c>
       <c r="L339" t="n">
-        <v>-4.11</v>
+        <v>-3.981</v>
       </c>
       <c r="M339" t="n">
-        <v>19.791</v>
+        <v>20.532</v>
       </c>
     </row>
     <row r="340">
@@ -17232,42 +17232,42 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E340" t="n">
-        <v>2.491</v>
+        <v>2.443</v>
       </c>
       <c r="F340" t="n">
-        <v>0.715</v>
+        <v>0.839</v>
       </c>
       <c r="G340" t="n">
-        <v>0.548</v>
+        <v>0.614</v>
       </c>
       <c r="H340" t="n">
-        <v>0.0805</v>
+        <v>0.0953</v>
       </c>
       <c r="I340" t="n">
-        <v>25.21</v>
+        <v>24.02</v>
       </c>
       <c r="J340" t="n">
-        <v>348.7</v>
+        <v>324.9</v>
       </c>
       <c r="K340" t="n">
-        <v>5.5</v>
+        <v>5.921</v>
       </c>
       <c r="L340" t="n">
-        <v>-3.981</v>
+        <v>-2.528</v>
       </c>
       <c r="M340" t="n">
-        <v>20.532</v>
+        <v>21.422</v>
       </c>
     </row>
     <row r="341">
@@ -17277,42 +17277,42 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E341" t="n">
-        <v>2.443</v>
+        <v>2.474</v>
       </c>
       <c r="F341" t="n">
-        <v>0.839</v>
+        <v>0.769</v>
       </c>
       <c r="G341" t="n">
-        <v>0.614</v>
+        <v>0.537</v>
       </c>
       <c r="H341" t="n">
-        <v>0.0953</v>
+        <v>0.079</v>
       </c>
       <c r="I341" t="n">
-        <v>24.02</v>
+        <v>25.24</v>
       </c>
       <c r="J341" t="n">
-        <v>324.9</v>
+        <v>348.7</v>
       </c>
       <c r="K341" t="n">
-        <v>5.921</v>
+        <v>5.56</v>
       </c>
       <c r="L341" t="n">
-        <v>-2.528</v>
+        <v>-3.96</v>
       </c>
       <c r="M341" t="n">
-        <v>21.422</v>
+        <v>20.624</v>
       </c>
     </row>
     <row r="342">
@@ -17322,42 +17322,42 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="D342" t="n">
         <v>-1</v>
       </c>
       <c r="E342" t="n">
-        <v>2.474</v>
+        <v>2.408</v>
       </c>
       <c r="F342" t="n">
-        <v>0.769</v>
+        <v>0.839</v>
       </c>
       <c r="G342" t="n">
-        <v>0.537</v>
+        <v>0.614</v>
       </c>
       <c r="H342" t="n">
-        <v>0.079</v>
+        <v>0.0953</v>
       </c>
       <c r="I342" t="n">
-        <v>25.24</v>
+        <v>25.09</v>
       </c>
       <c r="J342" t="n">
-        <v>348.7</v>
+        <v>337.4</v>
       </c>
       <c r="K342" t="n">
-        <v>5.56</v>
+        <v>5.886</v>
       </c>
       <c r="L342" t="n">
-        <v>-3.96</v>
+        <v>-3.847</v>
       </c>
       <c r="M342" t="n">
-        <v>20.624</v>
+        <v>21.371</v>
       </c>
     </row>
     <row r="343">
@@ -17367,18 +17367,18 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>JAX</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E343" t="n">
-        <v>2.408</v>
+        <v>2.443</v>
       </c>
       <c r="F343" t="n">
         <v>0.839</v>
@@ -17390,19 +17390,19 @@
         <v>0.0953</v>
       </c>
       <c r="I343" t="n">
-        <v>25.09</v>
+        <v>24.02</v>
       </c>
       <c r="J343" t="n">
-        <v>337.4</v>
+        <v>324.9</v>
       </c>
       <c r="K343" t="n">
-        <v>5.886</v>
+        <v>5.921</v>
       </c>
       <c r="L343" t="n">
-        <v>-3.847</v>
+        <v>-2.528</v>
       </c>
       <c r="M343" t="n">
-        <v>21.371</v>
+        <v>21.422</v>
       </c>
     </row>
     <row r="344">
@@ -17412,42 +17412,42 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E344" t="n">
-        <v>2.294</v>
+        <v>2.396</v>
       </c>
       <c r="F344" t="n">
-        <v>0.662</v>
+        <v>0.787</v>
       </c>
       <c r="G344" t="n">
-        <v>0.486</v>
+        <v>0.556</v>
       </c>
       <c r="H344" t="n">
-        <v>0.066</v>
+        <v>0.0736</v>
       </c>
       <c r="I344" t="n">
-        <v>23.99</v>
+        <v>25.7</v>
       </c>
       <c r="J344" t="n">
-        <v>335.1</v>
+        <v>345.4</v>
       </c>
       <c r="K344" t="n">
-        <v>4.986</v>
+        <v>5.524</v>
       </c>
       <c r="L344" t="n">
-        <v>-2.851</v>
+        <v>-3.973</v>
       </c>
       <c r="M344" t="n">
-        <v>19.546</v>
+        <v>18.588</v>
       </c>
     </row>
     <row r="345">
@@ -17457,42 +17457,42 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E345" t="n">
-        <v>2.396</v>
+        <v>2.537</v>
       </c>
       <c r="F345" t="n">
-        <v>0.787</v>
+        <v>0.861</v>
       </c>
       <c r="G345" t="n">
-        <v>0.556</v>
+        <v>0.532</v>
       </c>
       <c r="H345" t="n">
-        <v>0.0736</v>
+        <v>0.0872</v>
       </c>
       <c r="I345" t="n">
-        <v>25.7</v>
+        <v>24.49</v>
       </c>
       <c r="J345" t="n">
-        <v>345.4</v>
+        <v>332</v>
       </c>
       <c r="K345" t="n">
-        <v>5.524</v>
+        <v>5.846</v>
       </c>
       <c r="L345" t="n">
-        <v>-3.973</v>
+        <v>-2.554</v>
       </c>
       <c r="M345" t="n">
-        <v>18.588</v>
+        <v>21.175</v>
       </c>
     </row>
     <row r="346">
@@ -17502,42 +17502,42 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E346" t="n">
-        <v>2.537</v>
+        <v>2.373</v>
       </c>
       <c r="F346" t="n">
-        <v>0.861</v>
+        <v>0.825</v>
       </c>
       <c r="G346" t="n">
-        <v>0.532</v>
+        <v>0.49</v>
       </c>
       <c r="H346" t="n">
-        <v>0.0876</v>
+        <v>0.0954</v>
       </c>
       <c r="I346" t="n">
-        <v>24.49</v>
+        <v>24.95</v>
       </c>
       <c r="J346" t="n">
-        <v>332</v>
+        <v>345.4</v>
       </c>
       <c r="K346" t="n">
-        <v>5.849</v>
+        <v>5.575</v>
       </c>
       <c r="L346" t="n">
-        <v>-2.553</v>
+        <v>-3.955</v>
       </c>
       <c r="M346" t="n">
-        <v>21.18</v>
+        <v>20.822</v>
       </c>
     </row>
     <row r="347">
@@ -17547,42 +17547,42 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E347" t="n">
-        <v>2.373</v>
+        <v>2.425</v>
       </c>
       <c r="F347" t="n">
-        <v>0.825</v>
+        <v>0.7</v>
       </c>
       <c r="G347" t="n">
-        <v>0.49</v>
+        <v>0.496</v>
       </c>
       <c r="H347" t="n">
-        <v>0.0954</v>
+        <v>0.0696</v>
       </c>
       <c r="I347" t="n">
-        <v>24.95</v>
+        <v>23.6</v>
       </c>
       <c r="J347" t="n">
-        <v>345.4</v>
+        <v>341.6</v>
       </c>
       <c r="K347" t="n">
-        <v>5.575</v>
+        <v>5.235</v>
       </c>
       <c r="L347" t="n">
-        <v>-3.955</v>
+        <v>-4.073</v>
       </c>
       <c r="M347" t="n">
-        <v>20.822</v>
+        <v>19.98</v>
       </c>
     </row>
     <row r="348">
@@ -17592,87 +17592,87 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E348" t="n">
-        <v>2.425</v>
+        <v>2.222</v>
       </c>
       <c r="F348" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="G348" t="n">
-        <v>0.496</v>
+        <v>0.596</v>
       </c>
       <c r="H348" t="n">
-        <v>0.0697</v>
+        <v>0.0912</v>
       </c>
       <c r="I348" t="n">
-        <v>23.6</v>
+        <v>25.64</v>
       </c>
       <c r="J348" t="n">
-        <v>341.6</v>
+        <v>350.9</v>
       </c>
       <c r="K348" t="n">
-        <v>5.235</v>
+        <v>5.501</v>
       </c>
       <c r="L348" t="n">
-        <v>-4.073</v>
+        <v>-3.981</v>
       </c>
       <c r="M348" t="n">
-        <v>19.98</v>
+        <v>18.755</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E349" t="n">
-        <v>2.222</v>
+        <v>2.181</v>
       </c>
       <c r="F349" t="n">
-        <v>0.77</v>
+        <v>0.671</v>
       </c>
       <c r="G349" t="n">
-        <v>0.596</v>
+        <v>0.548</v>
       </c>
       <c r="H349" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.095</v>
       </c>
       <c r="I349" t="n">
-        <v>25.64</v>
+        <v>25.18</v>
       </c>
       <c r="J349" t="n">
-        <v>350.9</v>
+        <v>356.3</v>
       </c>
       <c r="K349" t="n">
-        <v>5.502</v>
+        <v>5.189</v>
       </c>
       <c r="L349" t="n">
-        <v>-3.98</v>
+        <v>-4.089</v>
       </c>
       <c r="M349" t="n">
-        <v>18.756</v>
+        <v>20.197</v>
       </c>
     </row>
     <row r="350">
@@ -17682,42 +17682,42 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E350" t="n">
-        <v>2.453</v>
+        <v>2.277</v>
       </c>
       <c r="F350" t="n">
-        <v>0.764</v>
+        <v>0.787</v>
       </c>
       <c r="G350" t="n">
-        <v>0.584</v>
+        <v>0.531</v>
       </c>
       <c r="H350" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0893</v>
       </c>
       <c r="I350" t="n">
-        <v>26.17</v>
+        <v>24.74</v>
       </c>
       <c r="J350" t="n">
-        <v>357.9</v>
+        <v>342.3</v>
       </c>
       <c r="K350" t="n">
-        <v>5.729</v>
+        <v>5.449</v>
       </c>
       <c r="L350" t="n">
-        <v>-3.902</v>
+        <v>-3.999</v>
       </c>
       <c r="M350" t="n">
-        <v>19.123</v>
+        <v>20.583</v>
       </c>
     </row>
     <row r="351">
@@ -17727,42 +17727,42 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E351" t="n">
-        <v>2.018</v>
+        <v>2.452</v>
       </c>
       <c r="F351" t="n">
-        <v>0.699</v>
+        <v>0.757</v>
       </c>
       <c r="G351" t="n">
-        <v>0.495</v>
+        <v>0.552</v>
       </c>
       <c r="H351" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="I351" t="n">
-        <v>26.23</v>
+        <v>25.96</v>
       </c>
       <c r="J351" t="n">
-        <v>359.9</v>
+        <v>353.4</v>
       </c>
       <c r="K351" t="n">
-        <v>4.927</v>
+        <v>5.603</v>
       </c>
       <c r="L351" t="n">
-        <v>-4.179</v>
+        <v>-3.945</v>
       </c>
       <c r="M351" t="n">
-        <v>17.75</v>
+        <v>18.837</v>
       </c>
     </row>
     <row r="352">
@@ -17772,42 +17772,42 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D352" t="n">
         <v>1</v>
       </c>
       <c r="E352" t="n">
-        <v>2.316</v>
+        <v>2.435</v>
       </c>
       <c r="F352" t="n">
-        <v>0.83</v>
+        <v>0.708</v>
       </c>
       <c r="G352" t="n">
-        <v>0.542</v>
+        <v>0.549</v>
       </c>
       <c r="H352" t="n">
-        <v>0.0906</v>
+        <v>0.1046</v>
       </c>
       <c r="I352" t="n">
-        <v>25.06</v>
+        <v>25.11</v>
       </c>
       <c r="J352" t="n">
-        <v>342.3</v>
+        <v>346.7</v>
       </c>
       <c r="K352" t="n">
-        <v>5.604</v>
+        <v>5.577</v>
       </c>
       <c r="L352" t="n">
-        <v>-3.945</v>
+        <v>-3.954</v>
       </c>
       <c r="M352" t="n">
-        <v>20.859</v>
+        <v>20.881</v>
       </c>
     </row>
     <row r="353">
@@ -17817,42 +17817,42 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="D353" t="n">
         <v>-1</v>
       </c>
       <c r="E353" t="n">
-        <v>2.493</v>
+        <v>2.495</v>
       </c>
       <c r="F353" t="n">
-        <v>0.785</v>
+        <v>0.861</v>
       </c>
       <c r="G353" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H353" t="n">
-        <v>0.0902</v>
+        <v>0.1275</v>
       </c>
       <c r="I353" t="n">
-        <v>26.21</v>
+        <v>25.62</v>
       </c>
       <c r="J353" t="n">
-        <v>353.4</v>
+        <v>347.7</v>
       </c>
       <c r="K353" t="n">
-        <v>5.72</v>
+        <v>6.242</v>
       </c>
       <c r="L353" t="n">
-        <v>-3.905</v>
+        <v>-3.724</v>
       </c>
       <c r="M353" t="n">
-        <v>19.034</v>
+        <v>20.229</v>
       </c>
     </row>
     <row r="354">
@@ -17862,42 +17862,42 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E354" t="n">
-        <v>2.467</v>
+        <v>2.414</v>
       </c>
       <c r="F354" t="n">
-        <v>0.742</v>
+        <v>0.767</v>
       </c>
       <c r="G354" t="n">
-        <v>0.556</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H354" t="n">
-        <v>0.1074</v>
+        <v>0.1087</v>
       </c>
       <c r="I354" t="n">
-        <v>25.36</v>
+        <v>26.27</v>
       </c>
       <c r="J354" t="n">
-        <v>346.7</v>
+        <v>351.3</v>
       </c>
       <c r="K354" t="n">
-        <v>5.707</v>
+        <v>5.714</v>
       </c>
       <c r="L354" t="n">
-        <v>-3.909</v>
+        <v>-3.907</v>
       </c>
       <c r="M354" t="n">
-        <v>21.126</v>
+        <v>19.193</v>
       </c>
     </row>
     <row r="355">
@@ -17907,42 +17907,42 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E355" t="n">
-        <v>2.533</v>
+        <v>2.199</v>
       </c>
       <c r="F355" t="n">
-        <v>0.881</v>
+        <v>0.779</v>
       </c>
       <c r="G355" t="n">
-        <v>0.638</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H355" t="n">
-        <v>0.1312</v>
+        <v>0.1032</v>
       </c>
       <c r="I355" t="n">
-        <v>25.88</v>
+        <v>24.38</v>
       </c>
       <c r="J355" t="n">
-        <v>347.7</v>
+        <v>347.9</v>
       </c>
       <c r="K355" t="n">
-        <v>6.358</v>
+        <v>5.748</v>
       </c>
       <c r="L355" t="n">
-        <v>-3.684</v>
+        <v>-3.895</v>
       </c>
       <c r="M355" t="n">
-        <v>20.429</v>
+        <v>21.256</v>
       </c>
     </row>
     <row r="356">
@@ -17952,42 +17952,42 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E356" t="n">
-        <v>2.451</v>
+        <v>2.202</v>
       </c>
       <c r="F356" t="n">
-        <v>0.795</v>
+        <v>0.669</v>
       </c>
       <c r="G356" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.455</v>
       </c>
       <c r="H356" t="n">
-        <v>0.1111</v>
+        <v>0.0944</v>
       </c>
       <c r="I356" t="n">
-        <v>26.4</v>
+        <v>24.69</v>
       </c>
       <c r="J356" t="n">
-        <v>351.3</v>
+        <v>345.1</v>
       </c>
       <c r="K356" t="n">
-        <v>5.84</v>
+        <v>5.016</v>
       </c>
       <c r="L356" t="n">
-        <v>-3.863</v>
+        <v>-4.149</v>
       </c>
       <c r="M356" t="n">
-        <v>19.416</v>
+        <v>19.855</v>
       </c>
     </row>
     <row r="357">
@@ -17997,42 +17997,42 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E357" t="n">
-        <v>2.218</v>
+        <v>2.066</v>
       </c>
       <c r="F357" t="n">
-        <v>0.804</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G357" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.474</v>
       </c>
       <c r="H357" t="n">
-        <v>0.1049</v>
+        <v>0.0965</v>
       </c>
       <c r="I357" t="n">
-        <v>24.54</v>
+        <v>25.96</v>
       </c>
       <c r="J357" t="n">
-        <v>347.9</v>
+        <v>357.8</v>
       </c>
       <c r="K357" t="n">
-        <v>5.821</v>
+        <v>4.965</v>
       </c>
       <c r="L357" t="n">
-        <v>-3.87</v>
+        <v>-4.166</v>
       </c>
       <c r="M357" t="n">
-        <v>21.381</v>
+        <v>17.868</v>
       </c>
     </row>
     <row r="358">
@@ -18042,42 +18042,42 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>JAX</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E358" t="n">
-        <v>2.406</v>
+        <v>2.331</v>
       </c>
       <c r="F358" t="n">
-        <v>0.852</v>
+        <v>0.838</v>
       </c>
       <c r="G358" t="n">
-        <v>0.605</v>
+        <v>0.58</v>
       </c>
       <c r="H358" t="n">
-        <v>0.1201</v>
+        <v>0.1162</v>
       </c>
       <c r="I358" t="n">
-        <v>24.63</v>
+        <v>25.29</v>
       </c>
       <c r="J358" t="n">
-        <v>340.5</v>
+        <v>349.4</v>
       </c>
       <c r="K358" t="n">
-        <v>6.041</v>
+        <v>5.864</v>
       </c>
       <c r="L358" t="n">
-        <v>-3.794</v>
+        <v>-3.855</v>
       </c>
       <c r="M358" t="n">
-        <v>21.806</v>
+        <v>21.49</v>
       </c>
     </row>
     <row r="359">
@@ -18087,132 +18087,42 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E359" t="n">
-        <v>2.102</v>
+        <v>2.384</v>
       </c>
       <c r="F359" t="n">
-        <v>0.722</v>
+        <v>0.764</v>
       </c>
       <c r="G359" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="H359" t="n">
-        <v>0.0988</v>
+        <v>0.1077</v>
       </c>
       <c r="I359" t="n">
-        <v>26.16</v>
+        <v>24.35</v>
       </c>
       <c r="J359" t="n">
-        <v>357.8</v>
+        <v>346.7</v>
       </c>
       <c r="K359" t="n">
-        <v>5.099</v>
+        <v>5.598</v>
       </c>
       <c r="L359" t="n">
-        <v>-4.12</v>
+        <v>-3.947</v>
       </c>
       <c r="M359" t="n">
-        <v>18.117</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B360" t="n">
-        <v>17</v>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>JAX</t>
-        </is>
-      </c>
-      <c r="D360" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E360" t="n">
-        <v>2.351</v>
-      </c>
-      <c r="F360" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="G360" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="H360" t="n">
-        <v>0.1201</v>
-      </c>
-      <c r="I360" t="n">
-        <v>25.59</v>
-      </c>
-      <c r="J360" t="n">
-        <v>349.4</v>
-      </c>
-      <c r="K360" t="n">
-        <v>5.986</v>
-      </c>
-      <c r="L360" t="n">
-        <v>-3.813</v>
-      </c>
-      <c r="M360" t="n">
-        <v>19.767</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
-      <c r="B361" t="n">
-        <v>18</v>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="D361" t="n">
-        <v>1</v>
-      </c>
-      <c r="E361" t="n">
-        <v>2.415</v>
-      </c>
-      <c r="F361" t="n">
-        <v>0.784</v>
-      </c>
-      <c r="G361" t="n">
-        <v>0.522</v>
-      </c>
-      <c r="H361" t="n">
-        <v>0.1106</v>
-      </c>
-      <c r="I361" t="n">
-        <v>24.73</v>
-      </c>
-      <c r="J361" t="n">
-        <v>346.7</v>
-      </c>
-      <c r="K361" t="n">
-        <v>5.691</v>
-      </c>
-      <c r="L361" t="n">
-        <v>-3.915</v>
-      </c>
-      <c r="M361" t="n">
-        <v>21.122</v>
+        <v>20.961</v>
       </c>
     </row>
   </sheetData>

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -522,7 +522,7 @@
         <v>3613</v>
       </c>
       <c r="I2" t="n">
-        <v>81.14</v>
+        <v>81.13</v>
       </c>
       <c r="J2" t="n">
         <v>35.46</v>
@@ -534,7 +534,7 @@
         <v>75.06</v>
       </c>
       <c r="M2" t="n">
-        <v>6.08</v>
+        <v>6.07</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -798,7 +798,7 @@
         <v>31.25</v>
       </c>
       <c r="K8" t="n">
-        <v>134.72</v>
+        <v>134.76</v>
       </c>
       <c r="L8" t="n">
         <v>74.41</v>
@@ -837,7 +837,7 @@
         <v>3561</v>
       </c>
       <c r="I9" t="n">
-        <v>65.95999999999999</v>
+        <v>65.95</v>
       </c>
       <c r="J9" t="n">
         <v>20.45</v>
@@ -849,7 +849,7 @@
         <v>59.53</v>
       </c>
       <c r="M9" t="n">
-        <v>6.43</v>
+        <v>6.42</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -978,7 +978,7 @@
         <v>30.02</v>
       </c>
       <c r="K12" t="n">
-        <v>136.41</v>
+        <v>136.45</v>
       </c>
       <c r="L12" t="n">
         <v>79.59</v>
@@ -1062,7 +1062,7 @@
         <v>3648</v>
       </c>
       <c r="I14" t="n">
-        <v>63.05</v>
+        <v>63.06</v>
       </c>
       <c r="J14" t="n">
         <v>28.79</v>
@@ -1074,7 +1074,7 @@
         <v>64.70999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.66</v>
+        <v>-1.65</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1287,7 +1287,7 @@
         <v>3605</v>
       </c>
       <c r="I19" t="n">
-        <v>62.23</v>
+        <v>62.22</v>
       </c>
       <c r="J19" t="n">
         <v>29.31</v>
@@ -1299,7 +1299,7 @@
         <v>64.06</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.83</v>
+        <v>-1.84</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1542,7 +1542,7 @@
         <v>26.62</v>
       </c>
       <c r="D25" t="n">
-        <v>8.27</v>
+        <v>8.26</v>
       </c>
       <c r="E25" t="n">
         <v>4.98</v>
@@ -1653,7 +1653,7 @@
         <v>27.76</v>
       </c>
       <c r="K27" t="n">
-        <v>127.41</v>
+        <v>127.44</v>
       </c>
       <c r="L27" t="n">
         <v>61.47</v>
@@ -1872,7 +1872,7 @@
         <v>3779</v>
       </c>
       <c r="I32" t="n">
-        <v>56.15</v>
+        <v>56.14</v>
       </c>
       <c r="J32" t="n">
         <v>14.56</v>
@@ -1884,7 +1884,7 @@
         <v>62.12</v>
       </c>
       <c r="M32" t="n">
-        <v>-5.97</v>
+        <v>-5.98</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
         <v>2.031</v>
       </c>
       <c r="F38" t="n">
-        <v>0.67</v>
+        <v>0.669</v>
       </c>
       <c r="G38" t="n">
         <v>0.454</v>
@@ -3671,10 +3671,10 @@
         <v>338.5</v>
       </c>
       <c r="K38" t="n">
-        <v>5</v>
+        <v>4.998</v>
       </c>
       <c r="L38" t="n">
-        <v>-4.154</v>
+        <v>-4.155</v>
       </c>
       <c r="M38" t="n">
         <v>20.053</v>
@@ -3926,7 +3926,7 @@
         <v>1.937</v>
       </c>
       <c r="F44" t="n">
-        <v>0.672</v>
+        <v>0.671</v>
       </c>
       <c r="G44" t="n">
         <v>0.454</v>
@@ -3941,13 +3941,13 @@
         <v>350.8</v>
       </c>
       <c r="K44" t="n">
-        <v>4.91</v>
+        <v>4.908</v>
       </c>
       <c r="L44" t="n">
-        <v>-4.185</v>
+        <v>-4.186</v>
       </c>
       <c r="M44" t="n">
-        <v>19.924</v>
+        <v>19.923</v>
       </c>
     </row>
     <row r="45">
@@ -4826,7 +4826,7 @@
         <v>2.191</v>
       </c>
       <c r="F64" t="n">
-        <v>0.657</v>
+        <v>0.655</v>
       </c>
       <c r="G64" t="n">
         <v>0.433</v>
@@ -4841,13 +4841,13 @@
         <v>348.2</v>
       </c>
       <c r="K64" t="n">
-        <v>5.073</v>
+        <v>5.069</v>
       </c>
       <c r="L64" t="n">
-        <v>-4.129</v>
+        <v>-4.13</v>
       </c>
       <c r="M64" t="n">
-        <v>20.11</v>
+        <v>20.109</v>
       </c>
     </row>
     <row r="65">
@@ -6806,28 +6806,28 @@
         <v>2.368</v>
       </c>
       <c r="F108" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="G108" t="n">
         <v>0.65</v>
       </c>
       <c r="H108" t="n">
-        <v>0.1551</v>
+        <v>0.1548</v>
       </c>
       <c r="I108" t="n">
-        <v>19.81</v>
+        <v>19.86</v>
       </c>
       <c r="J108" t="n">
         <v>330.7</v>
       </c>
       <c r="K108" t="n">
-        <v>7.141</v>
+        <v>7.137</v>
       </c>
       <c r="L108" t="n">
-        <v>-2.105</v>
+        <v>-2.107</v>
       </c>
       <c r="M108" t="n">
-        <v>22.551</v>
+        <v>22.545</v>
       </c>
     </row>
     <row r="109">
@@ -7166,7 +7166,7 @@
         <v>2.424</v>
       </c>
       <c r="F116" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="G116" t="n">
         <v>0.449</v>
@@ -7181,13 +7181,13 @@
         <v>341.8</v>
       </c>
       <c r="K116" t="n">
-        <v>5.391</v>
+        <v>5.389</v>
       </c>
       <c r="L116" t="n">
         <v>-4.019</v>
       </c>
       <c r="M116" t="n">
-        <v>20.249</v>
+        <v>20.248</v>
       </c>
     </row>
     <row r="117">
@@ -7931,7 +7931,7 @@
         <v>2.262</v>
       </c>
       <c r="F133" t="n">
-        <v>0.769</v>
+        <v>0.767</v>
       </c>
       <c r="G133" t="n">
         <v>0.451</v>
@@ -7940,19 +7940,19 @@
         <v>0.1103</v>
       </c>
       <c r="I133" t="n">
-        <v>20.94</v>
+        <v>20.96</v>
       </c>
       <c r="J133" t="n">
         <v>332.4</v>
       </c>
       <c r="K133" t="n">
-        <v>5.364</v>
+        <v>5.36</v>
       </c>
       <c r="L133" t="n">
-        <v>-2.72</v>
+        <v>-2.722</v>
       </c>
       <c r="M133" t="n">
-        <v>20.573</v>
+        <v>20.572</v>
       </c>
     </row>
     <row r="134">
@@ -8705,7 +8705,7 @@
         <v>0.093</v>
       </c>
       <c r="I150" t="n">
-        <v>23.07</v>
+        <v>23.08</v>
       </c>
       <c r="J150" t="n">
         <v>337.2</v>
@@ -8741,7 +8741,7 @@
         <v>2.076</v>
       </c>
       <c r="F151" t="n">
-        <v>0.645</v>
+        <v>0.644</v>
       </c>
       <c r="G151" t="n">
         <v>0.455</v>
@@ -8756,13 +8756,13 @@
         <v>341.1</v>
       </c>
       <c r="K151" t="n">
-        <v>4.865</v>
+        <v>4.863</v>
       </c>
       <c r="L151" t="n">
-        <v>-4.201</v>
+        <v>-4.202</v>
       </c>
       <c r="M151" t="n">
-        <v>19.656</v>
+        <v>19.655</v>
       </c>
     </row>
     <row r="152">
@@ -9467,22 +9467,22 @@
         <v>0.444</v>
       </c>
       <c r="H167" t="n">
-        <v>0.1125</v>
+        <v>0.1132</v>
       </c>
       <c r="I167" t="n">
-        <v>20.92</v>
+        <v>20.9</v>
       </c>
       <c r="J167" t="n">
         <v>340.9</v>
       </c>
       <c r="K167" t="n">
-        <v>5.549</v>
+        <v>5.553</v>
       </c>
       <c r="L167" t="n">
-        <v>-3.964</v>
+        <v>-3.963</v>
       </c>
       <c r="M167" t="n">
-        <v>20.888</v>
+        <v>20.897</v>
       </c>
     </row>
     <row r="168">
@@ -10460,7 +10460,7 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I189" t="n">
-        <v>21.48</v>
+        <v>21.52</v>
       </c>
       <c r="J189" t="n">
         <v>326.9</v>
@@ -10991,7 +10991,7 @@
         <v>1.99</v>
       </c>
       <c r="F201" t="n">
-        <v>0.656</v>
+        <v>0.655</v>
       </c>
       <c r="G201" t="n">
         <v>0.539</v>
@@ -11006,13 +11006,13 @@
         <v>346.1</v>
       </c>
       <c r="K201" t="n">
-        <v>4.942</v>
+        <v>4.94</v>
       </c>
       <c r="L201" t="n">
-        <v>-4.174</v>
+        <v>-4.175</v>
       </c>
       <c r="M201" t="n">
-        <v>19.798</v>
+        <v>19.797</v>
       </c>
     </row>
     <row r="202">
@@ -12746,7 +12746,7 @@
         <v>2.226</v>
       </c>
       <c r="F240" t="n">
-        <v>0.662</v>
+        <v>0.66</v>
       </c>
       <c r="G240" t="n">
         <v>0.54</v>
@@ -12761,13 +12761,13 @@
         <v>337.2</v>
       </c>
       <c r="K240" t="n">
-        <v>5.399</v>
+        <v>5.395</v>
       </c>
       <c r="L240" t="n">
-        <v>-4.016</v>
+        <v>-4.017</v>
       </c>
       <c r="M240" t="n">
-        <v>20.78</v>
+        <v>20.765</v>
       </c>
     </row>
     <row r="241">
@@ -13151,7 +13151,7 @@
         <v>2.283</v>
       </c>
       <c r="F249" t="n">
-        <v>0.66</v>
+        <v>0.658</v>
       </c>
       <c r="G249" t="n">
         <v>0.54</v>
@@ -13160,19 +13160,19 @@
         <v>0.1281</v>
       </c>
       <c r="I249" t="n">
-        <v>20.78</v>
+        <v>20.83</v>
       </c>
       <c r="J249" t="n">
         <v>326.2</v>
       </c>
       <c r="K249" t="n">
-        <v>5.452</v>
+        <v>5.448</v>
       </c>
       <c r="L249" t="n">
-        <v>-2.69</v>
+        <v>-2.691</v>
       </c>
       <c r="M249" t="n">
-        <v>20.851</v>
+        <v>20.849</v>
       </c>
     </row>
     <row r="250">
@@ -14102,22 +14102,22 @@
         <v>0.482</v>
       </c>
       <c r="H270" t="n">
-        <v>0.1202</v>
+        <v>0.1205</v>
       </c>
       <c r="I270" t="n">
-        <v>24.79</v>
+        <v>24.82</v>
       </c>
       <c r="J270" t="n">
         <v>349</v>
       </c>
       <c r="K270" t="n">
-        <v>5.555</v>
+        <v>5.557</v>
       </c>
       <c r="L270" t="n">
-        <v>-3.962</v>
+        <v>-3.961</v>
       </c>
       <c r="M270" t="n">
-        <v>20.997</v>
+        <v>21.002</v>
       </c>
     </row>
     <row r="271">
@@ -14186,7 +14186,7 @@
         <v>2.274</v>
       </c>
       <c r="F272" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.681</v>
       </c>
       <c r="G272" t="n">
         <v>0.577</v>
@@ -14201,13 +14201,13 @@
         <v>324.1</v>
       </c>
       <c r="K272" t="n">
-        <v>5.489</v>
+        <v>5.487</v>
       </c>
       <c r="L272" t="n">
-        <v>-3.985</v>
+        <v>-3.986</v>
       </c>
       <c r="M272" t="n">
-        <v>20.47</v>
+        <v>20.469</v>
       </c>
     </row>
     <row r="273">
@@ -14411,7 +14411,7 @@
         <v>2.177</v>
       </c>
       <c r="F277" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G277" t="n">
         <v>0.577</v>
@@ -14426,10 +14426,10 @@
         <v>333.9</v>
       </c>
       <c r="K277" t="n">
-        <v>5.396</v>
+        <v>5.394</v>
       </c>
       <c r="L277" t="n">
-        <v>-4.017</v>
+        <v>-4.018</v>
       </c>
       <c r="M277" t="n">
         <v>18.371</v>
@@ -14687,7 +14687,7 @@
         <v>0.443</v>
       </c>
       <c r="H283" t="n">
-        <v>0.1011</v>
+        <v>0.1017</v>
       </c>
       <c r="I283" t="n">
         <v>19.88</v>
@@ -14696,13 +14696,13 @@
         <v>333.3</v>
       </c>
       <c r="K283" t="n">
-        <v>6.492</v>
+        <v>6.495</v>
       </c>
       <c r="L283" t="n">
-        <v>-2.33</v>
+        <v>-2.329</v>
       </c>
       <c r="M283" t="n">
-        <v>21.034</v>
+        <v>21.047</v>
       </c>
     </row>
     <row r="284">
@@ -14867,7 +14867,7 @@
         <v>0.443</v>
       </c>
       <c r="H287" t="n">
-        <v>0.1011</v>
+        <v>0.1017</v>
       </c>
       <c r="I287" t="n">
         <v>21.21</v>
@@ -14876,13 +14876,13 @@
         <v>342.2</v>
       </c>
       <c r="K287" t="n">
-        <v>5.422</v>
+        <v>5.425</v>
       </c>
       <c r="L287" t="n">
-        <v>-4.008</v>
+        <v>-4.007</v>
       </c>
       <c r="M287" t="n">
-        <v>20.579</v>
+        <v>20.591</v>
       </c>
     </row>
     <row r="288">
@@ -15902,7 +15902,7 @@
         <v>0.529</v>
       </c>
       <c r="H310" t="n">
-        <v>0.1108</v>
+        <v>0.1115</v>
       </c>
       <c r="I310" t="n">
         <v>19.85</v>
@@ -15911,13 +15911,13 @@
         <v>317.9</v>
       </c>
       <c r="K310" t="n">
-        <v>6.861</v>
+        <v>6.865</v>
       </c>
       <c r="L310" t="n">
-        <v>-2.202</v>
+        <v>-2.201</v>
       </c>
       <c r="M310" t="n">
-        <v>21.746</v>
+        <v>21.759</v>
       </c>
     </row>
     <row r="311">
@@ -16262,22 +16262,22 @@
         <v>0.455</v>
       </c>
       <c r="H318" t="n">
-        <v>0.1212</v>
+        <v>0.1216</v>
       </c>
       <c r="I318" t="n">
-        <v>21.18</v>
+        <v>21.14</v>
       </c>
       <c r="J318" t="n">
         <v>335.9</v>
       </c>
       <c r="K318" t="n">
-        <v>5.634</v>
+        <v>5.637</v>
       </c>
       <c r="L318" t="n">
-        <v>-2.627</v>
+        <v>-2.626</v>
       </c>
       <c r="M318" t="n">
-        <v>21.06</v>
+        <v>21.065</v>
       </c>
     </row>
     <row r="319">

--- a/projections/def_2026_combined.xlsx
+++ b/projections/def_2026_combined.xlsx
@@ -798,7 +798,7 @@
         <v>31.25</v>
       </c>
       <c r="K8" t="n">
-        <v>134.76</v>
+        <v>134.72</v>
       </c>
       <c r="L8" t="n">
         <v>74.41</v>
@@ -978,7 +978,7 @@
         <v>30.02</v>
       </c>
       <c r="K12" t="n">
-        <v>136.45</v>
+        <v>136.41</v>
       </c>
       <c r="L12" t="n">
         <v>79.59</v>
@@ -1062,7 +1062,7 @@
         <v>3648</v>
       </c>
       <c r="I14" t="n">
-        <v>63.06</v>
+        <v>63.05</v>
       </c>
       <c r="J14" t="n">
         <v>28.79</v>
@@ -1074,7 +1074,7 @@
         <v>64.70999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.65</v>
+        <v>-1.66</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1653,7 +1653,7 @@
         <v>27.76</v>
       </c>
       <c r="K27" t="n">
-        <v>127.44</v>
+        <v>127.41</v>
       </c>
       <c r="L27" t="n">
         <v>61.47</v>
@@ -8705,7 +8705,7 @@
         <v>0.093</v>
       </c>
       <c r="I150" t="n">
-        <v>23.08</v>
+        <v>23.07</v>
       </c>
       <c r="J150" t="n">
         <v>337.2</v>
@@ -9467,22 +9467,22 @@
         <v>0.444</v>
       </c>
       <c r="H167" t="n">
-        <v>0.1132</v>
+        <v>0.1125</v>
       </c>
       <c r="I167" t="n">
-        <v>20.9</v>
+        <v>20.92</v>
       </c>
       <c r="J167" t="n">
         <v>340.9</v>
       </c>
       <c r="K167" t="n">
-        <v>5.553</v>
+        <v>5.549</v>
       </c>
       <c r="L167" t="n">
-        <v>-3.963</v>
+        <v>-3.964</v>
       </c>
       <c r="M167" t="n">
-        <v>20.897</v>
+        <v>20.888</v>
       </c>
     </row>
     <row r="168">
@@ -10460,7 +10460,7 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I189" t="n">
-        <v>21.52</v>
+        <v>21.48</v>
       </c>
       <c r="J189" t="n">
         <v>326.9</v>
@@ -14102,22 +14102,22 @@
         <v>0.482</v>
       </c>
       <c r="H270" t="n">
-        <v>0.1205</v>
+        <v>0.1202</v>
       </c>
       <c r="I270" t="n">
-        <v>24.82</v>
+        <v>24.79</v>
       </c>
       <c r="J270" t="n">
         <v>349</v>
       </c>
       <c r="K270" t="n">
-        <v>5.557</v>
+        <v>5.555</v>
       </c>
       <c r="L270" t="n">
-        <v>-3.961</v>
+        <v>-3.962</v>
       </c>
       <c r="M270" t="n">
-        <v>21.002</v>
+        <v>20.997</v>
       </c>
     </row>
     <row r="271">
@@ -14687,7 +14687,7 @@
         <v>0.443</v>
       </c>
       <c r="H283" t="n">
-        <v>0.1017</v>
+        <v>0.1011</v>
       </c>
       <c r="I283" t="n">
         <v>19.88</v>
@@ -14696,13 +14696,13 @@
         <v>333.3</v>
       </c>
       <c r="K283" t="n">
-        <v>6.495</v>
+        <v>6.492</v>
       </c>
       <c r="L283" t="n">
-        <v>-2.329</v>
+        <v>-2.33</v>
       </c>
       <c r="M283" t="n">
-        <v>21.047</v>
+        <v>21.034</v>
       </c>
     </row>
     <row r="284">
@@ -14867,7 +14867,7 @@
         <v>0.443</v>
       </c>
       <c r="H287" t="n">
-        <v>0.1017</v>
+        <v>0.1011</v>
       </c>
       <c r="I287" t="n">
         <v>21.21</v>
@@ -14876,13 +14876,13 @@
         <v>342.2</v>
       </c>
       <c r="K287" t="n">
-        <v>5.425</v>
+        <v>5.422</v>
       </c>
       <c r="L287" t="n">
-        <v>-4.007</v>
+        <v>-4.008</v>
       </c>
       <c r="M287" t="n">
-        <v>20.591</v>
+        <v>20.579</v>
       </c>
     </row>
     <row r="288">
@@ -15902,7 +15902,7 @@
         <v>0.529</v>
       </c>
       <c r="H310" t="n">
-        <v>0.1115</v>
+        <v>0.1108</v>
       </c>
       <c r="I310" t="n">
         <v>19.85</v>
@@ -15911,13 +15911,13 @@
         <v>317.9</v>
       </c>
       <c r="K310" t="n">
-        <v>6.865</v>
+        <v>6.861</v>
       </c>
       <c r="L310" t="n">
-        <v>-2.201</v>
+        <v>-2.202</v>
       </c>
       <c r="M310" t="n">
-        <v>21.759</v>
+        <v>21.746</v>
       </c>
     </row>
     <row r="311">
@@ -16262,22 +16262,22 @@
         <v>0.455</v>
       </c>
       <c r="H318" t="n">
-        <v>0.1216</v>
+        <v>0.1212</v>
       </c>
       <c r="I318" t="n">
-        <v>21.14</v>
+        <v>21.18</v>
       </c>
       <c r="J318" t="n">
         <v>335.9</v>
       </c>
       <c r="K318" t="n">
-        <v>5.637</v>
+        <v>5.634</v>
       </c>
       <c r="L318" t="n">
-        <v>-2.626</v>
+        <v>-2.627</v>
       </c>
       <c r="M318" t="n">
-        <v>21.065</v>
+        <v>21.06</v>
       </c>
     </row>
     <row r="319">
